--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="194">
   <si>
     <t>Priority</t>
   </si>
@@ -79,6 +79,348 @@
     <t>Open</t>
   </si>
   <si>
+    <t>NOEL PHARMA (INDIA) PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Mr. Prem Chand Goyal</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The Corporate Debtor is Not Operational for last 2 years. Form G published on 22.09.2026 in Financial Express (English, Lucknow Edition) &amp; Jansatta (Hindi, Lucknow Edition)</t>
+  </si>
+  <si>
+    <t>MATA RANI INFRASTRUCTURE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Jaishree Kannan</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>SNEH EXPORTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Garima diggiwal</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Chakrala Sannidhi</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>Shree Shiddhanath Cotex Private Limited</t>
+  </si>
+  <si>
+    <t>Textiles</t>
+  </si>
+  <si>
+    <t>Akhil Ahuja</t>
+  </si>
+  <si>
+    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
+  </si>
+  <si>
+    <t>H.Q LAMPS MANUFACTURING CO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Bihari Lal Chakravarti</t>
+  </si>
+  <si>
+    <t>INFO-DRIVE SOFTWARE LIMITED</t>
+  </si>
+  <si>
+    <t>Sumeet Surendra Chimbalkar</t>
+  </si>
+  <si>
+    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>A.P.J. LABORATORIES LIMITED</t>
+  </si>
+  <si>
+    <t>pooja damir miglani</t>
+  </si>
+  <si>
+    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
+  </si>
+  <si>
+    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>Mrs. Neeraja Kartik</t>
+  </si>
+  <si>
+    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
+  </si>
+  <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>OZONE HOMES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Ashok Mittal</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>OSIA HYPER RETAIL LIMITED</t>
+  </si>
+  <si>
+    <t>Retail / Consumer</t>
+  </si>
+  <si>
+    <t>Mr. Vinod Tarachand Agrawal</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>HEERA-IND TRADING PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Trading / Distribution</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>MORANI MOTORS PRIVATE LIMITED</t>
   </si>
   <si>
@@ -88,327 +430,12 @@
     <t>Mr. Satyendra Prasad Khorania</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
     <t>SAKET PROMOTERS LIMITED</t>
   </si>
   <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
     <t>Mr. Pratim Bayal</t>
   </si>
   <si>
-    <t>NOEL PHARMA (INDIA) PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Mr. Prem Chand Goyal</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The Corporate Debtor is Not Operational for last 2 years. Form G published on 22.09.2026 in Financial Express (English, Lucknow Edition) &amp; Jansatta (Hindi, Lucknow Edition)</t>
-  </si>
-  <si>
-    <t>MATA RANI INFRASTRUCTURE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Jaishree Kannan</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>SNEH EXPORTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>Garima diggiwal</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Chakrala Sannidhi</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>Shree Shiddhanath Cotex Private Limited</t>
-  </si>
-  <si>
-    <t>Textiles</t>
-  </si>
-  <si>
-    <t>Akhil Ahuja</t>
-  </si>
-  <si>
-    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
-  </si>
-  <si>
-    <t>H.Q LAMPS MANUFACTURING CO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Bihari Lal Chakravarti</t>
-  </si>
-  <si>
-    <t>INFO-DRIVE SOFTWARE LIMITED</t>
-  </si>
-  <si>
-    <t>Sumeet Surendra Chimbalkar</t>
-  </si>
-  <si>
-    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>A.P.J. LABORATORIES LIMITED</t>
-  </si>
-  <si>
-    <t>pooja damir miglani</t>
-  </si>
-  <si>
-    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
-  </si>
-  <si>
-    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>Mrs. Neeraja Kartik</t>
-  </si>
-  <si>
-    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
-  </si>
-  <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>HEERA-IND TRADING PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Trading / Distribution</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>OM SHRI SHUBH LABH AGRITECH PRIVATE LIMITED</t>
   </si>
   <si>
@@ -460,9 +487,6 @@
     <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
     <t>Company has two operational grocery marts in the name of Poonam Bazaar units in Nagpur. The grocery marts are in operational status, however the financials and custody of the assets of CD are yet to be handed over to the RP.</t>
   </si>
   <si>
@@ -496,9 +520,6 @@
     <t>ISHAPE APPLIANCES PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Retail / Consumer</t>
-  </si>
-  <si>
     <t>PRABHAT JAIN</t>
   </si>
   <si>
@@ -545,18 +566,6 @@
   </si>
   <si>
     <t>Gajesh Labhchand Jain</t>
-  </si>
-  <si>
-    <t>AMAR SEEDS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>SABBANI MARUTHI</t>
-  </si>
-  <si>
-    <t>NEXTGEN TEXTILE PARK PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The said FORM G has been published all over India and all the newspaper cuttings is attached in the attachment</t>
   </si>
   <si>
     <t>Started</t>
@@ -997,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1081,20 +1090,23 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="2">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="3">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
@@ -1103,13 +1115,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75886463693</v>
+        <v>46300.75885649968</v>
       </c>
       <c r="P2" s="2">
-        <v>46300.77186163223</v>
+        <v>46301.38234195765</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -1120,22 +1132,19 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="2">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H3" s="3">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>26</v>
@@ -1143,6 +1152,9 @@
       <c r="K3" s="2">
         <v>1</v>
       </c>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1150,13 +1162,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75886465221</v>
+        <v>46300.7588564394</v>
       </c>
       <c r="P3" s="2">
-        <v>46300.77186164244</v>
+        <v>46301.38234193892</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1167,28 +1179,31 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H4" s="3">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -1197,13 +1212,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75885649968</v>
+        <v>46300.75885645495</v>
       </c>
       <c r="P4" s="2">
-        <v>46300.77185342244</v>
+        <v>46300.7718533924</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1214,29 +1229,26 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" s="2">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H5" s="3">
         <v>46302</v>
       </c>
       <c r="I5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1244,13 +1256,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.7588564394</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P5" s="2">
-        <v>46300.77185338244</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>22</v>
+        <v>46301.38233288697</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1261,31 +1273,31 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" s="3">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="I6" s="2">
         <v>2</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
@@ -1294,13 +1306,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75885645495</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P6" s="2">
-        <v>46300.7718533924</v>
+        <v>46301.38233286788</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1311,22 +1323,22 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H7" s="3">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="I7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
@@ -1338,13 +1350,13 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75885647022</v>
+        <v>46300.75885634872</v>
       </c>
       <c r="P7" s="2">
-        <v>46300.77185340247</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>43</v>
+        <v>46301.38233285504</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1358,16 +1370,13 @@
         <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G8" s="2">
         <v>0.9399999999999999</v>
       </c>
       <c r="H8" s="3">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="I8" s="2">
         <v>3</v>
@@ -1376,7 +1385,7 @@
         <v>46</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>47</v>
@@ -1388,13 +1397,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.7588564207</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P8" s="2">
-        <v>46300.77185337251</v>
+        <v>46301.38233284863</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1411,10 +1420,10 @@
         <v>49</v>
       </c>
       <c r="G9" s="2">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="H9" s="3">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
@@ -1432,13 +1441,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75885634872</v>
+        <v>46300.75885629474</v>
       </c>
       <c r="P9" s="2">
-        <v>46300.77185333199</v>
+        <v>46301.38233284211</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1452,26 +1461,26 @@
         <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G10" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H10" s="3">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1479,13 +1488,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.7588563655</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P10" s="2">
-        <v>46300.77185334221</v>
+        <v>46301.38233283556</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1496,16 +1505,19 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G11" s="2">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="H11" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
@@ -1523,13 +1535,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.75885629474</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P11" s="2">
-        <v>46300.771853301</v>
+        <v>46301.38233282206</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1543,13 +1555,16 @@
         <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="G12" s="2">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
@@ -1570,13 +1585,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75885633306</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P12" s="2">
-        <v>46300.7718533219</v>
+        <v>46301.38233280889</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1590,26 +1605,29 @@
         <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H13" s="3">
         <v>46306</v>
       </c>
       <c r="I13" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
+      <c r="L13" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1617,13 +1635,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.75885622757</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P13" s="2">
-        <v>46300.77185325955</v>
+        <v>46301.38233280194</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1634,13 +1652,10 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2">
         <v>0.9399999999999999</v>
@@ -1649,16 +1664,16 @@
         <v>46306</v>
       </c>
       <c r="I14" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -1667,13 +1682,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75885624527</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P14" s="2">
-        <v>46300.77185326978</v>
+        <v>46301.38233281567</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1684,31 +1699,31 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="H15" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I15" s="2">
         <v>6</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
@@ -1717,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.7588562628</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P15" s="2">
-        <v>46300.77185328031</v>
+        <v>46301.38233277337</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1734,29 +1749,26 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="G16" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I16" s="2">
         <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1764,13 +1776,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46300.75885627908</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P16" s="2">
-        <v>46300.77185329074</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>22</v>
+        <v>46301.38233279494</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1784,19 +1796,19 @@
         <v>76</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="2">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="H17" s="3">
         <v>46307</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>78</v>
@@ -1804,9 +1816,6 @@
       <c r="K17" s="2">
         <v>1</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
       </c>
@@ -1814,13 +1823,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46300.75884793277</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P17" s="2">
-        <v>46300.77184465345</v>
+        <v>46300.77184467361</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1831,10 +1840,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G18" s="2">
         <v>0.2</v>
@@ -1843,14 +1852,17 @@
         <v>46307</v>
       </c>
       <c r="I18" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1858,13 +1870,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P18" s="2">
-        <v>46300.7718446638</v>
+        <v>46300.77185324822</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1878,22 +1890,19 @@
         <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="3">
         <v>46307</v>
       </c>
       <c r="I19" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K19" s="2">
         <v>1</v>
@@ -1905,13 +1914,13 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46300.75884796329</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P19" s="2">
-        <v>46300.77184467361</v>
+        <v>46301.38233276551</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1">
@@ -1922,22 +1931,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H20" s="3">
         <v>46307</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
@@ -1952,13 +1961,13 @@
         <v>18</v>
       </c>
       <c r="O20" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P20" s="2">
-        <v>46300.77185324822</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>43</v>
+        <v>46301.38233275072</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="2" customFormat="1">
@@ -1972,22 +1981,25 @@
         <v>87</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>88</v>
+        <v>55</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="G21" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H21" s="3">
         <v>46307</v>
       </c>
       <c r="I21" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -1996,13 +2008,13 @@
         <v>18</v>
       </c>
       <c r="O21" s="2">
-        <v>46300.75885617639</v>
+        <v>46301.38232484296</v>
       </c>
       <c r="P21" s="2">
-        <v>46300.77185321973</v>
+        <v>46301.38232484298</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1">
@@ -2013,22 +2025,25 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="G22" s="2">
         <v>0.91</v>
       </c>
       <c r="H22" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I22" s="2">
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K22" s="2">
         <v>1</v>
@@ -2043,91 +2058,85 @@
         <v>18</v>
       </c>
       <c r="O22" s="2">
-        <v>46300.75885619673</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P22" s="2">
-        <v>46300.77185323774</v>
+        <v>46301.38232478131</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="2" customFormat="1">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23">
-        <v>0.91</v>
+      <c r="E23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.2</v>
       </c>
       <c r="H23" s="3">
         <v>46308</v>
       </c>
-      <c r="I23">
-        <v>8</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="I23" s="2">
+        <v>7</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="2">
+        <v>46300.75884790152</v>
+      </c>
+      <c r="P23" s="2">
+        <v>46301.38232478769</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="2" customFormat="1">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23">
-        <v>46300.75884788632</v>
-      </c>
-      <c r="P23">
-        <v>46300.7718446229</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24">
+      <c r="E24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="2">
         <v>0.2</v>
       </c>
       <c r="H24" s="3">
         <v>46308</v>
       </c>
-      <c r="I24">
-        <v>8</v>
-      </c>
-      <c r="J24" t="s">
-        <v>96</v>
-      </c>
-      <c r="K24">
+      <c r="I24" s="2">
+        <v>7</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K24" s="2">
         <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
@@ -2136,14 +2145,14 @@
       <c r="N24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O24">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P24">
-        <v>46300.77184463335</v>
+      <c r="O24" s="2">
+        <v>46301.38232480602</v>
+      </c>
+      <c r="P24" s="2">
+        <v>46301.38232480604</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2154,10 +2163,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G25">
         <v>0.92</v>
@@ -2166,16 +2175,16 @@
         <v>46310</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
         <v>98</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25" t="s">
-        <v>99</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2187,10 +2196,10 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P25">
-        <v>46300.77184461303</v>
+        <v>46301.38232477474</v>
       </c>
       <c r="Q25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2201,10 +2210,10 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G26">
         <v>0.95</v>
@@ -2213,16 +2222,16 @@
         <v>46312</v>
       </c>
       <c r="I26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J26" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26" t="s">
         <v>101</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>102</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2234,10 +2243,10 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P26">
-        <v>46300.77184456182</v>
+        <v>46301.38232474073</v>
       </c>
       <c r="Q26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2248,10 +2257,10 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" t="s">
         <v>103</v>
-      </c>
-      <c r="E27" t="s">
-        <v>104</v>
       </c>
       <c r="G27">
         <v>0.93</v>
@@ -2260,10 +2269,10 @@
         <v>46312</v>
       </c>
       <c r="I27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2278,10 +2287,10 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P27">
-        <v>46300.77184457189</v>
+        <v>46301.3823247477</v>
       </c>
       <c r="Q27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2292,10 +2301,10 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G28">
         <v>0.93</v>
@@ -2304,16 +2313,16 @@
         <v>46312</v>
       </c>
       <c r="I28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J28" t="s">
+        <v>106</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" t="s">
         <v>107</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28" t="s">
-        <v>108</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
@@ -2325,10 +2334,10 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P28">
-        <v>46300.77184458252</v>
+        <v>46301.38232475457</v>
       </c>
       <c r="Q28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2339,10 +2348,10 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" t="s">
         <v>109</v>
-      </c>
-      <c r="E29" t="s">
-        <v>110</v>
       </c>
       <c r="G29">
         <v>0.91</v>
@@ -2351,16 +2360,16 @@
         <v>46312</v>
       </c>
       <c r="I29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
         <v>111</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29" t="s">
-        <v>112</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
@@ -2372,10 +2381,10 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P29">
-        <v>46300.77184459261</v>
+        <v>46301.38232476145</v>
       </c>
       <c r="Q29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2386,13 +2395,13 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" t="s">
         <v>113</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>114</v>
-      </c>
-      <c r="F30" t="s">
-        <v>115</v>
       </c>
       <c r="G30">
         <v>0.96</v>
@@ -2401,10 +2410,10 @@
         <v>46314</v>
       </c>
       <c r="I30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2419,10 +2428,10 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P30">
-        <v>46300.77184453</v>
+        <v>46301.38232472008</v>
       </c>
       <c r="Q30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2433,10 +2442,10 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G31">
         <v>0.2</v>
@@ -2445,10 +2454,10 @@
         <v>46314</v>
       </c>
       <c r="I31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2463,10 +2472,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P31">
-        <v>46300.77184454048</v>
+        <v>46301.38232472714</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2477,10 +2486,10 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G32">
         <v>0.93</v>
@@ -2489,10 +2498,10 @@
         <v>46314</v>
       </c>
       <c r="I32">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2507,10 +2516,10 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P32">
-        <v>46300.7718445514</v>
+        <v>46301.38232473391</v>
       </c>
       <c r="Q32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2521,10 +2530,10 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G33">
         <v>0.2</v>
@@ -2533,10 +2542,10 @@
         <v>46315</v>
       </c>
       <c r="I33">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2551,10 +2560,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P33">
-        <v>46300.77184451929</v>
+        <v>46301.382324713</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2565,19 +2574,19 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" t="s">
         <v>123</v>
       </c>
-      <c r="E34" t="s">
-        <v>41</v>
-      </c>
       <c r="G34">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
       <c r="H34" s="3">
-        <v>46326</v>
+        <v>46316</v>
       </c>
       <c r="I34">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J34" t="s">
         <v>124</v>
@@ -2592,13 +2601,13 @@
         <v>18</v>
       </c>
       <c r="O34">
-        <v>46300.75884768533</v>
+        <v>46301.38232470618</v>
       </c>
       <c r="P34">
-        <v>46300.77184447264</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>43</v>
+        <v>46301.3823247062</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2612,163 +2621,153 @@
         <v>125</v>
       </c>
       <c r="E35" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46317</v>
+      </c>
+      <c r="I35">
+        <v>16</v>
+      </c>
+      <c r="J35" t="s">
         <v>126</v>
       </c>
-      <c r="G35">
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P35">
+        <v>46301.38232468424</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36">
+        <v>0.2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I36">
+        <v>25</v>
+      </c>
+      <c r="J36" t="s">
+        <v>128</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P36">
+        <v>46301.38232457793</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37">
         <v>0.82</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H37" s="3">
         <v>46326</v>
       </c>
-      <c r="I35">
-        <v>26</v>
-      </c>
-      <c r="J35" t="s">
-        <v>124</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O35">
+      <c r="I37">
+        <v>25</v>
+      </c>
+      <c r="J37" t="s">
+        <v>128</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37">
         <v>46300.75884770849</v>
       </c>
-      <c r="P35">
-        <v>46300.77184450537</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H36" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I36" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K36" s="6">
-        <v>1</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O36" s="6">
-        <v>46300.75886466862</v>
-      </c>
-      <c r="P36" s="6">
-        <v>46300.77186165276</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="H37" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I37" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K37" s="6">
-        <v>1</v>
-      </c>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="6">
-        <v>46300.75886468366</v>
-      </c>
-      <c r="P37" s="6">
-        <v>46300.77186166309</v>
-      </c>
-      <c r="Q37" s="6" t="s">
-        <v>22</v>
+      <c r="P37">
+        <v>46301.38232455136</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H38" s="6">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="I38" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K38" s="6">
         <v>1</v>
@@ -2781,43 +2780,43 @@
         <v>18</v>
       </c>
       <c r="O38" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75886463693</v>
       </c>
       <c r="P38" s="6">
-        <v>46300.77186168291</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>43</v>
+        <v>46301.38234197814</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G39" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H39" s="6">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="I39" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K39" s="6">
         <v>1</v>
@@ -2830,48 +2829,48 @@
         <v>18</v>
       </c>
       <c r="O39" s="6">
-        <v>46300.75886472998</v>
+        <v>46300.75886465221</v>
       </c>
       <c r="P39" s="6">
-        <v>46300.77186169299</v>
+        <v>46301.38234197158</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H40" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I40" s="6">
         <v>-2</v>
       </c>
       <c r="J40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K40" s="6">
+        <v>1</v>
+      </c>
+      <c r="L40" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="K40" s="6">
-        <v>1</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="M40" s="6" t="s">
         <v>18</v>
       </c>
@@ -2879,48 +2878,48 @@
         <v>18</v>
       </c>
       <c r="O40" s="6">
-        <v>46300.75886474836</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P40" s="6">
-        <v>46300.77186170343</v>
-      </c>
-      <c r="Q40" s="6" t="s">
-        <v>22</v>
+        <v>46301.3823419983</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="G41" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H41" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I41" s="6">
         <v>-2</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="K41" s="6">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="s">
-        <v>142</v>
-      </c>
+      <c r="L41" s="6"/>
       <c r="M41" s="6" t="s">
         <v>18</v>
       </c>
@@ -2928,28 +2927,28 @@
         <v>18</v>
       </c>
       <c r="O41" s="6">
-        <v>46300.75886476378</v>
+        <v>46300.75886468366</v>
       </c>
       <c r="P41" s="6">
-        <v>46300.77186171332</v>
+        <v>46301.38234199157</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6">
@@ -2959,10 +2958,10 @@
         <v>46298</v>
       </c>
       <c r="I42" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K42" s="6">
         <v>1</v>
@@ -2975,50 +2974,48 @@
         <v>18</v>
       </c>
       <c r="O42" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P42" s="6">
-        <v>46300.77186173356</v>
+        <v>46301.38234201136</v>
       </c>
       <c r="Q42" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G43" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="6">
         <v>46298</v>
       </c>
       <c r="I43" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K43" s="6">
         <v>1</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>147</v>
-      </c>
+      <c r="L43" s="6"/>
       <c r="M43" s="6" t="s">
         <v>18</v>
       </c>
@@ -3026,48 +3023,48 @@
         <v>18</v>
       </c>
       <c r="O43" s="6">
-        <v>46300.75886484625</v>
+        <v>46300.75886472998</v>
       </c>
       <c r="P43" s="6">
-        <v>46300.77186176419</v>
+        <v>46301.38234203825</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6">
         <v>0.92</v>
       </c>
       <c r="H44" s="6">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="I44" s="6">
         <v>-3</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K44" s="6">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="K44" s="6">
-        <v>1</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="M44" s="6" t="s">
         <v>18</v>
       </c>
@@ -3075,48 +3072,48 @@
         <v>18</v>
       </c>
       <c r="O44" s="6">
-        <v>46300.75886486177</v>
+        <v>46300.75886474836</v>
       </c>
       <c r="P44" s="6">
-        <v>46300.77186177437</v>
+        <v>46301.38234202487</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>150</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H45" s="6">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="I45" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J45" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K45" s="6">
+        <v>1</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K45" s="6">
-        <v>1</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>152</v>
-      </c>
       <c r="M45" s="6" t="s">
         <v>18</v>
       </c>
@@ -3124,41 +3121,41 @@
         <v>18</v>
       </c>
       <c r="O45" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75886476378</v>
       </c>
       <c r="P45" s="6">
-        <v>46300.77186178449</v>
-      </c>
-      <c r="Q45" s="5" t="s">
-        <v>43</v>
+        <v>46301.38234205102</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6">
         <v>0.2</v>
       </c>
       <c r="H46" s="6">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="I46" s="6">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K46" s="6">
         <v>1</v>
@@ -3171,46 +3168,50 @@
         <v>18</v>
       </c>
       <c r="O46" s="6">
-        <v>46300.75887301003</v>
+        <v>46300.75886479358</v>
       </c>
       <c r="P46" s="6">
-        <v>46300.77186984384</v>
+        <v>46301.38234204441</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F47" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="G47" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H47" s="6">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="I47" s="6">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
       </c>
-      <c r="L47" s="6"/>
+      <c r="L47" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="M47" s="6" t="s">
         <v>18</v>
       </c>
@@ -3218,46 +3219,48 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46300.75887304553</v>
+        <v>46300.75886484625</v>
       </c>
       <c r="P47" s="6">
-        <v>46300.77186986821</v>
+        <v>46301.3823420574</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="H48" s="6">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I48" s="6">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K48" s="6">
-        <v>2</v>
-      </c>
-      <c r="L48" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="M48" s="6" t="s">
         <v>18</v>
       </c>
@@ -3265,47 +3268,47 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75887306096</v>
+        <v>46300.75886486177</v>
       </c>
       <c r="P48" s="6">
-        <v>46300.77186987809</v>
+        <v>46301.38234207036</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H49" s="6">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="I49" s="6">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K49" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>18</v>
@@ -3314,41 +3317,41 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.75887309557</v>
+        <v>46300.75886487812</v>
       </c>
       <c r="P49" s="6">
-        <v>46300.77186989888</v>
-      </c>
-      <c r="Q49" s="6" t="s">
-        <v>22</v>
+        <v>46301.38235023815</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
         <v>0.2</v>
       </c>
       <c r="H50" s="6">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I50" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K50" s="6">
         <v>1</v>
@@ -3361,48 +3364,46 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75887314334</v>
+        <v>46300.75887301003</v>
       </c>
       <c r="P50" s="6">
-        <v>46300.77186991942</v>
+        <v>46301.38235027138</v>
       </c>
       <c r="Q50" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H51" s="6">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I51" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K51" s="6">
-        <v>3</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>167</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L51" s="6"/>
       <c r="M51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3410,48 +3411,46 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46300.75887316054</v>
+        <v>46300.75887304553</v>
       </c>
       <c r="P51" s="6">
-        <v>46300.77186992981</v>
+        <v>46301.38235028457</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
       <c r="H52" s="6">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I52" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="K52" s="6">
-        <v>1</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>169</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L52" s="6"/>
       <c r="M52" s="6" t="s">
         <v>18</v>
       </c>
@@ -3459,47 +3458,47 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.75887317812</v>
+        <v>46300.75887306096</v>
       </c>
       <c r="P52" s="6">
-        <v>46300.77186993999</v>
-      </c>
-      <c r="Q52" s="5" t="s">
-        <v>43</v>
+        <v>46301.38235026403</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H53" s="6">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="I53" s="6">
         <v>-8</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K53" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>18</v>
@@ -3508,28 +3507,28 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.75887319581</v>
+        <v>46300.75887309557</v>
       </c>
       <c r="P53" s="6">
-        <v>46300.77186995011</v>
-      </c>
-      <c r="Q53" s="5" t="s">
-        <v>43</v>
+        <v>46301.38235029773</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6">
@@ -3539,13 +3538,13 @@
         <v>46292</v>
       </c>
       <c r="I54" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K54" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="6" t="s">
@@ -3555,46 +3554,48 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.75887321083</v>
+        <v>46300.75887314334</v>
       </c>
       <c r="P54" s="6">
-        <v>46300.7718699602</v>
+        <v>46301.38235032413</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
       <c r="H55" s="6">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="I55" s="6">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K55" s="6">
-        <v>1</v>
-      </c>
-      <c r="L55" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>174</v>
+      </c>
       <c r="M55" s="6" t="s">
         <v>18</v>
       </c>
@@ -3602,66 +3603,162 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75887322682</v>
+        <v>46300.75887316054</v>
       </c>
       <c r="P55" s="6">
-        <v>46300.77186996974</v>
-      </c>
-      <c r="Q55" s="5" t="s">
-        <v>43</v>
+        <v>46301.3823503047</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H56" s="6">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="I56" s="6">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
       </c>
       <c r="L56" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O56" s="6">
+        <v>46300.75887317812</v>
+      </c>
+      <c r="P56" s="6">
+        <v>46301.38235033712</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H57" s="6">
+        <v>46292</v>
+      </c>
+      <c r="I57" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J57" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="M56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O56" s="6">
-        <v>46300.75887324401</v>
-      </c>
-      <c r="P56" s="6">
-        <v>46300.77186997979</v>
-      </c>
-      <c r="Q56" s="6" t="s">
-        <v>22</v>
+      <c r="K57" s="6">
+        <v>1</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O57" s="6">
+        <v>46300.75887319581</v>
+      </c>
+      <c r="P57" s="6">
+        <v>46301.38235033053</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H58" s="6">
+        <v>46292</v>
+      </c>
+      <c r="I58" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K58" s="6">
+        <v>2</v>
+      </c>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O58" s="6">
+        <v>46300.75887321083</v>
+      </c>
+      <c r="P58" s="6">
+        <v>46301.38235031778</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q56"/>
+  <autoFilter ref="A1:Q58"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -3773,6 +3870,10 @@
     <hyperlink ref="N55" r:id="rId108"/>
     <hyperlink ref="M56" r:id="rId109"/>
     <hyperlink ref="N56" r:id="rId110"/>
+    <hyperlink ref="M57" r:id="rId111"/>
+    <hyperlink ref="N57" r:id="rId112"/>
+    <hyperlink ref="M58" r:id="rId113"/>
+    <hyperlink ref="N58" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3780,7 +3881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3859,10 +3960,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
@@ -3871,10 +3972,10 @@
         <v>46302</v>
       </c>
       <c r="I2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -3889,10 +3990,10 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P2" s="2">
-        <v>46300.77185340247</v>
+        <v>46301.38233288697</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -3903,10 +4004,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -3915,10 +4016,10 @@
         <v>46307</v>
       </c>
       <c r="I3" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -3933,10 +4034,10 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46300.7718446638</v>
+        <v>46301.38233279494</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -3947,10 +4048,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
@@ -3959,16 +4060,16 @@
         <v>46307</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -3983,35 +4084,35 @@
         <v>46300.77185324822</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="2" customFormat="1">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="2">
         <v>0.2</v>
       </c>
       <c r="H5" s="3">
         <v>46308</v>
       </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>96</v>
-      </c>
-      <c r="K5">
+      <c r="I5" s="2">
+        <v>7</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="M5" s="4" t="s">
@@ -4020,42 +4121,42 @@
       <c r="N5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2">
         <v>46300.75884790152</v>
       </c>
-      <c r="P5">
-        <v>46300.77184463335</v>
+      <c r="P5" s="2">
+        <v>46301.38232478769</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="2" customFormat="1">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="2">
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
-      <c r="J6" t="s">
-        <v>118</v>
-      </c>
-      <c r="K6">
+        <v>46308</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
@@ -4064,14 +4165,14 @@
       <c r="N6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O6">
-        <v>46300.75884775587</v>
-      </c>
-      <c r="P6">
-        <v>46300.77184454048</v>
+      <c r="O6" s="2">
+        <v>46301.38232480602</v>
+      </c>
+      <c r="P6" s="2">
+        <v>46301.38232480604</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -4082,22 +4183,22 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4109,13 +4210,13 @@
         <v>18</v>
       </c>
       <c r="O7">
-        <v>46300.75884772457</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P7">
-        <v>46300.77184451929</v>
+        <v>46301.38232472714</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4126,169 +4227,163 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G8">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
+        <v>46315</v>
+      </c>
+      <c r="I8">
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8">
+        <v>46300.75884772457</v>
+      </c>
+      <c r="P8">
+        <v>46301.382324713</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46317</v>
+      </c>
+      <c r="I9">
+        <v>16</v>
+      </c>
+      <c r="J9" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P9">
+        <v>46301.38232468424</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="3">
         <v>46326</v>
       </c>
-      <c r="I8">
-        <v>26</v>
-      </c>
-      <c r="J8" t="s">
-        <v>124</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8">
+      <c r="I10">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10">
         <v>46300.75884768533</v>
       </c>
-      <c r="P8">
-        <v>46300.77184447264</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H9" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I9" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="6">
-        <v>1</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" s="6">
-        <v>46300.75886466862</v>
-      </c>
-      <c r="P9" s="6">
-        <v>46300.77186165276</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H10" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I10" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K10" s="6">
-        <v>1</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" s="6">
-        <v>46300.75886471466</v>
-      </c>
-      <c r="P10" s="6">
-        <v>46300.77186168291</v>
+      <c r="P10">
+        <v>46301.38232457793</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6">
         <v>0.2</v>
       </c>
       <c r="H11" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I11" s="6">
         <v>-2</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="K11" s="6">
         <v>1</v>
       </c>
-      <c r="L11" s="6"/>
+      <c r="L11" s="6" t="s">
+        <v>139</v>
+      </c>
       <c r="M11" s="6" t="s">
         <v>18</v>
       </c>
@@ -4296,48 +4391,46 @@
         <v>18</v>
       </c>
       <c r="O11" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P11" s="6">
-        <v>46300.77186173356</v>
+        <v>46301.3823419983</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6">
         <v>0.2</v>
       </c>
       <c r="H12" s="6">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="I12" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>152</v>
-      </c>
+      <c r="L12" s="6"/>
       <c r="M12" s="6" t="s">
         <v>18</v>
       </c>
@@ -4345,41 +4438,41 @@
         <v>18</v>
       </c>
       <c r="O12" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P12" s="6">
-        <v>46300.77186178449</v>
+        <v>46301.38234201136</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
         <v>0.2</v>
       </c>
       <c r="H13" s="6">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="I13" s="6">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K13" s="6">
         <v>1</v>
@@ -4392,46 +4485,48 @@
         <v>18</v>
       </c>
       <c r="O13" s="6">
-        <v>46300.75887301003</v>
+        <v>46300.75886479358</v>
       </c>
       <c r="P13" s="6">
-        <v>46300.77186984384</v>
+        <v>46301.38234204441</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6">
         <v>0.2</v>
       </c>
       <c r="H14" s="6">
-        <v>46292</v>
+        <v>46296</v>
       </c>
       <c r="I14" s="6">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
       </c>
-      <c r="L14" s="6"/>
+      <c r="L14" s="6" t="s">
+        <v>160</v>
+      </c>
       <c r="M14" s="6" t="s">
         <v>18</v>
       </c>
@@ -4439,48 +4534,46 @@
         <v>18</v>
       </c>
       <c r="O14" s="6">
-        <v>46300.75887314334</v>
+        <v>46300.75886487812</v>
       </c>
       <c r="P14" s="6">
-        <v>46300.77186991942</v>
+        <v>46301.38235023815</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6">
         <v>0.2</v>
       </c>
       <c r="H15" s="6">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I15" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>169</v>
-      </c>
+      <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
         <v>18</v>
       </c>
@@ -4488,28 +4581,28 @@
         <v>18</v>
       </c>
       <c r="O15" s="6">
-        <v>46300.75887317812</v>
+        <v>46300.75887301003</v>
       </c>
       <c r="P15" s="6">
-        <v>46300.77186993999</v>
+        <v>46301.38235027138</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>170</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -4519,7 +4612,7 @@
         <v>46292</v>
       </c>
       <c r="I16" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>171</v>
@@ -4527,9 +4620,7 @@
       <c r="K16" s="6">
         <v>1</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>172</v>
-      </c>
+      <c r="L16" s="6"/>
       <c r="M16" s="6" t="s">
         <v>18</v>
       </c>
@@ -4537,28 +4628,28 @@
         <v>18</v>
       </c>
       <c r="O16" s="6">
-        <v>46300.75887319581</v>
+        <v>46300.75887314334</v>
       </c>
       <c r="P16" s="6">
-        <v>46300.77186995011</v>
+        <v>46301.38235032413</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
@@ -4568,15 +4659,17 @@
         <v>46292</v>
       </c>
       <c r="I17" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="K17" s="6">
-        <v>2</v>
-      </c>
-      <c r="L17" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="M17" s="6" t="s">
         <v>18</v>
       </c>
@@ -4584,46 +4677,48 @@
         <v>18</v>
       </c>
       <c r="O17" s="6">
-        <v>46300.75887321083</v>
+        <v>46300.75887317812</v>
       </c>
       <c r="P17" s="6">
-        <v>46300.7718699602</v>
+        <v>46301.38235033712</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6">
         <v>0.2</v>
       </c>
       <c r="H18" s="6">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="I18" s="6">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K18" s="6">
         <v>1</v>
       </c>
-      <c r="L18" s="6"/>
+      <c r="L18" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="M18" s="6" t="s">
         <v>18</v>
       </c>
@@ -4631,17 +4726,64 @@
         <v>18</v>
       </c>
       <c r="O18" s="6">
-        <v>46300.75887322682</v>
+        <v>46300.75887319581</v>
       </c>
       <c r="P18" s="6">
-        <v>46300.77186996974</v>
+        <v>46301.38235033053</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="6">
+        <v>46292</v>
+      </c>
+      <c r="I19" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K19" s="6">
+        <v>2</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="6">
+        <v>46300.75887321083</v>
+      </c>
+      <c r="P19" s="6">
+        <v>46301.38235031778</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q18"/>
+  <autoFilter ref="A1:Q19"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4677,6 +4819,8 @@
     <hyperlink ref="N17" r:id="rId32"/>
     <hyperlink ref="M18" r:id="rId33"/>
     <hyperlink ref="N18" r:id="rId34"/>
+    <hyperlink ref="M19" r:id="rId35"/>
+    <hyperlink ref="N19" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4684,7 +4828,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4694,51 +4838,51 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B2">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -4747,13 +4891,13 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4762,18 +4906,18 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B3">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D3">
         <v>8</v>
@@ -4782,21 +4926,56 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H3">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B4">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>160</v>
+      </c>
+      <c r="F4">
+        <v>157</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>132</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="189">
   <si>
     <t>Priority</t>
   </si>
@@ -79,445 +79,430 @@
     <t>Open</t>
   </si>
   <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The Corporate Debtor is Not Operational for last 2 years. Form G published on 22.09.2026 in Financial Express (English, Lucknow Edition) &amp; Jansatta (Hindi, Lucknow Edition)</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>SNEH EXPORTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Garima diggiwal</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Chakrala Sannidhi</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>Shree Shiddhanath Cotex Private Limited</t>
+  </si>
+  <si>
+    <t>Textiles</t>
+  </si>
+  <si>
+    <t>Akhil Ahuja</t>
+  </si>
+  <si>
+    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
+  </si>
+  <si>
+    <t>INFO-DRIVE SOFTWARE LIMITED</t>
+  </si>
+  <si>
+    <t>Sumeet Surendra Chimbalkar</t>
+  </si>
+  <si>
+    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>A.P.J. LABORATORIES LIMITED</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>pooja damir miglani</t>
+  </si>
+  <si>
+    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
+  </si>
+  <si>
+    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>Mrs. Neeraja Kartik</t>
+  </si>
+  <si>
+    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
+  </si>
+  <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>NOEL PHARMA (INDIA) PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
     <t>Mr. Prem Chand Goyal</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The Corporate Debtor is Not Operational for last 2 years. Form G published on 22.09.2026 in Financial Express (English, Lucknow Edition) &amp; Jansatta (Hindi, Lucknow Edition)</t>
-  </si>
-  <si>
-    <t>MATA RANI INFRASTRUCTURE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Jaishree Kannan</t>
+    <t>MORANI MOTORS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Mr. Satyendra Prasad Khorania</t>
+  </si>
+  <si>
+    <t>SAKET PROMOTERS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Pratim Bayal</t>
+  </si>
+  <si>
+    <t>OM SHRI SHUBH LABH AGRITECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Present status :1 Unit closed &amp; one operational under lease as per information available with RP.</t>
+  </si>
+  <si>
+    <t>TITLE DEVELOPERS LLP</t>
+  </si>
+  <si>
+    <t>Palak Swapnil Desai</t>
+  </si>
+  <si>
+    <t>UNITED MASTERBATCHES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRATAP MUKHERJEE</t>
+  </si>
+  <si>
+    <t>SUKRITI HOSPITAL AND RESEARCH CENTRE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>SECUREVALUE INDIA LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Mr. Brijendra Kumar Mishra</t>
+  </si>
+  <si>
+    <t>The Corporate Debtor does not own any land or building. The assets of the Corporate Debtor substantially comprise transportation vehicles numbering approximately 2,397 as on 31.12.2024, as per the books of accounts, (Fixed Assets Register) provided by the</t>
+  </si>
+  <si>
+    <t>SVP INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bhoopesh Gupta</t>
+  </si>
+  <si>
+    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Company has two operational grocery marts in the name of Poonam Bazaar units in Nagpur. The grocery marts are in operational status, however the financials and custody of the assets of CD are yet to be handed over to the RP.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>SNEH EXPORTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>Garima diggiwal</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Chakrala Sannidhi</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>Shree Shiddhanath Cotex Private Limited</t>
-  </si>
-  <si>
-    <t>Textiles</t>
-  </si>
-  <si>
-    <t>Akhil Ahuja</t>
-  </si>
-  <si>
-    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
-  </si>
-  <si>
-    <t>H.Q LAMPS MANUFACTURING CO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Bihari Lal Chakravarti</t>
-  </si>
-  <si>
-    <t>INFO-DRIVE SOFTWARE LIMITED</t>
-  </si>
-  <si>
-    <t>Sumeet Surendra Chimbalkar</t>
-  </si>
-  <si>
-    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>A.P.J. LABORATORIES LIMITED</t>
-  </si>
-  <si>
-    <t>pooja damir miglani</t>
-  </si>
-  <si>
-    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
-  </si>
-  <si>
-    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>Mrs. Neeraja Kartik</t>
-  </si>
-  <si>
-    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
-  </si>
-  <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>OZONE HOMES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Ashok Mittal</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>OSIA HYPER RETAIL LIMITED</t>
+    <t>ROYAL DRY FRUITS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>The Resolution Professional has issued an invitation for expression of interest on 01 September 2026.</t>
+  </si>
+  <si>
+    <t>SHAH LAXMICHAND VERSHI MASALAWALA LLP</t>
+  </si>
+  <si>
+    <t>Mr. Dakshesh Pravinchandra Choksi</t>
+  </si>
+  <si>
+    <t>AMISHI CONSUMER TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Amit Talwar</t>
+  </si>
+  <si>
+    <t>ISHAPE APPLIANCES PRIVATE LIMITED</t>
   </si>
   <si>
     <t>Retail / Consumer</t>
-  </si>
-  <si>
-    <t>Mr. Vinod Tarachand Agrawal</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>HEERA-IND TRADING PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Trading / Distribution</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
-    <t>MORANI MOTORS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Automotive</t>
-  </si>
-  <si>
-    <t>Mr. Satyendra Prasad Khorania</t>
-  </si>
-  <si>
-    <t>SAKET PROMOTERS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Pratim Bayal</t>
-  </si>
-  <si>
-    <t>OM SHRI SHUBH LABH AGRITECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Present status :1 Unit closed &amp; one operational under lease as per information available with RP.</t>
-  </si>
-  <si>
-    <t>TITLE DEVELOPERS LLP</t>
-  </si>
-  <si>
-    <t>Palak Swapnil Desai</t>
-  </si>
-  <si>
-    <t>UNITED MASTERBATCHES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRATAP MUKHERJEE</t>
-  </si>
-  <si>
-    <t>SUKRITI HOSPITAL AND RESEARCH CENTRE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>SECUREVALUE INDIA LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Mr. Brijendra Kumar Mishra</t>
-  </si>
-  <si>
-    <t>The Corporate Debtor does not own any land or building. The assets of the Corporate Debtor substantially comprise transportation vehicles numbering approximately 2,397 as on 31.12.2024, as per the books of accounts, (Fixed Assets Register) provided by the</t>
-  </si>
-  <si>
-    <t>DUNZO DIGITAL PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Fresh Form G is issued on 17/09/2026.</t>
-  </si>
-  <si>
-    <t>SVP INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bhoopesh Gupta</t>
-  </si>
-  <si>
-    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Company has two operational grocery marts in the name of Poonam Bazaar units in Nagpur. The grocery marts are in operational status, however the financials and custody of the assets of CD are yet to be handed over to the RP.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>ROYAL DRY FRUITS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>The Resolution Professional has issued an invitation for expression of interest on 01 September 2026.</t>
-  </si>
-  <si>
-    <t>SHAH LAXMICHAND VERSHI MASALAWALA LLP</t>
-  </si>
-  <si>
-    <t>Mr. Dakshesh Pravinchandra Choksi</t>
-  </si>
-  <si>
-    <t>AMISHI CONSUMER TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Amit Talwar</t>
-  </si>
-  <si>
-    <t>ISHAPE APPLIANCES PRIVATE LIMITED</t>
   </si>
   <si>
     <t>PRABHAT JAIN</t>
@@ -1006,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1090,24 +1075,24 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="G2" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="H2" s="3">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="2">
-        <v>2</v>
-      </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
       </c>
@@ -1115,10 +1100,10 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75885649968</v>
+        <v>46300.7588564394</v>
       </c>
       <c r="P2" s="2">
-        <v>46301.38234195765</v>
+        <v>46302.26843221064</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1138,13 +1123,13 @@
         <v>25</v>
       </c>
       <c r="G3" s="2">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="3">
         <v>46302</v>
       </c>
       <c r="I3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>26</v>
@@ -1152,23 +1137,20 @@
       <c r="K3" s="2">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.75885647022</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46302.26843222459</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.7588564394</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46301.38234193892</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1188,10 +1170,10 @@
         <v>30</v>
       </c>
       <c r="G4" s="2">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H4" s="3">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
@@ -1200,7 +1182,7 @@
         <v>31</v>
       </c>
       <c r="K4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>32</v>
@@ -1212,10 +1194,10 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75885645495</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P4" s="2">
-        <v>46300.7718533924</v>
+        <v>46302.26842387108</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1235,13 +1217,13 @@
         <v>34</v>
       </c>
       <c r="G5" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H5" s="3">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>35</v>
@@ -1256,13 +1238,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75885647022</v>
+        <v>46300.75885634872</v>
       </c>
       <c r="P5" s="2">
-        <v>46301.38233288697</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>36</v>
+        <v>46302.26842383233</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1273,32 +1255,29 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="G6" s="2">
         <v>0.9399999999999999</v>
       </c>
       <c r="H6" s="3">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="I6" s="2">
         <v>2</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="2">
-        <v>2</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1306,10 +1285,10 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.7588564207</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P6" s="2">
-        <v>46301.38233286788</v>
+        <v>46302.26842384538</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1323,26 +1302,29 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2">
         <v>0.91</v>
       </c>
       <c r="H7" s="3">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="I7" s="2">
         <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
+      <c r="L7" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1350,10 +1332,10 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75885634872</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P7" s="2">
-        <v>46301.38233285504</v>
+        <v>46302.26842380712</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1367,19 +1349,22 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G8" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H8" s="3">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>46</v>
@@ -1387,9 +1372,6 @@
       <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1397,10 +1379,10 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.7588563655</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P8" s="2">
-        <v>46301.38233284863</v>
+        <v>46302.26842375574</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>23</v>
@@ -1414,26 +1396,32 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="G9" s="2">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H9" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1441,10 +1429,10 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75885629474</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P9" s="2">
-        <v>46301.38233284211</v>
+        <v>46302.26842376858</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>23</v>
@@ -1461,25 +1449,28 @@
         <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G10" s="2">
         <v>0.91</v>
       </c>
       <c r="H10" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
@@ -1488,10 +1479,10 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75885633306</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P10" s="2">
-        <v>46301.38233283556</v>
+        <v>46302.26842378132</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>23</v>
@@ -1505,29 +1496,29 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H11" s="3">
         <v>46306</v>
       </c>
       <c r="I11" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
+      <c r="L11" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1535,10 +1526,10 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.75885622757</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P11" s="2">
-        <v>46301.38233282206</v>
+        <v>46302.26842374232</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>23</v>
@@ -1552,31 +1543,31 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H12" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I12" s="2">
         <v>5</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -1585,10 +1576,10 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75885624527</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P12" s="2">
-        <v>46301.38233280889</v>
+        <v>46302.2684236893</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1602,32 +1593,26 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G13" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1635,13 +1620,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.7588562628</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P13" s="2">
-        <v>46301.38233280194</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>23</v>
+        <v>46302.26842371625</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1652,29 +1637,29 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="G14" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H14" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -1682,10 +1667,10 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75885627908</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P14" s="2">
-        <v>46301.38233281567</v>
+        <v>46302.26842364718</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1702,29 +1687,26 @@
         <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="G15" s="2">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="3">
         <v>46307</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1732,13 +1714,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.75884793277</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P15" s="2">
-        <v>46301.38233277337</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>23</v>
+        <v>46302.26842366141</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1749,19 +1731,19 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="G16" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H16" s="3">
         <v>46307</v>
       </c>
       <c r="I16" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>75</v>
@@ -1776,13 +1758,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P16" s="2">
-        <v>46301.38233279494</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>36</v>
+        <v>46302.26842361677</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1796,26 +1778,26 @@
         <v>76</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="G17" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H17" s="3">
         <v>46307</v>
       </c>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
       </c>
+      <c r="L17" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
       </c>
@@ -1823,10 +1805,10 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46300.75884796329</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P17" s="2">
-        <v>46300.77184467361</v>
+        <v>46302.26842367557</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>23</v>
@@ -1840,28 +1822,31 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>34</v>
+      <c r="F18" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G18" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H18" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -1870,13 +1855,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P18" s="2">
-        <v>46300.77185324822</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>36</v>
+        <v>46302.26841531677</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1887,16 +1872,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
@@ -1914,13 +1899,13 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46300.75885617639</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P19" s="2">
-        <v>46301.38233276551</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>23</v>
+        <v>46302.26841530317</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1">
@@ -1934,26 +1919,23 @@
         <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G20" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
       </c>
@@ -1961,198 +1943,198 @@
         <v>18</v>
       </c>
       <c r="O20" s="2">
-        <v>46300.75885619673</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P20" s="2">
-        <v>46301.38233275072</v>
-      </c>
-      <c r="Q20" s="2" t="s">
+        <v>46302.2684152897</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>0.92</v>
+      </c>
+      <c r="H21" s="3">
+        <v>46310</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21">
+        <v>46300.75884787029</v>
+      </c>
+      <c r="P21">
+        <v>46302.26841527641</v>
+      </c>
+      <c r="Q21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="2" customFormat="1">
-      <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="2">
+    <row r="22" spans="1:17">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22">
+        <v>0.95</v>
+      </c>
+      <c r="H22" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>92</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22">
+        <v>46300.75884779022</v>
+      </c>
+      <c r="P22">
+        <v>46302.26841524903</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23">
         <v>0.93</v>
       </c>
-      <c r="H21" s="3">
-        <v>46307</v>
-      </c>
-      <c r="I21" s="2">
-        <v>6</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K21" s="2">
-        <v>2</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="2">
-        <v>46301.38232484296</v>
-      </c>
-      <c r="P21" s="2">
-        <v>46301.38232484298</v>
-      </c>
-      <c r="Q21" s="2" t="s">
+      <c r="H23" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23">
+        <v>46300.75884780569</v>
+      </c>
+      <c r="P23">
+        <v>46302.26841520685</v>
+      </c>
+      <c r="Q23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="2" customFormat="1">
-      <c r="A22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H22" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I22" s="2">
-        <v>7</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="2">
-        <v>46300.75884788632</v>
-      </c>
-      <c r="P22" s="2">
-        <v>46301.38232478131</v>
-      </c>
-      <c r="Q22" s="2" t="s">
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24">
+        <v>0.93</v>
+      </c>
+      <c r="H24" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24" t="s">
+        <v>97</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>98</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24">
+        <v>46300.75884782107</v>
+      </c>
+      <c r="P24">
+        <v>46302.26841522126</v>
+      </c>
+      <c r="Q24" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="2" customFormat="1">
-      <c r="A23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H23" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I23" s="2">
-        <v>7</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23" s="2">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P23" s="2">
-        <v>46301.38232478769</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" s="2" customFormat="1">
-      <c r="A24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H24" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I24" s="2">
-        <v>7</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K24" s="2">
-        <v>1</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O24" s="2">
-        <v>46301.38232480602</v>
-      </c>
-      <c r="P24" s="2">
-        <v>46301.38232480604</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2163,28 +2145,28 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H25" s="3">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K25">
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2193,10 +2175,10 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46300.75884787029</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P25">
-        <v>46301.38232477474</v>
+        <v>46302.26841523509</v>
       </c>
       <c r="Q25" t="s">
         <v>23</v>
@@ -2210,28 +2192,28 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="G26">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H26" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I26">
         <v>11</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2240,10 +2222,10 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46300.75884779022</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P26">
-        <v>46301.38232474073</v>
+        <v>46302.2684151932</v>
       </c>
       <c r="Q26" t="s">
         <v>23</v>
@@ -2257,22 +2239,25 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="F27" t="s">
+        <v>108</v>
       </c>
       <c r="G27">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="H27" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2284,10 +2269,10 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46300.75884780569</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P27">
-        <v>46301.3823247477</v>
+        <v>46302.26841513602</v>
       </c>
       <c r="Q27" t="s">
         <v>23</v>
@@ -2301,29 +2286,26 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
       </c>
       <c r="G28">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H28" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="L28" t="s">
-        <v>107</v>
-      </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
       </c>
@@ -2331,13 +2313,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46300.75884782107</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P28">
-        <v>46301.38232475457</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>23</v>
+        <v>46302.26841514941</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2348,29 +2330,26 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G29">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H29" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="L29" t="s">
-        <v>111</v>
-      </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2378,10 +2357,10 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46300.75884783743</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P29">
-        <v>46301.38232476145</v>
+        <v>46302.26841512165</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2395,19 +2374,16 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="G30">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I30">
         <v>13</v>
@@ -2425,13 +2401,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46300.75884774033</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P30">
-        <v>46301.38232472008</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>23</v>
+        <v>46302.26841510729</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2445,23 +2421,26 @@
         <v>116</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G31">
         <v>0.2</v>
       </c>
       <c r="H31" s="3">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="I31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31" t="s">
         <v>117</v>
       </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
       </c>
@@ -2469,13 +2448,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46300.75884775587</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P31">
-        <v>46301.38232472714</v>
+        <v>46302.26841507771</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2489,16 +2468,16 @@
         <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G32">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H32" s="3">
-        <v>46314</v>
+        <v>46317</v>
       </c>
       <c r="I32">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J32" t="s">
         <v>119</v>
@@ -2513,13 +2492,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46300.7588477715</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P32">
-        <v>46301.38232473391</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>23</v>
+        <v>46302.26841503391</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2533,16 +2512,19 @@
         <v>120</v>
       </c>
       <c r="E33" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
       </c>
       <c r="G33">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H33" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J33" t="s">
         <v>121</v>
@@ -2557,13 +2539,13 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>46300.75884772457</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P33">
-        <v>46301.382324713</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>36</v>
+        <v>46302.26841501555</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2577,202 +2559,217 @@
         <v>122</v>
       </c>
       <c r="E34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G34">
+        <v>0.2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I34">
+        <v>24</v>
+      </c>
+      <c r="J34" t="s">
         <v>123</v>
       </c>
-      <c r="G34">
-        <v>0.87</v>
-      </c>
-      <c r="H34" s="3">
-        <v>46316</v>
-      </c>
-      <c r="I34">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P34">
+        <v>46302.2684148914</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34">
-        <v>46301.38232470618</v>
-      </c>
-      <c r="P34">
-        <v>46301.3823247062</v>
-      </c>
-      <c r="Q34" t="s">
+      <c r="B35" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H35" s="6">
+        <v>46301</v>
+      </c>
+      <c r="I35" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="K35" s="6">
+        <v>2</v>
+      </c>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="6">
+        <v>46300.75885649968</v>
+      </c>
+      <c r="P35" s="6">
+        <v>46302.26843226571</v>
+      </c>
+      <c r="Q35" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
-      <c r="A35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" t="s">
+    <row r="36" spans="1:17">
+      <c r="A36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E35" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35">
-        <v>0.2</v>
-      </c>
-      <c r="H35" s="3">
-        <v>46317</v>
-      </c>
-      <c r="I35">
-        <v>16</v>
-      </c>
-      <c r="J35" t="s">
-        <v>126</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O35">
-        <v>46301.38232468421</v>
-      </c>
-      <c r="P35">
-        <v>46301.38232468424</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" t="s">
-        <v>34</v>
-      </c>
-      <c r="G36">
-        <v>0.2</v>
-      </c>
-      <c r="H36" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I36">
-        <v>25</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="C36" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O36">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P36">
-        <v>46301.38232457793</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>36</v>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H36" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I36" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K36" s="6">
+        <v>1</v>
+      </c>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36" s="6">
+        <v>46300.75886463693</v>
+      </c>
+      <c r="P36" s="6">
+        <v>46302.26843231679</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:17">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" t="s">
-        <v>130</v>
-      </c>
-      <c r="G37">
-        <v>0.82</v>
-      </c>
-      <c r="H37" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I37">
-        <v>25</v>
-      </c>
-      <c r="J37" t="s">
-        <v>128</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37">
-        <v>46300.75884770849</v>
-      </c>
-      <c r="P37">
-        <v>46301.38232455136</v>
-      </c>
-      <c r="Q37" t="s">
+      <c r="A37" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H37" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I37" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K37" s="6">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" s="6">
+        <v>46300.75886465221</v>
+      </c>
+      <c r="P37" s="6">
+        <v>46302.26843229142</v>
+      </c>
+      <c r="Q37" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="6">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="I38" s="6">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="K38" s="6">
         <v>1</v>
       </c>
-      <c r="L38" s="6"/>
+      <c r="L38" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="M38" s="6" t="s">
         <v>18</v>
       </c>
@@ -2780,43 +2777,43 @@
         <v>18</v>
       </c>
       <c r="O38" s="6">
-        <v>46300.75886463693</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P38" s="6">
-        <v>46301.38234197814</v>
-      </c>
-      <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>46302.2684323297</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G39" s="6">
         <v>0.93</v>
       </c>
       <c r="H39" s="6">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="I39" s="6">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K39" s="6">
         <v>1</v>
@@ -2829,10 +2826,10 @@
         <v>18</v>
       </c>
       <c r="O39" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.75886468366</v>
       </c>
       <c r="P39" s="6">
-        <v>46301.38234197158</v>
+        <v>46302.26843234283</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>23</v>
@@ -2840,37 +2837,35 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6">
         <v>0.2</v>
       </c>
       <c r="H40" s="6">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="I40" s="6">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="K40" s="6">
         <v>1</v>
       </c>
-      <c r="L40" s="6" t="s">
-        <v>139</v>
-      </c>
+      <c r="L40" s="6"/>
       <c r="M40" s="6" t="s">
         <v>18</v>
       </c>
@@ -2878,43 +2873,43 @@
         <v>18</v>
       </c>
       <c r="O40" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P40" s="6">
-        <v>46301.3823419983</v>
+        <v>46302.26843236869</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="G41" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H41" s="6">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="I41" s="6">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K41" s="6">
         <v>1</v>
@@ -2927,10 +2922,10 @@
         <v>18</v>
       </c>
       <c r="O41" s="6">
-        <v>46300.75886468366</v>
+        <v>46300.75886472998</v>
       </c>
       <c r="P41" s="6">
-        <v>46301.38234199157</v>
+        <v>46302.26844080219</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>23</v>
@@ -2938,27 +2933,27 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H42" s="6">
         <v>46298</v>
       </c>
       <c r="I42" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>143</v>
@@ -2966,7 +2961,9 @@
       <c r="K42" s="6">
         <v>1</v>
       </c>
-      <c r="L42" s="6"/>
+      <c r="L42" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="M42" s="6" t="s">
         <v>18</v>
       </c>
@@ -2974,43 +2971,41 @@
         <v>18</v>
       </c>
       <c r="O42" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75886474836</v>
       </c>
       <c r="P42" s="6">
-        <v>46301.38234201136</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>36</v>
+        <v>46302.26843238134</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>38</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H43" s="6">
         <v>46298</v>
       </c>
       <c r="I43" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K43" s="6">
         <v>1</v>
@@ -3023,48 +3018,50 @@
         <v>18</v>
       </c>
       <c r="O43" s="6">
-        <v>46300.75886472998</v>
+        <v>46300.75886479358</v>
       </c>
       <c r="P43" s="6">
-        <v>46301.38234203825</v>
-      </c>
-      <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>46302.26843244523</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F44" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="G44" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H44" s="6">
         <v>46298</v>
       </c>
       <c r="I44" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K44" s="6">
+        <v>1</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="K44" s="6">
-        <v>1</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="M44" s="6" t="s">
         <v>18</v>
       </c>
@@ -3072,10 +3069,10 @@
         <v>18</v>
       </c>
       <c r="O44" s="6">
-        <v>46300.75886474836</v>
+        <v>46300.75886484625</v>
       </c>
       <c r="P44" s="6">
-        <v>46301.38234202487</v>
+        <v>46302.26843240711</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>23</v>
@@ -3083,30 +3080,30 @@
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H45" s="6">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="I45" s="6">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="K45" s="6">
         <v>1</v>
@@ -3121,10 +3118,10 @@
         <v>18</v>
       </c>
       <c r="O45" s="6">
-        <v>46300.75886476378</v>
+        <v>46300.75886486177</v>
       </c>
       <c r="P45" s="6">
-        <v>46301.38234205102</v>
+        <v>46302.26844081699</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>23</v>
@@ -3132,27 +3129,27 @@
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6">
         <v>0.2</v>
       </c>
       <c r="H46" s="6">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="I46" s="6">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>153</v>
@@ -3160,7 +3157,9 @@
       <c r="K46" s="6">
         <v>1</v>
       </c>
-      <c r="L46" s="6"/>
+      <c r="L46" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="M46" s="6" t="s">
         <v>18</v>
       </c>
@@ -3168,50 +3167,46 @@
         <v>18</v>
       </c>
       <c r="O46" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886487812</v>
       </c>
       <c r="P46" s="6">
-        <v>46301.38234204441</v>
+        <v>46302.2684408316</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H47" s="6">
-        <v>46298</v>
+        <v>46294</v>
       </c>
       <c r="I47" s="6">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
       </c>
-      <c r="L47" s="6" t="s">
-        <v>155</v>
-      </c>
+      <c r="L47" s="6"/>
       <c r="M47" s="6" t="s">
         <v>18</v>
       </c>
@@ -3219,48 +3214,46 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46300.75886484625</v>
+        <v>46300.75887301003</v>
       </c>
       <c r="P47" s="6">
-        <v>46301.3823420574</v>
-      </c>
-      <c r="Q47" s="6" t="s">
-        <v>23</v>
+        <v>46302.26844087261</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H48" s="6">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="I48" s="6">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K48" s="6">
         <v>1</v>
       </c>
-      <c r="L48" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="L48" s="6"/>
       <c r="M48" s="6" t="s">
         <v>18</v>
       </c>
@@ -3268,10 +3261,10 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75886486177</v>
+        <v>46300.75887304553</v>
       </c>
       <c r="P48" s="6">
-        <v>46301.38234207036</v>
+        <v>46302.26844088648</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>23</v>
@@ -3279,37 +3272,35 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
       <c r="H49" s="6">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="I49" s="6">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K49" s="6">
-        <v>1</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>160</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L49" s="6"/>
       <c r="M49" s="6" t="s">
         <v>18</v>
       </c>
@@ -3317,46 +3308,48 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75887306096</v>
       </c>
       <c r="P49" s="6">
-        <v>46301.38235023815</v>
-      </c>
-      <c r="Q49" s="5" t="s">
-        <v>36</v>
+        <v>46302.26844089953</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H50" s="6">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="I50" s="6">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K50" s="6">
-        <v>1</v>
-      </c>
-      <c r="L50" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>164</v>
+      </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3364,41 +3357,41 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75887301003</v>
+        <v>46300.75887309557</v>
       </c>
       <c r="P50" s="6">
-        <v>46301.38235027138</v>
-      </c>
-      <c r="Q50" s="5" t="s">
-        <v>36</v>
+        <v>46302.26844093824</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H51" s="6">
-        <v>46294</v>
+        <v>46292</v>
       </c>
       <c r="I51" s="6">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K51" s="6">
         <v>1</v>
@@ -3411,46 +3404,48 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46300.75887304553</v>
+        <v>46300.75887314334</v>
       </c>
       <c r="P51" s="6">
-        <v>46301.38235028457</v>
-      </c>
-      <c r="Q51" s="6" t="s">
-        <v>23</v>
+        <v>46302.26844096425</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
         <v>0.87</v>
       </c>
       <c r="H52" s="6">
-        <v>46294</v>
+        <v>46292</v>
       </c>
       <c r="I52" s="6">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K52" s="6">
-        <v>2</v>
-      </c>
-      <c r="L52" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="M52" s="6" t="s">
         <v>18</v>
       </c>
@@ -3458,10 +3453,10 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.75887306096</v>
+        <v>46300.75887316054</v>
       </c>
       <c r="P52" s="6">
-        <v>46301.38235026403</v>
+        <v>46302.26844097774</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>23</v>
@@ -3469,13 +3464,13 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
@@ -3483,22 +3478,22 @@
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H53" s="6">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="I53" s="6">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="K53" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>18</v>
@@ -3507,28 +3502,28 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.75887309557</v>
+        <v>46300.75887317812</v>
       </c>
       <c r="P53" s="6">
-        <v>46301.38235029773</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>23</v>
+        <v>46302.26844100373</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6">
@@ -3538,15 +3533,17 @@
         <v>46292</v>
       </c>
       <c r="I54" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K54" s="6">
         <v>1</v>
       </c>
-      <c r="L54" s="6"/>
+      <c r="L54" s="6" t="s">
+        <v>174</v>
+      </c>
       <c r="M54" s="6" t="s">
         <v>18</v>
       </c>
@@ -3554,48 +3551,46 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.75887314334</v>
+        <v>46300.75887319581</v>
       </c>
       <c r="P54" s="6">
-        <v>46301.38235032413</v>
+        <v>46302.26844099083</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6">
-        <v>0.87</v>
+        <v>0.2</v>
       </c>
       <c r="H55" s="6">
         <v>46292</v>
       </c>
       <c r="I55" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K55" s="6">
-        <v>3</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>174</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L55" s="6"/>
       <c r="M55" s="6" t="s">
         <v>18</v>
       </c>
@@ -3603,162 +3598,17 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75887316054</v>
+        <v>46300.75887321083</v>
       </c>
       <c r="P55" s="6">
-        <v>46301.3823503047</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17">
-      <c r="A56" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H56" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I56" s="6">
-        <v>-9</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="K56" s="6">
-        <v>1</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O56" s="6">
-        <v>46300.75887317812</v>
-      </c>
-      <c r="P56" s="6">
-        <v>46301.38235033712</v>
-      </c>
-      <c r="Q56" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17">
-      <c r="A57" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H57" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I57" s="6">
-        <v>-9</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K57" s="6">
-        <v>1</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O57" s="6">
-        <v>46300.75887319581</v>
-      </c>
-      <c r="P57" s="6">
-        <v>46301.38235033053</v>
-      </c>
-      <c r="Q57" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17">
-      <c r="A58" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H58" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I58" s="6">
-        <v>-9</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="K58" s="6">
-        <v>2</v>
-      </c>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O58" s="6">
-        <v>46300.75887321083</v>
-      </c>
-      <c r="P58" s="6">
-        <v>46301.38235031778</v>
-      </c>
-      <c r="Q58" s="5" t="s">
-        <v>36</v>
+        <v>46302.26844095104</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q58"/>
+  <autoFilter ref="A1:Q55"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -3868,12 +3718,6 @@
     <hyperlink ref="N54" r:id="rId106"/>
     <hyperlink ref="M55" r:id="rId107"/>
     <hyperlink ref="N55" r:id="rId108"/>
-    <hyperlink ref="M56" r:id="rId109"/>
-    <hyperlink ref="N56" r:id="rId110"/>
-    <hyperlink ref="M57" r:id="rId111"/>
-    <hyperlink ref="N57" r:id="rId112"/>
-    <hyperlink ref="M58" r:id="rId113"/>
-    <hyperlink ref="N58" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3881,7 +3725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3960,10 +3804,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
@@ -3972,10 +3816,10 @@
         <v>46302</v>
       </c>
       <c r="I2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -3990,10 +3834,10 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P2" s="2">
-        <v>46301.38233288697</v>
+        <v>46302.26843222459</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4004,10 +3848,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -4016,10 +3860,10 @@
         <v>46307</v>
       </c>
       <c r="I3" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4034,10 +3878,10 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46301.38233279494</v>
+        <v>46302.26842371625</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4048,10 +3892,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
@@ -4060,16 +3904,16 @@
         <v>46307</v>
       </c>
       <c r="I4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -4081,10 +3925,10 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P4" s="2">
-        <v>46300.77185324822</v>
+        <v>46302.26842366141</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4095,10 +3939,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -4107,10 +3951,10 @@
         <v>46308</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -4125,10 +3969,10 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P5" s="2">
-        <v>46301.38232478769</v>
+        <v>46302.26841530317</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -4139,10 +3983,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2">
         <v>0.2</v>
@@ -4151,10 +3995,10 @@
         <v>46308</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -4169,10 +4013,10 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P6" s="2">
-        <v>46301.38232480604</v>
+        <v>46302.2684152897</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -4183,10 +4027,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G7">
         <v>0.2</v>
@@ -4195,10 +4039,10 @@
         <v>46314</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4213,10 +4057,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P7">
-        <v>46301.38232472714</v>
+        <v>46302.26841514941</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4227,10 +4071,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G8">
         <v>0.2</v>
@@ -4239,10 +4083,10 @@
         <v>46315</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -4257,10 +4101,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46301.382324713</v>
+        <v>46302.26841510729</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4271,25 +4115,28 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="I9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>117</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -4298,13 +4145,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46301.38232468421</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46301.38232468424</v>
+        <v>46302.26841507771</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4315,122 +4162,119 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
+        <v>46317</v>
+      </c>
+      <c r="I10">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P10">
+        <v>46302.26841503391</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="3">
         <v>46326</v>
       </c>
-      <c r="I10">
-        <v>25</v>
-      </c>
-      <c r="J10" t="s">
-        <v>128</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
+      <c r="I11">
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11">
         <v>46300.75884768533</v>
       </c>
-      <c r="P10">
-        <v>46301.38232457793</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H11" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I11" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="K11" s="6">
-        <v>1</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46300.75886466862</v>
-      </c>
-      <c r="P11" s="6">
-        <v>46301.3823419983</v>
+      <c r="P11">
+        <v>46302.2684148914</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6">
         <v>0.2</v>
       </c>
       <c r="H12" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I12" s="6">
         <v>-3</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
       </c>
-      <c r="L12" s="6"/>
+      <c r="L12" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="M12" s="6" t="s">
         <v>18</v>
       </c>
@@ -4438,28 +4282,28 @@
         <v>18</v>
       </c>
       <c r="O12" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P12" s="6">
-        <v>46301.38234201136</v>
+        <v>46302.2684323297</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
@@ -4469,10 +4313,10 @@
         <v>46298</v>
       </c>
       <c r="I13" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="K13" s="6">
         <v>1</v>
@@ -4485,48 +4329,46 @@
         <v>18</v>
       </c>
       <c r="O13" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P13" s="6">
-        <v>46301.38234204441</v>
+        <v>46302.26843236869</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6">
         <v>0.2</v>
       </c>
       <c r="H14" s="6">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="I14" s="6">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>160</v>
-      </c>
+      <c r="L14" s="6"/>
       <c r="M14" s="6" t="s">
         <v>18</v>
       </c>
@@ -4534,46 +4376,48 @@
         <v>18</v>
       </c>
       <c r="O14" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75886479358</v>
       </c>
       <c r="P14" s="6">
-        <v>46301.38235023815</v>
+        <v>46302.26843244523</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6">
         <v>0.2</v>
       </c>
       <c r="H15" s="6">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="I15" s="6">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
       </c>
-      <c r="L15" s="6"/>
+      <c r="L15" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="M15" s="6" t="s">
         <v>18</v>
       </c>
@@ -4581,41 +4425,41 @@
         <v>18</v>
       </c>
       <c r="O15" s="6">
-        <v>46300.75887301003</v>
+        <v>46300.75886487812</v>
       </c>
       <c r="P15" s="6">
-        <v>46301.38235027138</v>
+        <v>46302.2684408316</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
         <v>0.2</v>
       </c>
       <c r="H16" s="6">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I16" s="6">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="K16" s="6">
         <v>1</v>
@@ -4628,28 +4472,28 @@
         <v>18</v>
       </c>
       <c r="O16" s="6">
-        <v>46300.75887314334</v>
+        <v>46300.75887301003</v>
       </c>
       <c r="P16" s="6">
-        <v>46301.38235032413</v>
+        <v>46302.26844087261</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
@@ -4659,17 +4503,15 @@
         <v>46292</v>
       </c>
       <c r="I17" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="K17" s="6">
         <v>1</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>176</v>
-      </c>
+      <c r="L17" s="6"/>
       <c r="M17" s="6" t="s">
         <v>18</v>
       </c>
@@ -4677,28 +4519,28 @@
         <v>18</v>
       </c>
       <c r="O17" s="6">
-        <v>46300.75887317812</v>
+        <v>46300.75887314334</v>
       </c>
       <c r="P17" s="6">
-        <v>46301.38235033712</v>
+        <v>46302.26844096425</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6">
@@ -4708,16 +4550,16 @@
         <v>46292</v>
       </c>
       <c r="I18" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="K18" s="6">
         <v>1</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>18</v>
@@ -4726,28 +4568,28 @@
         <v>18</v>
       </c>
       <c r="O18" s="6">
-        <v>46300.75887319581</v>
+        <v>46300.75887317812</v>
       </c>
       <c r="P18" s="6">
-        <v>46301.38235033053</v>
+        <v>46302.26844100373</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6">
@@ -4757,33 +4599,82 @@
         <v>46292</v>
       </c>
       <c r="I19" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="6">
+        <v>46300.75887319581</v>
+      </c>
+      <c r="P19" s="6">
+        <v>46302.26844099083</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="6">
+        <v>46292</v>
+      </c>
+      <c r="I20" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K20" s="6">
         <v>2</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="6">
+      <c r="L20" s="6"/>
+      <c r="M20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="6">
         <v>46300.75887321083</v>
       </c>
-      <c r="P19" s="6">
-        <v>46301.38235031778</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>36</v>
+      <c r="P20" s="6">
+        <v>46302.26844095104</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q20"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4821,6 +4712,8 @@
     <hyperlink ref="N18" r:id="rId34"/>
     <hyperlink ref="M19" r:id="rId35"/>
     <hyperlink ref="N19" r:id="rId36"/>
+    <hyperlink ref="M20" r:id="rId37"/>
+    <hyperlink ref="N20" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4828,7 +4721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4838,86 +4731,86 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B2">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E2">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G2">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B3">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D3">
         <v>8</v>
@@ -4926,13 +4819,13 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4941,18 +4834,18 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B4">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -4961,21 +4854,56 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H4">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B5">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>160</v>
+      </c>
+      <c r="F5">
+        <v>157</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>132</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="189">
   <si>
     <t>Priority</t>
   </si>
@@ -1103,7 +1103,7 @@
         <v>46300.7588564394</v>
       </c>
       <c r="P2" s="2">
-        <v>46302.26843221064</v>
+        <v>46302.79192097764</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1147,7 +1147,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P3" s="2">
-        <v>46302.26843222459</v>
+        <v>46302.79192099054</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>27</v>
@@ -1197,7 +1197,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P4" s="2">
-        <v>46302.26842387108</v>
+        <v>46302.79191047805</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1241,7 +1241,7 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P5" s="2">
-        <v>46302.26842383233</v>
+        <v>46302.79191043837</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1288,7 +1288,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P6" s="2">
-        <v>46302.26842384538</v>
+        <v>46302.7919104524</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1335,7 +1335,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P7" s="2">
-        <v>46302.26842380712</v>
+        <v>46302.79191041266</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1382,7 +1382,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P8" s="2">
-        <v>46302.26842375574</v>
+        <v>46302.79191036006</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>23</v>
@@ -1432,7 +1432,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P9" s="2">
-        <v>46302.26842376858</v>
+        <v>46302.79191037345</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>23</v>
@@ -1482,7 +1482,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P10" s="2">
-        <v>46302.26842378132</v>
+        <v>46302.79191038655</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>23</v>
@@ -1529,7 +1529,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P11" s="2">
-        <v>46302.26842374232</v>
+        <v>46302.79191034697</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>23</v>
@@ -1579,7 +1579,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P12" s="2">
-        <v>46302.2684236893</v>
+        <v>46302.79191029487</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1623,7 +1623,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P13" s="2">
-        <v>46302.26842371625</v>
+        <v>46302.79191032116</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>27</v>
@@ -1670,7 +1670,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P14" s="2">
-        <v>46302.26842364718</v>
+        <v>46302.79191025375</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1717,7 +1717,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P15" s="2">
-        <v>46302.26842366141</v>
+        <v>46302.79191026733</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>27</v>
@@ -1761,7 +1761,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P16" s="2">
-        <v>46302.26842361677</v>
+        <v>46302.79191022492</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1808,7 +1808,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P17" s="2">
-        <v>46302.26842367557</v>
+        <v>46302.79191028092</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>23</v>
@@ -1858,7 +1858,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P18" s="2">
-        <v>46302.26841531677</v>
+        <v>46302.79189773565</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -1902,7 +1902,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P19" s="2">
-        <v>46302.26841530317</v>
+        <v>46302.79189772235</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>27</v>
@@ -1946,7 +1946,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P20" s="2">
-        <v>46302.2684152897</v>
+        <v>46302.79189770951</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>27</v>
@@ -1993,7 +1993,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P21">
-        <v>46302.26841527641</v>
+        <v>46302.79189769677</v>
       </c>
       <c r="Q21" t="s">
         <v>23</v>
@@ -2040,7 +2040,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P22">
-        <v>46302.26841524903</v>
+        <v>46302.79189767046</v>
       </c>
       <c r="Q22" t="s">
         <v>23</v>
@@ -2084,7 +2084,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P23">
-        <v>46302.26841520685</v>
+        <v>46302.79189763116</v>
       </c>
       <c r="Q23" t="s">
         <v>23</v>
@@ -2131,7 +2131,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P24">
-        <v>46302.26841522126</v>
+        <v>46302.79189764443</v>
       </c>
       <c r="Q24" t="s">
         <v>23</v>
@@ -2178,7 +2178,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P25">
-        <v>46302.26841523509</v>
+        <v>46302.79189765739</v>
       </c>
       <c r="Q25" t="s">
         <v>23</v>
@@ -2225,7 +2225,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P26">
-        <v>46302.2684151932</v>
+        <v>46302.79189761808</v>
       </c>
       <c r="Q26" t="s">
         <v>23</v>
@@ -2272,7 +2272,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P27">
-        <v>46302.26841513602</v>
+        <v>46302.79189759048</v>
       </c>
       <c r="Q27" t="s">
         <v>23</v>
@@ -2316,7 +2316,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P28">
-        <v>46302.26841514941</v>
+        <v>46302.79189760437</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>27</v>
@@ -2360,7 +2360,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P29">
-        <v>46302.26841512165</v>
+        <v>46302.79189757702</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2404,7 +2404,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P30">
-        <v>46302.26841510729</v>
+        <v>46302.79189756404</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>27</v>
@@ -2451,7 +2451,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P31">
-        <v>46302.26841507771</v>
+        <v>46302.79189753801</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>27</v>
@@ -2495,7 +2495,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P32">
-        <v>46302.26841503391</v>
+        <v>46302.79189752453</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>27</v>
@@ -2542,7 +2542,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P33">
-        <v>46302.26841501555</v>
+        <v>46302.79189751096</v>
       </c>
       <c r="Q33" t="s">
         <v>23</v>
@@ -2586,7 +2586,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P34">
-        <v>46302.2684148914</v>
+        <v>46302.79189749651</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>27</v>
@@ -2635,7 +2635,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P35" s="6">
-        <v>46302.26843226571</v>
+        <v>46302.79192102975</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>23</v>
@@ -2682,7 +2682,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P36" s="6">
-        <v>46302.26843231679</v>
+        <v>46302.79192108147</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>23</v>
@@ -2731,7 +2731,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P37" s="6">
-        <v>46302.26843229142</v>
+        <v>46302.79192105515</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>23</v>
@@ -2780,7 +2780,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P38" s="6">
-        <v>46302.2684323297</v>
+        <v>46302.79192109437</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>27</v>
@@ -2829,7 +2829,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P39" s="6">
-        <v>46302.26843234283</v>
+        <v>46302.79192110736</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>23</v>
@@ -2876,7 +2876,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P40" s="6">
-        <v>46302.26843236869</v>
+        <v>46302.79192113371</v>
       </c>
       <c r="Q40" s="5" t="s">
         <v>27</v>
@@ -2925,7 +2925,7 @@
         <v>46300.75886472998</v>
       </c>
       <c r="P41" s="6">
-        <v>46302.26844080219</v>
+        <v>46302.79193306002</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>23</v>
@@ -2974,7 +2974,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P42" s="6">
-        <v>46302.26843238134</v>
+        <v>46302.79192114654</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>23</v>
@@ -3021,7 +3021,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P43" s="6">
-        <v>46302.26843244523</v>
+        <v>46302.79192121145</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>27</v>
@@ -3072,7 +3072,7 @@
         <v>46300.75886484625</v>
       </c>
       <c r="P44" s="6">
-        <v>46302.26843240711</v>
+        <v>46302.79192117266</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>23</v>
@@ -3121,7 +3121,7 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P45" s="6">
-        <v>46302.26844081699</v>
+        <v>46302.79193307317</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>23</v>
@@ -3170,7 +3170,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P46" s="6">
-        <v>46302.2684408316</v>
+        <v>46302.79193308652</v>
       </c>
       <c r="Q46" s="5" t="s">
         <v>27</v>
@@ -3217,7 +3217,7 @@
         <v>46300.75887301003</v>
       </c>
       <c r="P47" s="6">
-        <v>46302.26844087261</v>
+        <v>46302.79193312495</v>
       </c>
       <c r="Q47" s="5" t="s">
         <v>27</v>
@@ -3264,7 +3264,7 @@
         <v>46300.75887304553</v>
       </c>
       <c r="P48" s="6">
-        <v>46302.26844088648</v>
+        <v>46302.79193313776</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>23</v>
@@ -3311,7 +3311,7 @@
         <v>46300.75887306096</v>
       </c>
       <c r="P49" s="6">
-        <v>46302.26844089953</v>
+        <v>46302.79193315036</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>23</v>
@@ -3360,7 +3360,7 @@
         <v>46300.75887309557</v>
       </c>
       <c r="P50" s="6">
-        <v>46302.26844093824</v>
+        <v>46302.79193318906</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3407,7 +3407,7 @@
         <v>46300.75887314334</v>
       </c>
       <c r="P51" s="6">
-        <v>46302.26844096425</v>
+        <v>46302.7919332146</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>27</v>
@@ -3456,7 +3456,7 @@
         <v>46300.75887316054</v>
       </c>
       <c r="P52" s="6">
-        <v>46302.26844097774</v>
+        <v>46302.79193322792</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>23</v>
@@ -3505,7 +3505,7 @@
         <v>46300.75887317812</v>
       </c>
       <c r="P53" s="6">
-        <v>46302.26844100373</v>
+        <v>46302.79193325419</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>27</v>
@@ -3554,7 +3554,7 @@
         <v>46300.75887319581</v>
       </c>
       <c r="P54" s="6">
-        <v>46302.26844099083</v>
+        <v>46302.79193324078</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>27</v>
@@ -3601,7 +3601,7 @@
         <v>46300.75887321083</v>
       </c>
       <c r="P55" s="6">
-        <v>46302.26844095104</v>
+        <v>46302.79193320179</v>
       </c>
       <c r="Q55" s="5" t="s">
         <v>27</v>
@@ -3834,7 +3834,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P2" s="2">
-        <v>46302.26843222459</v>
+        <v>46302.79192099054</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>27</v>
@@ -3878,7 +3878,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46302.26842371625</v>
+        <v>46302.79191032116</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>27</v>
@@ -3925,7 +3925,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P4" s="2">
-        <v>46302.26842366141</v>
+        <v>46302.79191026733</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>27</v>
@@ -3969,7 +3969,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P5" s="2">
-        <v>46302.26841530317</v>
+        <v>46302.79189772235</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>27</v>
@@ -4013,7 +4013,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P6" s="2">
-        <v>46302.2684152897</v>
+        <v>46302.79189770951</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>27</v>
@@ -4057,7 +4057,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P7">
-        <v>46302.26841514941</v>
+        <v>46302.79189760437</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>27</v>
@@ -4101,7 +4101,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46302.26841510729</v>
+        <v>46302.79189756404</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>27</v>
@@ -4148,7 +4148,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46302.26841507771</v>
+        <v>46302.79189753801</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>27</v>
@@ -4192,7 +4192,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P10">
-        <v>46302.26841503391</v>
+        <v>46302.79189752453</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>27</v>
@@ -4236,7 +4236,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P11">
-        <v>46302.2684148914</v>
+        <v>46302.79189749651</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>27</v>
@@ -4285,7 +4285,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P12" s="6">
-        <v>46302.2684323297</v>
+        <v>46302.79192109437</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>27</v>
@@ -4332,7 +4332,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P13" s="6">
-        <v>46302.26843236869</v>
+        <v>46302.79192113371</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>27</v>
@@ -4379,7 +4379,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P14" s="6">
-        <v>46302.26843244523</v>
+        <v>46302.79192121145</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>27</v>
@@ -4428,7 +4428,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P15" s="6">
-        <v>46302.2684408316</v>
+        <v>46302.79193308652</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>27</v>
@@ -4475,7 +4475,7 @@
         <v>46300.75887301003</v>
       </c>
       <c r="P16" s="6">
-        <v>46302.26844087261</v>
+        <v>46302.79193312495</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>27</v>
@@ -4522,7 +4522,7 @@
         <v>46300.75887314334</v>
       </c>
       <c r="P17" s="6">
-        <v>46302.26844096425</v>
+        <v>46302.7919332146</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>27</v>
@@ -4571,7 +4571,7 @@
         <v>46300.75887317812</v>
       </c>
       <c r="P18" s="6">
-        <v>46302.26844100373</v>
+        <v>46302.79193325419</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>27</v>
@@ -4620,7 +4620,7 @@
         <v>46300.75887319581</v>
       </c>
       <c r="P19" s="6">
-        <v>46302.26844099083</v>
+        <v>46302.79193324078</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>27</v>
@@ -4667,7 +4667,7 @@
         <v>46300.75887321083</v>
       </c>
       <c r="P20" s="6">
-        <v>46302.26844095104</v>
+        <v>46302.79193320179</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>27</v>
@@ -4721,7 +4721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B2">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C2" t="s">
         <v>188</v>
@@ -4784,16 +4784,16 @@
         <v>3820</v>
       </c>
       <c r="F2">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H2">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4804,45 +4804,45 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B3">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C3" t="s">
         <v>188</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E3">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G3">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B4">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C4" t="s">
         <v>188</v>
@@ -4854,13 +4854,13 @@
         <v>160</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4869,15 +4869,15 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B5">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C5" t="s">
         <v>188</v>
@@ -4889,21 +4889,56 @@
         <v>160</v>
       </c>
       <c r="F5">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H5">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B6">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>160</v>
+      </c>
+      <c r="F6">
+        <v>157</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>132</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="177">
   <si>
     <t>Priority</t>
   </si>
@@ -79,327 +79,327 @@
     <t>Open</t>
   </si>
   <si>
+    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Chakrala Sannidhi</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>Shree Shiddhanath Cotex Private Limited</t>
+  </si>
+  <si>
+    <t>Textiles</t>
+  </si>
+  <si>
+    <t>Akhil Ahuja</t>
+  </si>
+  <si>
+    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
+  </si>
+  <si>
+    <t>INFO-DRIVE SOFTWARE LIMITED</t>
+  </si>
+  <si>
+    <t>Sumeet Surendra Chimbalkar</t>
+  </si>
+  <si>
+    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>A.P.J. LABORATORIES LIMITED</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>pooja damir miglani</t>
+  </si>
+  <si>
+    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
+  </si>
+  <si>
+    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>Mrs. Neeraja Kartik</t>
+  </si>
+  <si>
+    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
+  </si>
+  <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
     <t>Mr. Manoj Sehgal</t>
   </si>
   <si>
     <t>The Corporate Debtor is Not Operational for last 2 years. Form G published on 22.09.2026 in Financial Express (English, Lucknow Edition) &amp; Jansatta (Hindi, Lucknow Edition)</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
     <t>SNEH EXPORTS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
     <t>Garima diggiwal</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Chakrala Sannidhi</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>Shree Shiddhanath Cotex Private Limited</t>
-  </si>
-  <si>
-    <t>Textiles</t>
-  </si>
-  <si>
-    <t>Akhil Ahuja</t>
-  </si>
-  <si>
-    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
-  </si>
-  <si>
-    <t>INFO-DRIVE SOFTWARE LIMITED</t>
-  </si>
-  <si>
-    <t>Sumeet Surendra Chimbalkar</t>
-  </si>
-  <si>
-    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>A.P.J. LABORATORIES LIMITED</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>pooja damir miglani</t>
-  </si>
-  <si>
-    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
-  </si>
-  <si>
-    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>Mrs. Neeraja Kartik</t>
-  </si>
-  <si>
-    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
-  </si>
-  <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>NOEL PHARMA (INDIA) PRIVATE LIMITED</t>
   </si>
   <si>
@@ -515,42 +515,6 @@
   </si>
   <si>
     <t>Assets of the Corporate Debtor and the Personal Guarantors are proposed to be clubbed under Sec.28A of IBC for the purpose of inviting resolution plans.</t>
-  </si>
-  <si>
-    <t>EYEMYEYE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Suresh Kannan</t>
-  </si>
-  <si>
-    <t>FUTURE CONSUMER LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Avil Jerome Menezes</t>
-  </si>
-  <si>
-    <t>Form G was published on 06 September 2026 for inviting expression of interest in the CIRP of Future Consumer Limited. The last date for submission of expression of interest is 27 September 2026.</t>
-  </si>
-  <si>
-    <t>Bhartiya Micro Credit</t>
-  </si>
-  <si>
-    <t>Reissuance of Form G, subject to the approval of the Committee of Creditors (CoC) and the Hon’ble NCLT.</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.09.2026.</t>
-  </si>
-  <si>
-    <t>JAI AMBE SPARES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Gajesh Labhchand Jain</t>
   </si>
   <si>
     <t>Started</t>
@@ -991,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1075,23 +1039,26 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="2">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" s="3">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
@@ -1100,13 +1067,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.7588564394</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P2" s="2">
-        <v>46302.79192097764</v>
+        <v>46303.38329450462</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -1117,40 +1084,40 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="H3" s="3">
+        <v>46304</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.75885634872</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46303.3832944789</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46302</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46302.79192099054</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1166,27 +1133,24 @@
       <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="G4" s="2">
         <v>0.9399999999999999</v>
       </c>
       <c r="H4" s="3">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="2">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1194,13 +1158,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.7588564207</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P4" s="2">
-        <v>46302.79191047805</v>
+        <v>46303.38329448765</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1211,26 +1175,29 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2">
         <v>0.91</v>
       </c>
       <c r="H5" s="3">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
+      <c r="L5" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1238,13 +1205,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75885634872</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P5" s="2">
-        <v>46302.79191043837</v>
+        <v>46303.38329446202</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1255,19 +1222,22 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H6" s="3">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>38</v>
@@ -1275,9 +1245,6 @@
       <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1285,13 +1252,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.7588563655</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P6" s="2">
-        <v>46302.7919104524</v>
+        <v>46303.38329442757</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1302,16 +1269,19 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="G7" s="2">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I7" s="2">
         <v>3</v>
@@ -1332,13 +1302,13 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75885633306</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P7" s="2">
-        <v>46302.79191041266</v>
+        <v>46303.38329443617</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1358,13 +1328,13 @@
         <v>45</v>
       </c>
       <c r="G8" s="2">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H8" s="3">
         <v>46306</v>
       </c>
       <c r="I8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>46</v>
@@ -1372,6 +1342,9 @@
       <c r="K8" s="2">
         <v>1</v>
       </c>
+      <c r="L8" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1379,13 +1352,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.75885622757</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P8" s="2">
-        <v>46302.79191036006</v>
+        <v>46303.38329444442</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1396,13 +1369,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2">
         <v>0.9399999999999999</v>
@@ -1411,16 +1381,16 @@
         <v>46306</v>
       </c>
       <c r="I9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -1429,13 +1399,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75885624527</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P9" s="2">
-        <v>46302.79191037345</v>
+        <v>46303.38329441878</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1446,31 +1416,31 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="H10" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
@@ -1479,13 +1449,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.7588562628</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P10" s="2">
-        <v>46302.79191038655</v>
+        <v>46303.38329438417</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1496,29 +1466,26 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1526,13 +1493,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.75885627908</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P11" s="2">
-        <v>46302.79191034697</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>23</v>
+        <v>46303.38329440156</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1543,22 +1510,22 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="2">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="H12" s="3">
         <v>46307</v>
       </c>
       <c r="I12" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>63</v>
@@ -1566,9 +1533,6 @@
       <c r="K12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
       </c>
@@ -1576,13 +1540,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75884793277</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P12" s="2">
-        <v>46302.79191029487</v>
+        <v>46303.3832943571</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1593,10 +1557,10 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2">
         <v>0.2</v>
@@ -1605,14 +1569,17 @@
         <v>46307</v>
       </c>
       <c r="I13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1620,13 +1587,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P13" s="2">
-        <v>46302.79191032116</v>
+        <v>46303.38329436627</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1640,19 +1607,16 @@
         <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H14" s="3">
         <v>46307</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>69</v>
@@ -1667,13 +1631,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75884796329</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P14" s="2">
-        <v>46302.79191025375</v>
+        <v>46303.38329433652</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1687,26 +1651,26 @@
         <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H15" s="3">
         <v>46307</v>
       </c>
       <c r="I15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1714,13 +1678,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P15" s="2">
-        <v>46302.79191026733</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>27</v>
+        <v>46303.38329437528</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1731,16 +1695,19 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G16" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H16" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
@@ -1751,6 +1718,9 @@
       <c r="K16" s="2">
         <v>1</v>
       </c>
+      <c r="L16" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1758,13 +1728,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46300.75885617639</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P16" s="2">
-        <v>46302.79191022492</v>
+        <v>46303.38328156831</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1775,29 +1745,26 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="G17" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H17" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I17" s="2">
         <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
       </c>
@@ -1805,13 +1772,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46300.75885619673</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P17" s="2">
-        <v>46302.79191028092</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>23</v>
+        <v>46303.38328155963</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1822,32 +1789,26 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="G18" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H18" s="3">
         <v>46308</v>
       </c>
       <c r="I18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1855,13 +1816,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46300.75884788632</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P18" s="2">
-        <v>46302.79189773565</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>23</v>
+        <v>46303.38328155097</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1872,26 +1833,29 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46310</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I19" s="2">
-        <v>6</v>
-      </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
       </c>
@@ -1899,42 +1863,45 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P19" s="2">
-        <v>46302.79189772235</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="2" customFormat="1">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="2" t="s">
+        <v>46303.38328154255</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.2</v>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20">
+        <v>0.95</v>
       </c>
       <c r="H20" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I20" s="2">
-        <v>6</v>
-      </c>
-      <c r="J20" s="2" t="s">
+        <v>46312</v>
+      </c>
+      <c r="I20">
+        <v>9</v>
+      </c>
+      <c r="J20" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="2">
-        <v>1</v>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>87</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -1942,14 +1909,14 @@
       <c r="N20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="2">
-        <v>46301.38232480602</v>
-      </c>
-      <c r="P20" s="2">
-        <v>46302.79189770951</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>27</v>
+      <c r="O20">
+        <v>46300.75884779022</v>
+      </c>
+      <c r="P20">
+        <v>46303.38328152523</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1960,29 +1927,26 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="G21">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H21" s="3">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21" t="s">
-        <v>89</v>
-      </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
       </c>
@@ -1990,13 +1954,13 @@
         <v>18</v>
       </c>
       <c r="O21">
-        <v>46300.75884787029</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P21">
-        <v>46302.79189769677</v>
+        <v>46303.38328149894</v>
       </c>
       <c r="Q21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2007,28 +1971,28 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G22">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="H22" s="3">
         <v>46312</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2037,13 +2001,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46300.75884779022</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P22">
-        <v>46302.79189767046</v>
+        <v>46303.38328150799</v>
       </c>
       <c r="Q22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2054,26 +2018,29 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G23">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H23" s="3">
         <v>46312</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
+      <c r="L23" t="s">
+        <v>97</v>
+      </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
       </c>
@@ -2081,13 +2048,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46300.75884780569</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P23">
-        <v>46302.79189763116</v>
+        <v>46303.38328151646</v>
       </c>
       <c r="Q23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2098,28 +2065,28 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G24">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H24" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
       <c r="J24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2128,13 +2095,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46300.75884782107</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P24">
-        <v>46302.79189764443</v>
+        <v>46303.38328149018</v>
       </c>
       <c r="Q24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2145,29 +2112,29 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
       </c>
       <c r="G25">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H25" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="L25" t="s">
-        <v>102</v>
-      </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
       </c>
@@ -2175,13 +2142,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46300.75884783743</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P25">
-        <v>46302.79189765739</v>
+        <v>46303.38328147282</v>
       </c>
       <c r="Q25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2192,28 +2159,25 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="G26">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I26">
         <v>11</v>
       </c>
       <c r="J26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K26">
-        <v>3</v>
-      </c>
-      <c r="L26" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2222,13 +2186,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46302.26841519317</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P26">
-        <v>46302.79189761808</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>23</v>
+        <v>46303.38328148136</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2239,25 +2203,22 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="G27">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H27" s="3">
         <v>46314</v>
       </c>
       <c r="I27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2269,13 +2230,13 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46300.75884774033</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P27">
-        <v>46302.79189759048</v>
+        <v>46303.38328146389</v>
       </c>
       <c r="Q27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2286,22 +2247,22 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G28">
         <v>0.2</v>
       </c>
       <c r="H28" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I28">
         <v>12</v>
       </c>
       <c r="J28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2313,13 +2274,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46300.75884775587</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P28">
-        <v>46302.79189760437</v>
+        <v>46303.38328145499</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2330,26 +2291,29 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I29">
+        <v>13</v>
+      </c>
+      <c r="J29" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29" t="s">
         <v>112</v>
       </c>
-      <c r="E29" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29">
-        <v>0.93</v>
-      </c>
-      <c r="H29" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I29">
-        <v>12</v>
-      </c>
-      <c r="J29" t="s">
-        <v>113</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2357,13 +2321,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46300.7588477715</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P29">
-        <v>46302.79189757702</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>23</v>
+        <v>46303.38328143695</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2374,22 +2338,22 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G30">
         <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2401,13 +2365,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46300.75884772457</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P30">
-        <v>46302.79189756404</v>
+        <v>46303.3832814277</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2418,28 +2382,28 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="F31" t="s">
+        <v>40</v>
       </c>
       <c r="G31">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H31" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I31">
         <v>14</v>
       </c>
       <c r="J31" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="K31">
-        <v>3</v>
-      </c>
-      <c r="L31" t="s">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2448,13 +2412,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46302.26841507768</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P31">
-        <v>46302.79189753801</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>27</v>
+        <v>46303.38328141814</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2465,149 +2429,154 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G32">
         <v>0.2</v>
       </c>
       <c r="H32" s="3">
-        <v>46317</v>
+        <v>46326</v>
       </c>
       <c r="I32">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J32" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P32">
+        <v>46303.38328140793</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O32">
-        <v>46301.38232468421</v>
-      </c>
-      <c r="P32">
-        <v>46302.79189752453</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E33" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H33" s="3">
-        <v>46317</v>
-      </c>
-      <c r="I33">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="C33" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33">
-        <v>46302.26841501552</v>
-      </c>
-      <c r="P33">
-        <v>46302.79189751096</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>23</v>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H33" s="6">
+        <v>46302</v>
+      </c>
+      <c r="I33" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K33" s="6">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33" s="6">
+        <v>46300.7588564394</v>
+      </c>
+      <c r="P33" s="6">
+        <v>46303.38330297283</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34">
+      <c r="A34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6">
         <v>0.2</v>
       </c>
-      <c r="H34" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I34">
-        <v>24</v>
-      </c>
-      <c r="J34" t="s">
-        <v>123</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P34">
-        <v>46302.79189749651</v>
+      <c r="H34" s="6">
+        <v>46302</v>
+      </c>
+      <c r="I34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="6">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34" s="6">
+        <v>46300.75885647022</v>
+      </c>
+      <c r="P34" s="6">
+        <v>46303.38330298233</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G35" s="6">
         <v>0.9399999999999999</v>
@@ -2616,7 +2585,7 @@
         <v>46301</v>
       </c>
       <c r="I35" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>127</v>
@@ -2635,18 +2604,18 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P35" s="6">
-        <v>46302.79192102975</v>
+        <v>46303.38330300884</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>128</v>
@@ -2663,7 +2632,7 @@
         <v>46300</v>
       </c>
       <c r="I36" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>130</v>
@@ -2682,28 +2651,28 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P36" s="6">
-        <v>46302.79192108147</v>
+        <v>46303.38330304309</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>131</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G37" s="6">
         <v>0.93</v>
@@ -2712,7 +2681,7 @@
         <v>46300</v>
       </c>
       <c r="I37" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>132</v>
@@ -2731,25 +2700,25 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P37" s="6">
-        <v>46302.79192105515</v>
+        <v>46303.3833030263</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
@@ -2759,10 +2728,10 @@
         <v>46299</v>
       </c>
       <c r="I38" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K38" s="6">
         <v>1</v>
@@ -2780,28 +2749,28 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P38" s="6">
-        <v>46302.79192109437</v>
+        <v>46303.38330305153</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>135</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G39" s="6">
         <v>0.93</v>
@@ -2810,7 +2779,7 @@
         <v>46299</v>
       </c>
       <c r="I39" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>136</v>
@@ -2829,25 +2798,25 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P39" s="6">
-        <v>46302.79192110736</v>
+        <v>46303.38330306018</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6">
@@ -2857,7 +2826,7 @@
         <v>46298</v>
       </c>
       <c r="I40" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>138</v>
@@ -2876,28 +2845,28 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P40" s="6">
-        <v>46302.79192113371</v>
+        <v>46303.38330307746</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>139</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G41" s="6">
         <v>0.9399999999999999</v>
@@ -2906,7 +2875,7 @@
         <v>46298</v>
       </c>
       <c r="I41" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>140</v>
@@ -2925,18 +2894,18 @@
         <v>46300.75886472998</v>
       </c>
       <c r="P41" s="6">
-        <v>46302.79193306002</v>
+        <v>46303.38331249326</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>141</v>
@@ -2953,7 +2922,7 @@
         <v>46298</v>
       </c>
       <c r="I42" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>143</v>
@@ -2974,25 +2943,25 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P42" s="6">
-        <v>46302.79192114654</v>
+        <v>46303.38330308611</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6">
@@ -3002,7 +2971,7 @@
         <v>46298</v>
       </c>
       <c r="I43" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>146</v>
@@ -3021,28 +2990,28 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P43" s="6">
-        <v>46302.79192121145</v>
+        <v>46303.38330312896</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>147</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G44" s="6">
         <v>0.93</v>
@@ -3051,10 +3020,10 @@
         <v>46298</v>
       </c>
       <c r="I44" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K44" s="6">
         <v>1</v>
@@ -3072,18 +3041,18 @@
         <v>46300.75886484625</v>
       </c>
       <c r="P44" s="6">
-        <v>46302.79192117266</v>
+        <v>46303.38330310328</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>149</v>
@@ -3100,7 +3069,7 @@
         <v>46297</v>
       </c>
       <c r="I45" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>150</v>
@@ -3121,25 +3090,25 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P45" s="6">
-        <v>46302.79193307317</v>
+        <v>46303.38331250347</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6">
@@ -3149,7 +3118,7 @@
         <v>46296</v>
       </c>
       <c r="I46" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>153</v>
@@ -3170,25 +3139,25 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P46" s="6">
-        <v>46302.79193308652</v>
+        <v>46303.3833125137</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>155</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6">
@@ -3198,7 +3167,7 @@
         <v>46294</v>
       </c>
       <c r="I47" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>156</v>
@@ -3217,25 +3186,25 @@
         <v>46300.75887301003</v>
       </c>
       <c r="P47" s="6">
-        <v>46302.79193312495</v>
+        <v>46303.38331254272</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>157</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6">
@@ -3245,7 +3214,7 @@
         <v>46294</v>
       </c>
       <c r="I48" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>158</v>
@@ -3264,18 +3233,18 @@
         <v>46300.75887304553</v>
       </c>
       <c r="P48" s="6">
-        <v>46302.79193313776</v>
+        <v>46303.38331255232</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>159</v>
@@ -3292,7 +3261,7 @@
         <v>46294</v>
       </c>
       <c r="I49" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>161</v>
@@ -3311,25 +3280,25 @@
         <v>46300.75887306096</v>
       </c>
       <c r="P49" s="6">
-        <v>46302.79193315036</v>
+        <v>46303.38331256139</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
@@ -3339,7 +3308,7 @@
         <v>46293</v>
       </c>
       <c r="I50" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>163</v>
@@ -3360,255 +3329,14 @@
         <v>46300.75887309557</v>
       </c>
       <c r="P50" s="6">
-        <v>46302.79193318906</v>
+        <v>46303.38331258995</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17">
-      <c r="A51" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H51" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I51" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K51" s="6">
-        <v>1</v>
-      </c>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N51" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O51" s="6">
-        <v>46300.75887314334</v>
-      </c>
-      <c r="P51" s="6">
-        <v>46302.7919332146</v>
-      </c>
-      <c r="Q51" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17">
-      <c r="A52" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="H52" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I52" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K52" s="6">
-        <v>3</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O52" s="6">
-        <v>46300.75887316054</v>
-      </c>
-      <c r="P52" s="6">
-        <v>46302.79193322792</v>
-      </c>
-      <c r="Q52" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17">
-      <c r="A53" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H53" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I53" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K53" s="6">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O53" s="6">
-        <v>46300.75887317812</v>
-      </c>
-      <c r="P53" s="6">
-        <v>46302.79193325419</v>
-      </c>
-      <c r="Q53" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17">
-      <c r="A54" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H54" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I54" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K54" s="6">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O54" s="6">
-        <v>46300.75887319581</v>
-      </c>
-      <c r="P54" s="6">
-        <v>46302.79193324078</v>
-      </c>
-      <c r="Q54" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17">
-      <c r="A55" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H55" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I55" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K55" s="6">
-        <v>2</v>
-      </c>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N55" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O55" s="6">
-        <v>46300.75887321083</v>
-      </c>
-      <c r="P55" s="6">
-        <v>46302.79193320179</v>
-      </c>
-      <c r="Q55" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q55"/>
+  <autoFilter ref="A1:Q50"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -3708,16 +3436,6 @@
     <hyperlink ref="N49" r:id="rId96"/>
     <hyperlink ref="M50" r:id="rId97"/>
     <hyperlink ref="N50" r:id="rId98"/>
-    <hyperlink ref="M51" r:id="rId99"/>
-    <hyperlink ref="N51" r:id="rId100"/>
-    <hyperlink ref="M52" r:id="rId101"/>
-    <hyperlink ref="N52" r:id="rId102"/>
-    <hyperlink ref="M53" r:id="rId103"/>
-    <hyperlink ref="N53" r:id="rId104"/>
-    <hyperlink ref="M54" r:id="rId105"/>
-    <hyperlink ref="N54" r:id="rId106"/>
-    <hyperlink ref="M55" r:id="rId107"/>
-    <hyperlink ref="N55" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3725,7 +3443,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3804,22 +3522,22 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
       </c>
       <c r="H2" s="3">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -3831,13 +3549,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75885647022</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P2" s="2">
-        <v>46302.79192099054</v>
+        <v>46303.38329440156</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -3848,10 +3566,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -3860,14 +3578,17 @@
         <v>46307</v>
       </c>
       <c r="I3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -3875,13 +3596,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P3" s="2">
-        <v>46302.79191032116</v>
+        <v>46303.38329436627</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -3892,29 +3613,26 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I4" s="2">
         <v>5</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -3922,13 +3640,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P4" s="2">
-        <v>46302.79191026733</v>
+        <v>46303.38328155963</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -3939,10 +3657,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -3951,10 +3669,10 @@
         <v>46308</v>
       </c>
       <c r="I5" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -3966,41 +3684,41 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884790152</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P5" s="2">
-        <v>46302.79189772235</v>
+        <v>46303.38328155097</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6">
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I6" s="2">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K6" s="2">
+        <v>46314</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
@@ -4009,14 +3727,14 @@
       <c r="N6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O6" s="2">
-        <v>46301.38232480602</v>
-      </c>
-      <c r="P6" s="2">
-        <v>46302.79189770951</v>
+      <c r="O6">
+        <v>46300.75884775587</v>
+      </c>
+      <c r="P6">
+        <v>46303.38328148136</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -4027,22 +3745,22 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I7">
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4054,13 +3772,13 @@
         <v>18</v>
       </c>
       <c r="O7">
-        <v>46300.75884775587</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P7">
-        <v>46302.79189760437</v>
+        <v>46303.38328145499</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4071,25 +3789,28 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I8">
         <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>112</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -4098,13 +3819,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46300.75884772457</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P8">
-        <v>46302.79189756404</v>
+        <v>46303.38328143695</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4115,28 +3836,25 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I9">
         <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="K9">
-        <v>3</v>
-      </c>
-      <c r="L9" t="s">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -4145,13 +3863,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46302.26841507768</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P9">
-        <v>46302.79189753801</v>
+        <v>46303.3832814277</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4162,99 +3880,102 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46317</v>
+        <v>46326</v>
       </c>
       <c r="I10">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P10">
+        <v>46303.38328140793</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
-        <v>46301.38232468421</v>
-      </c>
-      <c r="P10">
-        <v>46302.79189752453</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11">
+      <c r="B11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6">
         <v>0.2</v>
       </c>
-      <c r="H11" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I11">
-        <v>24</v>
-      </c>
-      <c r="J11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P11">
-        <v>46302.79189749651</v>
+      <c r="H11" s="6">
+        <v>46302</v>
+      </c>
+      <c r="I11" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" s="6">
+        <v>46300.75885647022</v>
+      </c>
+      <c r="P11" s="6">
+        <v>46303.38330298233</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6">
@@ -4264,10 +3985,10 @@
         <v>46299</v>
       </c>
       <c r="I12" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
@@ -4285,25 +4006,25 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P12" s="6">
-        <v>46302.79192109437</v>
+        <v>46303.38330305153</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
@@ -4313,7 +4034,7 @@
         <v>46298</v>
       </c>
       <c r="I13" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>138</v>
@@ -4332,25 +4053,25 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P13" s="6">
-        <v>46302.79192113371</v>
+        <v>46303.38330307746</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6">
@@ -4360,7 +4081,7 @@
         <v>46298</v>
       </c>
       <c r="I14" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>146</v>
@@ -4379,25 +4100,25 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P14" s="6">
-        <v>46302.79192121145</v>
+        <v>46303.38330312896</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6">
@@ -4407,7 +4128,7 @@
         <v>46296</v>
       </c>
       <c r="I15" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>153</v>
@@ -4428,25 +4149,25 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P15" s="6">
-        <v>46302.79193308652</v>
+        <v>46303.3833125137</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>155</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -4456,7 +4177,7 @@
         <v>46294</v>
       </c>
       <c r="I16" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>156</v>
@@ -4475,206 +4196,14 @@
         <v>46300.75887301003</v>
       </c>
       <c r="P16" s="6">
-        <v>46302.79193312495</v>
+        <v>46303.38331254272</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H17" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I17" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K17" s="6">
-        <v>1</v>
-      </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46300.75887314334</v>
-      </c>
-      <c r="P17" s="6">
-        <v>46302.7919332146</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H18" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I18" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K18" s="6">
-        <v>1</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" s="6">
-        <v>46300.75887317812</v>
-      </c>
-      <c r="P18" s="6">
-        <v>46302.79193325419</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I19" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K19" s="6">
-        <v>1</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="6">
-        <v>46300.75887319581</v>
-      </c>
-      <c r="P19" s="6">
-        <v>46302.79193324078</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="6">
-        <v>46292</v>
-      </c>
-      <c r="I20" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K20" s="6">
-        <v>2</v>
-      </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46300.75887321083</v>
-      </c>
-      <c r="P20" s="6">
-        <v>46302.79193320179</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q20"/>
+  <autoFilter ref="A1:Q16"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4706,14 +4235,6 @@
     <hyperlink ref="N15" r:id="rId28"/>
     <hyperlink ref="M16" r:id="rId29"/>
     <hyperlink ref="N16" r:id="rId30"/>
-    <hyperlink ref="M17" r:id="rId31"/>
-    <hyperlink ref="N17" r:id="rId32"/>
-    <hyperlink ref="M18" r:id="rId33"/>
-    <hyperlink ref="N18" r:id="rId34"/>
-    <hyperlink ref="M19" r:id="rId35"/>
-    <hyperlink ref="N19" r:id="rId36"/>
-    <hyperlink ref="M20" r:id="rId37"/>
-    <hyperlink ref="N20" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4721,7 +4242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4731,51 +4252,51 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B2">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D2">
         <v>191</v>
@@ -4787,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4804,13 +4325,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B3">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D3">
         <v>191</v>
@@ -4819,16 +4340,16 @@
         <v>3820</v>
       </c>
       <c r="F3">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H3">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -4839,48 +4360,48 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B4">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E4">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G4">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B5">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C5" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -4889,13 +4410,13 @@
         <v>160</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4904,18 +4425,18 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B6">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -4924,21 +4445,56 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H6">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B7">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>160</v>
+      </c>
+      <c r="F7">
+        <v>157</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>132</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="177">
   <si>
     <t>Priority</t>
   </si>
@@ -1070,7 +1070,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P2" s="2">
-        <v>46303.38329450462</v>
+        <v>46303.78903324551</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>24</v>
@@ -1114,7 +1114,7 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P3" s="2">
-        <v>46303.3832944789</v>
+        <v>46303.78903320204</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>24</v>
@@ -1161,7 +1161,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P4" s="2">
-        <v>46303.38329448765</v>
+        <v>46303.78903321669</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>24</v>
@@ -1208,7 +1208,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P5" s="2">
-        <v>46303.38329446202</v>
+        <v>46303.78903317315</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>24</v>
@@ -1255,7 +1255,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P6" s="2">
-        <v>46303.38329442757</v>
+        <v>46303.78903311479</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>24</v>
@@ -1305,7 +1305,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P7" s="2">
-        <v>46303.38329443617</v>
+        <v>46303.78903312911</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>24</v>
@@ -1355,7 +1355,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P8" s="2">
-        <v>46303.38329444442</v>
+        <v>46303.78903314354</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>24</v>
@@ -1402,7 +1402,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P9" s="2">
-        <v>46303.38329441878</v>
+        <v>46303.78903310001</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>24</v>
@@ -1452,7 +1452,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P10" s="2">
-        <v>46303.38329438417</v>
+        <v>46303.78903304238</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>24</v>
@@ -1496,7 +1496,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P11" s="2">
-        <v>46303.38329440156</v>
+        <v>46303.78903307128</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>60</v>
@@ -1543,7 +1543,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P12" s="2">
-        <v>46303.3832943571</v>
+        <v>46303.7890329982</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>24</v>
@@ -1590,7 +1590,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P13" s="2">
-        <v>46303.38329436627</v>
+        <v>46303.78903301315</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>60</v>
@@ -1634,7 +1634,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P14" s="2">
-        <v>46303.38329433652</v>
+        <v>46303.78903296705</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>24</v>
@@ -1681,7 +1681,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P15" s="2">
-        <v>46303.38329437528</v>
+        <v>46303.78903302801</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>24</v>
@@ -1731,7 +1731,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P16" s="2">
-        <v>46303.38328156831</v>
+        <v>46303.78902500809</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>24</v>
@@ -1775,7 +1775,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P17" s="2">
-        <v>46303.38328155963</v>
+        <v>46303.78902499317</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>60</v>
@@ -1819,7 +1819,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P18" s="2">
-        <v>46303.38328155097</v>
+        <v>46303.78902497852</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>60</v>
@@ -1866,7 +1866,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P19" s="2">
-        <v>46303.38328154255</v>
+        <v>46303.78902496338</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>24</v>
@@ -1913,7 +1913,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P20">
-        <v>46303.38328152523</v>
+        <v>46303.78902493456</v>
       </c>
       <c r="Q20" t="s">
         <v>24</v>
@@ -1957,7 +1957,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P21">
-        <v>46303.38328149894</v>
+        <v>46303.78902489004</v>
       </c>
       <c r="Q21" t="s">
         <v>24</v>
@@ -2004,7 +2004,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P22">
-        <v>46303.38328150799</v>
+        <v>46303.78902490489</v>
       </c>
       <c r="Q22" t="s">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P23">
-        <v>46303.38328151646</v>
+        <v>46303.78902491984</v>
       </c>
       <c r="Q23" t="s">
         <v>24</v>
@@ -2098,7 +2098,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P24">
-        <v>46303.38328149018</v>
+        <v>46303.78902487514</v>
       </c>
       <c r="Q24" t="s">
         <v>24</v>
@@ -2145,7 +2145,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P25">
-        <v>46303.38328147282</v>
+        <v>46303.78902484559</v>
       </c>
       <c r="Q25" t="s">
         <v>24</v>
@@ -2189,7 +2189,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P26">
-        <v>46303.38328148136</v>
+        <v>46303.7890248602</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>60</v>
@@ -2233,7 +2233,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P27">
-        <v>46303.38328146389</v>
+        <v>46303.78902483075</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -2277,7 +2277,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P28">
-        <v>46303.38328145499</v>
+        <v>46303.78902481608</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>60</v>
@@ -2324,7 +2324,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P29">
-        <v>46303.38328143695</v>
+        <v>46303.78902478614</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>60</v>
@@ -2368,7 +2368,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P30">
-        <v>46303.3832814277</v>
+        <v>46303.7890247705</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>60</v>
@@ -2415,7 +2415,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P31">
-        <v>46303.38328141814</v>
+        <v>46303.78902475473</v>
       </c>
       <c r="Q31" t="s">
         <v>24</v>
@@ -2459,7 +2459,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P32">
-        <v>46303.38328140793</v>
+        <v>46303.78902473875</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>60</v>
@@ -2508,7 +2508,7 @@
         <v>46300.7588564394</v>
       </c>
       <c r="P33" s="6">
-        <v>46303.38330297283</v>
+        <v>46303.78904116363</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>24</v>
@@ -2555,7 +2555,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P34" s="6">
-        <v>46303.38330298233</v>
+        <v>46303.78904117852</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>60</v>
@@ -2604,7 +2604,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P35" s="6">
-        <v>46303.38330300884</v>
+        <v>46303.78904122258</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>24</v>
@@ -2651,7 +2651,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P36" s="6">
-        <v>46303.38330304309</v>
+        <v>46303.7890412799</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>24</v>
@@ -2700,7 +2700,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P37" s="6">
-        <v>46303.3833030263</v>
+        <v>46303.78904125095</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>24</v>
@@ -2749,7 +2749,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P38" s="6">
-        <v>46303.38330305153</v>
+        <v>46303.78904129434</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>60</v>
@@ -2798,7 +2798,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P39" s="6">
-        <v>46303.38330306018</v>
+        <v>46303.78904130949</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>24</v>
@@ -2845,7 +2845,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P40" s="6">
-        <v>46303.38330307746</v>
+        <v>46303.7890413381</v>
       </c>
       <c r="Q40" s="5" t="s">
         <v>60</v>
@@ -2894,7 +2894,7 @@
         <v>46300.75886472998</v>
       </c>
       <c r="P41" s="6">
-        <v>46303.38331249326</v>
+        <v>46303.78904942831</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>24</v>
@@ -2943,7 +2943,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P42" s="6">
-        <v>46303.38330308611</v>
+        <v>46303.78904135231</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>24</v>
@@ -2990,7 +2990,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P43" s="6">
-        <v>46303.38330312896</v>
+        <v>46303.78904142418</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>60</v>
@@ -3041,7 +3041,7 @@
         <v>46300.75886484625</v>
       </c>
       <c r="P44" s="6">
-        <v>46303.38330310328</v>
+        <v>46303.78904138121</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>24</v>
@@ -3090,7 +3090,7 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P45" s="6">
-        <v>46303.38331250347</v>
+        <v>46303.78904944336</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>24</v>
@@ -3139,7 +3139,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P46" s="6">
-        <v>46303.3833125137</v>
+        <v>46303.78904946196</v>
       </c>
       <c r="Q46" s="5" t="s">
         <v>60</v>
@@ -3186,7 +3186,7 @@
         <v>46300.75887301003</v>
       </c>
       <c r="P47" s="6">
-        <v>46303.38331254272</v>
+        <v>46303.78904952588</v>
       </c>
       <c r="Q47" s="5" t="s">
         <v>60</v>
@@ -3233,7 +3233,7 @@
         <v>46300.75887304553</v>
       </c>
       <c r="P48" s="6">
-        <v>46303.38331255232</v>
+        <v>46303.78904954536</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>24</v>
@@ -3280,7 +3280,7 @@
         <v>46300.75887306096</v>
       </c>
       <c r="P49" s="6">
-        <v>46303.38331256139</v>
+        <v>46303.7890495669</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>24</v>
@@ -3329,7 +3329,7 @@
         <v>46300.75887309557</v>
       </c>
       <c r="P50" s="6">
-        <v>46303.38331258995</v>
+        <v>46303.78904962536</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>24</v>
@@ -3552,7 +3552,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P2" s="2">
-        <v>46303.38329440156</v>
+        <v>46303.78903307128</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>60</v>
@@ -3599,7 +3599,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P3" s="2">
-        <v>46303.38329436627</v>
+        <v>46303.78903301315</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>60</v>
@@ -3643,7 +3643,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P4" s="2">
-        <v>46303.38328155963</v>
+        <v>46303.78902499317</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>60</v>
@@ -3687,7 +3687,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P5" s="2">
-        <v>46303.38328155097</v>
+        <v>46303.78902497852</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>60</v>
@@ -3731,7 +3731,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P6">
-        <v>46303.38328148136</v>
+        <v>46303.7890248602</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>60</v>
@@ -3775,7 +3775,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P7">
-        <v>46303.38328145499</v>
+        <v>46303.78902481608</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>60</v>
@@ -3822,7 +3822,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P8">
-        <v>46303.38328143695</v>
+        <v>46303.78902478614</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>60</v>
@@ -3866,7 +3866,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P9">
-        <v>46303.3832814277</v>
+        <v>46303.7890247705</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>60</v>
@@ -3910,7 +3910,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P10">
-        <v>46303.38328140793</v>
+        <v>46303.78902473875</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>60</v>
@@ -3957,7 +3957,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P11" s="6">
-        <v>46303.38330298233</v>
+        <v>46303.78904117852</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>60</v>
@@ -4006,7 +4006,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P12" s="6">
-        <v>46303.38330305153</v>
+        <v>46303.78904129434</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>60</v>
@@ -4053,7 +4053,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P13" s="6">
-        <v>46303.38330307746</v>
+        <v>46303.7890413381</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>60</v>
@@ -4100,7 +4100,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P14" s="6">
-        <v>46303.38330312896</v>
+        <v>46303.78904142418</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>60</v>
@@ -4149,7 +4149,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P15" s="6">
-        <v>46303.3833125137</v>
+        <v>46303.78904946196</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>60</v>
@@ -4196,7 +4196,7 @@
         <v>46300.75887301003</v>
       </c>
       <c r="P16" s="6">
-        <v>46303.38331254272</v>
+        <v>46303.78904952588</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>60</v>
@@ -4242,7 +4242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B2">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C2" t="s">
         <v>176</v>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B3">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B4">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C4" t="s">
         <v>176</v>
@@ -4375,16 +4375,16 @@
         <v>3820</v>
       </c>
       <c r="F4">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H4">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4395,45 +4395,45 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B5">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C5" t="s">
         <v>176</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E5">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G5">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B6">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C6" t="s">
         <v>176</v>
@@ -4445,13 +4445,13 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4460,15 +4460,15 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B7">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C7" t="s">
         <v>176</v>
@@ -4480,21 +4480,56 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H7">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B8">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>160</v>
+      </c>
+      <c r="F8">
+        <v>157</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>132</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -13,14 +13,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="180">
   <si>
     <t>Priority</t>
   </si>
@@ -79,12 +79,348 @@
     <t>Open</t>
   </si>
   <si>
+    <t>INFO-DRIVE SOFTWARE LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>Sumeet Surendra Chimbalkar</t>
+  </si>
+  <si>
+    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
+  </si>
+  <si>
+    <t>Not in latest IBBI listing - verify with RP</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>A.P.J. LABORATORIES LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>pooja damir miglani</t>
+  </si>
+  <si>
+    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
+  </si>
+  <si>
+    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>Mrs. Neeraja Kartik</t>
+  </si>
+  <si>
+    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
+  </si>
+  <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>Shree Shiddhanath Cotex Private Limited</t>
+  </si>
+  <si>
+    <t>Textiles</t>
+  </si>
+  <si>
+    <t>Akhil Ahuja</t>
+  </si>
+  <si>
+    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
+  </si>
+  <si>
     <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
     <t>Healthcare</t>
   </si>
   <si>
@@ -94,297 +430,6 @@
     <t>_</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>Shree Shiddhanath Cotex Private Limited</t>
-  </si>
-  <si>
-    <t>Textiles</t>
-  </si>
-  <si>
-    <t>Akhil Ahuja</t>
-  </si>
-  <si>
-    <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
-  </si>
-  <si>
-    <t>INFO-DRIVE SOFTWARE LIMITED</t>
-  </si>
-  <si>
-    <t>Sumeet Surendra Chimbalkar</t>
-  </si>
-  <si>
-    <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>A.P.J. LABORATORIES LIMITED</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>pooja damir miglani</t>
-  </si>
-  <si>
-    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
-  </si>
-  <si>
-    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>Mrs. Neeraja Kartik</t>
-  </si>
-  <si>
-    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
-  </si>
-  <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
   </si>
   <si>
@@ -463,12 +508,6 @@
     <t>Mr. Bhoopesh Gupta</t>
   </si>
   <si>
-    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Company has two operational grocery marts in the name of Poonam Bazaar units in Nagpur. The grocery marts are in operational status, however the financials and custody of the assets of CD are yet to be handed over to the RP.</t>
-  </si>
-  <si>
     <t>VELEX LOGISTICS PRIVATE LIMITED</t>
   </si>
   <si>
@@ -485,36 +524,6 @@
   </si>
   <si>
     <t>The Resolution Professional has issued an invitation for expression of interest on 01 September 2026.</t>
-  </si>
-  <si>
-    <t>SHAH LAXMICHAND VERSHI MASALAWALA LLP</t>
-  </si>
-  <si>
-    <t>Mr. Dakshesh Pravinchandra Choksi</t>
-  </si>
-  <si>
-    <t>AMISHI CONSUMER TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Amit Talwar</t>
-  </si>
-  <si>
-    <t>ISHAPE APPLIANCES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Retail / Consumer</t>
-  </si>
-  <si>
-    <t>PRABHAT JAIN</t>
-  </si>
-  <si>
-    <t>JAISUBA AGRO PRODUCTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Rajendran Shanmugam</t>
-  </si>
-  <si>
-    <t>Assets of the Corporate Debtor and the Personal Guarantors are proposed to be clubbed under Sec.28A of IBC for the purpose of inviting resolution plans.</t>
   </si>
   <si>
     <t>Started</t>
@@ -970,7 +979,7 @@
     <col min="12" max="12" width="48.7109375" customWidth="1"/>
     <col min="13" max="14" width="12.7109375" customWidth="1"/>
     <col min="15" max="16" width="20.7109375" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="17" max="17" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1039,41 +1048,38 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="G2" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H2" s="3">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="2">
-        <v>2</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="2">
+        <v>46300.75885633306</v>
+      </c>
+      <c r="P2" s="2">
+        <v>46303.78903317315</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="2">
-        <v>46300.7588564207</v>
-      </c>
-      <c r="P2" s="2">
-        <v>46303.78903324551</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -1084,16 +1090,19 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="2">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H3" s="3">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
@@ -1111,13 +1120,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75885634872</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P3" s="2">
-        <v>46303.78903320204</v>
+        <v>46305.20576110142</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1128,28 +1137,31 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="G4" s="2">
         <v>0.9399999999999999</v>
       </c>
       <c r="H4" s="3">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -1158,13 +1170,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.7588563655</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P4" s="2">
-        <v>46303.78903321669</v>
+        <v>46305.20576108179</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1175,28 +1187,31 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="G5" s="2">
         <v>0.91</v>
       </c>
       <c r="H5" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
@@ -1205,13 +1220,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75885633306</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P5" s="2">
-        <v>46303.78903317315</v>
+        <v>46305.20576109179</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1222,29 +1237,29 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" s="3">
         <v>46306</v>
       </c>
       <c r="I6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
+      <c r="L6" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1252,13 +1267,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75885622757</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P6" s="2">
-        <v>46303.78903311479</v>
+        <v>46305.20576111179</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1269,31 +1284,31 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H7" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -1302,13 +1317,13 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75885624527</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P7" s="2">
-        <v>46303.78903312911</v>
+        <v>46305.20576101432</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1319,32 +1334,26 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1352,13 +1361,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.7588562628</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P8" s="2">
-        <v>46303.78903314354</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>24</v>
+        <v>46305.20576103318</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1369,29 +1378,29 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>25</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G9" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H9" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1399,13 +1408,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75885627908</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P9" s="2">
-        <v>46303.78903310001</v>
+        <v>46305.20576097554</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1416,31 +1425,28 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="3">
         <v>46307</v>
       </c>
       <c r="I10" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
@@ -1449,13 +1455,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75884793277</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P10" s="2">
-        <v>46303.78903304238</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>24</v>
+        <v>46305.20576098546</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1466,22 +1472,22 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H11" s="3">
         <v>46307</v>
       </c>
       <c r="I11" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -1493,13 +1499,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P11" s="2">
-        <v>46303.78903307128</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>60</v>
+        <v>46305.205761005</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1513,26 +1519,26 @@
         <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H12" s="3">
         <v>46307</v>
       </c>
       <c r="I12" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
+      <c r="L12" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
       </c>
@@ -1540,13 +1546,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75884796329</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P12" s="2">
-        <v>46303.7890329982</v>
+        <v>46305.20576099515</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1557,29 +1563,32 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="G13" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H13" s="3">
         <v>46307</v>
       </c>
       <c r="I13" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1587,13 +1596,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.75884799581</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P13" s="2">
-        <v>46303.78903301315</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>60</v>
+        <v>46305.20576106139</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1604,19 +1613,22 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H14" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>69</v>
@@ -1624,6 +1636,9 @@
       <c r="K14" s="2">
         <v>1</v>
       </c>
+      <c r="L14" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -1631,13 +1646,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75885617639</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P14" s="2">
-        <v>46303.78903296705</v>
+        <v>46305.20576095542</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1648,29 +1663,26 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G15" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1678,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.75885619673</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P15" s="2">
-        <v>46303.78903302801</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>24</v>
+        <v>46305.20576094543</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1695,32 +1707,26 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G16" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="3">
         <v>46308</v>
       </c>
       <c r="I16" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1728,13 +1734,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46300.75884788632</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P16" s="2">
-        <v>46303.78902500809</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>24</v>
+        <v>46305.20576093486</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1745,26 +1751,29 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="G17" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H17" s="3">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="I17" s="2">
         <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
       </c>
+      <c r="L17" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
       </c>
@@ -1772,13 +1781,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P17" s="2">
-        <v>46303.78902499317</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>60</v>
+        <v>46305.20576092294</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1789,26 +1798,29 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I18" s="2">
-        <v>5</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1816,13 +1828,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46301.38232480602</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P18" s="2">
-        <v>46303.78902497852</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>60</v>
+        <v>46305.20575279809</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1839,10 +1851,10 @@
         <v>82</v>
       </c>
       <c r="G19" s="2">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H19" s="3">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I19" s="2">
         <v>7</v>
@@ -1853,114 +1865,114 @@
       <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="2">
+        <v>46300.75884780569</v>
+      </c>
+      <c r="P19" s="2">
+        <v>46305.20575282763</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="2" customFormat="1">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="2">
-        <v>46300.75884787029</v>
-      </c>
-      <c r="P19" s="2">
-        <v>46303.78902496338</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20">
-        <v>0.95</v>
+      <c r="E20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.93</v>
       </c>
       <c r="H20" s="3">
         <v>46312</v>
       </c>
-      <c r="I20">
-        <v>9</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="I20" s="2">
+        <v>7</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="2">
+        <v>46300.75884782107</v>
+      </c>
+      <c r="P20" s="2">
+        <v>46305.20575281785</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="2" customFormat="1">
+      <c r="A21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20">
-        <v>46300.75884779022</v>
-      </c>
-      <c r="P20">
-        <v>46303.78902493456</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E21" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E21" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21">
-        <v>0.93</v>
+      <c r="G21" s="2">
+        <v>0.91</v>
       </c>
       <c r="H21" s="3">
         <v>46312</v>
       </c>
-      <c r="I21">
-        <v>9</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="I21" s="2">
+        <v>7</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="N21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O21">
-        <v>46300.75884780569</v>
-      </c>
-      <c r="P21">
-        <v>46303.78902489004</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>24</v>
+      <c r="O21" s="2">
+        <v>46300.75884783743</v>
+      </c>
+      <c r="P21" s="2">
+        <v>46305.20575280781</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1974,22 +1986,22 @@
         <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H22" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J22" t="s">
         <v>92</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" t="s">
         <v>93</v>
@@ -2001,13 +2013,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46300.75884782107</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P22">
-        <v>46303.78902490489</v>
+        <v>46305.20575278824</v>
       </c>
       <c r="Q22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2023,24 +2035,24 @@
       <c r="E23" t="s">
         <v>95</v>
       </c>
+      <c r="F23" t="s">
+        <v>96</v>
+      </c>
       <c r="G23">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H23" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I23">
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="L23" t="s">
-        <v>97</v>
-      </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
       </c>
@@ -2048,13 +2060,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46300.75884783743</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P23">
-        <v>46303.78902491984</v>
+        <v>46305.20575275837</v>
       </c>
       <c r="Q23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2068,25 +2080,22 @@
         <v>98</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G24">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H24" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24" t="s">
         <v>99</v>
       </c>
       <c r="K24">
-        <v>3</v>
-      </c>
-      <c r="L24" t="s">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2095,13 +2104,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46302.26841519317</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P24">
-        <v>46303.78902487514</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>24</v>
+        <v>46305.20575276836</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2112,25 +2121,22 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="G25">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H25" s="3">
         <v>46314</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2142,13 +2148,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46300.75884774033</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P25">
-        <v>46303.78902484559</v>
+        <v>46305.20575277831</v>
       </c>
       <c r="Q25" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2159,22 +2165,22 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G26">
         <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2186,13 +2192,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46300.75884775587</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P26">
-        <v>46303.7890248602</v>
+        <v>46305.20575274854</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2203,25 +2209,28 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="G27">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H27" s="3">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="I27">
         <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L27" t="s">
+        <v>106</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2230,13 +2239,13 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46300.7588477715</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P27">
-        <v>46303.78902483075</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>24</v>
+        <v>46305.20575272872</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2247,22 +2256,22 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G28">
         <v>0.2</v>
       </c>
       <c r="H28" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I28">
         <v>12</v>
       </c>
       <c r="J28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2274,13 +2283,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46300.75884772457</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P28">
-        <v>46303.78902481608</v>
+        <v>46305.20575271807</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2291,28 +2300,28 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
       </c>
       <c r="G29">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H29" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="K29">
-        <v>3</v>
-      </c>
-      <c r="L29" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
@@ -2321,13 +2330,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46302.26841507768</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P29">
-        <v>46303.78902478614</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>60</v>
+        <v>46305.20575270729</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2338,26 +2347,32 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30">
+        <v>0.96</v>
+      </c>
+      <c r="H30" s="3">
+        <v>46318</v>
+      </c>
+      <c r="I30">
+        <v>13</v>
+      </c>
+      <c r="J30" t="s">
+        <v>112</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
         <v>113</v>
       </c>
-      <c r="E30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30">
-        <v>0.2</v>
-      </c>
-      <c r="H30" s="3">
-        <v>46317</v>
-      </c>
-      <c r="I30">
-        <v>14</v>
-      </c>
-      <c r="J30" t="s">
-        <v>114</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
       <c r="M30" s="4" t="s">
         <v>18</v>
       </c>
@@ -2365,13 +2380,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46301.38232468421</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P30">
-        <v>46303.7890247705</v>
-      </c>
-      <c r="Q30" s="5" t="s">
-        <v>60</v>
+        <v>46305.20575267455</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2382,22 +2397,19 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" t="s">
         <v>115</v>
-      </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" t="s">
-        <v>40</v>
       </c>
       <c r="G31">
         <v>0.9399999999999999</v>
       </c>
       <c r="H31" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J31" t="s">
         <v>116</v>
@@ -2405,6 +2417,9 @@
       <c r="K31">
         <v>1</v>
       </c>
+      <c r="L31" t="s">
+        <v>117</v>
+      </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
       </c>
@@ -2412,13 +2427,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46302.26841501552</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P31">
-        <v>46303.78902475473</v>
+        <v>46305.20575269724</v>
       </c>
       <c r="Q31" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2429,169 +2444,165 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
       </c>
       <c r="G32">
+        <v>0.93</v>
+      </c>
+      <c r="H32" s="3">
+        <v>46319</v>
+      </c>
+      <c r="I32">
+        <v>14</v>
+      </c>
+      <c r="J32" t="s">
+        <v>119</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32" t="s">
+        <v>120</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32">
+        <v>46305.20575263901</v>
+      </c>
+      <c r="P32">
+        <v>46305.20575263904</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33">
         <v>0.2</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H33" s="3">
         <v>46326</v>
       </c>
-      <c r="I32">
-        <v>23</v>
-      </c>
-      <c r="J32" t="s">
-        <v>118</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O32">
+      <c r="I33">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>122</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33">
         <v>46300.75884768533</v>
       </c>
-      <c r="P32">
-        <v>46303.78902473875</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6">
+      <c r="P33">
+        <v>46305.20575261097</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34">
         <v>0.92</v>
       </c>
-      <c r="H33" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I33" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="6">
-        <v>1</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33" s="6">
-        <v>46300.7588564394</v>
-      </c>
-      <c r="P33" s="6">
-        <v>46303.78904116363</v>
-      </c>
-      <c r="Q33" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="H34" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I34">
+        <v>27</v>
+      </c>
+      <c r="J34" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H34" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I34" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K34" s="6">
-        <v>1</v>
-      </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P34" s="6">
-        <v>46303.78904117852</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>60</v>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34">
+        <v>46305.20575257758</v>
+      </c>
+      <c r="P34">
+        <v>46305.2057525776</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>40</v>
-      </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H35" s="6">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="I35" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="K35" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="6" t="s">
@@ -2601,21 +2612,21 @@
         <v>18</v>
       </c>
       <c r="O35" s="6">
-        <v>46300.75885649968</v>
+        <v>46300.75885634872</v>
       </c>
       <c r="P35" s="6">
-        <v>46303.78904122258</v>
+        <v>46305.20576919735</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>128</v>
@@ -2626,13 +2637,13 @@
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H36" s="6">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="I36" s="6">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>130</v>
@@ -2640,7 +2651,9 @@
       <c r="K36" s="6">
         <v>1</v>
       </c>
-      <c r="L36" s="6"/>
+      <c r="L36" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="M36" s="6" t="s">
         <v>18</v>
       </c>
@@ -2648,48 +2661,50 @@
         <v>18</v>
       </c>
       <c r="O36" s="6">
-        <v>46300.75886463693</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P36" s="6">
-        <v>46303.7890412799</v>
+        <v>46305.2057692078</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="G37" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H37" s="6">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="I37" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K37" s="6">
-        <v>1</v>
-      </c>
-      <c r="L37" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="M37" s="6" t="s">
         <v>18</v>
       </c>
@@ -2697,47 +2712,47 @@
         <v>18</v>
       </c>
       <c r="O37" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P37" s="6">
-        <v>46303.78904125095</v>
+        <v>46305.2057692176</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H38" s="6">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="I38" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="K38" s="6">
         <v>1</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>18</v>
@@ -2746,43 +2761,41 @@
         <v>18</v>
       </c>
       <c r="O38" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.7588564394</v>
       </c>
       <c r="P38" s="6">
-        <v>46303.78904129434</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>60</v>
+        <v>46305.20576924799</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>62</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H39" s="6">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="I39" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K39" s="6">
         <v>1</v>
@@ -2795,44 +2808,46 @@
         <v>18</v>
       </c>
       <c r="O39" s="6">
-        <v>46300.75886468366</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P39" s="6">
-        <v>46303.78904130949</v>
-      </c>
-      <c r="Q39" s="6" t="s">
-        <v>24</v>
+        <v>46305.20576926682</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F40" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="G40" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H40" s="6">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="I40" s="6">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K40" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6" t="s">
@@ -2842,43 +2857,41 @@
         <v>18</v>
       </c>
       <c r="O40" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75885649968</v>
       </c>
       <c r="P40" s="6">
-        <v>46303.7890413381</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>60</v>
+        <v>46305.20576929489</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="H41" s="6">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="I41" s="6">
         <v>-5</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K41" s="6">
         <v>1</v>
@@ -2891,48 +2904,48 @@
         <v>18</v>
       </c>
       <c r="O41" s="6">
-        <v>46300.75886472998</v>
+        <v>46300.75886463693</v>
       </c>
       <c r="P41" s="6">
-        <v>46303.78904942831</v>
+        <v>46305.20576932246</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="F42" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="G42" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H42" s="6">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="I42" s="6">
         <v>-5</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K42" s="6">
         <v>1</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>144</v>
-      </c>
+      <c r="L42" s="6"/>
       <c r="M42" s="6" t="s">
         <v>18</v>
       </c>
@@ -2940,46 +2953,48 @@
         <v>18</v>
       </c>
       <c r="O42" s="6">
-        <v>46300.75886474836</v>
+        <v>46300.75886465221</v>
       </c>
       <c r="P42" s="6">
-        <v>46303.78904135231</v>
+        <v>46305.20576930419</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6">
         <v>0.2</v>
       </c>
       <c r="H43" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I43" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="K43" s="6">
         <v>1</v>
       </c>
-      <c r="L43" s="6"/>
+      <c r="L43" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="M43" s="6" t="s">
         <v>18</v>
       </c>
@@ -2987,50 +3002,48 @@
         <v>18</v>
       </c>
       <c r="O43" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P43" s="6">
-        <v>46303.78904142418</v>
+        <v>46305.20576934127</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G44" s="6">
         <v>0.93</v>
       </c>
       <c r="H44" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I44" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="K44" s="6">
         <v>1</v>
       </c>
-      <c r="L44" s="6" t="s">
-        <v>148</v>
-      </c>
+      <c r="L44" s="6"/>
       <c r="M44" s="6" t="s">
         <v>18</v>
       </c>
@@ -3038,48 +3051,46 @@
         <v>18</v>
       </c>
       <c r="O44" s="6">
-        <v>46300.75886484625</v>
+        <v>46300.75886468366</v>
       </c>
       <c r="P44" s="6">
-        <v>46303.78904138121</v>
+        <v>46305.20576933161</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H45" s="6">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="I45" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K45" s="6">
         <v>1</v>
       </c>
-      <c r="L45" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="L45" s="6"/>
       <c r="M45" s="6" t="s">
         <v>18</v>
       </c>
@@ -3087,48 +3098,48 @@
         <v>18</v>
       </c>
       <c r="O45" s="6">
-        <v>46300.75886486177</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P45" s="6">
-        <v>46303.78904944336</v>
-      </c>
-      <c r="Q45" s="6" t="s">
-        <v>24</v>
+        <v>46305.20577780272</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="G46" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H46" s="6">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="I46" s="6">
         <v>-7</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K46" s="6">
         <v>1</v>
       </c>
-      <c r="L46" s="6" t="s">
-        <v>154</v>
-      </c>
+      <c r="L46" s="6"/>
       <c r="M46" s="6" t="s">
         <v>18</v>
       </c>
@@ -3136,46 +3147,48 @@
         <v>18</v>
       </c>
       <c r="O46" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75886472998</v>
       </c>
       <c r="P46" s="6">
-        <v>46303.78904946196</v>
+        <v>46303.78904942831</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H47" s="6">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="I47" s="6">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
       </c>
-      <c r="L47" s="6"/>
+      <c r="L47" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="M47" s="6" t="s">
         <v>18</v>
       </c>
@@ -3183,41 +3196,41 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46300.75887301003</v>
+        <v>46300.75886474836</v>
       </c>
       <c r="P47" s="6">
-        <v>46303.78904952588</v>
-      </c>
-      <c r="Q47" s="5" t="s">
-        <v>60</v>
+        <v>46305.20577781487</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H48" s="6">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="I48" s="6">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K48" s="6">
         <v>1</v>
@@ -3230,46 +3243,48 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75887304553</v>
+        <v>46300.75886479358</v>
       </c>
       <c r="P48" s="6">
-        <v>46303.78904954536</v>
-      </c>
-      <c r="Q48" s="6" t="s">
-        <v>24</v>
+        <v>46305.20576936999</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="H49" s="6">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="I49" s="6">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K49" s="6">
-        <v>2</v>
-      </c>
-      <c r="L49" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>164</v>
+      </c>
       <c r="M49" s="6" t="s">
         <v>18</v>
       </c>
@@ -3277,47 +3292,47 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.75887306096</v>
+        <v>46300.75886486177</v>
       </c>
       <c r="P49" s="6">
-        <v>46303.7890495669</v>
+        <v>46305.20577787467</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="6">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="I50" s="6">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K50" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
@@ -3326,13 +3341,13 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75887309557</v>
+        <v>46300.75886487812</v>
       </c>
       <c r="P50" s="6">
-        <v>46303.78904962536</v>
-      </c>
-      <c r="Q50" s="6" t="s">
-        <v>24</v>
+        <v>46305.20577788425</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3443,7 +3458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3458,7 +3473,7 @@
     <col min="12" max="12" width="48.7109375" customWidth="1"/>
     <col min="13" max="14" width="12.7109375" customWidth="1"/>
     <col min="15" max="16" width="20.7109375" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="17" max="17" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -3522,26 +3537,29 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H2" s="3">
-        <v>46307</v>
+        <v>46305</v>
       </c>
       <c r="I2" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
       </c>
@@ -3549,13 +3567,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P2" s="2">
-        <v>46303.78903307128</v>
+        <v>46303.78903317315</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -3566,10 +3584,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -3578,17 +3596,14 @@
         <v>46307</v>
       </c>
       <c r="I3" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -3596,13 +3611,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46303.78903301315</v>
+        <v>46305.20576103318</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -3613,26 +3628,29 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I4" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
+      <c r="L4" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -3640,13 +3658,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P4" s="2">
-        <v>46303.78902499317</v>
+        <v>46305.20576098546</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -3657,10 +3675,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -3669,10 +3687,10 @@
         <v>46308</v>
       </c>
       <c r="I5" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -3684,57 +3702,57 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
+        <v>46300.75884790152</v>
+      </c>
+      <c r="P5" s="2">
+        <v>46305.20576094543</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="2" customFormat="1">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46308</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="2">
         <v>46301.38232480602</v>
       </c>
-      <c r="P5" s="2">
-        <v>46303.78902497852</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>0.2</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6">
-        <v>46300.75884775587</v>
-      </c>
-      <c r="P6">
-        <v>46303.7890248602</v>
+      <c r="P6" s="2">
+        <v>46305.20576093486</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -3745,22 +3763,22 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J7" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -3772,13 +3790,13 @@
         <v>18</v>
       </c>
       <c r="O7">
-        <v>46300.75884772457</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P7">
-        <v>46303.78902481608</v>
+        <v>46305.20575276836</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3789,28 +3807,25 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -3819,13 +3834,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46302.26841507768</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46303.78902478614</v>
+        <v>46305.20575274854</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3836,25 +3851,28 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>106</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -3863,13 +3881,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46301.38232468421</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46303.7890247705</v>
+        <v>46305.20575272872</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -3880,122 +3898,117 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
+        <v>46317</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P10">
+        <v>46305.20575271807</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="3">
         <v>46326</v>
       </c>
-      <c r="I10">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
-        <v>118</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
+      <c r="I11">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>122</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11">
         <v>46300.75884768533</v>
       </c>
-      <c r="P10">
-        <v>46303.78902473875</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H11" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I11" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K11" s="6">
-        <v>1</v>
-      </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P11" s="6">
-        <v>46303.78904117852</v>
+      <c r="P11">
+        <v>46305.20575261097</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6">
         <v>0.2</v>
       </c>
       <c r="H12" s="6">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="I12" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="K12" s="6">
         <v>1</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>134</v>
-      </c>
+      <c r="L12" s="6"/>
       <c r="M12" s="6" t="s">
         <v>18</v>
       </c>
@@ -4003,46 +4016,48 @@
         <v>18</v>
       </c>
       <c r="O12" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P12" s="6">
-        <v>46303.78904129434</v>
+        <v>46305.20576926682</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
         <v>0.2</v>
       </c>
       <c r="H13" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I13" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="K13" s="6">
         <v>1</v>
       </c>
-      <c r="L13" s="6"/>
+      <c r="L13" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="M13" s="6" t="s">
         <v>18</v>
       </c>
@@ -4050,28 +4065,28 @@
         <v>18</v>
       </c>
       <c r="O13" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P13" s="6">
-        <v>46303.7890413381</v>
+        <v>46305.20576934127</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6">
@@ -4081,10 +4096,10 @@
         <v>46298</v>
       </c>
       <c r="I14" s="6">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K14" s="6">
         <v>1</v>
@@ -4097,48 +4112,48 @@
         <v>18</v>
       </c>
       <c r="O14" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P14" s="6">
-        <v>46303.78904142418</v>
+        <v>46305.20577780272</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="G15" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H15" s="6">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="I15" s="6">
         <v>-7</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>154</v>
-      </c>
+      <c r="L15" s="6"/>
       <c r="M15" s="6" t="s">
         <v>18</v>
       </c>
@@ -4146,41 +4161,41 @@
         <v>18</v>
       </c>
       <c r="O15" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75886472998</v>
       </c>
       <c r="P15" s="6">
-        <v>46303.78904946196</v>
+        <v>46303.78904942831</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
         <v>0.2</v>
       </c>
       <c r="H16" s="6">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="I16" s="6">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K16" s="6">
         <v>1</v>
@@ -4193,17 +4208,66 @@
         <v>18</v>
       </c>
       <c r="O16" s="6">
-        <v>46300.75887301003</v>
+        <v>46300.75886479358</v>
       </c>
       <c r="P16" s="6">
-        <v>46303.78904952588</v>
+        <v>46305.20576936999</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="6">
+        <v>46296</v>
+      </c>
+      <c r="I17" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" s="6">
+        <v>46300.75886487812</v>
+      </c>
+      <c r="P17" s="6">
+        <v>46305.20577788425</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q16"/>
+  <autoFilter ref="A1:Q17"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4235,6 +4299,8 @@
     <hyperlink ref="N15" r:id="rId28"/>
     <hyperlink ref="M16" r:id="rId29"/>
     <hyperlink ref="N16" r:id="rId30"/>
+    <hyperlink ref="M17" r:id="rId31"/>
+    <hyperlink ref="N17" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4242,7 +4308,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4252,86 +4318,86 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B2">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E2">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B3">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D3">
         <v>191</v>
@@ -4360,13 +4426,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B4">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D4">
         <v>191</v>
@@ -4378,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4395,13 +4461,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B5">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D5">
         <v>191</v>
@@ -4410,16 +4476,16 @@
         <v>3820</v>
       </c>
       <c r="F5">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H5">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4430,48 +4496,48 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B6">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E6">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G6">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B7">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -4480,13 +4546,13 @@
         <v>160</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4495,18 +4561,18 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B8">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -4515,21 +4581,56 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H8">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B9">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>160</v>
+      </c>
+      <c r="F9">
+        <v>157</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>132</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="180">
   <si>
     <t>Priority</t>
   </si>
@@ -1123,7 +1123,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P3" s="2">
-        <v>46305.20576110142</v>
+        <v>46305.36274242896</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>28</v>
@@ -1173,7 +1173,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P4" s="2">
-        <v>46305.20576108179</v>
+        <v>46305.36274241605</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>28</v>
@@ -1223,7 +1223,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P5" s="2">
-        <v>46305.20576109179</v>
+        <v>46305.36274242261</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>28</v>
@@ -1270,7 +1270,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P6" s="2">
-        <v>46305.20576111179</v>
+        <v>46305.36274243537</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>28</v>
@@ -1320,7 +1320,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P7" s="2">
-        <v>46305.20576101432</v>
+        <v>46305.36274238358</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>28</v>
@@ -1364,7 +1364,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P8" s="2">
-        <v>46305.20576103318</v>
+        <v>46305.36274239628</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>51</v>
@@ -1411,7 +1411,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P9" s="2">
-        <v>46305.20576097554</v>
+        <v>46305.36274235664</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>28</v>
@@ -1458,7 +1458,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P10" s="2">
-        <v>46305.20576098546</v>
+        <v>46305.36274236323</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>51</v>
@@ -1502,7 +1502,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P11" s="2">
-        <v>46305.205761005</v>
+        <v>46305.36274237684</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>28</v>
@@ -1549,7 +1549,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P12" s="2">
-        <v>46305.20576099515</v>
+        <v>46305.36274237</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>28</v>
@@ -1599,7 +1599,7 @@
         <v>46305.20576106136</v>
       </c>
       <c r="P13" s="2">
-        <v>46305.20576106139</v>
+        <v>46305.36274240285</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>28</v>
@@ -1649,7 +1649,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P14" s="2">
-        <v>46305.20576095542</v>
+        <v>46305.36274234272</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>28</v>
@@ -1693,7 +1693,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P15" s="2">
-        <v>46305.20576094543</v>
+        <v>46305.36274233532</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>51</v>
@@ -1737,7 +1737,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P16" s="2">
-        <v>46305.20576093486</v>
+        <v>46305.36274232762</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>51</v>
@@ -1784,7 +1784,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P17" s="2">
-        <v>46305.20576092294</v>
+        <v>46305.36274231809</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>28</v>
@@ -1831,7 +1831,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P18" s="2">
-        <v>46305.20575279809</v>
+        <v>46305.36273430099</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>28</v>
@@ -1875,7 +1875,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P19" s="2">
-        <v>46305.20575282763</v>
+        <v>46305.36273432023</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>28</v>
@@ -1922,7 +1922,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P20" s="2">
-        <v>46305.20575281785</v>
+        <v>46305.36273431396</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>28</v>
@@ -1969,7 +1969,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P21" s="2">
-        <v>46305.20575280781</v>
+        <v>46305.36273430726</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>28</v>
@@ -2016,7 +2016,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P22">
-        <v>46305.20575278824</v>
+        <v>46305.36273429449</v>
       </c>
       <c r="Q22" t="s">
         <v>28</v>
@@ -2063,7 +2063,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P23">
-        <v>46305.20575275837</v>
+        <v>46305.36273427486</v>
       </c>
       <c r="Q23" t="s">
         <v>28</v>
@@ -2107,7 +2107,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P24">
-        <v>46305.20575276836</v>
+        <v>46305.36273428139</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>51</v>
@@ -2151,7 +2151,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P25">
-        <v>46305.20575277831</v>
+        <v>46305.36273428804</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
@@ -2195,7 +2195,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P26">
-        <v>46305.20575274854</v>
+        <v>46305.36273426853</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>51</v>
@@ -2242,7 +2242,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P27">
-        <v>46305.20575272872</v>
+        <v>46305.36273425529</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>51</v>
@@ -2286,7 +2286,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P28">
-        <v>46305.20575271807</v>
+        <v>46305.36273424832</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>51</v>
@@ -2333,7 +2333,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P29">
-        <v>46305.20575270729</v>
+        <v>46305.36273424139</v>
       </c>
       <c r="Q29" t="s">
         <v>28</v>
@@ -2383,7 +2383,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P30">
-        <v>46305.20575267455</v>
+        <v>46305.36273422732</v>
       </c>
       <c r="Q30" t="s">
         <v>28</v>
@@ -2430,7 +2430,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P31">
-        <v>46305.20575269724</v>
+        <v>46305.36273423449</v>
       </c>
       <c r="Q31" t="s">
         <v>28</v>
@@ -2480,7 +2480,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P32">
-        <v>46305.20575263904</v>
+        <v>46305.36273421974</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
@@ -2524,7 +2524,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P33">
-        <v>46305.20575261097</v>
+        <v>46305.36273421196</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>51</v>
@@ -2568,7 +2568,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P34">
-        <v>46305.2057525776</v>
+        <v>46305.3627341853</v>
       </c>
       <c r="Q34" t="s">
         <v>28</v>
@@ -2615,7 +2615,7 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P35" s="6">
-        <v>46305.20576919735</v>
+        <v>46305.36275057897</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>28</v>
@@ -2664,7 +2664,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P36" s="6">
-        <v>46305.2057692078</v>
+        <v>46305.36275058663</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>28</v>
@@ -2715,7 +2715,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P37" s="6">
-        <v>46305.2057692176</v>
+        <v>46305.36275059347</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>28</v>
@@ -2764,7 +2764,7 @@
         <v>46300.7588564394</v>
       </c>
       <c r="P38" s="6">
-        <v>46305.20576924799</v>
+        <v>46305.36275061421</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>28</v>
@@ -2811,7 +2811,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P39" s="6">
-        <v>46305.20576926682</v>
+        <v>46305.36275062726</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>51</v>
@@ -2860,7 +2860,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P40" s="6">
-        <v>46305.20576929489</v>
+        <v>46305.36275064632</v>
       </c>
       <c r="Q40" s="6" t="s">
         <v>28</v>
@@ -2907,7 +2907,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P41" s="6">
-        <v>46305.20576932246</v>
+        <v>46305.36275066455</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>28</v>
@@ -2956,7 +2956,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P42" s="6">
-        <v>46305.20576930419</v>
+        <v>46305.36275065236</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P43" s="6">
-        <v>46305.20576934127</v>
+        <v>46305.36275067714</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>51</v>
@@ -3054,7 +3054,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P44" s="6">
-        <v>46305.20576933161</v>
+        <v>46305.36275067061</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>28</v>
@@ -3101,7 +3101,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P45" s="6">
-        <v>46305.20577780272</v>
+        <v>46305.36275876115</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>51</v>
@@ -3199,7 +3199,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P47" s="6">
-        <v>46305.20577781487</v>
+        <v>46305.36275877042</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>28</v>
@@ -3246,7 +3246,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P48" s="6">
-        <v>46305.20576936999</v>
+        <v>46305.36275069558</v>
       </c>
       <c r="Q48" s="5" t="s">
         <v>51</v>
@@ -3295,7 +3295,7 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P49" s="6">
-        <v>46305.20577787467</v>
+        <v>46305.36275881311</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>28</v>
@@ -3344,7 +3344,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P50" s="6">
-        <v>46305.20577788425</v>
+        <v>46305.36275881966</v>
       </c>
       <c r="Q50" s="5" t="s">
         <v>51</v>
@@ -3614,7 +3614,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46305.20576103318</v>
+        <v>46305.36274239628</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>51</v>
@@ -3661,7 +3661,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P4" s="2">
-        <v>46305.20576098546</v>
+        <v>46305.36274236323</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>51</v>
@@ -3705,7 +3705,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P5" s="2">
-        <v>46305.20576094543</v>
+        <v>46305.36274233532</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>51</v>
@@ -3749,7 +3749,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P6" s="2">
-        <v>46305.20576093486</v>
+        <v>46305.36274232762</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>51</v>
@@ -3793,7 +3793,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P7">
-        <v>46305.20575276836</v>
+        <v>46305.36273428139</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>51</v>
@@ -3837,7 +3837,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46305.20575274854</v>
+        <v>46305.36273426853</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>51</v>
@@ -3884,7 +3884,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46305.20575272872</v>
+        <v>46305.36273425529</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>51</v>
@@ -3928,7 +3928,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P10">
-        <v>46305.20575271807</v>
+        <v>46305.36273424832</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>51</v>
@@ -3972,7 +3972,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P11">
-        <v>46305.20575261097</v>
+        <v>46305.36273421196</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>51</v>
@@ -4019,7 +4019,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P12" s="6">
-        <v>46305.20576926682</v>
+        <v>46305.36275062726</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>51</v>
@@ -4068,7 +4068,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P13" s="6">
-        <v>46305.20576934127</v>
+        <v>46305.36275067714</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>51</v>
@@ -4115,7 +4115,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P14" s="6">
-        <v>46305.20577780272</v>
+        <v>46305.36275876115</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>51</v>
@@ -4211,7 +4211,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P16" s="6">
-        <v>46305.20576936999</v>
+        <v>46305.36275069558</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>51</v>
@@ -4260,7 +4260,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P17" s="6">
-        <v>46305.20577788425</v>
+        <v>46305.36275881966</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>51</v>
@@ -4308,7 +4308,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B2">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C2" t="s">
         <v>179</v>
@@ -4371,16 +4371,16 @@
         <v>3826</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4391,45 +4391,45 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B3">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C3" t="s">
         <v>179</v>
       </c>
       <c r="D3">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E3">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B4">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C4" t="s">
         <v>179</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B5">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C5" t="s">
         <v>179</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B6">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C6" t="s">
         <v>179</v>
@@ -4511,16 +4511,16 @@
         <v>3820</v>
       </c>
       <c r="F6">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H6">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4531,45 +4531,45 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B7">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E7">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G7">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B8">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
@@ -4581,13 +4581,13 @@
         <v>160</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4596,15 +4596,15 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B9">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C9" t="s">
         <v>179</v>
@@ -4616,21 +4616,56 @@
         <v>160</v>
       </c>
       <c r="F9">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H9">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B10">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>160</v>
+      </c>
+      <c r="F10">
+        <v>157</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>132</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="180">
   <si>
     <t>Priority</t>
   </si>
@@ -1123,7 +1123,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P3" s="2">
-        <v>46305.36274242896</v>
+        <v>46305.72545435187</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>28</v>
@@ -1173,7 +1173,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P4" s="2">
-        <v>46305.36274241605</v>
+        <v>46305.72545433335</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>28</v>
@@ -1223,7 +1223,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P5" s="2">
-        <v>46305.36274242261</v>
+        <v>46305.72545434292</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>28</v>
@@ -1270,7 +1270,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P6" s="2">
-        <v>46305.36274243537</v>
+        <v>46305.72545436121</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>28</v>
@@ -1320,7 +1320,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P7" s="2">
-        <v>46305.36274238358</v>
+        <v>46305.72545428615</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>28</v>
@@ -1364,7 +1364,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P8" s="2">
-        <v>46305.36274239628</v>
+        <v>46305.72545430451</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>51</v>
@@ -1411,7 +1411,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P9" s="2">
-        <v>46305.36274235664</v>
+        <v>46305.7254542472</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>28</v>
@@ -1458,7 +1458,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P10" s="2">
-        <v>46305.36274236323</v>
+        <v>46305.72545425688</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>51</v>
@@ -1502,7 +1502,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P11" s="2">
-        <v>46305.36274237684</v>
+        <v>46305.72545427667</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>28</v>
@@ -1549,7 +1549,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P12" s="2">
-        <v>46305.36274237</v>
+        <v>46305.72545426671</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>28</v>
@@ -1599,7 +1599,7 @@
         <v>46305.20576106136</v>
       </c>
       <c r="P13" s="2">
-        <v>46305.36274240285</v>
+        <v>46305.72545431391</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>28</v>
@@ -1649,7 +1649,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P14" s="2">
-        <v>46305.36274234272</v>
+        <v>46305.72545422736</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>28</v>
@@ -1693,7 +1693,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P15" s="2">
-        <v>46305.36274233532</v>
+        <v>46305.72545421727</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>51</v>
@@ -1737,7 +1737,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P16" s="2">
-        <v>46305.36274232762</v>
+        <v>46305.72545420671</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>51</v>
@@ -1784,7 +1784,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P17" s="2">
-        <v>46305.36274231809</v>
+        <v>46305.72545419462</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>28</v>
@@ -1831,7 +1831,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P18" s="2">
-        <v>46305.36273430099</v>
+        <v>46305.72544558345</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>28</v>
@@ -1875,7 +1875,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P19" s="2">
-        <v>46305.36273432023</v>
+        <v>46305.72544561344</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>28</v>
@@ -1922,7 +1922,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P20" s="2">
-        <v>46305.36273431396</v>
+        <v>46305.72544560267</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>28</v>
@@ -1969,7 +1969,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P21" s="2">
-        <v>46305.36273430726</v>
+        <v>46305.72544559299</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>28</v>
@@ -2016,7 +2016,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P22">
-        <v>46305.36273429449</v>
+        <v>46305.72544557391</v>
       </c>
       <c r="Q22" t="s">
         <v>28</v>
@@ -2063,7 +2063,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P23">
-        <v>46305.36273427486</v>
+        <v>46305.72544554438</v>
       </c>
       <c r="Q23" t="s">
         <v>28</v>
@@ -2107,7 +2107,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P24">
-        <v>46305.36273428139</v>
+        <v>46305.72544555414</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>51</v>
@@ -2151,7 +2151,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P25">
-        <v>46305.36273428804</v>
+        <v>46305.72544556411</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
@@ -2195,7 +2195,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P26">
-        <v>46305.36273426853</v>
+        <v>46305.72544553479</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>51</v>
@@ -2242,7 +2242,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P27">
-        <v>46305.36273425529</v>
+        <v>46305.7254455155</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>51</v>
@@ -2286,7 +2286,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P28">
-        <v>46305.36273424832</v>
+        <v>46305.72544550539</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>51</v>
@@ -2333,7 +2333,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P29">
-        <v>46305.36273424139</v>
+        <v>46305.7254454951</v>
       </c>
       <c r="Q29" t="s">
         <v>28</v>
@@ -2383,7 +2383,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P30">
-        <v>46305.36273422732</v>
+        <v>46305.72544547343</v>
       </c>
       <c r="Q30" t="s">
         <v>28</v>
@@ -2430,7 +2430,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P31">
-        <v>46305.36273423449</v>
+        <v>46305.72544548448</v>
       </c>
       <c r="Q31" t="s">
         <v>28</v>
@@ -2480,7 +2480,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P32">
-        <v>46305.36273421974</v>
+        <v>46305.72544546242</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
@@ -2524,7 +2524,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P33">
-        <v>46305.36273421196</v>
+        <v>46305.72544545171</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>51</v>
@@ -2568,7 +2568,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P34">
-        <v>46305.3627341853</v>
+        <v>46305.72544541569</v>
       </c>
       <c r="Q34" t="s">
         <v>28</v>
@@ -2615,7 +2615,7 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P35" s="6">
-        <v>46305.36275057897</v>
+        <v>46305.72546245658</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>28</v>
@@ -2664,7 +2664,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P36" s="6">
-        <v>46305.36275058663</v>
+        <v>46305.72546246747</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>28</v>
@@ -2715,7 +2715,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P37" s="6">
-        <v>46305.36275059347</v>
+        <v>46305.72546247725</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>28</v>
@@ -2764,7 +2764,7 @@
         <v>46300.7588564394</v>
       </c>
       <c r="P38" s="6">
-        <v>46305.36275061421</v>
+        <v>46305.7254625063</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>28</v>
@@ -2811,7 +2811,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P39" s="6">
-        <v>46305.36275062726</v>
+        <v>46305.7254625255</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>51</v>
@@ -2860,7 +2860,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P40" s="6">
-        <v>46305.36275064632</v>
+        <v>46305.72546255367</v>
       </c>
       <c r="Q40" s="6" t="s">
         <v>28</v>
@@ -2907,7 +2907,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P41" s="6">
-        <v>46305.36275066455</v>
+        <v>46305.72546258115</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>28</v>
@@ -2956,7 +2956,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P42" s="6">
-        <v>46305.36275065236</v>
+        <v>46305.72546256285</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>28</v>
@@ -3005,7 +3005,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P43" s="6">
-        <v>46305.36275067714</v>
+        <v>46305.72546260039</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>51</v>
@@ -3054,7 +3054,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P44" s="6">
-        <v>46305.36275067061</v>
+        <v>46305.72546259048</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>28</v>
@@ -3101,7 +3101,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P45" s="6">
-        <v>46305.36275876115</v>
+        <v>46305.72547073589</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>51</v>
@@ -3199,7 +3199,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P47" s="6">
-        <v>46305.36275877042</v>
+        <v>46305.72547074813</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>28</v>
@@ -3246,7 +3246,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P48" s="6">
-        <v>46305.36275069558</v>
+        <v>46305.72546262942</v>
       </c>
       <c r="Q48" s="5" t="s">
         <v>51</v>
@@ -3295,7 +3295,7 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P49" s="6">
-        <v>46305.36275881311</v>
+        <v>46305.72547080749</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>28</v>
@@ -3344,7 +3344,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P50" s="6">
-        <v>46305.36275881966</v>
+        <v>46305.72547081784</v>
       </c>
       <c r="Q50" s="5" t="s">
         <v>51</v>
@@ -3614,7 +3614,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46305.36274239628</v>
+        <v>46305.72545430451</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>51</v>
@@ -3661,7 +3661,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P4" s="2">
-        <v>46305.36274236323</v>
+        <v>46305.72545425688</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>51</v>
@@ -3705,7 +3705,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P5" s="2">
-        <v>46305.36274233532</v>
+        <v>46305.72545421727</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>51</v>
@@ -3749,7 +3749,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P6" s="2">
-        <v>46305.36274232762</v>
+        <v>46305.72545420671</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>51</v>
@@ -3793,7 +3793,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P7">
-        <v>46305.36273428139</v>
+        <v>46305.72544555414</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>51</v>
@@ -3837,7 +3837,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46305.36273426853</v>
+        <v>46305.72544553479</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>51</v>
@@ -3884,7 +3884,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46305.36273425529</v>
+        <v>46305.7254455155</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>51</v>
@@ -3928,7 +3928,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P10">
-        <v>46305.36273424832</v>
+        <v>46305.72544550539</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>51</v>
@@ -3972,7 +3972,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P11">
-        <v>46305.36273421196</v>
+        <v>46305.72544545171</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>51</v>
@@ -4019,7 +4019,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P12" s="6">
-        <v>46305.36275062726</v>
+        <v>46305.7254625255</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>51</v>
@@ -4068,7 +4068,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P13" s="6">
-        <v>46305.36275067714</v>
+        <v>46305.72546260039</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>51</v>
@@ -4115,7 +4115,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P14" s="6">
-        <v>46305.36275876115</v>
+        <v>46305.72547073589</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>51</v>
@@ -4211,7 +4211,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P16" s="6">
-        <v>46305.36275069558</v>
+        <v>46305.72546262942</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>51</v>
@@ -4260,7 +4260,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P17" s="6">
-        <v>46305.36275881966</v>
+        <v>46305.72547081784</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>51</v>
@@ -4308,7 +4308,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B2">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C2" t="s">
         <v>179</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B3">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C3" t="s">
         <v>179</v>
@@ -4406,16 +4406,16 @@
         <v>3826</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -4426,45 +4426,45 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B4">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C4" t="s">
         <v>179</v>
       </c>
       <c r="D4">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E4">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B5">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C5" t="s">
         <v>179</v>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B6">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C6" t="s">
         <v>179</v>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4531,10 +4531,10 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B7">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
@@ -4546,16 +4546,16 @@
         <v>3820</v>
       </c>
       <c r="F7">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H7">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -4566,45 +4566,45 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B8">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E8">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G8">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B9">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C9" t="s">
         <v>179</v>
@@ -4616,13 +4616,13 @@
         <v>160</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4631,15 +4631,15 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B10">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C10" t="s">
         <v>179</v>
@@ -4651,21 +4651,56 @@
         <v>160</v>
       </c>
       <c r="F10">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H10">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B11">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>160</v>
+      </c>
+      <c r="F11">
+        <v>157</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>132</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="180">
   <si>
     <t>Priority</t>
   </si>
@@ -79,12 +79,321 @@
     <t>Open</t>
   </si>
   <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>A.P.J. LABORATORIES LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>pooja damir miglani</t>
+  </si>
+  <si>
+    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
+  </si>
+  <si>
+    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>Mrs. Neeraja Kartik</t>
+  </si>
+  <si>
+    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
+  </si>
+  <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>INFO-DRIVE SOFTWARE LIMITED</t>
   </si>
   <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
     <t>Sumeet Surendra Chimbalkar</t>
   </si>
   <si>
@@ -92,315 +401,6 @@
   </si>
   <si>
     <t>Not in latest IBBI listing - verify with RP</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
-    <t>A.P.J. LABORATORIES LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>pooja damir miglani</t>
-  </si>
-  <si>
-    <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
-  </si>
-  <si>
-    <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>Mrs. Neeraja Kartik</t>
-  </si>
-  <si>
-    <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
-  </si>
-  <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
   </si>
   <si>
     <t>ALVI TECH SERVICES PVT LTD</t>
@@ -1048,24 +1048,24 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="2">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H2" s="3">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
       </c>
@@ -1073,12 +1073,12 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75885633306</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P2" s="2">
-        <v>46303.78903317315</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+        <v>46306.45019238699</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1099,13 +1099,13 @@
         <v>26</v>
       </c>
       <c r="G3" s="2">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H3" s="3">
         <v>46306</v>
       </c>
       <c r="I3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>27</v>
@@ -1113,6 +1113,9 @@
       <c r="K3" s="2">
         <v>1</v>
       </c>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1120,13 +1123,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75885622757</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P3" s="2">
-        <v>46305.72545435187</v>
+        <v>46306.45019235874</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1146,13 +1149,13 @@
         <v>31</v>
       </c>
       <c r="G4" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H4" s="3">
         <v>46306</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
@@ -1170,13 +1173,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75885624527</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P4" s="2">
-        <v>46305.72545433335</v>
+        <v>46306.45019237311</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1192,27 +1195,24 @@
       <c r="E5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G5" s="2">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H5" s="3">
         <v>46306</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1220,13 +1220,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.7588562628</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P5" s="2">
-        <v>46305.72545434292</v>
+        <v>46306.45019240092</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1237,16 +1237,19 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H6" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -1267,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75885627908</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P6" s="2">
-        <v>46305.72545436121</v>
+        <v>46306.45019228883</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1289,41 +1292,35 @@
       <c r="E7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="G7" s="2">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="3">
         <v>46307</v>
       </c>
       <c r="I7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="2">
+        <v>46300.7588479478</v>
+      </c>
+      <c r="P7" s="2">
+        <v>46306.45019231611</v>
+      </c>
+      <c r="Q7" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="2">
-        <v>46300.75884793277</v>
-      </c>
-      <c r="P7" s="2">
-        <v>46305.72545428615</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1334,22 +1331,25 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="G8" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H8" s="3">
         <v>46307</v>
       </c>
       <c r="I8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
@@ -1361,13 +1361,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P8" s="2">
-        <v>46305.72545430451</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>51</v>
+        <v>46306.4501922311</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1378,29 +1378,29 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="3">
         <v>46307</v>
       </c>
       <c r="I9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
+      <c r="L9" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1408,13 +1408,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75884796329</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P9" s="2">
-        <v>46305.7254542472</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>28</v>
+        <v>46306.45019224514</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1425,29 +1425,26 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H10" s="3">
         <v>46307</v>
       </c>
       <c r="I10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1455,13 +1452,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P10" s="2">
-        <v>46305.72545425688</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>51</v>
+        <v>46306.45019227484</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1472,26 +1469,29 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H11" s="3">
         <v>46307</v>
       </c>
       <c r="I11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
+      <c r="L11" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1499,13 +1499,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.75885617639</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P11" s="2">
-        <v>46305.72545427667</v>
+        <v>46306.45019226002</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1516,28 +1516,31 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F12" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G12" s="2">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H12" s="3">
         <v>46307</v>
       </c>
       <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="2">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
       <c r="L12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -1546,13 +1549,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75885619673</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P12" s="2">
-        <v>46305.72545426671</v>
+        <v>46306.45019233009</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1563,31 +1566,31 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H13" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I13" s="2">
         <v>2</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -1596,13 +1599,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46305.20576106136</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P13" s="2">
-        <v>46305.72545431391</v>
+        <v>46306.45019220237</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1613,32 +1616,26 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G14" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="3">
         <v>46308</v>
       </c>
       <c r="I14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
       </c>
-      <c r="L14" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -1646,13 +1643,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75884788632</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P14" s="2">
-        <v>46305.72545422736</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>28</v>
+        <v>46306.45019218787</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1663,10 +1660,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G15" s="2">
         <v>0.2</v>
@@ -1675,10 +1672,10 @@
         <v>46308</v>
       </c>
       <c r="I15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
@@ -1690,13 +1687,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.75884790152</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P15" s="2">
-        <v>46305.72545421727</v>
+        <v>46306.45019217338</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1707,26 +1704,29 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46310</v>
+      </c>
+      <c r="I16" s="2">
+        <v>4</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I16" s="2">
-        <v>3</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1734,13 +1734,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46301.38232480602</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P16" s="2">
-        <v>46305.72545420671</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>51</v>
+        <v>46306.45019215749</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1754,26 +1754,26 @@
         <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="H17" s="3">
-        <v>46310</v>
-      </c>
-      <c r="I17" s="2">
-        <v>5</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
       </c>
@@ -1781,13 +1781,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46300.75884787029</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P17" s="2">
-        <v>46305.72545419462</v>
+        <v>46306.45018428769</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1798,19 +1798,19 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="G18" s="2">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="H18" s="3">
         <v>46312</v>
       </c>
       <c r="I18" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>79</v>
@@ -1818,9 +1818,6 @@
       <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1828,13 +1825,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46300.75884779022</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P18" s="2">
-        <v>46305.72544558345</v>
+        <v>46306.4501843321</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1845,10 +1842,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2">
         <v>0.93</v>
@@ -1857,14 +1854,17 @@
         <v>46312</v>
       </c>
       <c r="I19" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K19" s="2">
         <v>1</v>
       </c>
+      <c r="L19" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
       </c>
@@ -1872,13 +1872,13 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46300.75884780569</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P19" s="2">
-        <v>46305.72544561344</v>
+        <v>46306.45018431723</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1">
@@ -1889,19 +1889,19 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="G20" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H20" s="3">
         <v>46312</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>85</v>
@@ -1919,13 +1919,13 @@
         <v>18</v>
       </c>
       <c r="O20" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P20" s="2">
-        <v>46305.72544560267</v>
+        <v>46306.45018430228</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="2" customFormat="1">
@@ -1939,26 +1939,26 @@
         <v>87</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2">
         <v>0.91</v>
       </c>
       <c r="H21" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I21" s="2">
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" s="2">
+        <v>3</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
       </c>
@@ -1966,13 +1966,13 @@
         <v>18</v>
       </c>
       <c r="O21" s="2">
-        <v>46300.75884783743</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P21" s="2">
-        <v>46305.72544559299</v>
+        <v>46306.45018427318</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1983,28 +1983,28 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" t="s">
         <v>91</v>
       </c>
-      <c r="E22" t="s">
-        <v>20</v>
+      <c r="F22" t="s">
+        <v>92</v>
       </c>
       <c r="G22">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H22" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I22">
         <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22" t="s">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2013,13 +2013,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46302.26841519317</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P22">
-        <v>46305.72544557391</v>
+        <v>46306.450184229</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2033,22 +2033,19 @@
         <v>94</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="G23">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="3">
         <v>46314</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2060,13 +2057,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46300.75884774033</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P23">
-        <v>46305.72544554438</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>28</v>
+        <v>46306.45018424345</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2077,22 +2074,22 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="G24">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H24" s="3">
         <v>46314</v>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2104,13 +2101,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46300.75884775587</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P24">
-        <v>46305.72544555414</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>51</v>
+        <v>46306.45018425787</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2121,22 +2118,22 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G25">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I25">
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2148,13 +2145,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46300.7588477715</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P25">
-        <v>46305.72544556411</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>28</v>
+        <v>46306.45018421479</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2165,25 +2162,28 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G26">
         <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L26" t="s">
+        <v>102</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2192,13 +2192,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46300.75884772457</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P26">
-        <v>46305.72544553479</v>
+        <v>46306.45018418654</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2209,28 +2209,25 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G27">
         <v>0.2</v>
       </c>
       <c r="H27" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I27">
         <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K27">
-        <v>3</v>
-      </c>
-      <c r="L27" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2239,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46302.26841507768</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P27">
-        <v>46305.7254455155</v>
+        <v>46306.45018417132</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2256,22 +2253,25 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
       </c>
       <c r="G28">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H28" s="3">
         <v>46317</v>
       </c>
       <c r="I28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J28" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2283,13 +2283,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46301.38232468421</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P28">
-        <v>46305.72544550539</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>51</v>
+        <v>46306.45018415671</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2300,29 +2300,32 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="G29">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="H29" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I29">
         <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
+      <c r="L29" t="s">
+        <v>109</v>
+      </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2330,13 +2333,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46302.26841501552</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P29">
-        <v>46305.7254454951</v>
+        <v>46306.45018412781</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2347,22 +2350,19 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" t="s">
         <v>111</v>
       </c>
-      <c r="E30" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" t="s">
-        <v>96</v>
-      </c>
       <c r="G30">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H30" s="3">
         <v>46318</v>
       </c>
       <c r="I30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J30" t="s">
         <v>112</v>
@@ -2380,13 +2380,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46305.20575267453</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P30">
-        <v>46305.72544547343</v>
+        <v>46306.45018414222</v>
       </c>
       <c r="Q30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2400,26 +2400,29 @@
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>20</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
       </c>
       <c r="G31">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H31" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I31">
         <v>13</v>
       </c>
       <c r="J31" t="s">
+        <v>115</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31" t="s">
         <v>116</v>
       </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31" t="s">
-        <v>117</v>
-      </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
       </c>
@@ -2427,13 +2430,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46305.20575269723</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P31">
-        <v>46305.72544548448</v>
+        <v>46306.45018411243</v>
       </c>
       <c r="Q31" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2444,31 +2447,25 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I32">
+        <v>20</v>
+      </c>
+      <c r="J32" t="s">
         <v>118</v>
       </c>
-      <c r="E32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32">
-        <v>0.93</v>
-      </c>
-      <c r="H32" s="3">
-        <v>46319</v>
-      </c>
-      <c r="I32">
-        <v>14</v>
-      </c>
-      <c r="J32" t="s">
-        <v>119</v>
-      </c>
       <c r="K32">
-        <v>2</v>
-      </c>
-      <c r="L32" t="s">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
@@ -2477,13 +2474,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46305.20575263901</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P32">
-        <v>46305.72544546242</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>28</v>
+        <v>46306.45018409734</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2494,99 +2491,104 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33">
+        <v>0.92</v>
+      </c>
+      <c r="H33" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I33">
+        <v>26</v>
+      </c>
+      <c r="J33" t="s">
+        <v>120</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33">
+        <v>46305.20575257758</v>
+      </c>
+      <c r="P33">
+        <v>46306.45018405222</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33">
-        <v>0.2</v>
-      </c>
-      <c r="H33" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I33">
-        <v>21</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="B34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P33">
-        <v>46305.72544545171</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="C34" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E34" t="s">
-        <v>75</v>
-      </c>
-      <c r="G34">
-        <v>0.92</v>
-      </c>
-      <c r="H34" s="3">
-        <v>46332</v>
-      </c>
-      <c r="I34">
-        <v>27</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H34" s="6">
+        <v>46305</v>
+      </c>
+      <c r="I34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="K34">
-        <v>4</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34">
-        <v>46305.20575257758</v>
-      </c>
-      <c r="P34">
-        <v>46305.72544541569</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>28</v>
+      <c r="K34" s="6">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34" s="6">
+        <v>46300.75885633306</v>
+      </c>
+      <c r="P34" s="6">
+        <v>46303.78903317315</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>127</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6">
@@ -2596,10 +2598,10 @@
         <v>46304</v>
       </c>
       <c r="I35" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K35" s="6">
         <v>1</v>
@@ -2615,18 +2617,18 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P35" s="6">
-        <v>46305.72546245658</v>
+        <v>46306.45020025707</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>128</v>
@@ -2643,7 +2645,7 @@
         <v>46304</v>
       </c>
       <c r="I36" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>130</v>
@@ -2664,25 +2666,25 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P36" s="6">
-        <v>46305.72546246747</v>
+        <v>46306.4502002715</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>132</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>133</v>
@@ -2694,7 +2696,7 @@
         <v>46303</v>
       </c>
       <c r="I37" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>134</v>
@@ -2715,25 +2717,25 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P37" s="6">
-        <v>46305.72546247725</v>
+        <v>46306.45020028572</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>136</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
@@ -2743,7 +2745,7 @@
         <v>46302</v>
       </c>
       <c r="I38" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>137</v>
@@ -2764,25 +2766,25 @@
         <v>46300.7588564394</v>
       </c>
       <c r="P38" s="6">
-        <v>46305.7254625063</v>
+        <v>46306.45020032745</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>139</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6">
@@ -2792,7 +2794,7 @@
         <v>46302</v>
       </c>
       <c r="I39" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>140</v>
@@ -2811,28 +2813,28 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P39" s="6">
-        <v>46305.7254625255</v>
+        <v>46306.45020035555</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G40" s="6">
         <v>0.9399999999999999</v>
@@ -2841,7 +2843,7 @@
         <v>46301</v>
       </c>
       <c r="I40" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>142</v>
@@ -2860,18 +2862,18 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P40" s="6">
-        <v>46305.72546255367</v>
+        <v>46306.45020039732</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>143</v>
@@ -2888,7 +2890,7 @@
         <v>46300</v>
       </c>
       <c r="I41" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>145</v>
@@ -2907,28 +2909,28 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P41" s="6">
-        <v>46305.72546258115</v>
+        <v>46306.45020043853</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>146</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G42" s="6">
         <v>0.93</v>
@@ -2937,7 +2939,7 @@
         <v>46300</v>
       </c>
       <c r="I42" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>147</v>
@@ -2956,25 +2958,25 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P42" s="6">
-        <v>46305.72546256285</v>
+        <v>46306.45020041129</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>148</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6">
@@ -2984,10 +2986,10 @@
         <v>46299</v>
       </c>
       <c r="I43" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K43" s="6">
         <v>1</v>
@@ -3005,28 +3007,28 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P43" s="6">
-        <v>46305.72546260039</v>
+        <v>46306.45020046723</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>150</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G44" s="6">
         <v>0.93</v>
@@ -3035,7 +3037,7 @@
         <v>46299</v>
       </c>
       <c r="I44" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>151</v>
@@ -3054,25 +3056,25 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P44" s="6">
-        <v>46305.72546259048</v>
+        <v>46306.45020045295</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
@@ -3082,7 +3084,7 @@
         <v>46298</v>
       </c>
       <c r="I45" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>153</v>
@@ -3101,25 +3103,25 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P45" s="6">
-        <v>46305.72547073589</v>
+        <v>46306.45020834605</v>
       </c>
       <c r="Q45" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>154</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>133</v>
@@ -3131,7 +3133,7 @@
         <v>46298</v>
       </c>
       <c r="I46" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>155</v>
@@ -3153,15 +3155,15 @@
         <v>46303.78904942831</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>156</v>
@@ -3178,7 +3180,7 @@
         <v>46298</v>
       </c>
       <c r="I47" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>158</v>
@@ -3199,25 +3201,25 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P47" s="6">
-        <v>46305.72547074813</v>
+        <v>46306.4502083617</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>160</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6">
@@ -3227,7 +3229,7 @@
         <v>46298</v>
       </c>
       <c r="I48" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>161</v>
@@ -3246,18 +3248,18 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P48" s="6">
-        <v>46305.72546262942</v>
+        <v>46306.45020050919</v>
       </c>
       <c r="Q48" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>162</v>
@@ -3274,7 +3276,7 @@
         <v>46297</v>
       </c>
       <c r="I49" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>163</v>
@@ -3295,25 +3297,25 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P49" s="6">
-        <v>46305.72547080749</v>
+        <v>46306.45020844889</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
@@ -3323,7 +3325,7 @@
         <v>46296</v>
       </c>
       <c r="I50" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>166</v>
@@ -3344,10 +3346,10 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P50" s="6">
-        <v>46305.72547081784</v>
+        <v>46306.45020846285</v>
       </c>
       <c r="Q50" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3537,29 +3539,26 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G2" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="3">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
       </c>
@@ -3567,13 +3566,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75885633306</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P2" s="2">
-        <v>46303.78903317315</v>
+        <v>46306.45019231611</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -3584,10 +3583,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -3596,14 +3595,17 @@
         <v>46307</v>
       </c>
       <c r="I3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
+      <c r="L3" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -3611,13 +3613,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P3" s="2">
-        <v>46305.72545430451</v>
+        <v>46306.45019224514</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -3628,29 +3630,26 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I4" s="2">
         <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -3658,13 +3657,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P4" s="2">
-        <v>46305.72545425688</v>
+        <v>46306.45019218787</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -3675,10 +3674,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -3687,10 +3686,10 @@
         <v>46308</v>
       </c>
       <c r="I5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -3702,41 +3701,41 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884790152</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P5" s="2">
-        <v>46305.72545421727</v>
+        <v>46306.45019217338</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6">
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I6" s="2">
-        <v>3</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="2">
+        <v>46314</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
@@ -3745,14 +3744,14 @@
       <c r="N6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O6" s="2">
-        <v>46301.38232480602</v>
-      </c>
-      <c r="P6" s="2">
-        <v>46305.72545420671</v>
+      <c r="O6">
+        <v>46300.75884775587</v>
+      </c>
+      <c r="P6">
+        <v>46306.45018424345</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -3766,13 +3765,13 @@
         <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -3790,13 +3789,13 @@
         <v>18</v>
       </c>
       <c r="O7">
-        <v>46300.75884775587</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P7">
-        <v>46305.72544555414</v>
+        <v>46306.45018421479</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3807,25 +3806,28 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G8">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I8">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>102</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -3834,13 +3836,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46300.75884772457</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P8">
-        <v>46305.72544553479</v>
+        <v>46306.45018418654</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3851,28 +3853,25 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I9">
         <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K9">
-        <v>3</v>
-      </c>
-      <c r="L9" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -3881,13 +3880,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46302.26841507768</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P9">
-        <v>46305.7254455155</v>
+        <v>46306.45018417132</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -3898,22 +3897,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46317</v>
+        <v>46326</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -3925,72 +3924,77 @@
         <v>18</v>
       </c>
       <c r="O10">
-        <v>46301.38232468421</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P10">
-        <v>46305.72544550539</v>
+        <v>46306.45018409734</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="A11" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
-        <v>0.2</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I11">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="B11" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P11">
-        <v>46305.72544545171</v>
+      <c r="C11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H11" s="6">
+        <v>46305</v>
+      </c>
+      <c r="I11" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" s="6">
+        <v>46300.75885633306</v>
+      </c>
+      <c r="P11" s="6">
+        <v>46303.78903317315</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>139</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6">
@@ -4000,7 +4004,7 @@
         <v>46302</v>
       </c>
       <c r="I12" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>140</v>
@@ -4019,25 +4023,25 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P12" s="6">
-        <v>46305.7254625255</v>
+        <v>46306.45020035555</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>148</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6">
@@ -4047,10 +4051,10 @@
         <v>46299</v>
       </c>
       <c r="I13" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K13" s="6">
         <v>1</v>
@@ -4068,25 +4072,25 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P13" s="6">
-        <v>46305.72546260039</v>
+        <v>46306.45020046723</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6">
@@ -4096,7 +4100,7 @@
         <v>46298</v>
       </c>
       <c r="I14" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>153</v>
@@ -4115,25 +4119,25 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P14" s="6">
-        <v>46305.72547073589</v>
+        <v>46306.45020834605</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>154</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>133</v>
@@ -4145,7 +4149,7 @@
         <v>46298</v>
       </c>
       <c r="I15" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>155</v>
@@ -4167,22 +4171,22 @@
         <v>46303.78904942831</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>160</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -4192,7 +4196,7 @@
         <v>46298</v>
       </c>
       <c r="I16" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>161</v>
@@ -4211,25 +4215,25 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P16" s="6">
-        <v>46305.72546262942</v>
+        <v>46306.45020050919</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
@@ -4239,7 +4243,7 @@
         <v>46296</v>
       </c>
       <c r="I17" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>166</v>
@@ -4260,10 +4264,10 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P17" s="6">
-        <v>46305.72547081784</v>
+        <v>46306.45020846285</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +4312,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4356,10 +4360,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B2">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C2" t="s">
         <v>179</v>
@@ -4374,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -4391,10 +4395,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B3">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C3" t="s">
         <v>179</v>
@@ -4426,10 +4430,10 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B4">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C4" t="s">
         <v>179</v>
@@ -4441,16 +4445,16 @@
         <v>3826</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4461,45 +4465,45 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B5">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C5" t="s">
         <v>179</v>
       </c>
       <c r="D5">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E5">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B6">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C6" t="s">
         <v>179</v>
@@ -4531,10 +4535,10 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B7">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
@@ -4549,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -4566,10 +4570,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B8">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
@@ -4581,16 +4585,16 @@
         <v>3820</v>
       </c>
       <c r="F8">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H8">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -4601,45 +4605,45 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B9">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C9" t="s">
         <v>179</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E9">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G9">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B10">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C10" t="s">
         <v>179</v>
@@ -4651,13 +4655,13 @@
         <v>160</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4666,15 +4670,15 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B11">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C11" t="s">
         <v>179</v>
@@ -4686,21 +4690,56 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H11">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B12">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>160</v>
+      </c>
+      <c r="F12">
+        <v>157</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <v>132</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="180">
   <si>
     <t>Priority</t>
   </si>
@@ -1076,7 +1076,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P2" s="2">
-        <v>46306.45019238699</v>
+        <v>46306.73889369357</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1126,7 +1126,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P3" s="2">
-        <v>46306.45019235874</v>
+        <v>46306.7388936651</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1176,7 +1176,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P4" s="2">
-        <v>46306.45019237311</v>
+        <v>46306.73889367961</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1223,7 +1223,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P5" s="2">
-        <v>46306.45019240092</v>
+        <v>46306.73889370801</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1273,7 +1273,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P6" s="2">
-        <v>46306.45019228883</v>
+        <v>46306.73889359355</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1317,7 +1317,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P7" s="2">
-        <v>46306.45019231611</v>
+        <v>46306.73889362151</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>46</v>
@@ -1364,7 +1364,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P8" s="2">
-        <v>46306.4501922311</v>
+        <v>46306.73889353455</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>23</v>
@@ -1411,7 +1411,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P9" s="2">
-        <v>46306.45019224514</v>
+        <v>46306.73889354909</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>46</v>
@@ -1455,7 +1455,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P10" s="2">
-        <v>46306.45019227484</v>
+        <v>46306.73889357936</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>23</v>
@@ -1502,7 +1502,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P11" s="2">
-        <v>46306.45019226002</v>
+        <v>46306.73889356442</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>23</v>
@@ -1552,7 +1552,7 @@
         <v>46305.20576106136</v>
       </c>
       <c r="P12" s="2">
-        <v>46306.45019233009</v>
+        <v>46306.73889363577</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1602,7 +1602,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P13" s="2">
-        <v>46306.45019220237</v>
+        <v>46306.7388935053</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>23</v>
@@ -1646,7 +1646,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P14" s="2">
-        <v>46306.45019218787</v>
+        <v>46306.73889349052</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>46</v>
@@ -1690,7 +1690,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P15" s="2">
-        <v>46306.45019217338</v>
+        <v>46306.73889347556</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -1737,7 +1737,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P16" s="2">
-        <v>46306.45019215749</v>
+        <v>46306.73889345909</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1784,7 +1784,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P17" s="2">
-        <v>46306.45018428769</v>
+        <v>46306.7388853133</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>23</v>
@@ -1828,7 +1828,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P18" s="2">
-        <v>46306.4501843321</v>
+        <v>46306.73888535729</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -1875,7 +1875,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P19" s="2">
-        <v>46306.45018431723</v>
+        <v>46306.73888534283</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>23</v>
@@ -1922,7 +1922,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P20" s="2">
-        <v>46306.45018430228</v>
+        <v>46306.73888532812</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>23</v>
@@ -1969,7 +1969,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P21" s="2">
-        <v>46306.45018427318</v>
+        <v>46306.73888529836</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>23</v>
@@ -2016,7 +2016,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P22">
-        <v>46306.450184229</v>
+        <v>46306.73888525447</v>
       </c>
       <c r="Q22" t="s">
         <v>23</v>
@@ -2060,7 +2060,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P23">
-        <v>46306.45018424345</v>
+        <v>46306.73888526922</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
@@ -2104,7 +2104,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P24">
-        <v>46306.45018425787</v>
+        <v>46306.7388852838</v>
       </c>
       <c r="Q24" t="s">
         <v>23</v>
@@ -2148,7 +2148,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P25">
-        <v>46306.45018421479</v>
+        <v>46306.73888524011</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>46</v>
@@ -2195,7 +2195,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P26">
-        <v>46306.45018418654</v>
+        <v>46306.73888521137</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>46</v>
@@ -2239,7 +2239,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P27">
-        <v>46306.45018417132</v>
+        <v>46306.73888519628</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>46</v>
@@ -2286,7 +2286,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P28">
-        <v>46306.45018415671</v>
+        <v>46306.73888518155</v>
       </c>
       <c r="Q28" t="s">
         <v>23</v>
@@ -2336,7 +2336,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P29">
-        <v>46306.45018412781</v>
+        <v>46306.73888515188</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2383,7 +2383,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P30">
-        <v>46306.45018414222</v>
+        <v>46306.73888516689</v>
       </c>
       <c r="Q30" t="s">
         <v>23</v>
@@ -2433,7 +2433,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P31">
-        <v>46306.45018411243</v>
+        <v>46306.73888513631</v>
       </c>
       <c r="Q31" t="s">
         <v>23</v>
@@ -2477,7 +2477,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P32">
-        <v>46306.45018409734</v>
+        <v>46306.73888512077</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>46</v>
@@ -2521,7 +2521,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P33">
-        <v>46306.45018405222</v>
+        <v>46306.73888507384</v>
       </c>
       <c r="Q33" t="s">
         <v>23</v>
@@ -2617,7 +2617,7 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P35" s="6">
-        <v>46306.45020025707</v>
+        <v>46306.73890189125</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>23</v>
@@ -2666,7 +2666,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P36" s="6">
-        <v>46306.4502002715</v>
+        <v>46306.7389019061</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>23</v>
@@ -2717,7 +2717,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P37" s="6">
-        <v>46306.45020028572</v>
+        <v>46306.73890192044</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>23</v>
@@ -2766,7 +2766,7 @@
         <v>46300.7588564394</v>
       </c>
       <c r="P38" s="6">
-        <v>46306.45020032745</v>
+        <v>46306.73890196386</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>23</v>
@@ -2813,7 +2813,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P39" s="6">
-        <v>46306.45020035555</v>
+        <v>46306.73890199242</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>46</v>
@@ -2862,7 +2862,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P40" s="6">
-        <v>46306.45020039732</v>
+        <v>46306.73890203507</v>
       </c>
       <c r="Q40" s="6" t="s">
         <v>23</v>
@@ -2909,7 +2909,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P41" s="6">
-        <v>46306.45020043853</v>
+        <v>46306.73890207729</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>23</v>
@@ -2958,7 +2958,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P42" s="6">
-        <v>46306.45020041129</v>
+        <v>46306.73890204917</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>23</v>
@@ -3007,7 +3007,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P43" s="6">
-        <v>46306.45020046723</v>
+        <v>46306.73890210572</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>46</v>
@@ -3056,7 +3056,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P44" s="6">
-        <v>46306.45020045295</v>
+        <v>46306.73890209116</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>23</v>
@@ -3103,7 +3103,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P45" s="6">
-        <v>46306.45020834605</v>
+        <v>46306.73891017484</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>46</v>
@@ -3201,7 +3201,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P47" s="6">
-        <v>46306.4502083617</v>
+        <v>46306.73891019166</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>23</v>
@@ -3248,7 +3248,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P48" s="6">
-        <v>46306.45020050919</v>
+        <v>46306.73890214869</v>
       </c>
       <c r="Q48" s="5" t="s">
         <v>46</v>
@@ -3297,7 +3297,7 @@
         <v>46300.75886486177</v>
       </c>
       <c r="P49" s="6">
-        <v>46306.45020844889</v>
+        <v>46306.73891028108</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>23</v>
@@ -3346,7 +3346,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P50" s="6">
-        <v>46306.45020846285</v>
+        <v>46306.7389102954</v>
       </c>
       <c r="Q50" s="5" t="s">
         <v>46</v>
@@ -3569,7 +3569,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P2" s="2">
-        <v>46306.45019231611</v>
+        <v>46306.73889362151</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>46</v>
@@ -3616,7 +3616,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P3" s="2">
-        <v>46306.45019224514</v>
+        <v>46306.73889354909</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>46</v>
@@ -3660,7 +3660,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P4" s="2">
-        <v>46306.45019218787</v>
+        <v>46306.73889349052</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>46</v>
@@ -3704,7 +3704,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P5" s="2">
-        <v>46306.45019217338</v>
+        <v>46306.73889347556</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>46</v>
@@ -3748,7 +3748,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P6">
-        <v>46306.45018424345</v>
+        <v>46306.73888526922</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>46</v>
@@ -3792,7 +3792,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P7">
-        <v>46306.45018421479</v>
+        <v>46306.73888524011</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>46</v>
@@ -3839,7 +3839,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P8">
-        <v>46306.45018418654</v>
+        <v>46306.73888521137</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
@@ -3883,7 +3883,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P9">
-        <v>46306.45018417132</v>
+        <v>46306.73888519628</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>46</v>
@@ -3927,7 +3927,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P10">
-        <v>46306.45018409734</v>
+        <v>46306.73888512077</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -4023,7 +4023,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P12" s="6">
-        <v>46306.45020035555</v>
+        <v>46306.73890199242</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>46</v>
@@ -4072,7 +4072,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P13" s="6">
-        <v>46306.45020046723</v>
+        <v>46306.73890210572</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -4119,7 +4119,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P14" s="6">
-        <v>46306.45020834605</v>
+        <v>46306.73891017484</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>46</v>
@@ -4215,7 +4215,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P16" s="6">
-        <v>46306.45020050919</v>
+        <v>46306.73890214869</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>46</v>
@@ -4264,7 +4264,7 @@
         <v>46300.75886487812</v>
       </c>
       <c r="P17" s="6">
-        <v>46306.45020846285</v>
+        <v>46306.7389102954</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -4312,7 +4312,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B2">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C2" t="s">
         <v>179</v>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B3">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C3" t="s">
         <v>179</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4430,10 +4430,10 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B4">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C4" t="s">
         <v>179</v>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B5">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C5" t="s">
         <v>179</v>
@@ -4480,16 +4480,16 @@
         <v>3826</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4500,45 +4500,45 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B6">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C6" t="s">
         <v>179</v>
       </c>
       <c r="D6">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E6">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B7">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C7" t="s">
         <v>179</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B8">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -4605,10 +4605,10 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B9">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C9" t="s">
         <v>179</v>
@@ -4620,16 +4620,16 @@
         <v>3820</v>
       </c>
       <c r="F9">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H9">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4640,45 +4640,45 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B10">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C10" t="s">
         <v>179</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E10">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G10">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B11">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C11" t="s">
         <v>179</v>
@@ -4690,13 +4690,13 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4705,15 +4705,15 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B12">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C12" t="s">
         <v>179</v>
@@ -4725,21 +4725,56 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H12">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B13">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>160</v>
+      </c>
+      <c r="F13">
+        <v>157</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>132</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="202">
   <si>
     <t>Priority</t>
   </si>
@@ -79,30 +79,387 @@
     <t>Open</t>
   </si>
   <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>Not in latest IBBI listing - verify with RP</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
     <t>Construction / EPC</t>
   </si>
   <si>
     <t>Manindra Kumar Tiwari</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
     <t>A.P.J. LABORATORIES LIMITED</t>
   </si>
   <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
     <t>pooja damir miglani</t>
   </si>
   <si>
@@ -127,270 +484,12 @@
     <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
     <t>Mrs. Neeraja Kartik</t>
   </si>
   <si>
     <t>250 MWh battery production capacity and 50 MWh cell production capacity</t>
   </si>
   <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>INFO-DRIVE SOFTWARE LIMITED</t>
   </si>
   <si>
@@ -400,9 +499,6 @@
     <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
   </si>
   <si>
-    <t>Not in latest IBBI listing - verify with RP</t>
-  </si>
-  <si>
     <t>ALVI TECH SERVICES PVT LTD</t>
   </si>
   <si>
@@ -430,15 +526,6 @@
     <t>_</t>
   </si>
   <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The Corporate Debtor is Not Operational for last 2 years. Form G published on 22.09.2026 in Financial Express (English, Lucknow Edition) &amp; Jansatta (Hindi, Lucknow Edition)</t>
-  </si>
-  <si>
     <t>SNEH EXPORTS PRIVATE LIMITED</t>
   </si>
   <si>
@@ -493,9 +580,6 @@
     <t>SECUREVALUE INDIA LIMITED</t>
   </si>
   <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
     <t>Mr. Brijendra Kumar Mishra</t>
   </si>
   <si>
@@ -506,24 +590,6 @@
   </si>
   <si>
     <t>Mr. Bhoopesh Gupta</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>ROYAL DRY FRUITS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>The Resolution Professional has issued an invitation for expression of interest on 01 September 2026.</t>
   </si>
   <si>
     <t>Started</t>
@@ -964,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1052,10 +1118,10 @@
         <v>21</v>
       </c>
       <c r="G2" s="2">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -1066,6 +1132,9 @@
       <c r="K2" s="2">
         <v>1</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
       </c>
@@ -1073,13 +1142,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75885622757</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P2" s="2">
-        <v>46306.73889369357</v>
+        <v>46307.3955139285</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -1090,19 +1159,16 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -1113,23 +1179,20 @@
       <c r="K3" s="2">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.7588479478</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46307.39551395869</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.75885624527</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46306.7388936651</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1149,10 +1212,10 @@
         <v>31</v>
       </c>
       <c r="G4" s="2">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H4" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -1163,23 +1226,20 @@
       <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="2">
+        <v>46300.75884796329</v>
+      </c>
+      <c r="P4" s="2">
+        <v>46306.73889353455</v>
+      </c>
+      <c r="Q4" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" s="2">
-        <v>46300.7588562628</v>
-      </c>
-      <c r="P4" s="2">
-        <v>46306.73889367961</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1193,26 +1253,26 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H5" s="3">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1220,13 +1280,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75885627908</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P5" s="2">
-        <v>46306.73889370801</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>23</v>
+        <v>46306.73889354909</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1237,32 +1297,26 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G6" s="2">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" s="3">
         <v>46307</v>
       </c>
       <c r="I6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1270,13 +1324,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75884793277</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P6" s="2">
-        <v>46306.73889359355</v>
+        <v>46307.39551391241</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1287,26 +1341,29 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H7" s="3">
         <v>46307</v>
       </c>
       <c r="I7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
+      <c r="L7" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1314,13 +1371,13 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P7" s="2">
-        <v>46306.73889362151</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>46</v>
+        <v>46307.39550561333</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1331,13 +1388,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G8" s="2">
         <v>0.93</v>
@@ -1346,13 +1403,16 @@
         <v>46307</v>
       </c>
       <c r="I8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -1361,13 +1421,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.75884796329</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P8" s="2">
-        <v>46306.73889353455</v>
+        <v>46307.3955139888</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1378,29 +1438,32 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46308</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46307</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1408,13 +1471,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P9" s="2">
-        <v>46306.73889354909</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>46</v>
+        <v>46307.39550553843</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1425,22 +1488,22 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G10" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -1452,13 +1515,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75885617639</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P10" s="2">
-        <v>46306.73889357936</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>23</v>
+        <v>46307.39550555297</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1469,29 +1532,26 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G11" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1499,13 +1559,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.75885619673</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P11" s="2">
-        <v>46306.73889356442</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>23</v>
+        <v>46307.39550552344</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1516,31 +1576,28 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H12" s="3">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -1549,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46305.20576106136</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P12" s="2">
-        <v>46306.73889363577</v>
+        <v>46307.39550550879</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1566,31 +1623,28 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="H13" s="3">
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="I13" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -1599,13 +1653,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.75884788632</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P13" s="2">
-        <v>46306.7388935053</v>
+        <v>46307.39550543506</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1616,22 +1670,22 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="G14" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H14" s="3">
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="I14" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
@@ -1643,13 +1697,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P14" s="2">
-        <v>46306.73889349052</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>46</v>
+        <v>46307.39550544995</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1660,26 +1714,29 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G15" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H15" s="3">
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="I15" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
+      <c r="L15" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1687,13 +1744,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46301.38232480602</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P15" s="2">
-        <v>46306.73889347556</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>46</v>
+        <v>46307.39550546476</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1704,29 +1761,29 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46310</v>
-      </c>
-      <c r="I16" s="2">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1734,13 +1791,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46300.75884787029</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P16" s="2">
-        <v>46306.73889345909</v>
+        <v>46307.39550547927</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1751,28 +1808,28 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G17" s="2">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H17" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I17" s="2">
         <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
@@ -1781,13 +1838,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46300.75884779022</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P17" s="2">
-        <v>46306.7388853133</v>
+        <v>46307.39550542011</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1798,23 +1855,26 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46314</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.93</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46312</v>
-      </c>
-      <c r="I18" s="2">
-        <v>6</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
@@ -1825,13 +1885,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46300.75884780569</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P18" s="2">
-        <v>46306.73888535729</v>
+        <v>46307.39550540552</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1842,29 +1902,26 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="G19" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I19" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
       </c>
@@ -1872,13 +1929,13 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P19" s="2">
-        <v>46306.73888534283</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>23</v>
+        <v>46307.3955053908</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1">
@@ -1889,75 +1946,69 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="H20" s="3">
+        <v>46314</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="2">
+        <v>46300.7588477715</v>
+      </c>
+      <c r="P20" s="2">
+        <v>46307.39550537582</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21">
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>46315</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46312</v>
-      </c>
-      <c r="I20" s="2">
-        <v>6</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="2">
-        <v>46300.75884783743</v>
-      </c>
-      <c r="P20" s="2">
-        <v>46306.73888532812</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="2" customFormat="1">
-      <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46313</v>
-      </c>
-      <c r="I21" s="2">
-        <v>7</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K21" s="2">
-        <v>3</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>89</v>
+      <c r="K21">
+        <v>1</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -1965,14 +2016,14 @@
       <c r="N21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O21" s="2">
-        <v>46302.26841519317</v>
-      </c>
-      <c r="P21" s="2">
-        <v>46306.73888529836</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>23</v>
+      <c r="O21">
+        <v>46300.75884772457</v>
+      </c>
+      <c r="P21">
+        <v>46307.39550536083</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1983,29 +2034,29 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G22">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H22" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I22">
         <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
+      <c r="L22" t="s">
+        <v>87</v>
+      </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
       </c>
@@ -2013,13 +2064,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46300.75884774033</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P22">
-        <v>46306.73888525447</v>
+        <v>46307.39550534706</v>
       </c>
       <c r="Q22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2030,25 +2081,28 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>0.2</v>
       </c>
       <c r="H23" s="3">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L23" t="s">
+        <v>90</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
@@ -2057,13 +2111,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46300.75884775587</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P23">
-        <v>46306.73888526922</v>
+        <v>46307.39549715862</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2074,25 +2128,28 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G24">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H24" s="3">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J24" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L24" t="s">
+        <v>94</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2101,13 +2158,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46300.7588477715</v>
+        <v>46307.39549714451</v>
       </c>
       <c r="P24">
-        <v>46306.7388852838</v>
+        <v>46307.39549714453</v>
       </c>
       <c r="Q24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2118,22 +2175,22 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G25">
         <v>0.2</v>
       </c>
       <c r="H25" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2145,13 +2202,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46300.75884772457</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P25">
-        <v>46306.73888524011</v>
+        <v>46307.3954971128</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2162,28 +2219,28 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>98</v>
+      </c>
+      <c r="F26" t="s">
+        <v>99</v>
       </c>
       <c r="G26">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H26" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>3</v>
-      </c>
-      <c r="L26" t="s">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2192,13 +2249,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46302.26841507768</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P26">
-        <v>46306.73888521137</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>46</v>
+        <v>46307.39549709752</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2209,26 +2266,32 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
+        <v>75</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
       </c>
       <c r="G27">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H27" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I27">
         <v>11</v>
       </c>
       <c r="J27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
+      <c r="L27" t="s">
+        <v>103</v>
+      </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
       </c>
@@ -2236,13 +2299,13 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46301.38232468421</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P27">
-        <v>46306.73888519628</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>46</v>
+        <v>46307.39549706617</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2253,19 +2316,16 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
         <v>105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>26</v>
       </c>
       <c r="G28">
         <v>0.9399999999999999</v>
       </c>
       <c r="H28" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I28">
         <v>11</v>
@@ -2276,6 +2336,9 @@
       <c r="K28">
         <v>1</v>
       </c>
+      <c r="L28" t="s">
+        <v>107</v>
+      </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
       </c>
@@ -2283,13 +2346,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46302.26841501552</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P28">
-        <v>46306.73888518155</v>
+        <v>46307.3954970824</v>
       </c>
       <c r="Q28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2300,31 +2363,31 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="G29">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H29" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I29">
         <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
@@ -2333,13 +2396,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46305.20575267453</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P29">
-        <v>46306.73888515188</v>
+        <v>46307.39549705025</v>
       </c>
       <c r="Q29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2350,16 +2413,16 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="G30">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I30">
         <v>12</v>
@@ -2368,7 +2431,7 @@
         <v>112</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" t="s">
         <v>113</v>
@@ -2380,13 +2443,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46305.20575269723</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P30">
-        <v>46306.73888516689</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>23</v>
+        <v>46307.39549700749</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2400,28 +2463,22 @@
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G31">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H31" s="3">
         <v>46319</v>
       </c>
       <c r="I31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J31" t="s">
         <v>115</v>
       </c>
       <c r="K31">
-        <v>2</v>
-      </c>
-      <c r="L31" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2430,13 +2487,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46305.20575263901</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P31">
-        <v>46306.73888513631</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>23</v>
+        <v>46307.39549703622</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2447,26 +2504,29 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32">
+        <v>0.92</v>
+      </c>
+      <c r="H32" s="3">
+        <v>46320</v>
+      </c>
+      <c r="I32">
+        <v>13</v>
+      </c>
+      <c r="J32" t="s">
         <v>117</v>
       </c>
-      <c r="E32" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32">
-        <v>0.2</v>
-      </c>
-      <c r="H32" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I32">
-        <v>20</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32" t="s">
         <v>118</v>
       </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
       </c>
@@ -2474,13 +2534,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46300.75884768533</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P32">
-        <v>46306.73888512077</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>46</v>
+        <v>46307.39549694471</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2494,455 +2554,434 @@
         <v>119</v>
       </c>
       <c r="E33" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="G33">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H33" s="3">
-        <v>46332</v>
+        <v>46320</v>
       </c>
       <c r="I33">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J33" t="s">
         <v>120</v>
       </c>
       <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33">
+        <v>46307.39549697415</v>
+      </c>
+      <c r="P33">
+        <v>46307.39549697418</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34">
+        <v>0.2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>46321</v>
+      </c>
+      <c r="I34">
+        <v>14</v>
+      </c>
+      <c r="J34" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34">
+        <v>46307.39549690609</v>
+      </c>
+      <c r="P34">
+        <v>46307.39549690611</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I35">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>124</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="L35" t="s">
+        <v>125</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35">
+        <v>46307.39549680641</v>
+      </c>
+      <c r="P35">
+        <v>46307.39549680644</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36">
+        <v>0.91</v>
+      </c>
+      <c r="H36" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I36">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>127</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>128</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36">
+        <v>46307.39549684311</v>
+      </c>
+      <c r="P36">
+        <v>46307.39549684314</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37">
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I37">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>130</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>131</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37">
+        <v>46307.39549687663</v>
+      </c>
+      <c r="P37">
+        <v>46307.39549687666</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I38">
+        <v>19</v>
+      </c>
+      <c r="J38" t="s">
+        <v>133</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P38">
+        <v>46307.39549675402</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E39" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39">
+        <v>0.92</v>
+      </c>
+      <c r="H39" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I39">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>135</v>
+      </c>
+      <c r="K39">
         <v>4</v>
       </c>
-      <c r="M33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33">
+      <c r="M39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39">
         <v>46305.20575257758</v>
       </c>
-      <c r="P33">
-        <v>46306.73888507384</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H34" s="6">
-        <v>46305</v>
-      </c>
-      <c r="I34" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="K34" s="6">
-        <v>1</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O34" s="6">
-        <v>46300.75885633306</v>
-      </c>
-      <c r="P34" s="6">
-        <v>46303.78903317315</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H35" s="6">
-        <v>46304</v>
-      </c>
-      <c r="I35" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K35" s="6">
-        <v>1</v>
-      </c>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O35" s="6">
-        <v>46300.75885634872</v>
-      </c>
-      <c r="P35" s="6">
-        <v>46306.73890189125</v>
-      </c>
-      <c r="Q35" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6">
+      <c r="P39">
+        <v>46307.39549673259</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40">
+        <v>0.95</v>
+      </c>
+      <c r="H40" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I40">
+        <v>26</v>
+      </c>
+      <c r="J40" t="s">
+        <v>115</v>
+      </c>
+      <c r="K40">
+        <v>4</v>
+      </c>
+      <c r="L40" t="s">
+        <v>137</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40">
+        <v>46307.39549666931</v>
+      </c>
+      <c r="P40">
+        <v>46307.39549666933</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H36" s="6">
-        <v>46304</v>
-      </c>
-      <c r="I36" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="K36" s="6">
-        <v>1</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O36" s="6">
-        <v>46300.7588563655</v>
-      </c>
-      <c r="P36" s="6">
-        <v>46306.7389019061</v>
-      </c>
-      <c r="Q36" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G37" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H37" s="6">
-        <v>46303</v>
-      </c>
-      <c r="I37" s="6">
-        <v>-3</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K37" s="6">
-        <v>2</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="6">
-        <v>46300.7588564207</v>
-      </c>
-      <c r="P37" s="6">
-        <v>46306.73890192044</v>
-      </c>
-      <c r="Q37" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="H38" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I38" s="6">
-        <v>-4</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K38" s="6">
-        <v>1</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38" s="6">
-        <v>46300.7588564394</v>
-      </c>
-      <c r="P38" s="6">
-        <v>46306.73890196386</v>
-      </c>
-      <c r="Q38" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17">
-      <c r="A39" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="H41" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I41">
+        <v>26</v>
+      </c>
+      <c r="J41" t="s">
         <v>139</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H39" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I39" s="6">
-        <v>-4</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K39" s="6">
-        <v>1</v>
-      </c>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O39" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P39" s="6">
-        <v>46306.73890199242</v>
-      </c>
-      <c r="Q39" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H40" s="6">
-        <v>46301</v>
-      </c>
-      <c r="I40" s="6">
-        <v>-5</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K40" s="6">
-        <v>2</v>
-      </c>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O40" s="6">
-        <v>46300.75885649968</v>
-      </c>
-      <c r="P40" s="6">
-        <v>46306.73890203507</v>
-      </c>
-      <c r="Q40" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="H41" s="6">
-        <v>46300</v>
-      </c>
-      <c r="I41" s="6">
-        <v>-6</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="K41" s="6">
-        <v>1</v>
-      </c>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O41" s="6">
-        <v>46300.75886463693</v>
-      </c>
-      <c r="P41" s="6">
-        <v>46306.73890207729</v>
-      </c>
-      <c r="Q41" s="6" t="s">
-        <v>23</v>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O41">
+        <v>46307.39549671811</v>
+      </c>
+      <c r="P41">
+        <v>46307.39549671813</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="G42" s="6">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="H42" s="6">
-        <v>46300</v>
+        <v>46306</v>
       </c>
       <c r="I42" s="6">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K42" s="6">
         <v>1</v>
@@ -2955,47 +2994,49 @@
         <v>18</v>
       </c>
       <c r="O42" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P42" s="6">
-        <v>46306.73890204917</v>
+        <v>46307.39551403373</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F43" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="G43" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="6">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="I43" s="6">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="K43" s="6">
         <v>1</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>18</v>
@@ -3004,40 +3045,40 @@
         <v>18</v>
       </c>
       <c r="O43" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P43" s="6">
-        <v>46306.73890210572</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>46</v>
+        <v>46307.39551400379</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="G44" s="6">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H44" s="6">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="I44" s="6">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>151</v>
@@ -3045,7 +3086,9 @@
       <c r="K44" s="6">
         <v>1</v>
       </c>
-      <c r="L44" s="6"/>
+      <c r="L44" s="6" t="s">
+        <v>152</v>
+      </c>
       <c r="M44" s="6" t="s">
         <v>18</v>
       </c>
@@ -3053,46 +3096,48 @@
         <v>18</v>
       </c>
       <c r="O44" s="6">
-        <v>46300.75886468366</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P44" s="6">
-        <v>46306.73890209116</v>
+        <v>46307.39551401839</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" s="6">
-        <v>46298</v>
+        <v>46306</v>
       </c>
       <c r="I45" s="6">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K45" s="6">
         <v>1</v>
       </c>
-      <c r="L45" s="6"/>
+      <c r="L45" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="M45" s="6" t="s">
         <v>18</v>
       </c>
@@ -3100,48 +3145,48 @@
         <v>18</v>
       </c>
       <c r="O45" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P45" s="6">
-        <v>46306.73891017484</v>
-      </c>
-      <c r="Q45" s="5" t="s">
-        <v>46</v>
+        <v>46307.39551404792</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>133</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H46" s="6">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="I46" s="6">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K46" s="6">
         <v>1</v>
       </c>
-      <c r="L46" s="6"/>
+      <c r="L46" s="6" t="s">
+        <v>158</v>
+      </c>
       <c r="M46" s="6" t="s">
         <v>18</v>
       </c>
@@ -3149,48 +3194,46 @@
         <v>18</v>
       </c>
       <c r="O46" s="6">
-        <v>46300.75886472998</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P46" s="6">
-        <v>46303.78904942831</v>
-      </c>
-      <c r="Q46" s="5" t="s">
-        <v>126</v>
+        <v>46307.39551407743</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H47" s="6">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="I47" s="6">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
       </c>
-      <c r="L47" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="L47" s="6"/>
       <c r="M47" s="6" t="s">
         <v>18</v>
       </c>
@@ -3198,46 +3241,48 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46300.75886474836</v>
+        <v>46300.75885634872</v>
       </c>
       <c r="P47" s="6">
-        <v>46306.73891019166</v>
+        <v>46307.39551410605</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>160</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H48" s="6">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="I48" s="6">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K48" s="6">
         <v>1</v>
       </c>
-      <c r="L48" s="6"/>
+      <c r="L48" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="M48" s="6" t="s">
         <v>18</v>
       </c>
@@ -3245,47 +3290,49 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P48" s="6">
-        <v>46306.73890214869</v>
-      </c>
-      <c r="Q48" s="5" t="s">
-        <v>46</v>
+        <v>46307.39551412096</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F49" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="G49" s="6">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H49" s="6">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="I49" s="6">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K49" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>18</v>
@@ -3294,48 +3341,46 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.75886486177</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P49" s="6">
-        <v>46306.73891028108</v>
+        <v>46307.395514164</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
         <v>0.2</v>
       </c>
       <c r="H50" s="6">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="I50" s="6">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K50" s="6">
         <v>1</v>
       </c>
-      <c r="L50" s="6" t="s">
-        <v>167</v>
-      </c>
+      <c r="L50" s="6"/>
       <c r="M50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3343,17 +3388,452 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P50" s="6">
-        <v>46306.7389102954</v>
+        <v>46307.39551417845</v>
       </c>
       <c r="Q50" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H51" s="6">
+        <v>46301</v>
+      </c>
+      <c r="I51" s="6">
+        <v>-6</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K51" s="6">
+        <v>2</v>
+      </c>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" s="6">
+        <v>46300.75885649968</v>
+      </c>
+      <c r="P51" s="6">
+        <v>46307.39552239229</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H52" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I52" s="6">
+        <v>-7</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K52" s="6">
+        <v>1</v>
+      </c>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O52" s="6">
+        <v>46300.75886463693</v>
+      </c>
+      <c r="P52" s="6">
+        <v>46307.39552240674</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H53" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I53" s="6">
+        <v>-7</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K53" s="6">
+        <v>1</v>
+      </c>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O53" s="6">
+        <v>46300.75886465221</v>
+      </c>
+      <c r="P53" s="6">
+        <v>46307.39552242085</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H54" s="6">
+        <v>46299</v>
+      </c>
+      <c r="I54" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O54" s="6">
+        <v>46300.75886466862</v>
+      </c>
+      <c r="P54" s="6">
+        <v>46307.39552244938</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H55" s="6">
+        <v>46299</v>
+      </c>
+      <c r="I55" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="K55" s="6">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O55" s="6">
+        <v>46300.75886468366</v>
+      </c>
+      <c r="P55" s="6">
+        <v>46307.39552246492</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H56" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I56" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K56" s="6">
+        <v>1</v>
+      </c>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O56" s="6">
+        <v>46300.75886471466</v>
+      </c>
+      <c r="P56" s="6">
+        <v>46307.39552250843</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H57" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I57" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K57" s="6">
+        <v>1</v>
+      </c>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O57" s="6">
+        <v>46300.75886472998</v>
+      </c>
+      <c r="P57" s="6">
+        <v>46307.3955225661</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H58" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I58" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K58" s="6">
+        <v>1</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O58" s="6">
+        <v>46300.75886474836</v>
+      </c>
+      <c r="P58" s="6">
+        <v>46307.39552249388</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="A59" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H59" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I59" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K59" s="6">
+        <v>1</v>
+      </c>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O59" s="6">
+        <v>46300.75886479358</v>
+      </c>
+      <c r="P59" s="6">
+        <v>46307.39552247916</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q50"/>
+  <autoFilter ref="A1:Q59"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -3453,6 +3933,24 @@
     <hyperlink ref="N49" r:id="rId96"/>
     <hyperlink ref="M50" r:id="rId97"/>
     <hyperlink ref="N50" r:id="rId98"/>
+    <hyperlink ref="M51" r:id="rId99"/>
+    <hyperlink ref="N51" r:id="rId100"/>
+    <hyperlink ref="M52" r:id="rId101"/>
+    <hyperlink ref="N52" r:id="rId102"/>
+    <hyperlink ref="M53" r:id="rId103"/>
+    <hyperlink ref="N53" r:id="rId104"/>
+    <hyperlink ref="M54" r:id="rId105"/>
+    <hyperlink ref="N54" r:id="rId106"/>
+    <hyperlink ref="M55" r:id="rId107"/>
+    <hyperlink ref="N55" r:id="rId108"/>
+    <hyperlink ref="M56" r:id="rId109"/>
+    <hyperlink ref="N56" r:id="rId110"/>
+    <hyperlink ref="M57" r:id="rId111"/>
+    <hyperlink ref="N57" r:id="rId112"/>
+    <hyperlink ref="M58" r:id="rId113"/>
+    <hyperlink ref="N58" r:id="rId114"/>
+    <hyperlink ref="M59" r:id="rId115"/>
+    <hyperlink ref="N59" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3539,10 +4037,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
@@ -3551,10 +4049,10 @@
         <v>46307</v>
       </c>
       <c r="I2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -3569,10 +4067,10 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P2" s="2">
-        <v>46306.73889362151</v>
+        <v>46307.39551395869</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -3583,29 +4081,29 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="G3" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H3" s="3">
         <v>46307</v>
       </c>
       <c r="I3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -3613,13 +4111,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75884799581</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P3" s="2">
-        <v>46306.73889354909</v>
+        <v>46306.73889353455</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -3630,26 +4128,29 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="I4" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
+      <c r="L4" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -3657,13 +4158,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P4" s="2">
-        <v>46306.73889349052</v>
+        <v>46306.73889354909</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -3674,10 +4175,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -3686,10 +4187,10 @@
         <v>46308</v>
       </c>
       <c r="I5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -3701,101 +4202,101 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
+        <v>46300.75884790152</v>
+      </c>
+      <c r="P5" s="2">
+        <v>46307.39550555297</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="2" customFormat="1">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46308</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="2">
         <v>46301.38232480602</v>
       </c>
-      <c r="P5" s="2">
-        <v>46306.73889347556</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6">
+      <c r="P6" s="2">
+        <v>46307.39550552344</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="2" customFormat="1">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="2">
         <v>0.2</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H7" s="3">
         <v>46314</v>
       </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6">
+      <c r="I7" s="2">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="2">
         <v>46300.75884775587</v>
       </c>
-      <c r="P6">
-        <v>46306.73888526922</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7">
-        <v>0.2</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46315</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>99</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7">
-        <v>46300.75884772457</v>
-      </c>
-      <c r="P7">
-        <v>46306.73888524011</v>
+      <c r="P7" s="2">
+        <v>46307.3955053908</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3806,28 +4307,25 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K8">
-        <v>3</v>
-      </c>
-      <c r="L8" t="s">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -3836,13 +4334,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46302.26841507768</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46306.73888521137</v>
+        <v>46307.39550536083</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3853,25 +4351,28 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G9">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>90</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -3880,13 +4381,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46301.38232468421</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46306.73888519628</v>
+        <v>46307.39549715862</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -3897,363 +4398,346 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
+        <v>46317</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P10">
+        <v>46307.3954971128</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46319</v>
+      </c>
+      <c r="I11">
+        <v>12</v>
+      </c>
+      <c r="J11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11" t="s">
+        <v>113</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11">
+        <v>46307.39549700746</v>
+      </c>
+      <c r="P11">
+        <v>46307.39549700749</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46319</v>
+      </c>
+      <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>46307.3954970362</v>
+      </c>
+      <c r="P12">
+        <v>46307.39549703622</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46321</v>
+      </c>
+      <c r="I13">
+        <v>14</v>
+      </c>
+      <c r="J13" t="s">
+        <v>122</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13">
+        <v>46307.39549690609</v>
+      </c>
+      <c r="P13">
+        <v>46307.39549690611</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I14">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14" t="s">
+        <v>125</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14">
+        <v>46307.39549680641</v>
+      </c>
+      <c r="P14">
+        <v>46307.39549680644</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>130</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15">
+        <v>46307.39549687663</v>
+      </c>
+      <c r="P15">
+        <v>46307.39549687666</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="3">
         <v>46326</v>
       </c>
-      <c r="I10">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
-        <v>118</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
+      <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
+        <v>133</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16">
         <v>46300.75884768533</v>
       </c>
-      <c r="P10">
-        <v>46306.73888512077</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H11" s="6">
-        <v>46305</v>
-      </c>
-      <c r="I11" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="K11" s="6">
-        <v>1</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="6">
-        <v>46300.75885633306</v>
-      </c>
-      <c r="P11" s="6">
-        <v>46303.78903317315</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H12" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I12" s="6">
-        <v>-4</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K12" s="6">
-        <v>1</v>
-      </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P12" s="6">
-        <v>46306.73890199242</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I13" s="6">
-        <v>-7</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="6">
-        <v>1</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" s="6">
-        <v>46300.75886466862</v>
-      </c>
-      <c r="P13" s="6">
-        <v>46306.73890210572</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H14" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I14" s="6">
-        <v>-8</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K14" s="6">
-        <v>1</v>
-      </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" s="6">
-        <v>46300.75886471466</v>
-      </c>
-      <c r="P14" s="6">
-        <v>46306.73891017484</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H15" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I15" s="6">
-        <v>-8</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K15" s="6">
-        <v>1</v>
-      </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" s="6">
-        <v>46300.75886472998</v>
-      </c>
-      <c r="P15" s="6">
-        <v>46303.78904942831</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I16" s="6">
-        <v>-8</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K16" s="6">
-        <v>1</v>
-      </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46300.75886479358</v>
-      </c>
-      <c r="P16" s="6">
-        <v>46306.73890214869</v>
+      <c r="P16">
+        <v>46307.39549675402</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="6" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
         <v>0.2</v>
       </c>
       <c r="H17" s="6">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="I17" s="6">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K17" s="6">
         <v>1</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>167</v>
-      </c>
+      <c r="L17" s="6"/>
       <c r="M17" s="6" t="s">
         <v>18</v>
       </c>
@@ -4261,17 +4745,160 @@
         <v>18</v>
       </c>
       <c r="O17" s="6">
-        <v>46300.75886487812</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P17" s="6">
-        <v>46306.7389102954</v>
+        <v>46307.39551417845</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="6">
+        <v>46299</v>
+      </c>
+      <c r="I18" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="6">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" s="6">
+        <v>46300.75886466862</v>
+      </c>
+      <c r="P18" s="6">
+        <v>46307.39552244938</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I19" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="6">
+        <v>46300.75886471466</v>
+      </c>
+      <c r="P19" s="6">
+        <v>46307.39552250843</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I20" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="6">
+        <v>46300.75886479358</v>
+      </c>
+      <c r="P20" s="6">
+        <v>46307.39552247916</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q17"/>
+  <autoFilter ref="A1:Q20"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4305,6 +4932,12 @@
     <hyperlink ref="N16" r:id="rId30"/>
     <hyperlink ref="M17" r:id="rId31"/>
     <hyperlink ref="N17" r:id="rId32"/>
+    <hyperlink ref="M18" r:id="rId33"/>
+    <hyperlink ref="N18" r:id="rId34"/>
+    <hyperlink ref="M19" r:id="rId35"/>
+    <hyperlink ref="N19" r:id="rId36"/>
+    <hyperlink ref="M20" r:id="rId37"/>
+    <hyperlink ref="N20" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4312,7 +4945,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4322,66 +4955,66 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B2">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D2">
         <v>192</v>
       </c>
       <c r="E2">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>369</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4390,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B3">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D3">
         <v>192</v>
@@ -4430,13 +5063,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B4">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D4">
         <v>192</v>
@@ -4448,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4465,13 +5098,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B5">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D5">
         <v>192</v>
@@ -4500,13 +5133,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B6">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D6">
         <v>192</v>
@@ -4515,16 +5148,16 @@
         <v>3826</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4535,48 +5168,48 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B7">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E7">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B8">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D8">
         <v>191</v>
@@ -4605,13 +5238,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B9">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D9">
         <v>191</v>
@@ -4623,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -4640,13 +5273,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B10">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D10">
         <v>191</v>
@@ -4655,16 +5288,16 @@
         <v>3820</v>
       </c>
       <c r="F10">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H10">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4675,48 +5308,48 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B11">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E11">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G11">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B12">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -4725,13 +5358,13 @@
         <v>160</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4740,18 +5373,18 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B13">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -4760,21 +5393,56 @@
         <v>160</v>
       </c>
       <c r="F13">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H13">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B14">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>160</v>
+      </c>
+      <c r="F14">
+        <v>157</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>132</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="202">
   <si>
     <t>Priority</t>
   </si>
@@ -1145,7 +1145,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P2" s="2">
-        <v>46307.3955139285</v>
+        <v>46307.88905263421</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>24</v>
@@ -1189,7 +1189,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P3" s="2">
-        <v>46307.39551395869</v>
+        <v>46307.88905266359</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>28</v>
@@ -1327,7 +1327,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P6" s="2">
-        <v>46307.39551391241</v>
+        <v>46307.88905261796</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>24</v>
@@ -1374,7 +1374,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P7" s="2">
-        <v>46307.39550561333</v>
+        <v>46307.88904476112</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>24</v>
@@ -1424,7 +1424,7 @@
         <v>46305.20576106136</v>
       </c>
       <c r="P8" s="2">
-        <v>46307.3955139888</v>
+        <v>46307.88905269294</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>24</v>
@@ -1474,7 +1474,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P9" s="2">
-        <v>46307.39550553843</v>
+        <v>46307.88904468949</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>24</v>
@@ -1518,7 +1518,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P10" s="2">
-        <v>46307.39550555297</v>
+        <v>46307.88904470354</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>28</v>
@@ -1562,7 +1562,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P11" s="2">
-        <v>46307.39550552344</v>
+        <v>46307.88904467553</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>28</v>
@@ -1609,7 +1609,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P12" s="2">
-        <v>46307.39550550879</v>
+        <v>46307.8890446615</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>24</v>
@@ -1656,7 +1656,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P13" s="2">
-        <v>46307.39550543506</v>
+        <v>46307.88904458907</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>24</v>
@@ -1700,7 +1700,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P14" s="2">
-        <v>46307.39550544995</v>
+        <v>46307.88904460396</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>24</v>
@@ -1747,7 +1747,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P15" s="2">
-        <v>46307.39550546476</v>
+        <v>46307.88904461851</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>24</v>
@@ -1794,7 +1794,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P16" s="2">
-        <v>46307.39550547927</v>
+        <v>46307.88904463262</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>24</v>
@@ -1841,7 +1841,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P17" s="2">
-        <v>46307.39550542011</v>
+        <v>46307.88904457432</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>24</v>
@@ -1888,7 +1888,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P18" s="2">
-        <v>46307.39550540552</v>
+        <v>46307.88904455974</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>24</v>
@@ -1932,7 +1932,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P19" s="2">
-        <v>46307.3955053908</v>
+        <v>46307.88904454507</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>28</v>
@@ -1976,7 +1976,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P20" s="2">
-        <v>46307.39550537582</v>
+        <v>46307.88904452906</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>24</v>
@@ -2020,7 +2020,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P21">
-        <v>46307.39550536083</v>
+        <v>46307.88904451401</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>28</v>
@@ -2067,7 +2067,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P22">
-        <v>46307.39550534706</v>
+        <v>46307.88904449896</v>
       </c>
       <c r="Q22" t="s">
         <v>24</v>
@@ -2114,7 +2114,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P23">
-        <v>46307.39549715862</v>
+        <v>46307.889036688</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>28</v>
@@ -2161,7 +2161,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P24">
-        <v>46307.39549714453</v>
+        <v>46307.88903667321</v>
       </c>
       <c r="Q24" t="s">
         <v>24</v>
@@ -2205,7 +2205,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P25">
-        <v>46307.3954971128</v>
+        <v>46307.8890366583</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>28</v>
@@ -2252,7 +2252,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P26">
-        <v>46307.39549709752</v>
+        <v>46307.88903664359</v>
       </c>
       <c r="Q26" t="s">
         <v>24</v>
@@ -2302,7 +2302,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P27">
-        <v>46307.39549706617</v>
+        <v>46307.88903661463</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -2349,7 +2349,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P28">
-        <v>46307.3954970824</v>
+        <v>46307.88903662929</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -2399,7 +2399,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P29">
-        <v>46307.39549705025</v>
+        <v>46307.88903659968</v>
       </c>
       <c r="Q29" t="s">
         <v>24</v>
@@ -2446,7 +2446,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P30">
-        <v>46307.39549700749</v>
+        <v>46307.88903657054</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>28</v>
@@ -2490,7 +2490,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P31">
-        <v>46307.39549703622</v>
+        <v>46307.88903658502</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P32">
-        <v>46307.39549694471</v>
+        <v>46307.88903654088</v>
       </c>
       <c r="Q32" t="s">
         <v>24</v>
@@ -2581,7 +2581,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P33">
-        <v>46307.39549697418</v>
+        <v>46307.88903655546</v>
       </c>
       <c r="Q33" t="s">
         <v>24</v>
@@ -2625,7 +2625,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P34">
-        <v>46307.39549690611</v>
+        <v>46307.88903652613</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>28</v>
@@ -2672,7 +2672,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P35">
-        <v>46307.39549680644</v>
+        <v>46307.88903648117</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>28</v>
@@ -2722,7 +2722,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P36">
-        <v>46307.39549684314</v>
+        <v>46307.88903649613</v>
       </c>
       <c r="Q36" t="s">
         <v>24</v>
@@ -2769,7 +2769,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P37">
-        <v>46307.39549687666</v>
+        <v>46307.88903651119</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P38">
-        <v>46307.39549675402</v>
+        <v>46307.88903644997</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>28</v>
@@ -2857,7 +2857,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P39">
-        <v>46307.39549673259</v>
+        <v>46307.88903643428</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
@@ -2904,7 +2904,7 @@
         <v>46307.39549666931</v>
       </c>
       <c r="P40">
-        <v>46307.39549666933</v>
+        <v>46307.88903638735</v>
       </c>
       <c r="Q40" t="s">
         <v>24</v>
@@ -2948,7 +2948,7 @@
         <v>46307.39549671811</v>
       </c>
       <c r="P41">
-        <v>46307.39549671813</v>
+        <v>46307.88903641787</v>
       </c>
       <c r="Q41" t="s">
         <v>24</v>
@@ -2997,7 +2997,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P42" s="6">
-        <v>46307.39551403373</v>
+        <v>46307.88905273634</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>24</v>
@@ -3048,7 +3048,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P43" s="6">
-        <v>46307.39551400379</v>
+        <v>46307.88905270749</v>
       </c>
       <c r="Q43" s="6" t="s">
         <v>24</v>
@@ -3099,7 +3099,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P44" s="6">
-        <v>46307.39551401839</v>
+        <v>46307.88905272199</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>24</v>
@@ -3148,7 +3148,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P45" s="6">
-        <v>46307.39551404792</v>
+        <v>46307.88905275082</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>24</v>
@@ -3197,7 +3197,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P46" s="6">
-        <v>46307.39551407743</v>
+        <v>46307.88905277973</v>
       </c>
       <c r="Q46" s="6" t="s">
         <v>24</v>
@@ -3244,7 +3244,7 @@
         <v>46300.75885634872</v>
       </c>
       <c r="P47" s="6">
-        <v>46307.39551410605</v>
+        <v>46307.88905280942</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>24</v>
@@ -3293,7 +3293,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P48" s="6">
-        <v>46307.39551412096</v>
+        <v>46307.88905282411</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>24</v>
@@ -3344,7 +3344,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P49" s="6">
-        <v>46307.395514164</v>
+        <v>46307.88905286766</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>24</v>
@@ -3391,7 +3391,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P50" s="6">
-        <v>46307.39551417845</v>
+        <v>46307.88905288192</v>
       </c>
       <c r="Q50" s="5" t="s">
         <v>28</v>
@@ -3440,7 +3440,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P51" s="6">
-        <v>46307.39552239229</v>
+        <v>46307.88906077829</v>
       </c>
       <c r="Q51" s="6" t="s">
         <v>24</v>
@@ -3487,7 +3487,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P52" s="6">
-        <v>46307.39552240674</v>
+        <v>46307.8890607925</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>24</v>
@@ -3536,7 +3536,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P53" s="6">
-        <v>46307.39552242085</v>
+        <v>46307.88906080725</v>
       </c>
       <c r="Q53" s="6" t="s">
         <v>24</v>
@@ -3585,7 +3585,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P54" s="6">
-        <v>46307.39552244938</v>
+        <v>46307.88906083583</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>28</v>
@@ -3634,7 +3634,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P55" s="6">
-        <v>46307.39552246492</v>
+        <v>46307.88906085039</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>24</v>
@@ -3681,7 +3681,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P56" s="6">
-        <v>46307.39552250843</v>
+        <v>46307.88906089382</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>28</v>
@@ -3730,7 +3730,7 @@
         <v>46300.75886472998</v>
       </c>
       <c r="P57" s="6">
-        <v>46307.3955225661</v>
+        <v>46307.88906095151</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>24</v>
@@ -3779,7 +3779,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P58" s="6">
-        <v>46307.39552249388</v>
+        <v>46307.88906087933</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>24</v>
@@ -3826,7 +3826,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P59" s="6">
-        <v>46307.39552247916</v>
+        <v>46307.88906086479</v>
       </c>
       <c r="Q59" s="5" t="s">
         <v>28</v>
@@ -4067,7 +4067,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P2" s="2">
-        <v>46307.39551395869</v>
+        <v>46307.88905266359</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P5" s="2">
-        <v>46307.39550555297</v>
+        <v>46307.88904470354</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>28</v>
@@ -4249,7 +4249,7 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P6" s="2">
-        <v>46307.39550552344</v>
+        <v>46307.88904467553</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>28</v>
@@ -4293,7 +4293,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P7" s="2">
-        <v>46307.3955053908</v>
+        <v>46307.88904454507</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
@@ -4337,7 +4337,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P8">
-        <v>46307.39550536083</v>
+        <v>46307.88904451401</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>28</v>
@@ -4384,7 +4384,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P9">
-        <v>46307.39549715862</v>
+        <v>46307.889036688</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>28</v>
@@ -4428,7 +4428,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P10">
-        <v>46307.3954971128</v>
+        <v>46307.8890366583</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>28</v>
@@ -4475,7 +4475,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P11">
-        <v>46307.39549700749</v>
+        <v>46307.88903657054</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>28</v>
@@ -4519,7 +4519,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P12">
-        <v>46307.39549703622</v>
+        <v>46307.88903658502</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>28</v>
@@ -4563,7 +4563,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P13">
-        <v>46307.39549690611</v>
+        <v>46307.88903652613</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>28</v>
@@ -4610,7 +4610,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P14">
-        <v>46307.39549680644</v>
+        <v>46307.88903648117</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>28</v>
@@ -4657,7 +4657,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P15">
-        <v>46307.39549687666</v>
+        <v>46307.88903651119</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>28</v>
@@ -4701,7 +4701,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P16">
-        <v>46307.39549675402</v>
+        <v>46307.88903644997</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>28</v>
@@ -4748,7 +4748,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P17" s="6">
-        <v>46307.39551417845</v>
+        <v>46307.88905288192</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>28</v>
@@ -4797,7 +4797,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P18" s="6">
-        <v>46307.39552244938</v>
+        <v>46307.88906083583</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>28</v>
@@ -4844,7 +4844,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P19" s="6">
-        <v>46307.39552250843</v>
+        <v>46307.88906089382</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>28</v>
@@ -4891,7 +4891,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P20" s="6">
-        <v>46307.39552247916</v>
+        <v>46307.88906086479</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>28</v>
@@ -4945,7 +4945,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B2">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C2" t="s">
         <v>201</v>
@@ -5008,13 +5008,13 @@
         <v>3838</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5028,10 +5028,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B3">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C3" t="s">
         <v>201</v>
@@ -5040,16 +5040,16 @@
         <v>192</v>
       </c>
       <c r="E3">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>369</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5058,15 +5058,15 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B4">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C4" t="s">
         <v>201</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B5">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C5" t="s">
         <v>201</v>
@@ -5116,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B6">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C6" t="s">
         <v>201</v>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B7">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C7" t="s">
         <v>201</v>
@@ -5183,16 +5183,16 @@
         <v>3826</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -5203,45 +5203,45 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B8">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C8" t="s">
         <v>201</v>
       </c>
       <c r="D8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E8">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B9">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C9" t="s">
         <v>201</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B10">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C10" t="s">
         <v>201</v>
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5308,10 +5308,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B11">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C11" t="s">
         <v>201</v>
@@ -5323,16 +5323,16 @@
         <v>3820</v>
       </c>
       <c r="F11">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H11">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -5343,45 +5343,45 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B12">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C12" t="s">
         <v>201</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E12">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G12">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B13">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C13" t="s">
         <v>201</v>
@@ -5393,13 +5393,13 @@
         <v>160</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -5408,15 +5408,15 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B14">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C14" t="s">
         <v>201</v>
@@ -5428,21 +5428,56 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H14">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B15">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>160</v>
+      </c>
+      <c r="F15">
+        <v>157</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>132</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="213">
   <si>
     <t>Priority</t>
   </si>
@@ -79,6 +79,357 @@
     <t>Open</t>
   </si>
   <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 28.09.2026.</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>Not in latest IBBI listing - verify with RP</t>
+  </si>
+  <si>
+    <t>KEW PRECISION PARTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shashi Bhushan Prasad</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Kamal Agarwal</t>
+  </si>
+  <si>
+    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>JRA INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Parshva Manoj Shah</t>
+  </si>
+  <si>
+    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>TECHNOFAB ENGINEERING LIMITED</t>
   </si>
   <si>
@@ -94,36 +445,18 @@
     <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
     <t>STC VENTURES PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
     <t>PURUSOTTAM BEHERA</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
     <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
     <t>Ms. Ritu Rastogi</t>
   </si>
   <si>
-    <t>Not in latest IBBI listing - verify with RP</t>
-  </si>
-  <si>
     <t>EXTOL INDUSTRIES LIMITED</t>
   </si>
   <si>
@@ -136,318 +469,21 @@
     <t>SURYA FOUNDRY PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
     <t>Mr. Reetesh Kumar Agarwal</t>
   </si>
   <si>
     <t>XYRON TECHNOLOGIES LIMITED</t>
   </si>
   <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
     <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
   </si>
   <si>
     <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
     <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
   </si>
   <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dev Vrat Rana</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
-  </si>
-  <si>
-    <t>SWADESH GREEN INFRA LIMITED</t>
-  </si>
-  <si>
-    <t>Niraj Kumar</t>
-  </si>
-  <si>
-    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
-  </si>
-  <si>
-    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bishwa Ranjan Chatterjee</t>
-  </si>
-  <si>
-    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
-  </si>
-  <si>
-    <t>Resonance Paper Mill Private Limited</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
   </si>
   <si>
@@ -497,9 +533,6 @@
   </si>
   <si>
     <t>The CIRP of the Corporate Debtor (“CD”) has been reinstated pursuant to the order passed by the Hon’ble NCLAT. Further, considering that 360 days of the CIRP period had already elapsed as on the date of appointment of the undersigned (Co</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
   </si>
   <si>
     <t>Shree Shiddhanath Cotex Private Limited</t>
@@ -1030,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1118,10 +1151,10 @@
         <v>21</v>
       </c>
       <c r="G2" s="2">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="H2" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -1142,10 +1175,10 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75884793277</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P2" s="2">
-        <v>46307.88905263421</v>
+        <v>46308.39987957306</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>24</v>
@@ -1168,7 +1201,7 @@
         <v>0.2</v>
       </c>
       <c r="H3" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -1186,10 +1219,10 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P3" s="2">
-        <v>46307.88905266359</v>
+        <v>46308.39987060975</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>28</v>
@@ -1206,22 +1239,19 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -1233,13 +1263,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884796329</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P4" s="2">
-        <v>46306.73889353455</v>
+        <v>46307.88904467553</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1250,7 +1280,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
@@ -1259,20 +1289,17 @@
         <v>0.2</v>
       </c>
       <c r="H5" s="3">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1280,13 +1307,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884799581</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P5" s="2">
-        <v>46306.73889354909</v>
+        <v>46308.39987059969</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1297,26 +1324,29 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46310</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46307</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1324,10 +1354,10 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75885617639</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P6" s="2">
-        <v>46307.88905261796</v>
+        <v>46308.39987057789</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>24</v>
@@ -1341,29 +1371,29 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46307</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1371,10 +1401,10 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75885619673</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P7" s="2">
-        <v>46307.88904476112</v>
+        <v>46308.39987055867</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>24</v>
@@ -1388,31 +1418,25 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="G8" s="2">
         <v>0.93</v>
       </c>
       <c r="H8" s="3">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -1421,10 +1445,10 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46305.20576106136</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P8" s="2">
-        <v>46307.88905269294</v>
+        <v>46308.3998705492</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>24</v>
@@ -1438,32 +1462,29 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I9" s="2">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1471,10 +1492,10 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75884788632</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P9" s="2">
-        <v>46307.88904468949</v>
+        <v>46308.39987053999</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>24</v>
@@ -1488,26 +1509,29 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I10" s="2">
+        <v>4</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1515,13 +1539,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P10" s="2">
-        <v>46307.88904470354</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>28</v>
+        <v>46308.3998705304</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1532,25 +1556,28 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="G11" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H11" s="3">
-        <v>46308</v>
+        <v>46313</v>
       </c>
       <c r="I11" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K11" s="2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
@@ -1559,13 +1586,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46301.38232480602</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P11" s="2">
-        <v>46307.88904467553</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>28</v>
+        <v>46308.39987052104</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1576,29 +1603,29 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="G12" s="2">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H12" s="3">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="I12" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
       </c>
@@ -1606,10 +1633,10 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75884787029</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P12" s="2">
-        <v>46307.8890446615</v>
+        <v>46308.39987050221</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>24</v>
@@ -1623,29 +1650,26 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G13" s="2">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I13" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1653,13 +1677,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.75884779022</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P13" s="2">
-        <v>46307.88904458907</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>24</v>
+        <v>46308.3998705116</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1670,19 +1694,19 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2">
         <v>0.93</v>
       </c>
       <c r="H14" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>63</v>
@@ -1697,10 +1721,10 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.75884780569</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P14" s="2">
-        <v>46307.88904460396</v>
+        <v>46308.39987049278</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>24</v>
@@ -1717,16 +1741,16 @@
         <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="3">
-        <v>46312</v>
+        <v>46315</v>
       </c>
       <c r="I15" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>65</v>
@@ -1734,9 +1758,6 @@
       <c r="K15" s="2">
         <v>1</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1744,13 +1765,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P15" s="2">
-        <v>46307.88904461851</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>24</v>
+        <v>46308.39987048287</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1761,29 +1782,29 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="G16" s="2">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46315</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46312</v>
-      </c>
-      <c r="I16" s="2">
-        <v>5</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1791,135 +1812,135 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46300.75884783743</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P16" s="2">
-        <v>46307.88904463262</v>
+        <v>46308.39987047307</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="2" customFormat="1">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2" t="s">
+    <row r="17" spans="1:17">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H17" s="3">
-        <v>46313</v>
-      </c>
-      <c r="I17" s="2">
-        <v>6</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17">
+        <v>3</v>
+      </c>
+      <c r="L17" t="s">
         <v>72</v>
       </c>
-      <c r="K17" s="2">
-        <v>3</v>
-      </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17">
+        <v>46302.26841507768</v>
+      </c>
+      <c r="P17">
+        <v>46308.39987044345</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
         <v>73</v>
       </c>
-      <c r="M17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" s="2">
-        <v>46302.26841519317</v>
-      </c>
-      <c r="P17" s="2">
-        <v>46307.88904457432</v>
-      </c>
-      <c r="Q17" s="2" t="s">
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18">
+        <v>0.92</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I18">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18" t="s">
+        <v>76</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18">
+        <v>46307.39549714451</v>
+      </c>
+      <c r="P18">
+        <v>46308.39987046314</v>
+      </c>
+      <c r="Q18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="2" customFormat="1">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.96</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I18" s="2">
-        <v>7</v>
-      </c>
-      <c r="J18" s="2" t="s">
+    <row r="19" spans="1:17">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
         <v>77</v>
       </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" s="2">
-        <v>46300.75884774033</v>
-      </c>
-      <c r="P18" s="2">
-        <v>46307.88904455974</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="2" customFormat="1">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46317</v>
+      </c>
+      <c r="I19">
+        <v>9</v>
+      </c>
+      <c r="J19" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I19" s="2">
-        <v>7</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" s="2">
+      <c r="K19">
         <v>1</v>
       </c>
       <c r="M19" s="4" t="s">
@@ -1928,42 +1949,45 @@
       <c r="N19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O19" s="2">
-        <v>46300.75884775587</v>
-      </c>
-      <c r="P19" s="2">
-        <v>46307.88904454507</v>
+      <c r="O19">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P19">
+        <v>46308.39987043281</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="2" customFormat="1">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="2" t="s">
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.93</v>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20">
+        <v>0.9399999999999999</v>
       </c>
       <c r="H20" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I20" s="2">
-        <v>7</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20" s="2">
+        <v>46317</v>
+      </c>
+      <c r="I20">
+        <v>9</v>
+      </c>
+      <c r="J20" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20">
         <v>1</v>
       </c>
       <c r="M20" s="4" t="s">
@@ -1972,13 +1996,13 @@
       <c r="N20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="2">
-        <v>46300.7588477715</v>
-      </c>
-      <c r="P20" s="2">
-        <v>46307.88904452906</v>
-      </c>
-      <c r="Q20" s="2" t="s">
+      <c r="O20">
+        <v>46302.26841501552</v>
+      </c>
+      <c r="P20">
+        <v>46308.39987042029</v>
+      </c>
+      <c r="Q20" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1990,26 +2014,32 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
       </c>
       <c r="G21">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H21" s="3">
-        <v>46315</v>
+        <v>46318</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
+      <c r="L21" t="s">
+        <v>85</v>
+      </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
       </c>
@@ -2017,13 +2047,13 @@
         <v>18</v>
       </c>
       <c r="O21">
-        <v>46300.75884772457</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P21">
-        <v>46307.88904451401</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>28</v>
+        <v>46308.39986133329</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2034,28 +2064,28 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G22">
         <v>0.9399999999999999</v>
       </c>
       <c r="H22" s="3">
-        <v>46315</v>
+        <v>46318</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2064,10 +2094,10 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46307.39550534703</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P22">
-        <v>46307.88904449896</v>
+        <v>46308.39986129606</v>
       </c>
       <c r="Q22" t="s">
         <v>24</v>
@@ -2081,28 +2111,28 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="G23">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H23" s="3">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="K23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
@@ -2111,13 +2141,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46302.26841507768</v>
+        <v>46308.39986132324</v>
       </c>
       <c r="P23">
-        <v>46307.889036688</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>28</v>
+        <v>46308.39986132326</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2128,28 +2158,31 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="F24" t="s">
+        <v>94</v>
       </c>
       <c r="G24">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H24" s="3">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K24">
         <v>2</v>
       </c>
       <c r="L24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2158,10 +2191,10 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46307.39549714451</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P24">
-        <v>46307.88903667321</v>
+        <v>46308.39986127555</v>
       </c>
       <c r="Q24" t="s">
         <v>24</v>
@@ -2175,7 +2208,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
         <v>26</v>
@@ -2184,16 +2217,19 @@
         <v>0.2</v>
       </c>
       <c r="H25" s="3">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L25" t="s">
+        <v>99</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2202,10 +2238,10 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46301.38232468421</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P25">
-        <v>46307.8890366583</v>
+        <v>46308.39986128596</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>28</v>
@@ -2219,25 +2255,22 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F26" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2249,13 +2282,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46302.26841501552</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P26">
-        <v>46307.88903664359</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>24</v>
+        <v>46308.39986126537</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2266,31 +2299,28 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="G27">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="H27" s="3">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="I27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2299,10 +2329,10 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46305.20575267453</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P27">
-        <v>46307.88903661463</v>
+        <v>46308.39986125505</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -2316,19 +2346,19 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="G28">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H28" s="3">
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="I28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" t="s">
         <v>106</v>
@@ -2336,9 +2366,6 @@
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="L28" t="s">
-        <v>107</v>
-      </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
       </c>
@@ -2346,10 +2373,10 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46305.20575269723</v>
+        <v>46307.39549697415</v>
       </c>
       <c r="P28">
-        <v>46307.88903662929</v>
+        <v>46308.39986124422</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -2363,31 +2390,25 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G29">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H29" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I29">
         <v>12</v>
       </c>
       <c r="J29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K29">
-        <v>2</v>
-      </c>
-      <c r="L29" t="s">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
@@ -2396,13 +2417,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46305.20575263901</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P29">
-        <v>46307.88903659968</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>24</v>
+        <v>46308.39986123199</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2413,7 +2434,7 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -2422,19 +2443,16 @@
         <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="I30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K30">
-        <v>2</v>
-      </c>
-      <c r="L30" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>18</v>
@@ -2443,10 +2461,10 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46307.39549700746</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P30">
-        <v>46307.88903657054</v>
+        <v>46308.3998612119</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>28</v>
@@ -2460,7 +2478,7 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
@@ -2469,16 +2487,19 @@
         <v>0.2</v>
       </c>
       <c r="H31" s="3">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L31" t="s">
+        <v>113</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2487,10 +2508,10 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46307.3954970362</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P31">
-        <v>46307.88903658502</v>
+        <v>46308.39986118091</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>28</v>
@@ -2504,29 +2525,32 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0.91</v>
+      </c>
+      <c r="H32" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I32">
+        <v>14</v>
+      </c>
+      <c r="J32" t="s">
+        <v>115</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
         <v>116</v>
       </c>
-      <c r="E32" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32">
-        <v>0.92</v>
-      </c>
-      <c r="H32" s="3">
-        <v>46320</v>
-      </c>
-      <c r="I32">
-        <v>13</v>
-      </c>
-      <c r="J32" t="s">
-        <v>117</v>
-      </c>
-      <c r="K32">
-        <v>2</v>
-      </c>
-      <c r="L32" t="s">
-        <v>118</v>
-      </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
       </c>
@@ -2534,10 +2558,10 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46307.3954969447</v>
+        <v>46307.39549684311</v>
       </c>
       <c r="P32">
-        <v>46307.88903654088</v>
+        <v>46308.39986119147</v>
       </c>
       <c r="Q32" t="s">
         <v>24</v>
@@ -2551,26 +2575,29 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33">
+        <v>0.2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I33">
+        <v>14</v>
+      </c>
+      <c r="J33" t="s">
+        <v>118</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
         <v>119</v>
       </c>
-      <c r="E33" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33">
-        <v>0.91</v>
-      </c>
-      <c r="H33" s="3">
-        <v>46320</v>
-      </c>
-      <c r="I33">
-        <v>13</v>
-      </c>
-      <c r="J33" t="s">
-        <v>120</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
       <c r="M33" s="4" t="s">
         <v>18</v>
       </c>
@@ -2578,13 +2605,13 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>46307.39549697415</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P33">
-        <v>46307.88903655546</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>24</v>
+        <v>46308.39986120164</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2595,26 +2622,32 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>93</v>
+      </c>
+      <c r="F34" t="s">
+        <v>94</v>
       </c>
       <c r="G34">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H34" s="3">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I34">
         <v>14</v>
       </c>
       <c r="J34" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
         <v>122</v>
       </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
       <c r="M34" s="4" t="s">
         <v>18</v>
       </c>
@@ -2622,13 +2655,13 @@
         <v>18</v>
       </c>
       <c r="O34">
-        <v>46307.39549690609</v>
+        <v>46308.39986117012</v>
       </c>
       <c r="P34">
-        <v>46307.88903652613</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>28</v>
+        <v>46308.39986117014</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2648,19 +2681,16 @@
         <v>0.2</v>
       </c>
       <c r="H35" s="3">
-        <v>46322</v>
+        <v>46326</v>
       </c>
       <c r="I35">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s">
         <v>124</v>
       </c>
       <c r="K35">
-        <v>2</v>
-      </c>
-      <c r="L35" t="s">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>18</v>
@@ -2669,10 +2699,10 @@
         <v>18</v>
       </c>
       <c r="O35">
-        <v>46307.39549680641</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P35">
-        <v>46307.88903648117</v>
+        <v>46308.3998611354</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>28</v>
@@ -2686,32 +2716,32 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="G36">
         <v>0.91</v>
       </c>
       <c r="H36" s="3">
-        <v>46322</v>
+        <v>46328</v>
       </c>
       <c r="I36">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s">
+        <v>126</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36" t="s">
         <v>127</v>
       </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="L36" t="s">
-        <v>128</v>
-      </c>
       <c r="M36" s="4" t="s">
         <v>18</v>
       </c>
@@ -2719,10 +2749,10 @@
         <v>18</v>
       </c>
       <c r="O36">
-        <v>46307.39549684311</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P36">
-        <v>46307.88903649613</v>
+        <v>46308.39986111097</v>
       </c>
       <c r="Q36" t="s">
         <v>24</v>
@@ -2736,28 +2766,25 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37">
+        <v>0.92</v>
+      </c>
+      <c r="H37" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I37">
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
         <v>129</v>
       </c>
-      <c r="E37" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37">
-        <v>0.2</v>
-      </c>
-      <c r="H37" s="3">
-        <v>46322</v>
-      </c>
-      <c r="I37">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>130</v>
-      </c>
       <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>18</v>
@@ -2766,13 +2793,13 @@
         <v>18</v>
       </c>
       <c r="O37">
-        <v>46307.39549687663</v>
+        <v>46305.20575257758</v>
       </c>
       <c r="P37">
-        <v>46307.88903651119</v>
-      </c>
-      <c r="Q37" s="5" t="s">
-        <v>28</v>
+        <v>46308.39986101075</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2783,25 +2810,28 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G38">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H38" s="3">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="I38">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L38" t="s">
+        <v>131</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>18</v>
@@ -2810,13 +2840,13 @@
         <v>18</v>
       </c>
       <c r="O38">
-        <v>46300.75884768533</v>
+        <v>46307.39549666931</v>
       </c>
       <c r="P38">
-        <v>46307.88903644997</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>28</v>
+        <v>46308.39986099937</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2827,25 +2857,25 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="G39">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H39" s="3">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="I39">
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>18</v>
@@ -2854,128 +2884,135 @@
         <v>18</v>
       </c>
       <c r="O39">
-        <v>46305.20575257758</v>
+        <v>46307.39549671811</v>
       </c>
       <c r="P39">
-        <v>46307.88903643428</v>
+        <v>46308.39986097639</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:17">
-      <c r="A40" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="A40" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G40">
-        <v>0.95</v>
-      </c>
-      <c r="H40" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I40">
+      <c r="D40" s="6"/>
+      <c r="E40" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="H40" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I40" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K40" s="6">
+        <v>1</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40" s="6">
+        <v>46300.75884793277</v>
+      </c>
+      <c r="P40" s="6">
+        <v>46308.3998796047</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J40" t="s">
-        <v>115</v>
-      </c>
-      <c r="K40">
-        <v>4</v>
-      </c>
-      <c r="L40" t="s">
-        <v>137</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O40">
-        <v>46307.39549666931</v>
-      </c>
-      <c r="P40">
-        <v>46307.88903638735</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I41">
-        <v>26</v>
-      </c>
-      <c r="J41" t="s">
-        <v>139</v>
-      </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O41">
-        <v>46307.39549671811</v>
-      </c>
-      <c r="P41">
-        <v>46307.88903641787</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>24</v>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I41" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K41" s="6">
+        <v>1</v>
+      </c>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O41" s="6">
+        <v>46300.7588479478</v>
+      </c>
+      <c r="P41" s="6">
+        <v>46308.39987963301</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="G42" s="6">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="H42" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I42" s="6">
         <v>-1</v>
@@ -2994,10 +3031,10 @@
         <v>18</v>
       </c>
       <c r="O42" s="6">
-        <v>46300.75885622757</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P42" s="6">
-        <v>46307.88905273634</v>
+        <v>46308.39987966143</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>24</v>
@@ -3005,26 +3042,24 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H43" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I43" s="6">
         <v>-1</v>
@@ -3045,50 +3080,46 @@
         <v>18</v>
       </c>
       <c r="O43" s="6">
-        <v>46300.75885624527</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P43" s="6">
-        <v>46307.88905270749</v>
-      </c>
-      <c r="Q43" s="6" t="s">
-        <v>24</v>
+        <v>46308.39987962354</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>148</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>150</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="6">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H44" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I44" s="6">
         <v>-1</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K44" s="6">
         <v>1</v>
       </c>
-      <c r="L44" s="6" t="s">
-        <v>152</v>
-      </c>
+      <c r="L44" s="6"/>
       <c r="M44" s="6" t="s">
         <v>18</v>
       </c>
@@ -3096,10 +3127,10 @@
         <v>18</v>
       </c>
       <c r="O44" s="6">
-        <v>46300.7588562628</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P44" s="6">
-        <v>46307.88905272199</v>
+        <v>46308.39987959508</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>24</v>
@@ -3107,36 +3138,36 @@
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H45" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I45" s="6">
         <v>-1</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="K45" s="6">
         <v>1</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>18</v>
@@ -3145,10 +3176,10 @@
         <v>18</v>
       </c>
       <c r="O45" s="6">
-        <v>46300.75885627908</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P45" s="6">
-        <v>46307.88905275082</v>
+        <v>46308.39987958469</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>24</v>
@@ -3156,36 +3187,38 @@
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="G46" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H46" s="6">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="I46" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="K46" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>18</v>
@@ -3194,10 +3227,10 @@
         <v>18</v>
       </c>
       <c r="O46" s="6">
-        <v>46300.75885633306</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P46" s="6">
-        <v>46307.88905277973</v>
+        <v>46308.39987965173</v>
       </c>
       <c r="Q46" s="6" t="s">
         <v>24</v>
@@ -3205,30 +3238,32 @@
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="G47" s="6">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H47" s="6">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I47" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
@@ -3241,10 +3276,10 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46300.75885634872</v>
+        <v>46300.75885622757</v>
       </c>
       <c r="P47" s="6">
-        <v>46307.88905280942</v>
+        <v>46308.39987969933</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>24</v>
@@ -3252,36 +3287,38 @@
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F48" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="G48" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H48" s="6">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I48" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K48" s="6">
         <v>1</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>18</v>
@@ -3290,10 +3327,10 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.7588563655</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P48" s="6">
-        <v>46307.88905282411</v>
+        <v>46308.39987968035</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>24</v>
@@ -3301,38 +3338,38 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G49" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H49" s="6">
-        <v>46303</v>
+        <v>46306</v>
       </c>
       <c r="I49" s="6">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K49" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>18</v>
@@ -3341,10 +3378,10 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.7588564207</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P49" s="6">
-        <v>46307.88905286766</v>
+        <v>46308.39987970874</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>24</v>
@@ -3352,35 +3389,37 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H50" s="6">
-        <v>46302</v>
+        <v>46306</v>
       </c>
       <c r="I50" s="6">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K50" s="6">
         <v>1</v>
       </c>
-      <c r="L50" s="6"/>
+      <c r="L50" s="6" t="s">
+        <v>167</v>
+      </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3388,48 +3427,48 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75885647022</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P50" s="6">
-        <v>46307.88905288192</v>
-      </c>
-      <c r="Q50" s="5" t="s">
-        <v>28</v>
+        <v>46308.39987968992</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>99</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H51" s="6">
-        <v>46301</v>
+        <v>46305</v>
       </c>
       <c r="I51" s="6">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K51" s="6">
-        <v>2</v>
-      </c>
-      <c r="L51" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="M51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3437,10 +3476,10 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46300.75885649968</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P51" s="6">
-        <v>46307.88906077829</v>
+        <v>46308.39987973654</v>
       </c>
       <c r="Q51" s="6" t="s">
         <v>24</v>
@@ -3448,35 +3487,37 @@
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H52" s="6">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="I52" s="6">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K52" s="6">
+        <v>1</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="K52" s="6">
-        <v>1</v>
-      </c>
-      <c r="L52" s="6"/>
       <c r="M52" s="6" t="s">
         <v>18</v>
       </c>
@@ -3484,10 +3525,10 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.75886463693</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P52" s="6">
-        <v>46307.8890607925</v>
+        <v>46308.39987975493</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>24</v>
@@ -3495,37 +3536,39 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>175</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>31</v>
+        <v>176</v>
       </c>
       <c r="G53" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H53" s="6">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="I53" s="6">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K53" s="6">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="M53" s="6" t="s">
         <v>18</v>
       </c>
@@ -3533,10 +3576,10 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P53" s="6">
-        <v>46307.88906080725</v>
+        <v>46308.39988845142</v>
       </c>
       <c r="Q53" s="6" t="s">
         <v>24</v>
@@ -3544,13 +3587,13 @@
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
@@ -3561,20 +3604,18 @@
         <v>0.2</v>
       </c>
       <c r="H54" s="6">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="I54" s="6">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="K54" s="6">
         <v>1</v>
       </c>
-      <c r="L54" s="6" t="s">
-        <v>178</v>
-      </c>
+      <c r="L54" s="6"/>
       <c r="M54" s="6" t="s">
         <v>18</v>
       </c>
@@ -3582,10 +3623,10 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P54" s="6">
-        <v>46307.88906083583</v>
+        <v>46308.39988849323</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>28</v>
@@ -3593,35 +3634,35 @@
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="G55" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H55" s="6">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="I55" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K55" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="6" t="s">
@@ -3631,10 +3672,10 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75886468366</v>
+        <v>46300.75885649968</v>
       </c>
       <c r="P55" s="6">
-        <v>46307.88906085039</v>
+        <v>46308.39988853089</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>24</v>
@@ -3642,30 +3683,30 @@
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H56" s="6">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="I56" s="6">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
@@ -3678,43 +3719,43 @@
         <v>18</v>
       </c>
       <c r="O56" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75886463693</v>
       </c>
       <c r="P56" s="6">
-        <v>46307.88906089382</v>
-      </c>
-      <c r="Q56" s="5" t="s">
-        <v>28</v>
+        <v>46308.39988854004</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="G57" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H57" s="6">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="I57" s="6">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K57" s="6">
         <v>1</v>
@@ -3727,10 +3768,10 @@
         <v>18</v>
       </c>
       <c r="O57" s="6">
-        <v>46300.75886472998</v>
+        <v>46300.75886465221</v>
       </c>
       <c r="P57" s="6">
-        <v>46307.88906095151</v>
+        <v>46308.39988854943</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>24</v>
@@ -3738,36 +3779,36 @@
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H58" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I58" s="6">
         <v>-9</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>18</v>
@@ -3776,41 +3817,43 @@
         <v>18</v>
       </c>
       <c r="O58" s="6">
-        <v>46300.75886474836</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P58" s="6">
-        <v>46307.88906087933</v>
-      </c>
-      <c r="Q58" s="6" t="s">
-        <v>24</v>
+        <v>46308.39988856782</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F59" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="G59" s="6">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H59" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I59" s="6">
         <v>-9</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K59" s="6">
         <v>1</v>
@@ -3823,17 +3866,209 @@
         <v>18</v>
       </c>
       <c r="O59" s="6">
+        <v>46300.75886468366</v>
+      </c>
+      <c r="P59" s="6">
+        <v>46308.39988857728</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="A60" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H60" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I60" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K60" s="6">
+        <v>1</v>
+      </c>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O60" s="6">
+        <v>46300.75886471466</v>
+      </c>
+      <c r="P60" s="6">
+        <v>46308.39989750899</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G61" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H61" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I61" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O61" s="6">
+        <v>46300.75886472998</v>
+      </c>
+      <c r="P61" s="6">
+        <v>46307.88906095151</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H62" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I62" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K62" s="6">
+        <v>1</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O62" s="6">
+        <v>46300.75886474836</v>
+      </c>
+      <c r="P62" s="6">
+        <v>46308.39989751922</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H63" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I63" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1</v>
+      </c>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O63" s="6">
         <v>46300.75886479358</v>
       </c>
-      <c r="P59" s="6">
-        <v>46307.88906086479</v>
-      </c>
-      <c r="Q59" s="5" t="s">
+      <c r="P63" s="6">
+        <v>46308.39988862519</v>
+      </c>
+      <c r="Q63" s="5" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q59"/>
+  <autoFilter ref="A1:Q63"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -3951,6 +4186,14 @@
     <hyperlink ref="N58" r:id="rId114"/>
     <hyperlink ref="M59" r:id="rId115"/>
     <hyperlink ref="N59" r:id="rId116"/>
+    <hyperlink ref="M60" r:id="rId117"/>
+    <hyperlink ref="N60" r:id="rId118"/>
+    <hyperlink ref="M61" r:id="rId119"/>
+    <hyperlink ref="N61" r:id="rId120"/>
+    <hyperlink ref="M62" r:id="rId121"/>
+    <hyperlink ref="N62" r:id="rId122"/>
+    <hyperlink ref="M63" r:id="rId123"/>
+    <hyperlink ref="N63" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3958,7 +4201,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4046,7 +4289,7 @@
         <v>0.2</v>
       </c>
       <c r="H2" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -4064,10 +4307,10 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.7588479478</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P2" s="2">
-        <v>46307.88905266359</v>
+        <v>46308.39987060975</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>28</v>
@@ -4084,22 +4327,19 @@
         <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="3">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4111,13 +4351,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75884796329</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P3" s="2">
-        <v>46306.73889353455</v>
+        <v>46307.88904467553</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4128,7 +4368,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>26</v>
@@ -4137,20 +4377,17 @@
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -4158,13 +4395,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884799581</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P4" s="2">
-        <v>46306.73889354909</v>
+        <v>46308.39987059969</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4175,7 +4412,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
@@ -4184,13 +4421,13 @@
         <v>0.2</v>
       </c>
       <c r="H5" s="3">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -4202,10 +4439,10 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884790152</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P5" s="2">
-        <v>46307.88904470354</v>
+        <v>46308.3998705116</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>28</v>
@@ -4219,7 +4456,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>26</v>
@@ -4228,13 +4465,13 @@
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="I6" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -4246,42 +4483,45 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46301.38232480602</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P6" s="2">
-        <v>46307.88904467553</v>
+        <v>46308.39987048287</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="2" t="s">
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
+        <v>46316</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7" t="s">
+        <v>72</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4289,11 +4529,11 @@
       <c r="N7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="2">
-        <v>46300.75884775587</v>
-      </c>
-      <c r="P7" s="2">
-        <v>46307.88904454507</v>
+      <c r="O7">
+        <v>46302.26841507768</v>
+      </c>
+      <c r="P7">
+        <v>46308.39987044345</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
@@ -4307,7 +4547,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
@@ -4316,13 +4556,13 @@
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -4334,10 +4574,10 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46300.75884772457</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P8">
-        <v>46307.88904451401</v>
+        <v>46308.39987043281</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>28</v>
@@ -4351,7 +4591,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>26</v>
@@ -4360,19 +4600,19 @@
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -4381,10 +4621,10 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46302.26841507768</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P9">
-        <v>46307.889036688</v>
+        <v>46308.39986128596</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>28</v>
@@ -4398,7 +4638,7 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
@@ -4407,13 +4647,13 @@
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4425,10 +4665,10 @@
         <v>18</v>
       </c>
       <c r="O10">
-        <v>46301.38232468421</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P10">
-        <v>46307.8890366583</v>
+        <v>46308.39986126537</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>28</v>
@@ -4442,7 +4682,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
@@ -4451,19 +4691,16 @@
         <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I11">
         <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
@@ -4472,10 +4709,10 @@
         <v>18</v>
       </c>
       <c r="O11">
-        <v>46307.39549700746</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46307.88903657054</v>
+        <v>46308.39986123199</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>28</v>
@@ -4489,7 +4726,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
@@ -4498,13 +4735,13 @@
         <v>0.2</v>
       </c>
       <c r="H12" s="3">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -4516,10 +4753,10 @@
         <v>18</v>
       </c>
       <c r="O12">
-        <v>46307.3954970362</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46307.88903658502</v>
+        <v>46308.3998612119</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>28</v>
@@ -4533,7 +4770,7 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
         <v>26</v>
@@ -4542,16 +4779,19 @@
         <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I13">
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>113</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4560,10 +4800,10 @@
         <v>18</v>
       </c>
       <c r="O13">
-        <v>46307.39549690609</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46307.88903652613</v>
+        <v>46308.39986118091</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>28</v>
@@ -4577,7 +4817,7 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
@@ -4589,16 +4829,16 @@
         <v>46322</v>
       </c>
       <c r="I14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -4607,10 +4847,10 @@
         <v>18</v>
       </c>
       <c r="O14">
-        <v>46307.39549680641</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46307.88903648117</v>
+        <v>46308.39986120164</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>28</v>
@@ -4624,7 +4864,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
         <v>26</v>
@@ -4633,20 +4873,17 @@
         <v>0.2</v>
       </c>
       <c r="H15" s="3">
-        <v>46322</v>
+        <v>46326</v>
       </c>
       <c r="I15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="L15" t="s">
-        <v>131</v>
-      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -4654,54 +4891,57 @@
         <v>18</v>
       </c>
       <c r="O15">
-        <v>46307.39549687663</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P15">
-        <v>46307.88903651119</v>
+        <v>46308.3998611354</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="A16" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G16">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6">
         <v>0.2</v>
       </c>
-      <c r="H16" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I16">
-        <v>19</v>
-      </c>
-      <c r="J16" t="s">
-        <v>133</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P16">
-        <v>46307.88903644997</v>
+      <c r="H16" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I16" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K16" s="6">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="6">
+        <v>46300.7588479478</v>
+      </c>
+      <c r="P16" s="6">
+        <v>46308.39987963301</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>28</v>
@@ -4709,13 +4949,13 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
@@ -4726,18 +4966,20 @@
         <v>0.2</v>
       </c>
       <c r="H17" s="6">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="I17" s="6">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="K17" s="6">
         <v>1</v>
       </c>
-      <c r="L17" s="6"/>
+      <c r="L17" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="M17" s="6" t="s">
         <v>18</v>
       </c>
@@ -4745,10 +4987,10 @@
         <v>18</v>
       </c>
       <c r="O17" s="6">
-        <v>46300.75885647022</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P17" s="6">
-        <v>46307.88905288192</v>
+        <v>46308.39987962354</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>28</v>
@@ -4756,13 +4998,13 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
@@ -4773,20 +5015,18 @@
         <v>0.2</v>
       </c>
       <c r="H18" s="6">
-        <v>46299</v>
+        <v>46302</v>
       </c>
       <c r="I18" s="6">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="K18" s="6">
         <v>1</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>178</v>
-      </c>
+      <c r="L18" s="6"/>
       <c r="M18" s="6" t="s">
         <v>18</v>
       </c>
@@ -4794,10 +5034,10 @@
         <v>18</v>
       </c>
       <c r="O18" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P18" s="6">
-        <v>46307.88906083583</v>
+        <v>46308.39988849323</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>28</v>
@@ -4805,13 +5045,13 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
@@ -4822,18 +5062,20 @@
         <v>0.2</v>
       </c>
       <c r="H19" s="6">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I19" s="6">
         <v>-9</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="K19" s="6">
         <v>1</v>
       </c>
-      <c r="L19" s="6"/>
+      <c r="L19" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="M19" s="6" t="s">
         <v>18</v>
       </c>
@@ -4841,10 +5083,10 @@
         <v>18</v>
       </c>
       <c r="O19" s="6">
-        <v>46300.75886471466</v>
+        <v>46300.75886466862</v>
       </c>
       <c r="P19" s="6">
-        <v>46307.88906089382</v>
+        <v>46308.39988856782</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>28</v>
@@ -4852,13 +5094,13 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
@@ -4872,10 +5114,10 @@
         <v>46298</v>
       </c>
       <c r="I20" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K20" s="6">
         <v>1</v>
@@ -4888,17 +5130,113 @@
         <v>18</v>
       </c>
       <c r="O20" s="6">
-        <v>46300.75886479358</v>
+        <v>46300.75886471466</v>
       </c>
       <c r="P20" s="6">
-        <v>46307.88906086479</v>
+        <v>46308.39989750899</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H21" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I21" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="6">
+        <v>46300.75886472998</v>
+      </c>
+      <c r="P21" s="6">
+        <v>46307.88906095151</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="6">
+        <v>46298</v>
+      </c>
+      <c r="I22" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="K22" s="6">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="6">
+        <v>46300.75886479358</v>
+      </c>
+      <c r="P22" s="6">
+        <v>46308.39988862519</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q20"/>
+  <autoFilter ref="A1:Q22"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4938,6 +5276,10 @@
     <hyperlink ref="N19" r:id="rId36"/>
     <hyperlink ref="M20" r:id="rId37"/>
     <hyperlink ref="N20" r:id="rId38"/>
+    <hyperlink ref="M21" r:id="rId39"/>
+    <hyperlink ref="N21" r:id="rId40"/>
+    <hyperlink ref="M22" r:id="rId41"/>
+    <hyperlink ref="N22" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4945,7 +5287,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4955,86 +5297,86 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B2">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E2">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>381</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B3">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D3">
         <v>192</v>
@@ -5043,13 +5385,13 @@
         <v>3838</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5063,28 +5405,28 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B4">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D4">
         <v>192</v>
       </c>
       <c r="E4">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>369</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5093,18 +5435,18 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B5">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D5">
         <v>192</v>
@@ -5133,13 +5475,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B6">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D6">
         <v>192</v>
@@ -5151,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5168,13 +5510,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B7">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D7">
         <v>192</v>
@@ -5203,13 +5545,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B8">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D8">
         <v>192</v>
@@ -5218,16 +5560,16 @@
         <v>3826</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -5238,48 +5580,48 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B9">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C9" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D9">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E9">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B10">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D10">
         <v>191</v>
@@ -5308,13 +5650,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B11">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C11" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D11">
         <v>191</v>
@@ -5326,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5343,13 +5685,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B12">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D12">
         <v>191</v>
@@ -5358,16 +5700,16 @@
         <v>3820</v>
       </c>
       <c r="F12">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H12">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -5378,48 +5720,48 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B13">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E13">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G13">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B14">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C14" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -5428,13 +5770,13 @@
         <v>160</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -5443,18 +5785,18 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B15">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C15" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -5463,21 +5805,56 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H15">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B16">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C16" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>160</v>
+      </c>
+      <c r="F16">
+        <v>157</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>132</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="213">
   <si>
     <t>Priority</t>
   </si>
@@ -1178,7 +1178,7 @@
         <v>46300.75884788632</v>
       </c>
       <c r="P2" s="2">
-        <v>46308.39987957306</v>
+        <v>46308.80860865589</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>24</v>
@@ -1222,7 +1222,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P3" s="2">
-        <v>46308.39987060975</v>
+        <v>46308.80860069162</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>28</v>
@@ -1310,7 +1310,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P5" s="2">
-        <v>46308.39987059969</v>
+        <v>46308.8086006791</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>28</v>
@@ -1357,7 +1357,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P6" s="2">
-        <v>46308.39987057789</v>
+        <v>46308.8086006663</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>24</v>
@@ -1404,7 +1404,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P7" s="2">
-        <v>46308.39987055867</v>
+        <v>46308.8086006416</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>24</v>
@@ -1448,7 +1448,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P8" s="2">
-        <v>46308.3998705492</v>
+        <v>46308.8086006291</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>24</v>
@@ -1495,7 +1495,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P9" s="2">
-        <v>46308.39987053999</v>
+        <v>46308.80860061695</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>24</v>
@@ -1542,7 +1542,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P10" s="2">
-        <v>46308.3998705304</v>
+        <v>46308.80860060442</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>24</v>
@@ -1589,7 +1589,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P11" s="2">
-        <v>46308.39987052104</v>
+        <v>46308.80860059104</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>24</v>
@@ -1636,7 +1636,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P12" s="2">
-        <v>46308.39987050221</v>
+        <v>46308.80860056587</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>24</v>
@@ -1680,7 +1680,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P13" s="2">
-        <v>46308.3998705116</v>
+        <v>46308.80860057846</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>28</v>
@@ -1724,7 +1724,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P14" s="2">
-        <v>46308.39987049278</v>
+        <v>46308.80860055199</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>24</v>
@@ -1768,7 +1768,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P15" s="2">
-        <v>46308.39987048287</v>
+        <v>46308.80860053844</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>28</v>
@@ -1815,7 +1815,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P16" s="2">
-        <v>46308.39987047307</v>
+        <v>46308.80860052589</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>24</v>
@@ -1862,7 +1862,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P17">
-        <v>46308.39987044345</v>
+        <v>46308.80860048686</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>28</v>
@@ -1909,7 +1909,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P18">
-        <v>46308.39987046314</v>
+        <v>46308.80860051262</v>
       </c>
       <c r="Q18" t="s">
         <v>24</v>
@@ -1953,7 +1953,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P19">
-        <v>46308.39987043281</v>
+        <v>46308.80860047329</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>28</v>
@@ -2000,7 +2000,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P20">
-        <v>46308.39987042029</v>
+        <v>46308.80860045793</v>
       </c>
       <c r="Q20" t="s">
         <v>24</v>
@@ -2050,7 +2050,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P21">
-        <v>46308.39986133329</v>
+        <v>46308.80859260492</v>
       </c>
       <c r="Q21" t="s">
         <v>24</v>
@@ -2097,7 +2097,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P22">
-        <v>46308.39986129606</v>
+        <v>46308.80859258032</v>
       </c>
       <c r="Q22" t="s">
         <v>24</v>
@@ -2144,7 +2144,7 @@
         <v>46308.39986132324</v>
       </c>
       <c r="P23">
-        <v>46308.39986132326</v>
+        <v>46308.80859259245</v>
       </c>
       <c r="Q23" t="s">
         <v>24</v>
@@ -2194,7 +2194,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P24">
-        <v>46308.39986127555</v>
+        <v>46308.80859255515</v>
       </c>
       <c r="Q24" t="s">
         <v>24</v>
@@ -2241,7 +2241,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P25">
-        <v>46308.39986128596</v>
+        <v>46308.808592568</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>28</v>
@@ -2285,7 +2285,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P26">
-        <v>46308.39986126537</v>
+        <v>46308.8085925427</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>28</v>
@@ -2332,7 +2332,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P27">
-        <v>46308.39986125505</v>
+        <v>46308.8085925304</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -2376,7 +2376,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P28">
-        <v>46308.39986124422</v>
+        <v>46308.80859251739</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -2420,7 +2420,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P29">
-        <v>46308.39986123199</v>
+        <v>46308.80859250448</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>28</v>
@@ -2464,7 +2464,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P30">
-        <v>46308.3998612119</v>
+        <v>46308.80859249179</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>28</v>
@@ -2511,7 +2511,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P31">
-        <v>46308.39986118091</v>
+        <v>46308.80859245299</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>28</v>
@@ -2561,7 +2561,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P32">
-        <v>46308.39986119147</v>
+        <v>46308.80859246592</v>
       </c>
       <c r="Q32" t="s">
         <v>24</v>
@@ -2608,7 +2608,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P33">
-        <v>46308.39986120164</v>
+        <v>46308.80859247913</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>28</v>
@@ -2658,7 +2658,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P34">
-        <v>46308.39986117014</v>
+        <v>46308.80859243982</v>
       </c>
       <c r="Q34" t="s">
         <v>24</v>
@@ -2702,7 +2702,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P35">
-        <v>46308.3998611354</v>
+        <v>46308.80859242669</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>28</v>
@@ -2752,7 +2752,7 @@
         <v>46308.39986111095</v>
       </c>
       <c r="P36">
-        <v>46308.39986111097</v>
+        <v>46308.80859240023</v>
       </c>
       <c r="Q36" t="s">
         <v>24</v>
@@ -2796,7 +2796,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P37">
-        <v>46308.39986101075</v>
+        <v>46308.80859238569</v>
       </c>
       <c r="Q37" t="s">
         <v>24</v>
@@ -2843,7 +2843,7 @@
         <v>46307.39549666931</v>
       </c>
       <c r="P38">
-        <v>46308.39986099937</v>
+        <v>46308.80859237124</v>
       </c>
       <c r="Q38" t="s">
         <v>24</v>
@@ -2887,7 +2887,7 @@
         <v>46307.39549671811</v>
       </c>
       <c r="P39">
-        <v>46308.39986097639</v>
+        <v>46308.80859234113</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
@@ -2938,7 +2938,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P40" s="6">
-        <v>46308.3998796047</v>
+        <v>46308.80860869765</v>
       </c>
       <c r="Q40" s="6" t="s">
         <v>24</v>
@@ -2985,7 +2985,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P41" s="6">
-        <v>46308.39987963301</v>
+        <v>46308.8086087364</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>28</v>
@@ -3034,7 +3034,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P42" s="6">
-        <v>46308.39987966143</v>
+        <v>46308.8086087774</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>24</v>
@@ -3083,7 +3083,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P43" s="6">
-        <v>46308.39987962354</v>
+        <v>46308.80860872313</v>
       </c>
       <c r="Q43" s="5" t="s">
         <v>28</v>
@@ -3130,7 +3130,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P44" s="6">
-        <v>46308.39987959508</v>
+        <v>46308.80860868467</v>
       </c>
       <c r="Q44" s="6" t="s">
         <v>24</v>
@@ -3179,7 +3179,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P45" s="6">
-        <v>46308.39987958469</v>
+        <v>46308.80860867112</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>24</v>
@@ -3230,7 +3230,7 @@
         <v>46305.20576106136</v>
       </c>
       <c r="P46" s="6">
-        <v>46308.39987965173</v>
+        <v>46308.80860876467</v>
       </c>
       <c r="Q46" s="6" t="s">
         <v>24</v>
@@ -3279,7 +3279,7 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P47" s="6">
-        <v>46308.39987969933</v>
+        <v>46308.80860882727</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>24</v>
@@ -3330,7 +3330,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P48" s="6">
-        <v>46308.39987968035</v>
+        <v>46308.80860880234</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>24</v>
@@ -3381,7 +3381,7 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P49" s="6">
-        <v>46308.39987970874</v>
+        <v>46308.80860883948</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>24</v>
@@ -3430,7 +3430,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P50" s="6">
-        <v>46308.39987968992</v>
+        <v>46308.80860881492</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>24</v>
@@ -3479,7 +3479,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P51" s="6">
-        <v>46308.39987973654</v>
+        <v>46308.80860887733</v>
       </c>
       <c r="Q51" s="6" t="s">
         <v>24</v>
@@ -3528,7 +3528,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P52" s="6">
-        <v>46308.39987975493</v>
+        <v>46308.80860890263</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>24</v>
@@ -3579,7 +3579,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P53" s="6">
-        <v>46308.39988845142</v>
+        <v>46308.80861677252</v>
       </c>
       <c r="Q53" s="6" t="s">
         <v>24</v>
@@ -3626,7 +3626,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P54" s="6">
-        <v>46308.39988849323</v>
+        <v>46308.80861682777</v>
       </c>
       <c r="Q54" s="5" t="s">
         <v>28</v>
@@ -3675,7 +3675,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P55" s="6">
-        <v>46308.39988853089</v>
+        <v>46308.80861687777</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>24</v>
@@ -3722,7 +3722,7 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P56" s="6">
-        <v>46308.39988854004</v>
+        <v>46308.80861688962</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>24</v>
@@ -3771,7 +3771,7 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P57" s="6">
-        <v>46308.39988854943</v>
+        <v>46308.80861690162</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>24</v>
@@ -3820,7 +3820,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P58" s="6">
-        <v>46308.39988856782</v>
+        <v>46308.80861692582</v>
       </c>
       <c r="Q58" s="5" t="s">
         <v>28</v>
@@ -3869,7 +3869,7 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P59" s="6">
-        <v>46308.39988857728</v>
+        <v>46308.80861693832</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>24</v>
@@ -3916,7 +3916,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P60" s="6">
-        <v>46308.39989750899</v>
+        <v>46308.80862494551</v>
       </c>
       <c r="Q60" s="5" t="s">
         <v>28</v>
@@ -4014,7 +4014,7 @@
         <v>46300.75886474836</v>
       </c>
       <c r="P62" s="6">
-        <v>46308.39989751922</v>
+        <v>46308.80862495991</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>24</v>
@@ -4061,7 +4061,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P63" s="6">
-        <v>46308.39988862519</v>
+        <v>46308.80861700077</v>
       </c>
       <c r="Q63" s="5" t="s">
         <v>28</v>
@@ -4310,7 +4310,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P2" s="2">
-        <v>46308.39987060975</v>
+        <v>46308.80860069162</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>28</v>
@@ -4398,7 +4398,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P4" s="2">
-        <v>46308.39987059969</v>
+        <v>46308.8086006791</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>28</v>
@@ -4442,7 +4442,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P5" s="2">
-        <v>46308.3998705116</v>
+        <v>46308.80860057846</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>28</v>
@@ -4486,7 +4486,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P6" s="2">
-        <v>46308.39987048287</v>
+        <v>46308.80860053844</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>28</v>
@@ -4533,7 +4533,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P7">
-        <v>46308.39987044345</v>
+        <v>46308.80860048686</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
@@ -4577,7 +4577,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P8">
-        <v>46308.39987043281</v>
+        <v>46308.80860047329</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>28</v>
@@ -4624,7 +4624,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P9">
-        <v>46308.39986128596</v>
+        <v>46308.808592568</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>28</v>
@@ -4668,7 +4668,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P10">
-        <v>46308.39986126537</v>
+        <v>46308.8085925427</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>28</v>
@@ -4712,7 +4712,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46308.39986123199</v>
+        <v>46308.80859250448</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>28</v>
@@ -4756,7 +4756,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46308.3998612119</v>
+        <v>46308.80859249179</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>28</v>
@@ -4803,7 +4803,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46308.39986118091</v>
+        <v>46308.80859245299</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>28</v>
@@ -4850,7 +4850,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46308.39986120164</v>
+        <v>46308.80859247913</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>28</v>
@@ -4894,7 +4894,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P15">
-        <v>46308.3998611354</v>
+        <v>46308.80859242669</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>28</v>
@@ -4941,7 +4941,7 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P16" s="6">
-        <v>46308.39987963301</v>
+        <v>46308.8086087364</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>28</v>
@@ -4990,7 +4990,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P17" s="6">
-        <v>46308.39987962354</v>
+        <v>46308.80860872313</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>28</v>
@@ -5037,7 +5037,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P18" s="6">
-        <v>46308.39988849323</v>
+        <v>46308.80861682777</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>28</v>
@@ -5086,7 +5086,7 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P19" s="6">
-        <v>46308.39988856782</v>
+        <v>46308.80861692582</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>28</v>
@@ -5133,7 +5133,7 @@
         <v>46300.75886471466</v>
       </c>
       <c r="P20" s="6">
-        <v>46308.39989750899</v>
+        <v>46308.80862494551</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>28</v>
@@ -5229,7 +5229,7 @@
         <v>46300.75886479358</v>
       </c>
       <c r="P22" s="6">
-        <v>46308.39988862519</v>
+        <v>46308.80861700077</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>28</v>
@@ -5287,7 +5287,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5335,10 +5335,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B2">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C2" t="s">
         <v>212</v>
@@ -5350,16 +5350,16 @@
         <v>3844</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -5370,45 +5370,45 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B3">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C3" t="s">
         <v>212</v>
       </c>
       <c r="D3">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E3">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>381</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B4">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C4" t="s">
         <v>212</v>
@@ -5420,13 +5420,13 @@
         <v>3838</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B5">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C5" t="s">
         <v>212</v>
@@ -5452,16 +5452,16 @@
         <v>192</v>
       </c>
       <c r="E5">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>369</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5470,15 +5470,15 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B6">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C6" t="s">
         <v>212</v>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B7">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C7" t="s">
         <v>212</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B8">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C8" t="s">
         <v>212</v>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B9">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C9" t="s">
         <v>212</v>
@@ -5595,16 +5595,16 @@
         <v>3826</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -5615,45 +5615,45 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B10">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C10" t="s">
         <v>212</v>
       </c>
       <c r="D10">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E10">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B11">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C11" t="s">
         <v>212</v>
@@ -5685,10 +5685,10 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B12">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C12" t="s">
         <v>212</v>
@@ -5703,7 +5703,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5720,10 +5720,10 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B13">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C13" t="s">
         <v>212</v>
@@ -5735,16 +5735,16 @@
         <v>3820</v>
       </c>
       <c r="F13">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H13">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -5755,45 +5755,45 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B14">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C14" t="s">
         <v>212</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E14">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G14">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B15">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C15" t="s">
         <v>212</v>
@@ -5805,13 +5805,13 @@
         <v>160</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -5820,15 +5820,15 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B16">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C16" t="s">
         <v>212</v>
@@ -5840,21 +5840,56 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H16">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B17">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>160</v>
+      </c>
+      <c r="F17">
+        <v>157</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>132</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="204">
   <si>
     <t>Priority</t>
   </si>
@@ -79,36 +79,348 @@
     <t>Open</t>
   </si>
   <si>
+    <t>KEW PRECISION PARTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Mr. Shashi Bhushan Prasad</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Kamal Agarwal</t>
+  </si>
+  <si>
+    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>JRA INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Parshva Manoj Shah</t>
+  </si>
+  <si>
+    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
   </si>
   <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
     <t>Mr. Bimal Kumar Agarwal</t>
   </si>
   <si>
     <t>The Form G has been published on 28.09.2026.</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
     <t>TV VISION LIMITED</t>
   </si>
   <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
     <t>ALOK KUMAR MURARKA</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
     <t>INDO PACIFIC PROJECTS LIMITED</t>
   </si>
   <si>
@@ -118,318 +430,6 @@
     <t>Not in latest IBBI listing - verify with RP</t>
   </si>
   <si>
-    <t>KEW PRECISION PARTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Shashi Bhushan Prasad</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>The addendum to form G was issued on 10th October, 2026.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>SUNSHINE FASTECH LIMITED</t>
-  </si>
-  <si>
-    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
-  </si>
-  <si>
-    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dev Vrat Rana</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
-  </si>
-  <si>
-    <t>SWADESH GREEN INFRA LIMITED</t>
-  </si>
-  <si>
-    <t>Niraj Kumar</t>
-  </si>
-  <si>
-    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
-  </si>
-  <si>
-    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bishwa Ranjan Chatterjee</t>
-  </si>
-  <si>
-    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
-  </si>
-  <si>
-    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Kamal Agarwal</t>
-  </si>
-  <si>
-    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>JRA INFRASTRUCTURE LIMITED</t>
-  </si>
-  <si>
-    <t>Parshva Manoj Shah</t>
-  </si>
-  <si>
-    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
-  </si>
-  <si>
-    <t>Resonance Paper Mill Private Limited</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>TECHNOFAB ENGINEERING LIMITED</t>
   </si>
   <si>
@@ -596,33 +596,6 @@
   </si>
   <si>
     <t>Palak Swapnil Desai</t>
-  </si>
-  <si>
-    <t>UNITED MASTERBATCHES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRATAP MUKHERJEE</t>
-  </si>
-  <si>
-    <t>SUKRITI HOSPITAL AND RESEARCH CENTRE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>SECUREVALUE INDIA LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Brijendra Kumar Mishra</t>
-  </si>
-  <si>
-    <t>The Corporate Debtor does not own any land or building. The assets of the Corporate Debtor substantially comprise transportation vehicles numbering approximately 2,397 as on 31.12.2024, as per the books of accounts, (Fixed Assets Register) provided by the</t>
-  </si>
-  <si>
-    <t>SVP INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bhoopesh Gupta</t>
   </si>
   <si>
     <t>Started</t>
@@ -1063,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1147,41 +1120,35 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="G2" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="3">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="2">
+        <v>46308.39987059968</v>
+      </c>
+      <c r="P2" s="2">
+        <v>46309.32659368968</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="2">
-        <v>46300.75884788632</v>
-      </c>
-      <c r="P2" s="2">
-        <v>46308.80860865589</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -1192,40 +1159,43 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="H3" s="3">
+        <v>46310</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46308</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.75884787029</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46309.32659368317</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46308.80860069162</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1236,19 +1206,19 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="G4" s="2">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="3">
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>30</v>
@@ -1256,6 +1226,9 @@
       <c r="K4" s="2">
         <v>1</v>
       </c>
+      <c r="L4" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1263,13 +1236,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46301.38232480602</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P4" s="2">
-        <v>46307.88904467553</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>31</v>
+        <v>46309.32659367001</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1283,19 +1256,19 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H5" s="3">
-        <v>46309</v>
+        <v>46312</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -1307,13 +1280,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46308.39987059968</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P5" s="2">
-        <v>46308.8086006791</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>28</v>
+        <v>46309.32659366349</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1324,19 +1297,19 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H6" s="3">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>36</v>
@@ -1354,13 +1327,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75884787029</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P6" s="2">
-        <v>46308.8086006663</v>
+        <v>46309.32659365699</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1377,13 +1350,13 @@
         <v>39</v>
       </c>
       <c r="G7" s="2">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H7" s="3">
         <v>46312</v>
       </c>
       <c r="I7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>40</v>
@@ -1401,13 +1374,13 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75884779022</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P7" s="2">
-        <v>46308.8086006416</v>
+        <v>46309.32659365023</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1424,10 +1397,10 @@
         <v>43</v>
       </c>
       <c r="G8" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H8" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I8" s="2">
         <v>4</v>
@@ -1436,7 +1409,10 @@
         <v>44</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -1445,13 +1421,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.75884780569</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P8" s="2">
-        <v>46308.8086006291</v>
+        <v>46309.32659364375</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1462,29 +1438,29 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="G9" s="2">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="H9" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I9" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1492,13 +1468,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P9" s="2">
-        <v>46308.80860061695</v>
+        <v>46309.3265936305</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1509,29 +1485,26 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1539,13 +1512,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75884783743</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P10" s="2">
-        <v>46308.80860060442</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>24</v>
+        <v>46309.32659363702</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1559,25 +1532,22 @@
         <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G11" s="2">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H11" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K11" s="2">
-        <v>3</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
@@ -1586,13 +1556,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46302.26841519317</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P11" s="2">
-        <v>46308.80860059104</v>
+        <v>46309.32659362342</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1603,25 +1573,22 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I12" s="2">
         <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
@@ -1633,13 +1600,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75884774033</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P12" s="2">
-        <v>46308.80860056587</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>24</v>
+        <v>46309.32659361638</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1650,26 +1617,29 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H13" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I13" s="2">
         <v>6</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
+      <c r="L13" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1677,13 +1647,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46300.75884775587</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P13" s="2">
-        <v>46308.80860057846</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>28</v>
+        <v>46309.32659360963</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1694,26 +1664,29 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="2">
+        <v>3</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.93</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I14" s="2">
-        <v>6</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -1721,13 +1694,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46300.7588477715</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P14" s="2">
-        <v>46308.80860055199</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>24</v>
+        <v>46309.32659358825</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1738,16 +1711,16 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="G15" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H15" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I15" s="2">
         <v>7</v>
@@ -1756,7 +1729,10 @@
         <v>65</v>
       </c>
       <c r="K15" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
@@ -1765,45 +1741,42 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46300.75884772457</v>
+        <v>46307.39549714451</v>
       </c>
       <c r="P15" s="2">
-        <v>46308.80860053844</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="2" customFormat="1">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="2" t="s">
+        <v>46309.32659360249</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="2">
-        <v>0.9399999999999999</v>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>0.2</v>
       </c>
       <c r="H16" s="3">
-        <v>46315</v>
-      </c>
-      <c r="I16" s="2">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="s">
+        <v>46317</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>69</v>
+      <c r="K16">
+        <v>1</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
@@ -1811,14 +1784,14 @@
       <c r="N16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O16" s="2">
-        <v>46307.39550534703</v>
-      </c>
-      <c r="P16" s="2">
-        <v>46308.80860052589</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>24</v>
+      <c r="O16">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P16">
+        <v>46309.32659358035</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1829,28 +1802,28 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" t="s">
-        <v>26</v>
+      <c r="F17" t="s">
+        <v>71</v>
       </c>
       <c r="G17">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H17" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I17">
         <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K17">
-        <v>3</v>
-      </c>
-      <c r="L17" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
@@ -1859,13 +1832,13 @@
         <v>18</v>
       </c>
       <c r="O17">
-        <v>46302.26841507768</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P17">
-        <v>46308.80860048686</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>28</v>
+        <v>46309.32659357139</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1879,26 +1852,29 @@
         <v>73</v>
       </c>
       <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18">
+        <v>0.96</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46318</v>
+      </c>
+      <c r="I18">
+        <v>9</v>
+      </c>
+      <c r="J18" t="s">
         <v>74</v>
       </c>
-      <c r="G18">
-        <v>0.92</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46316</v>
-      </c>
-      <c r="I18">
-        <v>8</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
         <v>75</v>
       </c>
-      <c r="K18">
-        <v>2</v>
-      </c>
-      <c r="L18" t="s">
-        <v>76</v>
-      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1906,13 +1882,13 @@
         <v>18</v>
       </c>
       <c r="O18">
-        <v>46307.39549714451</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P18">
-        <v>46308.80860051262</v>
+        <v>46309.32658564518</v>
       </c>
       <c r="Q18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1923,16 +1899,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
         <v>77</v>
       </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
       <c r="G19">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -1943,6 +1919,9 @@
       <c r="K19">
         <v>1</v>
       </c>
+      <c r="L19" t="s">
+        <v>79</v>
+      </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
       </c>
@@ -1950,13 +1929,13 @@
         <v>18</v>
       </c>
       <c r="O19">
-        <v>46301.38232468421</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P19">
-        <v>46308.80860047329</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>28</v>
+        <v>46309.32658563174</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1967,28 +1946,28 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="G20">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H20" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I20">
         <v>9</v>
       </c>
       <c r="J20" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L20" t="s">
+        <v>81</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -1997,13 +1976,13 @@
         <v>18</v>
       </c>
       <c r="O20">
-        <v>46302.26841501552</v>
+        <v>46308.39986132324</v>
       </c>
       <c r="P20">
-        <v>46308.80860045793</v>
+        <v>46309.32658563834</v>
       </c>
       <c r="Q20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -2014,31 +1993,31 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
         <v>83</v>
       </c>
-      <c r="E21" t="s">
-        <v>57</v>
-      </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G21">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H21" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I21">
         <v>10</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -2047,13 +2026,13 @@
         <v>18</v>
       </c>
       <c r="O21">
-        <v>46305.20575267453</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P21">
-        <v>46308.80859260492</v>
+        <v>46309.32658561814</v>
       </c>
       <c r="Q21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2064,16 +2043,16 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H22" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I22">
         <v>10</v>
@@ -2082,7 +2061,7 @@
         <v>88</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" t="s">
         <v>89</v>
@@ -2094,13 +2073,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46305.20575269723</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P22">
-        <v>46308.80859258032</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>24</v>
+        <v>46309.32658562508</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2114,25 +2093,22 @@
         <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G23">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="K23">
-        <v>2</v>
-      </c>
-      <c r="L23" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
@@ -2141,13 +2117,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46308.39986132324</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P23">
-        <v>46308.80859259245</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>24</v>
+        <v>46309.32658561136</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2161,28 +2137,25 @@
         <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H24" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I24">
         <v>11</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K24">
         <v>2</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2191,13 +2164,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46305.20575263901</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P24">
-        <v>46308.80859255515</v>
+        <v>46309.32658560448</v>
       </c>
       <c r="Q24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2208,28 +2181,25 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G25">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H25" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I25">
         <v>11</v>
       </c>
       <c r="J25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K25">
-        <v>2</v>
-      </c>
-      <c r="L25" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2238,13 +2208,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46307.39549700746</v>
+        <v>46307.39549697415</v>
       </c>
       <c r="P25">
-        <v>46308.808592568</v>
-      </c>
-      <c r="Q25" s="5" t="s">
-        <v>28</v>
+        <v>46309.32658559736</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2255,22 +2225,22 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G26">
         <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I26">
         <v>11</v>
       </c>
       <c r="J26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2282,13 +2252,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46307.3954970362</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P26">
-        <v>46308.8085925427</v>
+        <v>46309.32658558995</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2299,28 +2269,25 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G27">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H27" s="3">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="I27">
         <v>12</v>
       </c>
       <c r="J27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>2</v>
-      </c>
-      <c r="L27" t="s">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2329,13 +2296,13 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46307.3954969447</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P27">
-        <v>46308.8085925304</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>24</v>
+        <v>46309.32658558308</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2346,25 +2313,28 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="G28">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H28" s="3">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="I28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L28" t="s">
+        <v>103</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
@@ -2373,13 +2343,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46307.39549697415</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P28">
-        <v>46308.80859251739</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>24</v>
+        <v>46309.32658556175</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2390,26 +2360,32 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29">
+        <v>0.91</v>
+      </c>
+      <c r="H29" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I29">
+        <v>13</v>
+      </c>
+      <c r="J29" t="s">
         <v>107</v>
       </c>
-      <c r="E29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29">
-        <v>0.2</v>
-      </c>
-      <c r="H29" s="3">
-        <v>46320</v>
-      </c>
-      <c r="I29">
-        <v>12</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
         <v>108</v>
       </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2417,13 +2393,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46308.39986123197</v>
+        <v>46307.39549684311</v>
       </c>
       <c r="P29">
-        <v>46308.80859250448</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>28</v>
+        <v>46309.32658556899</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2437,13 +2413,13 @@
         <v>109</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G30">
         <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I30">
         <v>13</v>
@@ -2454,6 +2430,9 @@
       <c r="K30">
         <v>1</v>
       </c>
+      <c r="L30" t="s">
+        <v>111</v>
+      </c>
       <c r="M30" s="4" t="s">
         <v>18</v>
       </c>
@@ -2461,13 +2440,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46307.39549690609</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P30">
-        <v>46308.80859249179</v>
+        <v>46309.32658557613</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2478,28 +2457,31 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>83</v>
+      </c>
+      <c r="F31" t="s">
+        <v>84</v>
       </c>
       <c r="G31">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H31" s="3">
         <v>46322</v>
       </c>
       <c r="I31">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2508,13 +2490,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46307.39549680641</v>
+        <v>46308.39986117012</v>
       </c>
       <c r="P31">
-        <v>46308.80859245299</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>28</v>
+        <v>46309.32658555431</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2525,32 +2507,26 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
       </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
       <c r="G32">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H32" s="3">
-        <v>46322</v>
+        <v>46326</v>
       </c>
       <c r="I32">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="L32" t="s">
-        <v>116</v>
-      </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
       </c>
@@ -2558,13 +2534,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46307.39549684311</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P32">
-        <v>46308.80859246592</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>24</v>
+        <v>46309.3265855467</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2578,22 +2554,25 @@
         <v>117</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
+        <v>106</v>
       </c>
       <c r="G33">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H33" s="3">
-        <v>46322</v>
+        <v>46328</v>
       </c>
       <c r="I33">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J33" t="s">
         <v>118</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" t="s">
         <v>119</v>
@@ -2605,13 +2584,13 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>46307.39549687663</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P33">
-        <v>46308.80859247913</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>28</v>
+        <v>46309.32658553129</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2625,28 +2604,22 @@
         <v>120</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="G34">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H34" s="3">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="I34">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J34" t="s">
         <v>121</v>
       </c>
       <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="L34" t="s">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>18</v>
@@ -2655,13 +2628,13 @@
         <v>18</v>
       </c>
       <c r="O34">
-        <v>46308.39986117012</v>
+        <v>46305.20575257758</v>
       </c>
       <c r="P34">
-        <v>46308.80859243982</v>
+        <v>46309.32658552284</v>
       </c>
       <c r="Q34" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2672,26 +2645,29 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" t="s">
+        <v>57</v>
+      </c>
+      <c r="G35">
+        <v>0.95</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I35">
+        <v>24</v>
+      </c>
+      <c r="J35" t="s">
+        <v>91</v>
+      </c>
+      <c r="K35">
+        <v>4</v>
+      </c>
+      <c r="L35" t="s">
         <v>123</v>
       </c>
-      <c r="E35" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35">
-        <v>0.2</v>
-      </c>
-      <c r="H35" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I35">
-        <v>18</v>
-      </c>
-      <c r="J35" t="s">
-        <v>124</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
       <c r="M35" s="4" t="s">
         <v>18</v>
       </c>
@@ -2699,13 +2675,13 @@
         <v>18</v>
       </c>
       <c r="O35">
-        <v>46300.75884768533</v>
+        <v>46307.39549666931</v>
       </c>
       <c r="P35">
-        <v>46308.80859242669</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>28</v>
+        <v>46309.32658551402</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2716,189 +2692,193 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H36" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I36">
+        <v>24</v>
+      </c>
+      <c r="J36" t="s">
         <v>125</v>
       </c>
-      <c r="E36" t="s">
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36">
+        <v>46307.39549671811</v>
+      </c>
+      <c r="P36">
+        <v>46309.32658549539</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H37" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I37" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K37" s="6">
+        <v>1</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" s="6">
+        <v>46300.75884788632</v>
+      </c>
+      <c r="P37" s="6">
+        <v>46309.32660914837</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36">
-        <v>0.91</v>
-      </c>
-      <c r="H36" s="3">
-        <v>46328</v>
-      </c>
-      <c r="I36">
+      <c r="F38" s="6"/>
+      <c r="G38" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I38" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K38" s="6">
+        <v>1</v>
+      </c>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38" s="6">
+        <v>46300.75884790152</v>
+      </c>
+      <c r="P38" s="6">
+        <v>46309.32659369619</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J36" t="s">
-        <v>126</v>
-      </c>
-      <c r="K36">
-        <v>2</v>
-      </c>
-      <c r="L36" t="s">
-        <v>127</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O36">
-        <v>46308.39986111095</v>
-      </c>
-      <c r="P36">
-        <v>46308.80859240023</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37">
-        <v>0.92</v>
-      </c>
-      <c r="H37" s="3">
-        <v>46332</v>
-      </c>
-      <c r="I37">
-        <v>24</v>
-      </c>
-      <c r="J37" t="s">
-        <v>129</v>
-      </c>
-      <c r="K37">
-        <v>4</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37">
-        <v>46305.20575257758</v>
-      </c>
-      <c r="P37">
-        <v>46308.80859238569</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38">
-        <v>0.95</v>
-      </c>
-      <c r="H38" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I38">
-        <v>25</v>
-      </c>
-      <c r="J38" t="s">
-        <v>101</v>
-      </c>
-      <c r="K38">
-        <v>4</v>
-      </c>
-      <c r="L38" t="s">
-        <v>131</v>
-      </c>
-      <c r="M38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38">
-        <v>46307.39549666931</v>
-      </c>
-      <c r="P38">
-        <v>46308.80859237124</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17">
-      <c r="A39" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H39" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I39">
-        <v>25</v>
-      </c>
-      <c r="J39" t="s">
-        <v>133</v>
-      </c>
-      <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="M39" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O39">
-        <v>46307.39549671811</v>
-      </c>
-      <c r="P39">
-        <v>46308.80859234113</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>24</v>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H39" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I39" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K39" s="6">
+        <v>1</v>
+      </c>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39" s="6">
+        <v>46301.38232480602</v>
+      </c>
+      <c r="P39" s="6">
+        <v>46307.88904467553</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>136</v>
@@ -2917,7 +2897,7 @@
         <v>46307</v>
       </c>
       <c r="I40" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>139</v>
@@ -2938,25 +2918,25 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P40" s="6">
-        <v>46308.80860869765</v>
+        <v>46309.32660917217</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6">
@@ -2966,7 +2946,7 @@
         <v>46307</v>
       </c>
       <c r="I41" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>142</v>
@@ -2985,28 +2965,28 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P41" s="6">
-        <v>46308.8086087364</v>
+        <v>46309.32660919259</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G42" s="6">
         <v>0.93</v>
@@ -3015,7 +2995,7 @@
         <v>46307</v>
       </c>
       <c r="I42" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>144</v>
@@ -3034,25 +3014,25 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P42" s="6">
-        <v>46308.8086087774</v>
+        <v>46309.3266092123</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6">
@@ -3062,7 +3042,7 @@
         <v>46307</v>
       </c>
       <c r="I43" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>146</v>
@@ -3083,25 +3063,25 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P43" s="6">
-        <v>46308.80860872313</v>
+        <v>46309.32660918596</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>148</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6">
@@ -3111,7 +3091,7 @@
         <v>46307</v>
       </c>
       <c r="I44" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>149</v>
@@ -3130,25 +3110,25 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P44" s="6">
-        <v>46308.80860868467</v>
+        <v>46309.3266091652</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>150</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6">
@@ -3158,7 +3138,7 @@
         <v>46307</v>
       </c>
       <c r="I45" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>146</v>
@@ -3179,28 +3159,28 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P45" s="6">
-        <v>46308.80860867112</v>
+        <v>46309.32660915743</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>152</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G46" s="6">
         <v>0.93</v>
@@ -3209,10 +3189,10 @@
         <v>46307</v>
       </c>
       <c r="I46" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="K46" s="6">
         <v>2</v>
@@ -3230,25 +3210,25 @@
         <v>46305.20576106136</v>
       </c>
       <c r="P46" s="6">
-        <v>46308.80860876467</v>
+        <v>46309.3266092056</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>154</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>155</v>
@@ -3260,7 +3240,7 @@
         <v>46306</v>
       </c>
       <c r="I47" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>156</v>
@@ -3279,28 +3259,28 @@
         <v>46300.75885622757</v>
       </c>
       <c r="P47" s="6">
-        <v>46308.80860882727</v>
+        <v>46309.32660923808</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>157</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G48" s="6">
         <v>0.9399999999999999</v>
@@ -3309,7 +3289,7 @@
         <v>46306</v>
       </c>
       <c r="I48" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>158</v>
@@ -3330,18 +3310,18 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P48" s="6">
-        <v>46308.80860880234</v>
+        <v>46309.32660922525</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>160</v>
@@ -3360,7 +3340,7 @@
         <v>46306</v>
       </c>
       <c r="I49" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>163</v>
@@ -3381,25 +3361,25 @@
         <v>46300.7588562628</v>
       </c>
       <c r="P49" s="6">
-        <v>46308.80860883948</v>
+        <v>46309.32660924443</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
@@ -3409,7 +3389,7 @@
         <v>46306</v>
       </c>
       <c r="I50" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>166</v>
@@ -3430,25 +3410,25 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P50" s="6">
-        <v>46308.80860881492</v>
+        <v>46309.32660923177</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>168</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
@@ -3458,7 +3438,7 @@
         <v>46305</v>
       </c>
       <c r="I51" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>169</v>
@@ -3479,18 +3459,18 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P51" s="6">
-        <v>46308.80860887733</v>
+        <v>46309.32660926376</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>171</v>
@@ -3507,7 +3487,7 @@
         <v>46304</v>
       </c>
       <c r="I52" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>173</v>
@@ -3528,25 +3508,25 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P52" s="6">
-        <v>46308.80860890263</v>
+        <v>46309.32660927699</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>175</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>176</v>
@@ -3558,7 +3538,7 @@
         <v>46303</v>
       </c>
       <c r="I53" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>177</v>
@@ -3579,25 +3559,25 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P53" s="6">
-        <v>46308.80861677252</v>
+        <v>46309.32661719847</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>179</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6">
@@ -3607,7 +3587,7 @@
         <v>46302</v>
       </c>
       <c r="I54" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>180</v>
@@ -3626,28 +3606,28 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P54" s="6">
-        <v>46308.80861682777</v>
+        <v>46309.32661722977</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>181</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G55" s="6">
         <v>0.9399999999999999</v>
@@ -3656,7 +3636,7 @@
         <v>46301</v>
       </c>
       <c r="I55" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>182</v>
@@ -3675,18 +3655,18 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P55" s="6">
-        <v>46308.80861687777</v>
+        <v>46309.32661725709</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>183</v>
@@ -3703,7 +3683,7 @@
         <v>46300</v>
       </c>
       <c r="I56" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>185</v>
@@ -3722,28 +3702,28 @@
         <v>46300.75886463693</v>
       </c>
       <c r="P56" s="6">
-        <v>46308.80861688962</v>
+        <v>46309.32661726358</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>186</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G57" s="6">
         <v>0.93</v>
@@ -3752,7 +3732,7 @@
         <v>46300</v>
       </c>
       <c r="I57" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J57" s="6" t="s">
         <v>187</v>
@@ -3771,25 +3751,25 @@
         <v>46300.75886465221</v>
       </c>
       <c r="P57" s="6">
-        <v>46308.80861690162</v>
+        <v>46309.32661726989</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>188</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6">
@@ -3799,7 +3779,7 @@
         <v>46299</v>
       </c>
       <c r="I58" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>146</v>
@@ -3820,28 +3800,28 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P58" s="6">
-        <v>46308.80861692582</v>
+        <v>46309.32661728276</v>
       </c>
       <c r="Q58" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>190</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G59" s="6">
         <v>0.93</v>
@@ -3850,7 +3830,7 @@
         <v>46299</v>
       </c>
       <c r="I59" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J59" s="6" t="s">
         <v>191</v>
@@ -3869,206 +3849,14 @@
         <v>46300.75886468366</v>
       </c>
       <c r="P59" s="6">
-        <v>46308.80861693832</v>
+        <v>46309.32661728934</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17">
-      <c r="A60" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H60" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I60" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K60" s="6">
-        <v>1</v>
-      </c>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O60" s="6">
-        <v>46300.75886471466</v>
-      </c>
-      <c r="P60" s="6">
-        <v>46308.80862494551</v>
-      </c>
-      <c r="Q60" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17">
-      <c r="A61" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G61" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H61" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I61" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="K61" s="6">
-        <v>1</v>
-      </c>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N61" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O61" s="6">
-        <v>46300.75886472998</v>
-      </c>
-      <c r="P61" s="6">
-        <v>46307.88906095151</v>
-      </c>
-      <c r="Q61" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17">
-      <c r="A62" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="H62" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I62" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="K62" s="6">
-        <v>1</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O62" s="6">
-        <v>46300.75886474836</v>
-      </c>
-      <c r="P62" s="6">
-        <v>46308.80862495991</v>
-      </c>
-      <c r="Q62" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17">
-      <c r="A63" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H63" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I63" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K63" s="6">
-        <v>1</v>
-      </c>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O63" s="6">
-        <v>46300.75886479358</v>
-      </c>
-      <c r="P63" s="6">
-        <v>46308.80861700077</v>
-      </c>
-      <c r="Q63" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q63"/>
+  <autoFilter ref="A1:Q59"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4186,14 +3974,6 @@
     <hyperlink ref="N58" r:id="rId114"/>
     <hyperlink ref="M59" r:id="rId115"/>
     <hyperlink ref="N59" r:id="rId116"/>
-    <hyperlink ref="M60" r:id="rId117"/>
-    <hyperlink ref="N60" r:id="rId118"/>
-    <hyperlink ref="M61" r:id="rId119"/>
-    <hyperlink ref="N61" r:id="rId120"/>
-    <hyperlink ref="M62" r:id="rId121"/>
-    <hyperlink ref="N62" r:id="rId122"/>
-    <hyperlink ref="M63" r:id="rId123"/>
-    <hyperlink ref="N63" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4201,7 +3981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4280,22 +4060,22 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
       </c>
       <c r="H2" s="3">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -4307,13 +4087,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75884790152</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P2" s="2">
-        <v>46308.80860069162</v>
+        <v>46309.32659368968</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4324,22 +4104,22 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
       </c>
       <c r="H3" s="3">
-        <v>46308</v>
+        <v>46314</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4351,13 +4131,13 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46301.38232480602</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P3" s="2">
-        <v>46307.88904467553</v>
+        <v>46309.32659363702</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4368,22 +4148,22 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -4395,13 +4175,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46308.39987059968</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P4" s="2">
-        <v>46308.8086006791</v>
+        <v>46309.32659361638</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4415,22 +4195,25 @@
         <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
       </c>
       <c r="H5" s="3">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="I5" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>61</v>
       </c>
       <c r="K5" s="2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
@@ -4439,41 +4222,41 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884775587</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P5" s="2">
-        <v>46308.80860057846</v>
+        <v>46309.32659358825</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="2" customFormat="1">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6">
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
-        <v>46315</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="2">
+        <v>46317</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
@@ -4482,14 +4265,14 @@
       <c r="N6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O6" s="2">
-        <v>46300.75884772457</v>
-      </c>
-      <c r="P6" s="2">
-        <v>46308.80860053844</v>
+      <c r="O6">
+        <v>46301.38232468421</v>
+      </c>
+      <c r="P6">
+        <v>46309.32659358035</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -4500,28 +4283,28 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46316</v>
+        <v>46319</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4530,13 +4313,13 @@
         <v>18</v>
       </c>
       <c r="O7">
-        <v>46302.26841507768</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P7">
-        <v>46308.80860048686</v>
+        <v>46309.32658562508</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4547,22 +4330,22 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G8">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -4574,13 +4357,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46301.38232468421</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P8">
-        <v>46308.80860047329</v>
+        <v>46309.32658561136</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4594,13 +4377,13 @@
         <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G9">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I9">
         <v>11</v>
@@ -4609,10 +4392,7 @@
         <v>98</v>
       </c>
       <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
@@ -4621,13 +4401,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46307.39549700746</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P9">
-        <v>46308.808592568</v>
+        <v>46309.32658558995</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4638,22 +4418,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4665,13 +4445,13 @@
         <v>18</v>
       </c>
       <c r="O10">
-        <v>46307.3954970362</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P10">
-        <v>46308.8085925427</v>
+        <v>46309.32658558308</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -4682,25 +4462,28 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G11">
         <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L11" t="s">
+        <v>103</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
@@ -4709,13 +4492,13 @@
         <v>18</v>
       </c>
       <c r="O11">
-        <v>46308.39986123197</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P11">
-        <v>46308.80859250448</v>
+        <v>46309.32658556175</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -4729,13 +4512,13 @@
         <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>0.2</v>
       </c>
       <c r="H12" s="3">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I12">
         <v>13</v>
@@ -4746,6 +4529,9 @@
       <c r="K12">
         <v>1</v>
       </c>
+      <c r="L12" t="s">
+        <v>111</v>
+      </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
       </c>
@@ -4753,13 +4539,13 @@
         <v>18</v>
       </c>
       <c r="O12">
-        <v>46307.39549690609</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P12">
-        <v>46308.80859249179</v>
+        <v>46309.32658557613</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -4770,28 +4556,25 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G13">
         <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46322</v>
+        <v>46326</v>
       </c>
       <c r="I13">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4800,119 +4583,122 @@
         <v>18</v>
       </c>
       <c r="O13">
-        <v>46307.39549680641</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P13">
-        <v>46308.80859245299</v>
+        <v>46309.3265855467</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14">
+      <c r="A14" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6">
         <v>0.2</v>
       </c>
-      <c r="H14" s="3">
-        <v>46322</v>
-      </c>
-      <c r="I14">
-        <v>14</v>
-      </c>
-      <c r="J14" t="s">
-        <v>118</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14" t="s">
-        <v>119</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14">
-        <v>46307.39549687663</v>
-      </c>
-      <c r="P14">
-        <v>46308.80859247913</v>
+      <c r="H14" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I14" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="6">
+        <v>46300.75884790152</v>
+      </c>
+      <c r="P14" s="6">
+        <v>46309.32659369619</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15">
+      <c r="A15" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6">
         <v>0.2</v>
       </c>
-      <c r="H15" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I15">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>124</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P15">
-        <v>46308.80859242669</v>
+      <c r="H15" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I15" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" s="6">
+        <v>46301.38232480602</v>
+      </c>
+      <c r="P15" s="6">
+        <v>46307.88904467553</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -4922,7 +4708,7 @@
         <v>46307</v>
       </c>
       <c r="I16" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>142</v>
@@ -4941,25 +4727,25 @@
         <v>46300.7588479478</v>
       </c>
       <c r="P16" s="6">
-        <v>46308.8086087364</v>
+        <v>46309.32660919259</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6">
@@ -4969,7 +4755,7 @@
         <v>46307</v>
       </c>
       <c r="I17" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>146</v>
@@ -4990,25 +4776,25 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P17" s="6">
-        <v>46308.80860872313</v>
+        <v>46309.32660918596</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>179</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6">
@@ -5018,7 +4804,7 @@
         <v>46302</v>
       </c>
       <c r="I18" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>180</v>
@@ -5037,25 +4823,25 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P18" s="6">
-        <v>46308.80861682777</v>
+        <v>46309.32661722977</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>188</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6">
@@ -5065,7 +4851,7 @@
         <v>46299</v>
       </c>
       <c r="I19" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>146</v>
@@ -5086,157 +4872,14 @@
         <v>46300.75886466862</v>
       </c>
       <c r="P19" s="6">
-        <v>46308.80861692582</v>
+        <v>46309.32661728276</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I20" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K20" s="6">
-        <v>1</v>
-      </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46300.75886471466</v>
-      </c>
-      <c r="P20" s="6">
-        <v>46308.80862494551</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H21" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I21" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="K21" s="6">
-        <v>1</v>
-      </c>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="6">
-        <v>46300.75886472998</v>
-      </c>
-      <c r="P21" s="6">
-        <v>46307.88906095151</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="A22" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H22" s="6">
-        <v>46298</v>
-      </c>
-      <c r="I22" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K22" s="6">
-        <v>1</v>
-      </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="6">
-        <v>46300.75886479358</v>
-      </c>
-      <c r="P22" s="6">
-        <v>46308.80861700077</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q22"/>
+  <autoFilter ref="A1:Q19"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -5274,12 +4917,6 @@
     <hyperlink ref="N18" r:id="rId34"/>
     <hyperlink ref="M19" r:id="rId35"/>
     <hyperlink ref="N19" r:id="rId36"/>
-    <hyperlink ref="M20" r:id="rId37"/>
-    <hyperlink ref="N20" r:id="rId38"/>
-    <hyperlink ref="M21" r:id="rId39"/>
-    <hyperlink ref="N21" r:id="rId40"/>
-    <hyperlink ref="M22" r:id="rId41"/>
-    <hyperlink ref="N22" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5287,7 +4924,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5297,51 +4934,51 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B2">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D2">
         <v>193</v>
@@ -5353,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5370,13 +5007,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B3">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D3">
         <v>193</v>
@@ -5385,16 +5022,16 @@
         <v>3844</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -5405,48 +5042,48 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B4">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D4">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>381</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B5">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D5">
         <v>192</v>
@@ -5455,13 +5092,13 @@
         <v>3838</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5475,28 +5112,28 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B6">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D6">
         <v>192</v>
       </c>
       <c r="E6">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>369</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5505,18 +5142,18 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B7">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D7">
         <v>192</v>
@@ -5545,13 +5182,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B8">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D8">
         <v>192</v>
@@ -5563,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5580,13 +5217,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B9">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D9">
         <v>192</v>
@@ -5615,13 +5252,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B10">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D10">
         <v>192</v>
@@ -5630,16 +5267,16 @@
         <v>3826</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -5650,48 +5287,48 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B11">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D11">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E11">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B12">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D12">
         <v>191</v>
@@ -5720,13 +5357,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B13">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C13" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D13">
         <v>191</v>
@@ -5738,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5755,13 +5392,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B14">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D14">
         <v>191</v>
@@ -5770,16 +5407,16 @@
         <v>3820</v>
       </c>
       <c r="F14">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H14">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -5790,48 +5427,48 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B15">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E15">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G15">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B16">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -5840,13 +5477,13 @@
         <v>160</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5855,18 +5492,18 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B17">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -5875,21 +5512,56 @@
         <v>160</v>
       </c>
       <c r="F17">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H17">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B18">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C18" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>160</v>
+      </c>
+      <c r="F18">
+        <v>157</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <v>132</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="220">
   <si>
     <t>Priority</t>
   </si>
@@ -241,6 +241,12 @@
     <t>kuldeep tank</t>
   </si>
   <si>
+    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chandra Kumar Jain</t>
+  </si>
+  <si>
     <t>Sion Panvel Tollways Private Limited</t>
   </si>
   <si>
@@ -298,6 +304,18 @@
     <t>Mr. Bijay Murmuria</t>
   </si>
   <si>
+    <t>SMO FERRO ALLOYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Rajesh Lohia</t>
+  </si>
+  <si>
+    <t>ALCOB INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRASHANT KHATAVKAR</t>
+  </si>
+  <si>
     <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
   </si>
   <si>
@@ -367,6 +385,48 @@
     <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
   </si>
   <si>
+    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Abhit Kumar Singh</t>
+  </si>
+  <si>
+    <t>KUTE SONS DAIRYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ritesh R Mahajan</t>
+  </si>
+  <si>
+    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chirag Rajendra Kumar Shah</t>
+  </si>
+  <si>
+    <t>Form G published on 13th October 2026.</t>
+  </si>
+  <si>
+    <t>STUTI COMTRADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
+  </si>
+  <si>
+    <t>2nd Form G.</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
+  </si>
+  <si>
     <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
   </si>
   <si>
@@ -427,9 +487,6 @@
     <t>Mrs. Megha Agrawal</t>
   </si>
   <si>
-    <t>Not in latest IBBI listing - verify with RP</t>
-  </si>
-  <si>
     <t>TECHNOFAB ENGINEERING LIMITED</t>
   </si>
   <si>
@@ -482,15 +539,6 @@
   </si>
   <si>
     <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
   </si>
   <si>
     <t>A.P.J. LABORATORIES LIMITED</t>
@@ -1036,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1145,7 +1193,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P2" s="2">
-        <v>46309.32659368968</v>
+        <v>46309.72496064098</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>22</v>
@@ -1192,7 +1240,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P3" s="2">
-        <v>46309.32659368317</v>
+        <v>46309.72496062564</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>27</v>
@@ -1239,7 +1287,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P4" s="2">
-        <v>46309.32659367001</v>
+        <v>46309.72496058067</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>27</v>
@@ -1283,7 +1331,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P5" s="2">
-        <v>46309.32659366349</v>
+        <v>46309.72496059525</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>27</v>
@@ -1330,7 +1378,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P6" s="2">
-        <v>46309.32659365699</v>
+        <v>46309.72496056608</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>27</v>
@@ -1377,7 +1425,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P7" s="2">
-        <v>46309.32659365023</v>
+        <v>46309.72496055074</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>27</v>
@@ -1424,7 +1472,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P8" s="2">
-        <v>46309.32659364375</v>
+        <v>46309.72496053454</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>27</v>
@@ -1471,7 +1519,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P9" s="2">
-        <v>46309.3265936305</v>
+        <v>46309.72495190653</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>27</v>
@@ -1515,7 +1563,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P10" s="2">
-        <v>46309.32659363702</v>
+        <v>46309.72495193577</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>22</v>
@@ -1559,7 +1607,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P11" s="2">
-        <v>46309.32659362342</v>
+        <v>46309.72495192118</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>27</v>
@@ -1603,7 +1651,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P12" s="2">
-        <v>46309.32659361638</v>
+        <v>46309.72495189186</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>22</v>
@@ -1650,7 +1698,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P13" s="2">
-        <v>46309.32659360963</v>
+        <v>46309.72495187746</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>27</v>
@@ -1697,7 +1745,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P14" s="2">
-        <v>46309.32659358825</v>
+        <v>46309.72495186308</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>22</v>
@@ -1744,7 +1792,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P15" s="2">
-        <v>46309.32659360249</v>
+        <v>46309.72495183346</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>27</v>
@@ -1788,7 +1836,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P16">
-        <v>46309.32659358035</v>
+        <v>46309.7249518034</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>22</v>
@@ -1835,7 +1883,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P17">
-        <v>46309.32659357139</v>
+        <v>46309.72495181867</v>
       </c>
       <c r="Q17" t="s">
         <v>27</v>
@@ -1852,19 +1900,16 @@
         <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H18" s="3">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="I18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J18" t="s">
         <v>74</v>
@@ -1872,9 +1917,6 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="L18" t="s">
-        <v>75</v>
-      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1882,13 +1924,13 @@
         <v>18</v>
       </c>
       <c r="O18">
-        <v>46305.20575267453</v>
+        <v>46309.72495178872</v>
       </c>
       <c r="P18">
-        <v>46309.32658564518</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>27</v>
+        <v>46309.72495178875</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1899,13 +1941,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
       </c>
       <c r="G19">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="H19" s="3">
         <v>46318</v>
@@ -1914,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -1929,10 +1974,10 @@
         <v>18</v>
       </c>
       <c r="O19">
-        <v>46305.20575269723</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P19">
-        <v>46309.32658563174</v>
+        <v>46309.72495174378</v>
       </c>
       <c r="Q19" t="s">
         <v>27</v>
@@ -1946,13 +1991,13 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G20">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H20" s="3">
         <v>46318</v>
@@ -1961,10 +2006,10 @@
         <v>9</v>
       </c>
       <c r="J20" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="s">
         <v>81</v>
@@ -1976,10 +2021,10 @@
         <v>18</v>
       </c>
       <c r="O20">
-        <v>46308.39986132324</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P20">
-        <v>46309.32658563834</v>
+        <v>46309.72495175941</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
@@ -1996,28 +2041,25 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="G21">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H21" s="3">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="K21">
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -2026,10 +2068,10 @@
         <v>18</v>
       </c>
       <c r="O21">
-        <v>46305.20575263901</v>
+        <v>46308.39986132324</v>
       </c>
       <c r="P21">
-        <v>46309.32658561814</v>
+        <v>46309.72495172822</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
@@ -2043,13 +2085,16 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>85</v>
+      </c>
+      <c r="F22" t="s">
+        <v>86</v>
       </c>
       <c r="G22">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H22" s="3">
         <v>46319</v>
@@ -2058,13 +2103,13 @@
         <v>10</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K22">
         <v>2</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2073,13 +2118,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46307.39549700746</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P22">
-        <v>46309.32658562508</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>22</v>
+        <v>46309.72495158993</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2090,7 +2135,7 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
@@ -2105,11 +2150,14 @@
         <v>10</v>
       </c>
       <c r="J23" t="s">
+        <v>90</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23" t="s">
         <v>91</v>
       </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
       </c>
@@ -2117,10 +2165,10 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46307.3954970362</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P23">
-        <v>46309.32658561136</v>
+        <v>46309.72495162148</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>22</v>
@@ -2137,25 +2185,22 @@
         <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G24">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H24" s="3">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="I24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" t="s">
         <v>93</v>
       </c>
       <c r="K24">
-        <v>2</v>
-      </c>
-      <c r="L24" t="s">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2164,13 +2209,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46307.3954969447</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P24">
-        <v>46309.32658560448</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>27</v>
+        <v>46309.724951606</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2181,25 +2226,25 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25">
+        <v>0.95</v>
+      </c>
+      <c r="H25" s="3">
+        <v>46319</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25" t="s">
         <v>95</v>
       </c>
-      <c r="E25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25">
-        <v>0.91</v>
-      </c>
-      <c r="H25" s="3">
-        <v>46320</v>
-      </c>
-      <c r="I25">
-        <v>11</v>
-      </c>
-      <c r="J25" t="s">
-        <v>96</v>
-      </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2208,10 +2253,10 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46307.39549697415</v>
+        <v>46309.72495168629</v>
       </c>
       <c r="P25">
-        <v>46309.32658559736</v>
+        <v>46309.72495168629</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
@@ -2225,7 +2270,7 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -2234,13 +2279,13 @@
         <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="I26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2252,10 +2297,10 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46308.39986123197</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P26">
-        <v>46309.32658558995</v>
+        <v>46309.72495171531</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>22</v>
@@ -2269,26 +2314,29 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27">
+        <v>0.92</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46320</v>
+      </c>
+      <c r="I27">
+        <v>11</v>
+      </c>
+      <c r="J27" t="s">
         <v>99</v>
       </c>
-      <c r="E27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27">
-        <v>0.2</v>
-      </c>
-      <c r="H27" s="3">
-        <v>46321</v>
-      </c>
-      <c r="I27">
-        <v>12</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27" t="s">
         <v>100</v>
       </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
       </c>
@@ -2296,13 +2344,13 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46307.39549690609</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P27">
-        <v>46309.32658558308</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>22</v>
+        <v>46309.72494274736</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2316,25 +2364,22 @@
         <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G28">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H28" s="3">
-        <v>46322</v>
+        <v>46320</v>
       </c>
       <c r="I28">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J28" t="s">
         <v>102</v>
       </c>
       <c r="K28">
-        <v>2</v>
-      </c>
-      <c r="L28" t="s">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
@@ -2343,13 +2388,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46307.39549680641</v>
+        <v>46307.39549697415</v>
       </c>
       <c r="P28">
-        <v>46309.32658556175</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>22</v>
+        <v>46309.72494273229</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2360,32 +2405,26 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>46320</v>
+      </c>
+      <c r="I29">
+        <v>11</v>
+      </c>
+      <c r="J29" t="s">
         <v>104</v>
       </c>
-      <c r="E29" t="s">
-        <v>105</v>
-      </c>
-      <c r="F29" t="s">
-        <v>106</v>
-      </c>
-      <c r="G29">
-        <v>0.91</v>
-      </c>
-      <c r="H29" s="3">
-        <v>46322</v>
-      </c>
-      <c r="I29">
-        <v>13</v>
-      </c>
-      <c r="J29" t="s">
-        <v>107</v>
-      </c>
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="L29" t="s">
-        <v>108</v>
-      </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2393,13 +2432,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46307.39549684311</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P29">
-        <v>46309.32658556899</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>27</v>
+        <v>46309.72494271736</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2410,7 +2449,7 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
@@ -2419,20 +2458,17 @@
         <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="I30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J30" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="L30" t="s">
-        <v>111</v>
-      </c>
       <c r="M30" s="4" t="s">
         <v>18</v>
       </c>
@@ -2440,10 +2476,10 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46307.39549687663</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P30">
-        <v>46309.32658557613</v>
+        <v>46309.72494270258</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>22</v>
@@ -2457,16 +2493,13 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
-      </c>
-      <c r="F31" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H31" s="3">
         <v>46322</v>
@@ -2475,13 +2508,13 @@
         <v>13</v>
       </c>
       <c r="J31" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2490,13 +2523,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46308.39986117012</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P31">
-        <v>46309.32658555431</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>27</v>
+        <v>46309.72494267265</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2507,26 +2540,32 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>111</v>
+      </c>
+      <c r="F32" t="s">
+        <v>112</v>
       </c>
       <c r="G32">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H32" s="3">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="I32">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
+      <c r="L32" t="s">
+        <v>114</v>
+      </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
       </c>
@@ -2534,13 +2573,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46300.75884768533</v>
+        <v>46307.39549684311</v>
       </c>
       <c r="P32">
-        <v>46309.3265855467</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>22</v>
+        <v>46309.72494265691</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2551,32 +2590,29 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33">
+        <v>0.2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I33">
+        <v>13</v>
+      </c>
+      <c r="J33" t="s">
+        <v>116</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
         <v>117</v>
       </c>
-      <c r="E33" t="s">
-        <v>105</v>
-      </c>
-      <c r="F33" t="s">
-        <v>106</v>
-      </c>
-      <c r="G33">
-        <v>0.91</v>
-      </c>
-      <c r="H33" s="3">
-        <v>46328</v>
-      </c>
-      <c r="I33">
-        <v>19</v>
-      </c>
-      <c r="J33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K33">
-        <v>2</v>
-      </c>
-      <c r="L33" t="s">
-        <v>119</v>
-      </c>
       <c r="M33" s="4" t="s">
         <v>18</v>
       </c>
@@ -2584,13 +2620,13 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>46308.39986111095</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P33">
-        <v>46309.32658553129</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>27</v>
+        <v>46309.72494264157</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2601,26 +2637,32 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34">
+        <v>0.93</v>
+      </c>
+      <c r="H34" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I34">
+        <v>13</v>
+      </c>
+      <c r="J34" t="s">
+        <v>119</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
         <v>120</v>
       </c>
-      <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34">
-        <v>0.92</v>
-      </c>
-      <c r="H34" s="3">
-        <v>46332</v>
-      </c>
-      <c r="I34">
-        <v>23</v>
-      </c>
-      <c r="J34" t="s">
-        <v>121</v>
-      </c>
-      <c r="K34">
-        <v>4</v>
-      </c>
       <c r="M34" s="4" t="s">
         <v>18</v>
       </c>
@@ -2628,10 +2670,10 @@
         <v>18</v>
       </c>
       <c r="O34">
-        <v>46305.20575257758</v>
+        <v>46308.39986117012</v>
       </c>
       <c r="P34">
-        <v>46309.32658552284</v>
+        <v>46309.72494268755</v>
       </c>
       <c r="Q34" t="s">
         <v>27</v>
@@ -2645,28 +2687,25 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
+      <c r="J35" t="s">
         <v>122</v>
       </c>
-      <c r="E35" t="s">
-        <v>57</v>
-      </c>
-      <c r="G35">
-        <v>0.95</v>
-      </c>
-      <c r="H35" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I35">
-        <v>24</v>
-      </c>
-      <c r="J35" t="s">
-        <v>91</v>
-      </c>
       <c r="K35">
-        <v>4</v>
-      </c>
-      <c r="L35" t="s">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>18</v>
@@ -2675,13 +2714,13 @@
         <v>18</v>
       </c>
       <c r="O35">
-        <v>46307.39549666931</v>
+        <v>46309.72494256633</v>
       </c>
       <c r="P35">
-        <v>46309.32658551402</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>27</v>
+        <v>46309.72494256635</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2692,462 +2731,449 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36">
+        <v>0.2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I36">
+        <v>14</v>
+      </c>
+      <c r="J36" t="s">
         <v>124</v>
       </c>
-      <c r="E36" t="s">
-        <v>77</v>
-      </c>
-      <c r="G36">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H36" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I36">
-        <v>24</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36">
+        <v>46309.72494259723</v>
+      </c>
+      <c r="P36">
+        <v>46309.72494259725</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
         <v>125</v>
       </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O36">
-        <v>46307.39549671811</v>
-      </c>
-      <c r="P36">
-        <v>46309.32658549539</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="6" t="s">
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37">
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I37">
+        <v>14</v>
+      </c>
+      <c r="J37" t="s">
         <v>126</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="M37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37">
+        <v>46309.72494262765</v>
+      </c>
+      <c r="P37">
+        <v>46309.72494262768</v>
+      </c>
+      <c r="Q37" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
         <v>128</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G37" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H37" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I37" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J37" s="6" t="s">
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>46324</v>
+      </c>
+      <c r="I38">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s">
         <v>129</v>
       </c>
-      <c r="K37" s="6">
-        <v>1</v>
-      </c>
-      <c r="L37" s="6" t="s">
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
         <v>130</v>
       </c>
-      <c r="M37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="6">
-        <v>46300.75884788632</v>
-      </c>
-      <c r="P37" s="6">
-        <v>46309.32660914837</v>
-      </c>
-      <c r="Q37" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H38" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I38" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K38" s="6">
-        <v>1</v>
-      </c>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38" s="6">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P38" s="6">
-        <v>46309.32659369619</v>
+      <c r="M38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38">
+        <v>46309.72494253634</v>
+      </c>
+      <c r="P38">
+        <v>46309.72494253636</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="A39" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39">
+        <v>0.89</v>
+      </c>
+      <c r="H39" s="3">
+        <v>46325</v>
+      </c>
+      <c r="I39">
+        <v>16</v>
+      </c>
+      <c r="J39" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6" t="s">
+      <c r="K39">
+        <v>2</v>
+      </c>
+      <c r="L39" t="s">
+        <v>134</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39">
+        <v>46309.72494249383</v>
+      </c>
+      <c r="P39">
+        <v>46309.72494249386</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="E40" t="s">
         <v>20</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6">
+      <c r="G40">
         <v>0.2</v>
       </c>
-      <c r="H39" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I39" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K39" s="6">
-        <v>1</v>
-      </c>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O39" s="6">
-        <v>46301.38232480602</v>
-      </c>
-      <c r="P39" s="6">
-        <v>46307.88904467553</v>
-      </c>
-      <c r="Q39" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="H40" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I40">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s">
         <v>136</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6" t="s">
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P40">
+        <v>46309.72494233132</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
         <v>137</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="E41" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41">
+        <v>0.91</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46328</v>
+      </c>
+      <c r="I41">
+        <v>19</v>
+      </c>
+      <c r="J41" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="H40" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I40" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J40" s="6" t="s">
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="L41" t="s">
         <v>139</v>
       </c>
-      <c r="K40" s="6">
-        <v>1</v>
-      </c>
-      <c r="L40" s="6" t="s">
+      <c r="M41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O41">
+        <v>46308.39986111095</v>
+      </c>
+      <c r="P41">
+        <v>46309.72494231576</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
         <v>140</v>
       </c>
-      <c r="M40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O40" s="6">
-        <v>46300.75884793277</v>
-      </c>
-      <c r="P40" s="6">
-        <v>46309.32660917217</v>
-      </c>
-      <c r="Q40" s="6" t="s">
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42">
+        <v>0.92</v>
+      </c>
+      <c r="H42" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I42">
+        <v>23</v>
+      </c>
+      <c r="J42" t="s">
+        <v>141</v>
+      </c>
+      <c r="K42">
+        <v>4</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O42">
+        <v>46305.20575257758</v>
+      </c>
+      <c r="P42">
+        <v>46309.7249422997</v>
+      </c>
+      <c r="Q42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H41" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I41" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J41" s="6" t="s">
+    <row r="43" spans="1:17">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
         <v>142</v>
       </c>
-      <c r="K41" s="6">
-        <v>1</v>
-      </c>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O41" s="6">
-        <v>46300.7588479478</v>
-      </c>
-      <c r="P41" s="6">
-        <v>46309.32660919259</v>
-      </c>
-      <c r="Q41" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17">
-      <c r="A42" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="E43" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43">
+        <v>0.95</v>
+      </c>
+      <c r="H43" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I43">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
+        <v>93</v>
+      </c>
+      <c r="K43">
+        <v>4</v>
+      </c>
+      <c r="L43" t="s">
         <v>143</v>
       </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G42" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="H42" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I42" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J42" s="6" t="s">
+      <c r="M43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O43">
+        <v>46307.39549666931</v>
+      </c>
+      <c r="P43">
+        <v>46309.72494225264</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
         <v>144</v>
       </c>
-      <c r="K42" s="6">
-        <v>1</v>
-      </c>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O42" s="6">
-        <v>46300.75884796329</v>
-      </c>
-      <c r="P42" s="6">
-        <v>46309.3266092123</v>
-      </c>
-      <c r="Q42" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17">
-      <c r="A43" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="E44" t="s">
+        <v>79</v>
+      </c>
+      <c r="G44">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H44" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I44">
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
         <v>145</v>
       </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H43" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I43" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K43" s="6">
-        <v>1</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O43" s="6">
-        <v>46300.75884799581</v>
-      </c>
-      <c r="P43" s="6">
-        <v>46309.32660918596</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17">
-      <c r="A44" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H44" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I44" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K44" s="6">
-        <v>1</v>
-      </c>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O44" s="6">
-        <v>46300.75885617639</v>
-      </c>
-      <c r="P44" s="6">
-        <v>46309.3266091652</v>
-      </c>
-      <c r="Q44" s="6" t="s">
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44">
+        <v>46307.39549671811</v>
+      </c>
+      <c r="P44">
+        <v>46309.72494228279</v>
+      </c>
+      <c r="Q44" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F45" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="G45" s="6">
         <v>0.91</v>
       </c>
       <c r="H45" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I45" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K45" s="6">
         <v>1</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>18</v>
@@ -3156,10 +3182,10 @@
         <v>18</v>
       </c>
       <c r="O45" s="6">
-        <v>46300.75885619673</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P45" s="6">
-        <v>46309.32660915743</v>
+        <v>46309.72496065593</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>27</v>
@@ -3167,39 +3193,35 @@
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H46" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I46" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="K46" s="6">
-        <v>2</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>153</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L46" s="6"/>
       <c r="M46" s="6" t="s">
         <v>18</v>
       </c>
@@ -3207,43 +3229,41 @@
         <v>18</v>
       </c>
       <c r="O46" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P46" s="6">
-        <v>46309.3266092056</v>
-      </c>
-      <c r="Q46" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496068516</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>155</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="6">
-        <v>0.89</v>
+        <v>0.2</v>
       </c>
       <c r="H47" s="6">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="I47" s="6">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
@@ -3256,40 +3276,40 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46300.75885622757</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P47" s="6">
-        <v>46309.32660923808</v>
-      </c>
-      <c r="Q47" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496067041</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="G48" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H48" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I48" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>158</v>
@@ -3307,10 +3327,10 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75885624527</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P48" s="6">
-        <v>46309.32660922525</v>
+        <v>46309.72496069972</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>27</v>
@@ -3318,39 +3338,35 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>160</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H49" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I49" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G49" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H49" s="6">
-        <v>46306</v>
-      </c>
-      <c r="I49" s="6">
-        <v>-3</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="K49" s="6">
         <v>1</v>
       </c>
-      <c r="L49" s="6" t="s">
-        <v>164</v>
-      </c>
+      <c r="L49" s="6"/>
       <c r="M49" s="6" t="s">
         <v>18</v>
       </c>
@@ -3358,48 +3374,48 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.7588562628</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P49" s="6">
-        <v>46309.32660924443</v>
-      </c>
-      <c r="Q49" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496071397</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="G50" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H50" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I50" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K50" s="6">
         <v>1</v>
       </c>
-      <c r="L50" s="6" t="s">
-        <v>167</v>
-      </c>
+      <c r="L50" s="6"/>
       <c r="M50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3407,10 +3423,10 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75885627908</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P50" s="6">
-        <v>46309.32660923177</v>
+        <v>46309.72497154441</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>27</v>
@@ -3418,36 +3434,36 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H51" s="6">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="I51" s="6">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K51" s="6">
         <v>1</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>18</v>
@@ -3456,48 +3472,46 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46300.75885633306</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P51" s="6">
-        <v>46309.32660926376</v>
-      </c>
-      <c r="Q51" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496072845</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H52" s="6">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="I52" s="6">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K52" s="6">
         <v>1</v>
       </c>
-      <c r="L52" s="6" t="s">
-        <v>174</v>
-      </c>
+      <c r="L52" s="6"/>
       <c r="M52" s="6" t="s">
         <v>18</v>
       </c>
@@ -3505,10 +3519,10 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.7588563655</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P52" s="6">
-        <v>46309.32660927699</v>
+        <v>46309.72496081555</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>27</v>
@@ -3516,38 +3530,36 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>176</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H53" s="6">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="I53" s="6">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="K53" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>18</v>
@@ -3556,10 +3568,10 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.7588564207</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P53" s="6">
-        <v>46309.32661719847</v>
+        <v>46309.72496075697</v>
       </c>
       <c r="Q53" s="6" t="s">
         <v>27</v>
@@ -3567,35 +3579,39 @@
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="G54" s="6">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H54" s="6">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="I54" s="6">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="K54" s="6">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="M54" s="6" t="s">
         <v>18</v>
       </c>
@@ -3603,24 +3619,24 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.75885647022</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P54" s="6">
-        <v>46309.32661722977</v>
-      </c>
-      <c r="Q54" s="5" t="s">
-        <v>22</v>
+        <v>46309.72496078632</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
@@ -3633,18 +3649,20 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="H55" s="6">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="I55" s="6">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="K55" s="6">
-        <v>2</v>
-      </c>
-      <c r="L55" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="M55" s="6" t="s">
         <v>18</v>
       </c>
@@ -3652,10 +3670,10 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75885649968</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P55" s="6">
-        <v>46309.32661725709</v>
+        <v>46309.72497156039</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>27</v>
@@ -3663,35 +3681,39 @@
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F56" s="6"/>
+        <v>177</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="G56" s="6">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H56" s="6">
-        <v>46300</v>
+        <v>46306</v>
       </c>
       <c r="I56" s="6">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
       </c>
-      <c r="L56" s="6"/>
+      <c r="L56" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="M56" s="6" t="s">
         <v>18</v>
       </c>
@@ -3699,10 +3721,10 @@
         <v>18</v>
       </c>
       <c r="O56" s="6">
-        <v>46300.75886463693</v>
+        <v>46300.7588562628</v>
       </c>
       <c r="P56" s="6">
-        <v>46309.32661726358</v>
+        <v>46309.72497157565</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>27</v>
@@ -3710,37 +3732,37 @@
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H57" s="6">
-        <v>46300</v>
+        <v>46306</v>
       </c>
       <c r="I57" s="6">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="K57" s="6">
         <v>1</v>
       </c>
-      <c r="L57" s="6"/>
+      <c r="L57" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="M57" s="6" t="s">
         <v>18</v>
       </c>
@@ -3748,10 +3770,10 @@
         <v>18</v>
       </c>
       <c r="O57" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P57" s="6">
-        <v>46309.32661726989</v>
+        <v>46309.72497158999</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>27</v>
@@ -3759,36 +3781,36 @@
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H58" s="6">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="I58" s="6">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>18</v>
@@ -3797,48 +3819,48 @@
         <v>18</v>
       </c>
       <c r="O58" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P58" s="6">
-        <v>46309.32661728276</v>
-      </c>
-      <c r="Q58" s="5" t="s">
-        <v>22</v>
+        <v>46309.7249716339</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F59" s="6"/>
       <c r="G59" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H59" s="6">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="I59" s="6">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K59" s="6">
         <v>1</v>
       </c>
-      <c r="L59" s="6"/>
+      <c r="L59" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="M59" s="6" t="s">
         <v>18</v>
       </c>
@@ -3846,17 +3868,358 @@
         <v>18</v>
       </c>
       <c r="O59" s="6">
-        <v>46300.75886468366</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P59" s="6">
-        <v>46309.32661728934</v>
+        <v>46309.72497167712</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="60" spans="1:17">
+      <c r="A60" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G60" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H60" s="6">
+        <v>46303</v>
+      </c>
+      <c r="I60" s="6">
+        <v>-6</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K60" s="6">
+        <v>2</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O60" s="6">
+        <v>46300.7588564207</v>
+      </c>
+      <c r="P60" s="6">
+        <v>46309.72497172017</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H61" s="6">
+        <v>46302</v>
+      </c>
+      <c r="I61" s="6">
+        <v>-7</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O61" s="6">
+        <v>46300.75885647022</v>
+      </c>
+      <c r="P61" s="6">
+        <v>46309.72497174865</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G62" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H62" s="6">
+        <v>46301</v>
+      </c>
+      <c r="I62" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="K62" s="6">
+        <v>2</v>
+      </c>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O62" s="6">
+        <v>46300.75885649968</v>
+      </c>
+      <c r="P62" s="6">
+        <v>46309.72497177708</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H63" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I63" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1</v>
+      </c>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O63" s="6">
+        <v>46300.75886463693</v>
+      </c>
+      <c r="P63" s="6">
+        <v>46309.7249804657</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
+      <c r="A64" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G64" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H64" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I64" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K64" s="6">
+        <v>1</v>
+      </c>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O64" s="6">
+        <v>46300.75886465221</v>
+      </c>
+      <c r="P64" s="6">
+        <v>46309.72497182001</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
+      <c r="A65" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H65" s="6">
+        <v>46299</v>
+      </c>
+      <c r="I65" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O65" s="6">
+        <v>46300.75886466862</v>
+      </c>
+      <c r="P65" s="6">
+        <v>46309.7249804969</v>
+      </c>
+      <c r="Q65" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G66" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H66" s="6">
+        <v>46299</v>
+      </c>
+      <c r="I66" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O66" s="6">
+        <v>46300.75886468366</v>
+      </c>
+      <c r="P66" s="6">
+        <v>46309.724980512</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q59"/>
+  <autoFilter ref="A1:Q66"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -3974,6 +4337,20 @@
     <hyperlink ref="N58" r:id="rId114"/>
     <hyperlink ref="M59" r:id="rId115"/>
     <hyperlink ref="N59" r:id="rId116"/>
+    <hyperlink ref="M60" r:id="rId117"/>
+    <hyperlink ref="N60" r:id="rId118"/>
+    <hyperlink ref="M61" r:id="rId119"/>
+    <hyperlink ref="N61" r:id="rId120"/>
+    <hyperlink ref="M62" r:id="rId121"/>
+    <hyperlink ref="N62" r:id="rId122"/>
+    <hyperlink ref="M63" r:id="rId123"/>
+    <hyperlink ref="N63" r:id="rId124"/>
+    <hyperlink ref="M64" r:id="rId125"/>
+    <hyperlink ref="N64" r:id="rId126"/>
+    <hyperlink ref="M65" r:id="rId127"/>
+    <hyperlink ref="N65" r:id="rId128"/>
+    <hyperlink ref="M66" r:id="rId129"/>
+    <hyperlink ref="N66" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3981,7 +4358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4090,7 +4467,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P2" s="2">
-        <v>46309.32659368968</v>
+        <v>46309.72496064098</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>22</v>
@@ -4134,7 +4511,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P3" s="2">
-        <v>46309.32659363702</v>
+        <v>46309.72495193577</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>22</v>
@@ -4178,7 +4555,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P4" s="2">
-        <v>46309.32659361638</v>
+        <v>46309.72495189186</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>22</v>
@@ -4225,7 +4602,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P5" s="2">
-        <v>46309.32659358825</v>
+        <v>46309.72495186308</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>22</v>
@@ -4269,7 +4646,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P6">
-        <v>46309.32659358035</v>
+        <v>46309.7249518034</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>22</v>
@@ -4283,7 +4660,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -4292,19 +4669,16 @@
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4313,10 +4687,10 @@
         <v>18</v>
       </c>
       <c r="O7">
-        <v>46307.39549700746</v>
+        <v>46309.72495178872</v>
       </c>
       <c r="P7">
-        <v>46309.32658562508</v>
+        <v>46309.72495178875</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>22</v>
@@ -4330,7 +4704,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -4345,11 +4719,14 @@
         <v>10</v>
       </c>
       <c r="J8" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8" t="s">
         <v>91</v>
       </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -4357,10 +4734,10 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46307.3954970362</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P8">
-        <v>46309.32658561136</v>
+        <v>46309.72495162148</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>22</v>
@@ -4374,7 +4751,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -4383,13 +4760,13 @@
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4401,10 +4778,10 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46308.39986123197</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P9">
-        <v>46309.32658558995</v>
+        <v>46309.724951606</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>22</v>
@@ -4418,7 +4795,7 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4427,13 +4804,13 @@
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46321</v>
+        <v>46319</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4445,10 +4822,10 @@
         <v>18</v>
       </c>
       <c r="O10">
-        <v>46307.39549690609</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P10">
-        <v>46309.32658558308</v>
+        <v>46309.72495171531</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>22</v>
@@ -4462,7 +4839,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -4471,19 +4848,16 @@
         <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46322</v>
+        <v>46320</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11" t="s">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
@@ -4492,10 +4866,10 @@
         <v>18</v>
       </c>
       <c r="O11">
-        <v>46307.39549680641</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46309.32658556175</v>
+        <v>46309.72494271736</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>22</v>
@@ -4509,7 +4883,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -4518,20 +4892,17 @@
         <v>0.2</v>
       </c>
       <c r="H12" s="3">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" t="s">
-        <v>111</v>
-      </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
       </c>
@@ -4539,10 +4910,10 @@
         <v>18</v>
       </c>
       <c r="O12">
-        <v>46307.39549687663</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46309.32658557613</v>
+        <v>46309.72494270258</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>22</v>
@@ -4556,7 +4927,7 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -4565,16 +4936,19 @@
         <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="I13">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>109</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4583,303 +4957,576 @@
         <v>18</v>
       </c>
       <c r="O13">
-        <v>46300.75884768533</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46309.3265855467</v>
+        <v>46309.72494267265</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6">
+      <c r="G14">
         <v>0.2</v>
       </c>
-      <c r="H14" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I14" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K14" s="6">
-        <v>1</v>
-      </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O14" s="6">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P14" s="6">
-        <v>46309.32659369619</v>
+      <c r="H14" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
+      <c r="J14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14">
+        <v>46307.39549687663</v>
+      </c>
+      <c r="P14">
+        <v>46309.72494264157</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="s">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6">
+      <c r="G15">
         <v>0.2</v>
       </c>
-      <c r="H15" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I15" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="6">
-        <v>1</v>
-      </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O15" s="6">
-        <v>46301.38232480602</v>
-      </c>
-      <c r="P15" s="6">
-        <v>46307.88904467553</v>
+      <c r="H15" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
+      <c r="J15" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15">
+        <v>46309.72494256633</v>
+      </c>
+      <c r="P15">
+        <v>46309.72494256635</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6">
+      <c r="G16">
         <v>0.2</v>
       </c>
-      <c r="H16" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I16" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K16" s="6">
-        <v>1</v>
-      </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46300.7588479478</v>
-      </c>
-      <c r="P16" s="6">
-        <v>46309.32660919259</v>
+      <c r="H16" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I16">
+        <v>14</v>
+      </c>
+      <c r="J16" t="s">
+        <v>124</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16">
+        <v>46309.72494259723</v>
+      </c>
+      <c r="P16">
+        <v>46309.72494259725</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="6" t="s">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I17">
+        <v>14</v>
+      </c>
+      <c r="J17" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H17" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I17" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K17" s="6">
-        <v>1</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46300.75884799581</v>
-      </c>
-      <c r="P17" s="6">
-        <v>46309.32660918596</v>
+      <c r="M17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17">
+        <v>46309.72494262765</v>
+      </c>
+      <c r="P17">
+        <v>46309.72494262768</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6" t="s">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6">
+      <c r="G18">
         <v>0.2</v>
       </c>
-      <c r="H18" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I18" s="6">
-        <v>-7</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K18" s="6">
-        <v>1</v>
-      </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O18" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P18" s="6">
-        <v>46309.32661722977</v>
+      <c r="H18" s="3">
+        <v>46324</v>
+      </c>
+      <c r="I18">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>129</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>130</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18">
+        <v>46309.72494253634</v>
+      </c>
+      <c r="P18">
+        <v>46309.72494253636</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6" t="s">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6">
+      <c r="G19">
         <v>0.2</v>
       </c>
-      <c r="H19" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I19" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K19" s="6">
-        <v>1</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="6">
-        <v>46300.75886466862</v>
-      </c>
-      <c r="P19" s="6">
-        <v>46309.32661728276</v>
+      <c r="H19" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I19">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19">
+        <v>46300.75884768533</v>
+      </c>
+      <c r="P19">
+        <v>46309.72494233132</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I20" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="6">
+        <v>46300.75884790152</v>
+      </c>
+      <c r="P20" s="6">
+        <v>46309.72496068516</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I21" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="6">
+        <v>46301.38232480602</v>
+      </c>
+      <c r="P21" s="6">
+        <v>46309.72496067041</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I22" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K22" s="6">
+        <v>1</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="6">
+        <v>46300.7588479478</v>
+      </c>
+      <c r="P22" s="6">
+        <v>46309.72496071397</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I23" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="6">
+        <v>46300.75884799581</v>
+      </c>
+      <c r="P23" s="6">
+        <v>46309.72496072845</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="6">
+        <v>46302</v>
+      </c>
+      <c r="I24" s="6">
+        <v>-7</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K24" s="6">
+        <v>1</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="6">
+        <v>46300.75885647022</v>
+      </c>
+      <c r="P24" s="6">
+        <v>46309.72497174865</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H25" s="6">
+        <v>46299</v>
+      </c>
+      <c r="I25" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="6">
+        <v>46300.75886466862</v>
+      </c>
+      <c r="P25" s="6">
+        <v>46309.7249804969</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q25"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4917,6 +5564,18 @@
     <hyperlink ref="N18" r:id="rId34"/>
     <hyperlink ref="M19" r:id="rId35"/>
     <hyperlink ref="N19" r:id="rId36"/>
+    <hyperlink ref="M20" r:id="rId37"/>
+    <hyperlink ref="N20" r:id="rId38"/>
+    <hyperlink ref="M21" r:id="rId39"/>
+    <hyperlink ref="N21" r:id="rId40"/>
+    <hyperlink ref="M22" r:id="rId41"/>
+    <hyperlink ref="N22" r:id="rId42"/>
+    <hyperlink ref="M23" r:id="rId43"/>
+    <hyperlink ref="N23" r:id="rId44"/>
+    <hyperlink ref="M24" r:id="rId45"/>
+    <hyperlink ref="N24" r:id="rId46"/>
+    <hyperlink ref="M25" r:id="rId47"/>
+    <hyperlink ref="N25" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4924,7 +5583,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -4934,86 +5593,86 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B2">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D2">
         <v>193</v>
       </c>
       <c r="E2">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B3">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D3">
         <v>193</v>
@@ -5025,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5042,13 +5701,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B4">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D4">
         <v>193</v>
@@ -5057,16 +5716,16 @@
         <v>3844</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -5077,48 +5736,48 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B5">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D5">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E5">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>381</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B6">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D6">
         <v>192</v>
@@ -5127,13 +5786,13 @@
         <v>3838</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5147,28 +5806,28 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B7">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D7">
         <v>192</v>
       </c>
       <c r="E7">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>369</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5177,18 +5836,18 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B8">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D8">
         <v>192</v>
@@ -5217,13 +5876,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B9">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D9">
         <v>192</v>
@@ -5235,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5252,13 +5911,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B10">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D10">
         <v>192</v>
@@ -5287,13 +5946,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B11">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D11">
         <v>192</v>
@@ -5302,16 +5961,16 @@
         <v>3826</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -5322,48 +5981,48 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B12">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C12" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D12">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E12">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B13">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D13">
         <v>191</v>
@@ -5392,13 +6051,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B14">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D14">
         <v>191</v>
@@ -5410,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5427,13 +6086,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B15">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D15">
         <v>191</v>
@@ -5442,16 +6101,16 @@
         <v>3820</v>
       </c>
       <c r="F15">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H15">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -5462,48 +6121,48 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B16">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E16">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G16">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B17">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C17" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -5512,13 +6171,13 @@
         <v>160</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5527,18 +6186,18 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B18">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -5547,21 +6206,56 @@
         <v>160</v>
       </c>
       <c r="F18">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H18">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B19">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C19" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>160</v>
+      </c>
+      <c r="F19">
+        <v>157</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+      <c r="H19">
+        <v>132</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -13,14 +13,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="224">
   <si>
     <t>Priority</t>
   </si>
@@ -79,393 +79,432 @@
     <t>Open</t>
   </si>
   <si>
+    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Tripti Agarwal</t>
+  </si>
+  <si>
+    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>Not in latest IBBI listing - verify with RP</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chandra Kumar Jain</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SMO FERRO ALLOYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Rajesh Lohia</t>
+  </si>
+  <si>
+    <t>ALCOB INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRASHANT KHATAVKAR</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Kamal Agarwal</t>
+  </si>
+  <si>
+    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
+  </si>
+  <si>
+    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Abhit Kumar Singh</t>
+  </si>
+  <si>
+    <t>KUTE SONS DAIRYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ritesh R Mahajan</t>
+  </si>
+  <si>
+    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chirag Rajendra Kumar Shah</t>
+  </si>
+  <si>
+    <t>Form G published on 13th October 2026.</t>
+  </si>
+  <si>
+    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Hotel / Hospitality</t>
+  </si>
+  <si>
+    <t>Hotels / Resorts</t>
+  </si>
+  <si>
+    <t>Harsh Kumar Arora</t>
+  </si>
+  <si>
+    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
+  </si>
+  <si>
+    <t>STUTI COMTRADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
+  </si>
+  <si>
+    <t>2nd Form G.</t>
+  </si>
+  <si>
+    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shaikh Nafis Anjum</t>
+  </si>
+  <si>
+    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>JRA INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Parshva Manoj Shah</t>
+  </si>
+  <si>
+    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>KEW PRECISION PARTS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
     <t>Mr. Shashi Bhushan Prasad</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Tripti Agarwal</t>
-  </si>
-  <si>
-    <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
-  </si>
-  <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chandra Kumar Jain</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>The addendum to form G was issued on 10th October, 2026.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SMO FERRO ALLOYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Rajesh Lohia</t>
-  </si>
-  <si>
-    <t>ALCOB INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRASHANT KHATAVKAR</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>SUNSHINE FASTECH LIMITED</t>
-  </si>
-  <si>
-    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
-  </si>
-  <si>
-    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dev Vrat Rana</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
-  </si>
-  <si>
-    <t>SWADESH GREEN INFRA LIMITED</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Niraj Kumar</t>
-  </si>
-  <si>
-    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
-  </si>
-  <si>
-    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bishwa Ranjan Chatterjee</t>
-  </si>
-  <si>
-    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
-  </si>
-  <si>
-    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Kamal Agarwal</t>
-  </si>
-  <si>
-    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
-  </si>
-  <si>
-    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Abhit Kumar Singh</t>
-  </si>
-  <si>
-    <t>KUTE SONS DAIRYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ritesh R Mahajan</t>
-  </si>
-  <si>
-    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chirag Rajendra Kumar Shah</t>
-  </si>
-  <si>
-    <t>Form G published on 13th October 2026.</t>
-  </si>
-  <si>
-    <t>STUTI COMTRADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
-  </si>
-  <si>
-    <t>2nd Form G.</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>JRA INFRASTRUCTURE LIMITED</t>
-  </si>
-  <si>
-    <t>Parshva Manoj Shah</t>
-  </si>
-  <si>
-    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
-  </si>
-  <si>
-    <t>Resonance Paper Mill Private Limited</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
   </si>
   <si>
@@ -550,21 +589,6 @@
     <t>No Fixed Assets are available, except one disputed and contiguous piece of land at Village Ambwala, Nwada Road Tehsil Paonta Sahib, Distt Sirmaur, Himachal Pradesh, India, 173025</t>
   </si>
   <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>At present, the Corporate Debtor is not operational and not a going concern. Revenue from Operation for the financial year ended 31.03.2025 is ?44,98,79,958.90</t>
-  </si>
-  <si>
     <t>LOG 9 MATERIALS SCIENTIFIC PRIVATE LIMITED</t>
   </si>
   <si>
@@ -632,18 +656,6 @@
   </si>
   <si>
     <t>Mr. Pratim Bayal</t>
-  </si>
-  <si>
-    <t>OM SHRI SHUBH LABH AGRITECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Present status :1 Unit closed &amp; one operational under lease as per information available with RP.</t>
-  </si>
-  <si>
-    <t>TITLE DEVELOPERS LLP</t>
-  </si>
-  <si>
-    <t>Palak Swapnil Desai</t>
   </si>
   <si>
     <t>Started</t>
@@ -1169,10 +1181,10 @@
         <v>20</v>
       </c>
       <c r="G2" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H2" s="3">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -1183,6 +1195,9 @@
       <c r="K2" s="2">
         <v>1</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
       </c>
@@ -1190,13 +1205,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46308.39987059968</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P2" s="2">
-        <v>46309.72496064098</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707892606</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -1207,43 +1222,43 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H3" s="3">
+        <v>46312</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.75884779022</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46310.31707885113</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46310</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.75884787029</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46309.72496062564</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1260,13 +1275,13 @@
         <v>29</v>
       </c>
       <c r="G4" s="2">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="H4" s="3">
         <v>46312</v>
       </c>
       <c r="I4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>30</v>
@@ -1274,9 +1289,6 @@
       <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1284,13 +1296,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884779022</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P4" s="2">
-        <v>46309.72496058067</v>
+        <v>46310.31707889567</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1301,10 +1313,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2">
         <v>0.93</v>
@@ -1313,14 +1325,17 @@
         <v>46312</v>
       </c>
       <c r="I5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
+      <c r="L5" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1328,13 +1343,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884780569</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P5" s="2">
-        <v>46309.72496059525</v>
+        <v>46310.3170788808</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1345,19 +1360,19 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H6" s="3">
         <v>46312</v>
       </c>
       <c r="I6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>36</v>
@@ -1375,13 +1390,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P6" s="2">
-        <v>46309.72496056608</v>
+        <v>46310.31707886575</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1401,7 +1416,7 @@
         <v>0.91</v>
       </c>
       <c r="H7" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I7" s="2">
         <v>3</v>
@@ -1410,7 +1425,7 @@
         <v>40</v>
       </c>
       <c r="K7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>41</v>
@@ -1422,13 +1437,13 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75884783743</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P7" s="2">
-        <v>46309.72496055074</v>
+        <v>46310.31707883633</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -1444,23 +1459,23 @@
       <c r="E8" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="G8" s="2">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H8" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I8" s="2">
         <v>4</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" s="2">
-        <v>3</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -1469,13 +1484,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46302.26841519317</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P8" s="2">
-        <v>46309.72496053454</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>27</v>
+        <v>46309.72495190653</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1486,22 +1501,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G9" s="2">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="3">
         <v>46314</v>
       </c>
       <c r="I9" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>49</v>
@@ -1516,13 +1528,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75884774033</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P9" s="2">
-        <v>46309.72495190653</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>27</v>
+        <v>46310.3170788213</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1533,22 +1545,22 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H10" s="3">
         <v>46314</v>
       </c>
       <c r="I10" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -1560,13 +1572,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75884775587</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P10" s="2">
-        <v>46309.72495193577</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707880468</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1577,22 +1589,22 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I11" s="2">
         <v>5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -1604,13 +1616,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.7588477715</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P11" s="2">
-        <v>46309.72495192118</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>27</v>
+        <v>46310.31707061251</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1621,26 +1633,29 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G12" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" s="3">
         <v>46315</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
+      <c r="L12" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
       </c>
@@ -1648,13 +1663,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46300.75884772457</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P12" s="2">
-        <v>46309.72495189186</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707059883</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1665,28 +1680,28 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I13" s="2">
         <v>6</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -1695,13 +1710,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46307.39550534703</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P13" s="2">
-        <v>46309.72495187746</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>27</v>
+        <v>46310.3170705706</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1712,28 +1727,28 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H14" s="3">
         <v>46316</v>
       </c>
       <c r="I14" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -1742,13 +1757,13 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46302.26841507768</v>
+        <v>46307.39549714451</v>
       </c>
       <c r="P14" s="2">
-        <v>46309.72495186308</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707058447</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="2" customFormat="1">
@@ -1759,28 +1774,25 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I15" s="2">
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K15" s="2">
-        <v>2</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
@@ -1789,41 +1801,44 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46307.39549714451</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P15" s="2">
-        <v>46309.72495183346</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16">
-        <v>0.2</v>
+        <v>46310.31707052737</v>
+      </c>
+      <c r="Q15" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="2" customFormat="1">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.9399999999999999</v>
       </c>
       <c r="H16" s="3">
         <v>46317</v>
       </c>
-      <c r="I16">
-        <v>8</v>
-      </c>
-      <c r="J16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16">
+      <c r="I16" s="2">
+        <v>7</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="2">
         <v>1</v>
       </c>
       <c r="M16" s="4" t="s">
@@ -1832,45 +1847,42 @@
       <c r="N16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O16">
-        <v>46301.38232468421</v>
-      </c>
-      <c r="P16">
-        <v>46309.7249518034</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17">
-        <v>0.9399999999999999</v>
+      <c r="O16" s="2">
+        <v>46302.26841501552</v>
+      </c>
+      <c r="P16" s="2">
+        <v>46310.31707054178</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="2" customFormat="1">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.2</v>
       </c>
       <c r="H17" s="3">
         <v>46317</v>
       </c>
-      <c r="I17">
-        <v>8</v>
-      </c>
-      <c r="J17" t="s">
-        <v>72</v>
-      </c>
-      <c r="K17">
+      <c r="I17" s="2">
+        <v>7</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" s="2">
         <v>1</v>
       </c>
       <c r="M17" s="4" t="s">
@@ -1879,14 +1891,14 @@
       <c r="N17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O17">
-        <v>46302.26841501552</v>
-      </c>
-      <c r="P17">
-        <v>46309.72495181867</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>27</v>
+      <c r="O17" s="2">
+        <v>46309.72495178872</v>
+      </c>
+      <c r="P17" s="2">
+        <v>46310.31707051331</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1897,26 +1909,32 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H18" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I18">
         <v>8</v>
       </c>
       <c r="J18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
+      <c r="L18" t="s">
+        <v>76</v>
+      </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
       </c>
@@ -1924,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="O18">
-        <v>46309.72495178872</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P18">
-        <v>46309.72495178875</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707047093</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1941,31 +1959,28 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G19">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="3">
         <v>46318</v>
       </c>
       <c r="I19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -1974,13 +1989,13 @@
         <v>18</v>
       </c>
       <c r="O19">
-        <v>46305.20575267453</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P19">
-        <v>46309.72495174378</v>
+        <v>46310.31707048484</v>
       </c>
       <c r="Q19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1991,28 +2006,28 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G20">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H20" s="3">
         <v>46318</v>
       </c>
       <c r="I20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J20" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -2021,13 +2036,13 @@
         <v>18</v>
       </c>
       <c r="O20">
-        <v>46305.20575269723</v>
+        <v>46308.39986132324</v>
       </c>
       <c r="P20">
-        <v>46309.72495175941</v>
+        <v>46310.31707049905</v>
       </c>
       <c r="Q20" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -2038,28 +2053,31 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>84</v>
+      </c>
+      <c r="F21" t="s">
+        <v>85</v>
       </c>
       <c r="G21">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H21" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I21">
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="K21">
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -2068,13 +2086,13 @@
         <v>18</v>
       </c>
       <c r="O21">
-        <v>46308.39986132324</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P21">
-        <v>46309.72495172822</v>
+        <v>46310.31707039779</v>
       </c>
       <c r="Q21" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2085,31 +2103,28 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="G22">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H22" s="3">
         <v>46319</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K22">
         <v>2</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2118,13 +2133,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46305.20575263901</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P22">
-        <v>46309.72495158993</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>27</v>
+        <v>46310.31707042759</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2135,10 +2150,10 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G23">
         <v>0.2</v>
@@ -2147,16 +2162,13 @@
         <v>46319</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K23">
-        <v>2</v>
-      </c>
-      <c r="L23" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
@@ -2165,13 +2177,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46307.39549700746</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P23">
-        <v>46309.72495162148</v>
+        <v>46310.31707041276</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2182,25 +2194,25 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H24" s="3">
         <v>46319</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2209,13 +2221,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46307.3954970362</v>
+        <v>46309.72495168629</v>
       </c>
       <c r="P24">
-        <v>46309.724951606</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707045649</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2226,25 +2238,25 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G25">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="3">
         <v>46319</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2253,13 +2265,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46309.72495168629</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P25">
-        <v>46309.72495168629</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>27</v>
+        <v>46310.31707034108</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2270,25 +2282,28 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="F26" t="s">
+        <v>99</v>
       </c>
       <c r="G26">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H26" s="3">
         <v>46319</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2297,13 +2312,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46309.72495171529</v>
+        <v>46310.31707038325</v>
       </c>
       <c r="P26">
-        <v>46309.72495171531</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>22</v>
+        <v>46310.31707038327</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2314,10 +2329,10 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G27">
         <v>0.92</v>
@@ -2326,16 +2341,16 @@
         <v>46320</v>
       </c>
       <c r="I27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
       <c r="L27" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2347,10 +2362,10 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P27">
-        <v>46309.72494274736</v>
+        <v>46310.31706154611</v>
       </c>
       <c r="Q27" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2361,10 +2376,10 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G28">
         <v>0.91</v>
@@ -2373,10 +2388,10 @@
         <v>46320</v>
       </c>
       <c r="I28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2391,10 +2406,10 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P28">
-        <v>46309.72494273229</v>
+        <v>46310.31706153003</v>
       </c>
       <c r="Q28" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2405,10 +2420,10 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G29">
         <v>0.2</v>
@@ -2417,10 +2432,10 @@
         <v>46320</v>
       </c>
       <c r="I29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2435,10 +2450,10 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P29">
-        <v>46309.72494271736</v>
+        <v>46310.31707032494</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2449,10 +2464,10 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G30">
         <v>0.2</v>
@@ -2461,10 +2476,10 @@
         <v>46321</v>
       </c>
       <c r="I30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J30" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2479,10 +2494,10 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P30">
-        <v>46309.72494270258</v>
+        <v>46310.31706151488</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2493,10 +2508,10 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G31">
         <v>0.2</v>
@@ -2505,16 +2520,16 @@
         <v>46322</v>
       </c>
       <c r="I31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K31">
         <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2526,10 +2541,10 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P31">
-        <v>46309.72494267265</v>
+        <v>46310.31706145219</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2540,13 +2555,13 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G32">
         <v>0.91</v>
@@ -2555,16 +2570,16 @@
         <v>46322</v>
       </c>
       <c r="I32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J32" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
@@ -2576,10 +2591,10 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P32">
-        <v>46309.72494265691</v>
+        <v>46310.3170614677</v>
       </c>
       <c r="Q32" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2590,10 +2605,10 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G33">
         <v>0.2</v>
@@ -2602,16 +2617,16 @@
         <v>46322</v>
       </c>
       <c r="I33">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J33" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K33">
         <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>18</v>
@@ -2623,10 +2638,10 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P33">
-        <v>46309.72494264157</v>
+        <v>46310.31706150002</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2637,13 +2652,13 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" t="s">
         <v>85</v>
-      </c>
-      <c r="F34" t="s">
-        <v>86</v>
       </c>
       <c r="G34">
         <v>0.93</v>
@@ -2652,16 +2667,16 @@
         <v>46322</v>
       </c>
       <c r="I34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J34" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K34">
         <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>18</v>
@@ -2673,10 +2688,10 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P34">
-        <v>46309.72494268755</v>
+        <v>46310.31706148342</v>
       </c>
       <c r="Q34" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2687,10 +2702,10 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G35">
         <v>0.2</v>
@@ -2699,10 +2714,10 @@
         <v>46323</v>
       </c>
       <c r="I35">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J35" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2717,10 +2732,10 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P35">
-        <v>46309.72494256635</v>
+        <v>46310.31706140641</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2731,10 +2746,10 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G36">
         <v>0.2</v>
@@ -2743,10 +2758,10 @@
         <v>46323</v>
       </c>
       <c r="I36">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -2761,10 +2776,10 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P36">
-        <v>46309.72494259725</v>
+        <v>46310.31706142161</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2775,10 +2790,10 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G37">
         <v>0.2</v>
@@ -2787,16 +2802,16 @@
         <v>46323</v>
       </c>
       <c r="I37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J37" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>18</v>
@@ -2808,10 +2823,10 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P37">
-        <v>46309.72494262768</v>
+        <v>46310.31706143728</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2822,28 +2837,31 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
+        <v>133</v>
       </c>
       <c r="G38">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H38" s="3">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I38">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J38" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K38">
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>18</v>
@@ -2852,13 +2870,13 @@
         <v>18</v>
       </c>
       <c r="O38">
-        <v>46309.72494253634</v>
+        <v>46310.31706138982</v>
       </c>
       <c r="P38">
-        <v>46309.72494253636</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>22</v>
+        <v>46310.31706138986</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2869,31 +2887,28 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="G39">
-        <v>0.89</v>
+        <v>0.2</v>
       </c>
       <c r="H39" s="3">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="I39">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>18</v>
@@ -2902,13 +2917,13 @@
         <v>18</v>
       </c>
       <c r="O39">
-        <v>46309.72494249383</v>
+        <v>46309.72494253634</v>
       </c>
       <c r="P39">
-        <v>46309.72494249386</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>27</v>
+        <v>46310.3170613514</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2919,26 +2934,29 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G40">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H40" s="3">
-        <v>46326</v>
+        <v>46324</v>
       </c>
       <c r="I40">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
+      <c r="L40" t="s">
+        <v>141</v>
+      </c>
       <c r="M40" s="4" t="s">
         <v>18</v>
       </c>
@@ -2946,13 +2964,13 @@
         <v>18</v>
       </c>
       <c r="O40">
-        <v>46300.75884768533</v>
+        <v>46310.31706133292</v>
       </c>
       <c r="P40">
-        <v>46309.72494233132</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>22</v>
+        <v>46310.31706133294</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2963,31 +2981,31 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="G41">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H41" s="3">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="I41">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J41" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K41">
         <v>2</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M41" s="4" t="s">
         <v>18</v>
@@ -2996,13 +3014,13 @@
         <v>18</v>
       </c>
       <c r="O41">
-        <v>46308.39986111095</v>
+        <v>46309.72494249383</v>
       </c>
       <c r="P41">
-        <v>46309.72494231576</v>
+        <v>46310.31706117826</v>
       </c>
       <c r="Q41" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -3013,25 +3031,25 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G42">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H42" s="3">
-        <v>46332</v>
+        <v>46326</v>
       </c>
       <c r="I42">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J42" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>18</v>
@@ -3040,13 +3058,13 @@
         <v>18</v>
       </c>
       <c r="O42">
-        <v>46305.20575257758</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P42">
-        <v>46309.7249422997</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>27</v>
+        <v>46310.31706114814</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -3057,28 +3075,31 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>114</v>
+      </c>
+      <c r="F43" t="s">
+        <v>115</v>
       </c>
       <c r="G43">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H43" s="3">
-        <v>46333</v>
+        <v>46328</v>
       </c>
       <c r="I43">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L43" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>18</v>
@@ -3087,13 +3108,13 @@
         <v>18</v>
       </c>
       <c r="O43">
-        <v>46307.39549666931</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P43">
-        <v>46309.72494225264</v>
+        <v>46310.31706113207</v>
       </c>
       <c r="Q43" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -3104,166 +3125,159 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="G44">
+        <v>0.92</v>
+      </c>
+      <c r="H44" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I44">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>152</v>
+      </c>
+      <c r="K44">
+        <v>4</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44">
+        <v>46305.20575257758</v>
+      </c>
+      <c r="P44">
+        <v>46310.31706111562</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G45">
+        <v>0.95</v>
+      </c>
+      <c r="H45" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I45">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>92</v>
+      </c>
+      <c r="K45">
+        <v>4</v>
+      </c>
+      <c r="L45" t="s">
+        <v>154</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45">
+        <v>46307.39549666931</v>
+      </c>
+      <c r="P45">
+        <v>46310.31706109887</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E46" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H46" s="3">
         <v>46333</v>
       </c>
-      <c r="I44">
-        <v>24</v>
-      </c>
-      <c r="J44" t="s">
-        <v>145</v>
-      </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O44">
+      <c r="I46">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
+        <v>156</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46">
         <v>46307.39549671811</v>
       </c>
-      <c r="P44">
-        <v>46309.72494228279</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17">
-      <c r="A45" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G45" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H45" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I45" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K45" s="6">
-        <v>1</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O45" s="6">
-        <v>46300.75884788632</v>
-      </c>
-      <c r="P45" s="6">
-        <v>46309.72496065593</v>
-      </c>
-      <c r="Q45" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
-      <c r="A46" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H46" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I46" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="K46" s="6">
-        <v>1</v>
-      </c>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O46" s="6">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P46" s="6">
-        <v>46309.72496068516</v>
-      </c>
-      <c r="Q46" s="5" t="s">
-        <v>22</v>
+      <c r="P46">
+        <v>46310.31706106838</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6">
         <v>0.2</v>
       </c>
       <c r="H47" s="6">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I47" s="6">
         <v>-1</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K47" s="6">
         <v>1</v>
@@ -3276,49 +3290,49 @@
         <v>18</v>
       </c>
       <c r="O47" s="6">
-        <v>46301.38232480602</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P47" s="6">
-        <v>46309.72496067041</v>
+        <v>46310.31707894053</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="G48" s="6">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="H48" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I48" s="6">
         <v>-2</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K48" s="6">
         <v>1</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>18</v>
@@ -3327,41 +3341,41 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75884793277</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P48" s="6">
-        <v>46309.72496069972</v>
+        <v>46310.31707895547</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6">
         <v>0.2</v>
       </c>
       <c r="H49" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I49" s="6">
         <v>-2</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K49" s="6">
         <v>1</v>
@@ -3374,43 +3388,41 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.7588479478</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P49" s="6">
-        <v>46309.72496071397</v>
+        <v>46310.31707898439</v>
       </c>
       <c r="Q49" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I50" s="6">
         <v>-2</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K50" s="6">
         <v>1</v>
@@ -3423,47 +3435,49 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75884796329</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P50" s="6">
-        <v>46309.72497154441</v>
-      </c>
-      <c r="Q50" s="6" t="s">
-        <v>27</v>
+        <v>46310.31707896989</v>
+      </c>
+      <c r="Q50" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="6"/>
+        <v>169</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="G51" s="6">
-        <v>0.2</v>
+        <v>0.88</v>
       </c>
       <c r="H51" s="6">
         <v>46307</v>
       </c>
       <c r="I51" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="K51" s="6">
         <v>1</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>18</v>
@@ -3472,41 +3486,41 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46300.75884799581</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P51" s="6">
-        <v>46309.72496072845</v>
-      </c>
-      <c r="Q51" s="5" t="s">
-        <v>22</v>
+        <v>46310.31708858236</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H52" s="6">
         <v>46307</v>
       </c>
       <c r="I52" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K52" s="6">
         <v>1</v>
@@ -3519,48 +3533,48 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.75885617639</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P52" s="6">
-        <v>46309.72496081555</v>
-      </c>
-      <c r="Q52" s="6" t="s">
-        <v>27</v>
+        <v>46310.31708860076</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F53" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="G53" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H53" s="6">
         <v>46307</v>
       </c>
       <c r="I53" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="K53" s="6">
         <v>1</v>
       </c>
-      <c r="L53" s="6" t="s">
-        <v>170</v>
-      </c>
+      <c r="L53" s="6"/>
       <c r="M53" s="6" t="s">
         <v>18</v>
       </c>
@@ -3568,49 +3582,47 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.75885619673</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P53" s="6">
-        <v>46309.72496075697</v>
+        <v>46310.31707907124</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F54" s="6"/>
       <c r="G54" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H54" s="6">
         <v>46307</v>
       </c>
       <c r="I54" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="K54" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>18</v>
@@ -3619,50 +3631,46 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P54" s="6">
-        <v>46309.72496078632</v>
-      </c>
-      <c r="Q54" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496072845</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F55" s="6"/>
       <c r="G55" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H55" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I55" s="6">
         <v>-3</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K55" s="6">
         <v>1</v>
       </c>
-      <c r="L55" s="6" t="s">
-        <v>175</v>
-      </c>
+      <c r="L55" s="6"/>
       <c r="M55" s="6" t="s">
         <v>18</v>
       </c>
@@ -3670,49 +3678,47 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75885624527</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P55" s="6">
-        <v>46309.72497156039</v>
+        <v>46310.31707899934</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>178</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F56" s="6"/>
       <c r="G56" s="6">
         <v>0.91</v>
       </c>
       <c r="H56" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I56" s="6">
         <v>-3</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>18</v>
@@ -3721,47 +3727,49 @@
         <v>18</v>
       </c>
       <c r="O56" s="6">
-        <v>46300.7588562628</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P56" s="6">
-        <v>46309.72497157565</v>
-      </c>
-      <c r="Q56" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496075697</v>
+      </c>
+      <c r="Q56" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F57" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="G57" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H57" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I57" s="6">
         <v>-3</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="K57" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>18</v>
@@ -3770,47 +3778,49 @@
         <v>18</v>
       </c>
       <c r="O57" s="6">
-        <v>46300.75885627908</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P57" s="6">
-        <v>46309.72497158999</v>
-      </c>
-      <c r="Q57" s="6" t="s">
-        <v>27</v>
+        <v>46309.72496078632</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F58" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="G58" s="6">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H58" s="6">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I58" s="6">
         <v>-4</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>18</v>
@@ -3819,47 +3829,47 @@
         <v>18</v>
       </c>
       <c r="O58" s="6">
-        <v>46300.75885633306</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P58" s="6">
-        <v>46309.7249716339</v>
+        <v>46310.31708867416</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H59" s="6">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I59" s="6">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K59" s="6">
         <v>1</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>18</v>
@@ -3868,46 +3878,44 @@
         <v>18</v>
       </c>
       <c r="O59" s="6">
-        <v>46300.7588563655</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P59" s="6">
-        <v>46309.72497167712</v>
+        <v>46310.31708865982</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>192</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F60" s="6"/>
       <c r="G60" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H60" s="6">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="I60" s="6">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="J60" s="6" t="s">
         <v>193</v>
       </c>
       <c r="K60" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="6" t="s">
         <v>194</v>
@@ -3919,46 +3927,48 @@
         <v>18</v>
       </c>
       <c r="O60" s="6">
-        <v>46300.7588564207</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P60" s="6">
-        <v>46309.72497172017</v>
+        <v>46310.31708870408</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>195</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H61" s="6">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="I61" s="6">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K61" s="6">
         <v>1</v>
       </c>
-      <c r="L61" s="6"/>
+      <c r="L61" s="6" t="s">
+        <v>198</v>
+      </c>
       <c r="M61" s="6" t="s">
         <v>18</v>
       </c>
@@ -3966,48 +3976,50 @@
         <v>18</v>
       </c>
       <c r="O61" s="6">
-        <v>46300.75885647022</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P61" s="6">
-        <v>46309.72497174865</v>
-      </c>
-      <c r="Q61" s="5" t="s">
-        <v>22</v>
+        <v>46310.31708873354</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:17">
       <c r="A62" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="G62" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H62" s="6">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="I62" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K62" s="6">
         <v>2</v>
       </c>
-      <c r="L62" s="6"/>
+      <c r="L62" s="6" t="s">
+        <v>202</v>
+      </c>
       <c r="M62" s="6" t="s">
         <v>18</v>
       </c>
@@ -4015,41 +4027,41 @@
         <v>18</v>
       </c>
       <c r="O62" s="6">
-        <v>46300.75885649968</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P62" s="6">
-        <v>46309.72497177708</v>
+        <v>46310.31708879175</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:17">
       <c r="A63" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H63" s="6">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="I63" s="6">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K63" s="6">
         <v>1</v>
@@ -4062,46 +4074,46 @@
         <v>18</v>
       </c>
       <c r="O63" s="6">
-        <v>46300.75886463693</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P63" s="6">
-        <v>46309.7249804657</v>
-      </c>
-      <c r="Q63" s="6" t="s">
-        <v>27</v>
+        <v>46310.31708883602</v>
+      </c>
+      <c r="Q63" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G64" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H64" s="6">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="I64" s="6">
         <v>-9</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K64" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="6"/>
       <c r="M64" s="6" t="s">
@@ -4111,48 +4123,46 @@
         <v>18</v>
       </c>
       <c r="O64" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.75885649968</v>
       </c>
       <c r="P64" s="6">
-        <v>46309.72497182001</v>
+        <v>46310.31708886509</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:17">
       <c r="A65" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H65" s="6">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="I65" s="6">
         <v>-10</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="K65" s="6">
         <v>1</v>
       </c>
-      <c r="L65" s="6" t="s">
-        <v>205</v>
-      </c>
+      <c r="L65" s="6"/>
       <c r="M65" s="6" t="s">
         <v>18</v>
       </c>
@@ -4160,43 +4170,43 @@
         <v>18</v>
       </c>
       <c r="O65" s="6">
-        <v>46300.75886466862</v>
+        <v>46300.75886463693</v>
       </c>
       <c r="P65" s="6">
-        <v>46309.7249804969</v>
-      </c>
-      <c r="Q65" s="5" t="s">
-        <v>22</v>
+        <v>46310.31709693522</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:17">
       <c r="A66" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F66" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="G66" s="6">
         <v>0.93</v>
       </c>
       <c r="H66" s="6">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="I66" s="6">
         <v>-10</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K66" s="6">
         <v>1</v>
@@ -4209,13 +4219,13 @@
         <v>18</v>
       </c>
       <c r="O66" s="6">
-        <v>46300.75886468366</v>
+        <v>46300.75886465221</v>
       </c>
       <c r="P66" s="6">
-        <v>46309.724980512</v>
+        <v>46310.31709691979</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -4358,7 +4368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4437,22 +4447,25 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="G2" s="2">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H2" s="3">
-        <v>46309</v>
+        <v>46314</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -4464,13 +4477,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46308.39987059968</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P2" s="2">
-        <v>46309.72496064098</v>
+        <v>46309.72495190653</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4481,10 +4494,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -4493,10 +4506,10 @@
         <v>46314</v>
       </c>
       <c r="I3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4511,10 +4524,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P3" s="2">
-        <v>46309.72495193577</v>
+        <v>46310.3170788213</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4525,10 +4538,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
@@ -4537,10 +4550,10 @@
         <v>46315</v>
       </c>
       <c r="I4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -4555,10 +4568,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P4" s="2">
-        <v>46309.72495189186</v>
+        <v>46310.31707061251</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4569,10 +4582,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -4581,16 +4594,16 @@
         <v>46316</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K5" s="2">
         <v>3</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
@@ -4602,38 +4615,38 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P5" s="2">
-        <v>46309.72495186308</v>
+        <v>46310.3170705706</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="2" customFormat="1">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="2">
         <v>0.2</v>
       </c>
       <c r="H6" s="3">
         <v>46317</v>
       </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6">
+      <c r="I6" s="2">
+        <v>7</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
@@ -4642,42 +4655,42 @@
       <c r="N6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="2">
         <v>46301.38232468421</v>
       </c>
-      <c r="P6">
-        <v>46309.7249518034</v>
+      <c r="P6" s="2">
+        <v>46310.31707052737</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="2" customFormat="1">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
         <v>46317</v>
       </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7">
+      <c r="I7" s="2">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="2">
         <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
@@ -4686,14 +4699,14 @@
       <c r="N7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="2">
         <v>46309.72495178872</v>
       </c>
-      <c r="P7">
-        <v>46309.72495178875</v>
+      <c r="P7" s="2">
+        <v>46310.31707051331</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4704,10 +4717,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>0.2</v>
@@ -4716,16 +4729,16 @@
         <v>46319</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K8">
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -4737,10 +4750,10 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P8">
-        <v>46309.72495162148</v>
+        <v>46310.31707042759</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4751,10 +4764,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G9">
         <v>0.2</v>
@@ -4763,10 +4776,10 @@
         <v>46319</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4781,10 +4794,10 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P9">
-        <v>46309.724951606</v>
+        <v>46310.31707041276</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4795,10 +4808,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>0.2</v>
@@ -4807,10 +4820,10 @@
         <v>46319</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4825,10 +4838,10 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P10">
-        <v>46309.72495171531</v>
+        <v>46310.31707034108</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -4839,10 +4852,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G11">
         <v>0.2</v>
@@ -4851,10 +4864,10 @@
         <v>46320</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4869,10 +4882,10 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46309.72494271736</v>
+        <v>46310.31707032494</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -4883,10 +4896,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G12">
         <v>0.2</v>
@@ -4895,10 +4908,10 @@
         <v>46321</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -4913,10 +4926,10 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46309.72494270258</v>
+        <v>46310.31706151488</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -4927,10 +4940,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G13">
         <v>0.2</v>
@@ -4939,16 +4952,16 @@
         <v>46322</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4960,10 +4973,10 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46309.72494267265</v>
+        <v>46310.31706145219</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -4974,10 +4987,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G14">
         <v>0.2</v>
@@ -4986,16 +4999,16 @@
         <v>46322</v>
       </c>
       <c r="I14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -5007,10 +5020,10 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46309.72494264157</v>
+        <v>46310.31706150002</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -5021,10 +5034,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G15">
         <v>0.2</v>
@@ -5033,10 +5046,10 @@
         <v>46323</v>
       </c>
       <c r="I15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -5051,10 +5064,10 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P15">
-        <v>46309.72494256635</v>
+        <v>46310.31706140641</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -5065,10 +5078,10 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G16">
         <v>0.2</v>
@@ -5077,10 +5090,10 @@
         <v>46323</v>
       </c>
       <c r="I16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -5095,10 +5108,10 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P16">
-        <v>46309.72494259725</v>
+        <v>46310.31706142161</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -5109,10 +5122,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G17">
         <v>0.2</v>
@@ -5121,16 +5134,16 @@
         <v>46323</v>
       </c>
       <c r="I17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
@@ -5142,10 +5155,10 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P17">
-        <v>46309.72494262768</v>
+        <v>46310.31706143728</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -5156,10 +5169,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G18">
         <v>0.2</v>
@@ -5168,16 +5181,16 @@
         <v>46324</v>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -5189,10 +5202,10 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P18">
-        <v>46309.72494253636</v>
+        <v>46310.3170613514</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -5203,10 +5216,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G19">
         <v>0.2</v>
@@ -5215,10 +5228,10 @@
         <v>46326</v>
       </c>
       <c r="I19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -5233,38 +5246,38 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P19">
-        <v>46309.72494233132</v>
+        <v>46310.31706114814</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6">
         <v>0.2</v>
       </c>
       <c r="H20" s="6">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I20" s="6">
         <v>-1</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="K20" s="6">
         <v>1</v>
@@ -5277,28 +5290,28 @@
         <v>18</v>
       </c>
       <c r="O20" s="6">
-        <v>46300.75884790152</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P20" s="6">
-        <v>46309.72496068516</v>
+        <v>46310.31707894053</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6">
@@ -5308,10 +5321,10 @@
         <v>46308</v>
       </c>
       <c r="I21" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="K21" s="6">
         <v>1</v>
@@ -5324,41 +5337,41 @@
         <v>18</v>
       </c>
       <c r="O21" s="6">
-        <v>46301.38232480602</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P21" s="6">
-        <v>46309.72496067041</v>
+        <v>46310.31707898439</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6">
         <v>0.2</v>
       </c>
       <c r="H22" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I22" s="6">
         <v>-2</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K22" s="6">
         <v>1</v>
@@ -5371,28 +5384,28 @@
         <v>18</v>
       </c>
       <c r="O22" s="6">
-        <v>46300.7588479478</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P22" s="6">
-        <v>46309.72496071397</v>
+        <v>46310.31707896989</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6">
@@ -5402,17 +5415,15 @@
         <v>46307</v>
       </c>
       <c r="I23" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>166</v>
-      </c>
+      <c r="L23" s="6"/>
       <c r="M23" s="6" t="s">
         <v>18</v>
       </c>
@@ -5420,46 +5431,48 @@
         <v>18</v>
       </c>
       <c r="O23" s="6">
-        <v>46300.75884799581</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P23" s="6">
-        <v>46309.72496072845</v>
+        <v>46310.31708860076</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6">
         <v>0.2</v>
       </c>
       <c r="H24" s="6">
-        <v>46302</v>
+        <v>46307</v>
       </c>
       <c r="I24" s="6">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="K24" s="6">
         <v>1</v>
       </c>
-      <c r="L24" s="6"/>
+      <c r="L24" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="M24" s="6" t="s">
         <v>18</v>
       </c>
@@ -5467,66 +5480,164 @@
         <v>18</v>
       </c>
       <c r="O24" s="6">
-        <v>46300.75885647022</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P24" s="6">
-        <v>46309.72497174865</v>
+        <v>46309.72496072845</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H25" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I25" s="6">
+        <v>-3</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="6">
+        <v>46300.75885619673</v>
+      </c>
+      <c r="P25" s="6">
+        <v>46309.72496075697</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H26" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I26" s="6">
+        <v>-3</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K26" s="6">
+        <v>2</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="6">
+        <v>46305.20576106136</v>
+      </c>
+      <c r="P26" s="6">
+        <v>46309.72496078632</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6">
         <v>0.2</v>
       </c>
-      <c r="H25" s="6">
-        <v>46299</v>
-      </c>
-      <c r="I25" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K25" s="6">
-        <v>1</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O25" s="6">
-        <v>46300.75886466862</v>
-      </c>
-      <c r="P25" s="6">
-        <v>46309.7249804969</v>
-      </c>
-      <c r="Q25" s="5" t="s">
-        <v>22</v>
+      <c r="H27" s="6">
+        <v>46302</v>
+      </c>
+      <c r="I27" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K27" s="6">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="6">
+        <v>46300.75885647022</v>
+      </c>
+      <c r="P27" s="6">
+        <v>46310.31708883602</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q25"/>
+  <autoFilter ref="A1:Q27"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -5576,6 +5687,10 @@
     <hyperlink ref="N24" r:id="rId46"/>
     <hyperlink ref="M25" r:id="rId47"/>
     <hyperlink ref="N25" r:id="rId48"/>
+    <hyperlink ref="M26" r:id="rId49"/>
+    <hyperlink ref="N26" r:id="rId50"/>
+    <hyperlink ref="M27" r:id="rId51"/>
+    <hyperlink ref="N27" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5583,7 +5698,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5593,66 +5708,66 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B2">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D2">
         <v>193</v>
       </c>
       <c r="E2">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -5661,53 +5776,53 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B3">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D3">
         <v>193</v>
       </c>
       <c r="E3">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B4">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D4">
         <v>193</v>
@@ -5719,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5736,13 +5851,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B5">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D5">
         <v>193</v>
@@ -5751,16 +5866,16 @@
         <v>3844</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -5771,48 +5886,48 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B6">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D6">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E6">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>381</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B7">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D7">
         <v>192</v>
@@ -5821,13 +5936,13 @@
         <v>3838</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5841,28 +5956,28 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B8">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D8">
         <v>192</v>
       </c>
       <c r="E8">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>369</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5871,18 +5986,18 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B9">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D9">
         <v>192</v>
@@ -5911,13 +6026,13 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B10">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10">
         <v>192</v>
@@ -5929,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5946,13 +6061,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B11">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D11">
         <v>192</v>
@@ -5981,13 +6096,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B12">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D12">
         <v>192</v>
@@ -5996,16 +6111,16 @@
         <v>3826</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -6016,48 +6131,48 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B13">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D13">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E13">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B14">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D14">
         <v>191</v>
@@ -6086,13 +6201,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B15">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D15">
         <v>191</v>
@@ -6104,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -6121,13 +6236,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B16">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D16">
         <v>191</v>
@@ -6136,16 +6251,16 @@
         <v>3820</v>
       </c>
       <c r="F16">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H16">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -6156,48 +6271,48 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B17">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E17">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G17">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B18">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -6206,13 +6321,13 @@
         <v>160</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -6221,18 +6336,18 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B19">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -6241,21 +6356,56 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H19">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B20">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C20" t="s">
+        <v>223</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>160</v>
+      </c>
+      <c r="F20">
+        <v>157</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>132</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="229">
   <si>
     <t>Priority</t>
   </si>
@@ -160,192 +160,192 @@
     <t>Mr. Ashish Saoji</t>
   </si>
   <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chandra Kumar Jain</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SMO FERRO ALLOYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Rajesh Lohia</t>
+  </si>
+  <si>
+    <t>ALCOB INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRASHANT KHATAVKAR</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
     <t>Not in latest IBBI listing - verify with RP</t>
   </si>
   <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chandra Kumar Jain</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>The addendum to form G was issued on 10th October, 2026.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SMO FERRO ALLOYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Rajesh Lohia</t>
-  </si>
-  <si>
-    <t>ALCOB INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRASHANT KHATAVKAR</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>SUNSHINE FASTECH LIMITED</t>
-  </si>
-  <si>
-    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
-  </si>
-  <si>
     <t>HOURS OVERSEAS PRIVATE LIMITED</t>
   </si>
   <si>
@@ -430,6 +430,15 @@
     <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
   </si>
   <si>
+    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Prashant Jain</t>
+  </si>
+  <si>
+    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
+  </si>
+  <si>
     <t>STUTI COMTRADE PRIVATE LIMITED</t>
   </si>
   <si>
@@ -524,6 +533,12 @@
   </si>
   <si>
     <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>CITRON INFRAPROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Sunil Kumar Kabra</t>
   </si>
   <si>
     <t>TECHNOFAB ENGINEERING LIMITED</t>
@@ -1096,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1208,7 +1223,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P2" s="2">
-        <v>46310.31707892606</v>
+        <v>46310.71708385317</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1255,7 +1270,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P3" s="2">
-        <v>46310.31707885113</v>
+        <v>46310.71708378154</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1299,7 +1314,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P4" s="2">
-        <v>46310.31707889567</v>
+        <v>46310.71708379548</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1346,7 +1361,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P5" s="2">
-        <v>46310.3170788808</v>
+        <v>46310.71708380998</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1393,7 +1408,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P6" s="2">
-        <v>46310.31707886575</v>
+        <v>46310.7170838247</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1440,7 +1455,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P7" s="2">
-        <v>46310.31707883633</v>
+        <v>46310.71708376709</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1487,10 +1502,10 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P8" s="2">
-        <v>46309.72495190653</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>46</v>
+        <v>46310.71708372193</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1501,10 +1516,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G9" s="2">
         <v>0.2</v>
@@ -1516,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -1531,10 +1546,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P9" s="2">
-        <v>46310.3170788213</v>
+        <v>46310.71708373787</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1545,7 +1560,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>29</v>
@@ -1560,7 +1575,7 @@
         <v>4</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -1575,7 +1590,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P10" s="2">
-        <v>46310.31707880468</v>
+        <v>46310.71708375273</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>23</v>
@@ -1589,10 +1604,10 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2">
         <v>0.2</v>
@@ -1604,7 +1619,7 @@
         <v>5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -1619,10 +1634,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P11" s="2">
-        <v>46310.31707061251</v>
+        <v>46310.71707578342</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1633,10 +1648,10 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G12" s="2">
         <v>0.9399999999999999</v>
@@ -1648,13 +1663,13 @@
         <v>5</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -1666,7 +1681,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P12" s="2">
-        <v>46310.31707059883</v>
+        <v>46310.71707579794</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1680,10 +1695,10 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="2">
         <v>0.2</v>
@@ -1695,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13" s="2">
         <v>3</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -1713,10 +1728,10 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P13" s="2">
-        <v>46310.3170705706</v>
+        <v>46310.71707575507</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1727,10 +1742,10 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G14" s="2">
         <v>0.92</v>
@@ -1742,13 +1757,13 @@
         <v>6</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K14" s="2">
         <v>2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -1760,7 +1775,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P14" s="2">
-        <v>46310.31707058447</v>
+        <v>46310.71707576897</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1774,10 +1789,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="2">
         <v>0.2</v>
@@ -1789,7 +1804,7 @@
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
@@ -1804,10 +1819,10 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P15" s="2">
-        <v>46310.31707052737</v>
+        <v>46310.71707571246</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1818,13 +1833,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="G16" s="2">
         <v>0.9399999999999999</v>
@@ -1836,7 +1851,7 @@
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
@@ -1851,7 +1866,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P16" s="2">
-        <v>46310.31707054178</v>
+        <v>46310.71707569752</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1865,10 +1880,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17" s="2">
         <v>0.2</v>
@@ -1880,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
@@ -1895,10 +1910,10 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P17" s="2">
-        <v>46310.31707051331</v>
+        <v>46310.71707572688</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1909,7 +1924,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>43</v>
@@ -1927,13 +1942,13 @@
         <v>8</v>
       </c>
       <c r="J18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
         <v>75</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>76</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -1945,7 +1960,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P18">
-        <v>46310.31707047093</v>
+        <v>46310.71707568316</v>
       </c>
       <c r="Q18" t="s">
         <v>23</v>
@@ -1959,10 +1974,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
         <v>77</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
       </c>
       <c r="G19">
         <v>0.9399999999999999</v>
@@ -1974,13 +1989,13 @@
         <v>8</v>
       </c>
       <c r="J19" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
         <v>79</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>80</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -1992,7 +2007,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P19">
-        <v>46310.31707048484</v>
+        <v>46310.7170756687</v>
       </c>
       <c r="Q19" t="s">
         <v>23</v>
@@ -2006,7 +2021,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>39</v>
@@ -2021,13 +2036,13 @@
         <v>8</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K20">
         <v>2</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -2039,7 +2054,7 @@
         <v>46308.39986132324</v>
       </c>
       <c r="P20">
-        <v>46310.31707049905</v>
+        <v>46310.71707565407</v>
       </c>
       <c r="Q20" t="s">
         <v>23</v>
@@ -2053,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
         <v>83</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>84</v>
-      </c>
-      <c r="F21" t="s">
-        <v>85</v>
       </c>
       <c r="G21">
         <v>0.93</v>
@@ -2071,13 +2086,13 @@
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K21">
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -2089,7 +2104,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P21">
-        <v>46310.31707039779</v>
+        <v>46310.71707563939</v>
       </c>
       <c r="Q21" t="s">
         <v>23</v>
@@ -2103,10 +2118,10 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22">
         <v>0.2</v>
@@ -2118,13 +2133,13 @@
         <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K22">
         <v>2</v>
       </c>
       <c r="L22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2136,10 +2151,10 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P22">
-        <v>46310.31707042759</v>
+        <v>46310.71707561009</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2150,10 +2165,10 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G23">
         <v>0.2</v>
@@ -2165,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2180,10 +2195,10 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P23">
-        <v>46310.31707041276</v>
+        <v>46310.71707562462</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2194,7 +2209,7 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
@@ -2209,7 +2224,7 @@
         <v>9</v>
       </c>
       <c r="J24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K24">
         <v>2</v>
@@ -2224,7 +2239,7 @@
         <v>46309.72495168629</v>
       </c>
       <c r="P24">
-        <v>46310.31707045649</v>
+        <v>46310.71707558073</v>
       </c>
       <c r="Q24" t="s">
         <v>23</v>
@@ -2238,10 +2253,10 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25">
         <v>0.2</v>
@@ -2253,7 +2268,7 @@
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2268,10 +2283,10 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P25">
-        <v>46310.31707034108</v>
+        <v>46310.71707556527</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2282,13 +2297,13 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" t="s">
         <v>97</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>98</v>
-      </c>
-      <c r="F26" t="s">
-        <v>99</v>
       </c>
       <c r="G26">
         <v>0.91</v>
@@ -2300,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K26">
         <v>2</v>
@@ -2315,7 +2330,7 @@
         <v>46310.31707038325</v>
       </c>
       <c r="P26">
-        <v>46310.31707038327</v>
+        <v>46310.71707554919</v>
       </c>
       <c r="Q26" t="s">
         <v>23</v>
@@ -2329,7 +2344,7 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
         <v>20</v>
@@ -2344,13 +2359,13 @@
         <v>10</v>
       </c>
       <c r="J27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2362,7 +2377,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P27">
-        <v>46310.31706154611</v>
+        <v>46310.71707551496</v>
       </c>
       <c r="Q27" t="s">
         <v>23</v>
@@ -2376,7 +2391,7 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
         <v>39</v>
@@ -2391,7 +2406,7 @@
         <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2406,7 +2421,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P28">
-        <v>46310.31706153003</v>
+        <v>46310.7170755324</v>
       </c>
       <c r="Q28" t="s">
         <v>23</v>
@@ -2420,10 +2435,10 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G29">
         <v>0.2</v>
@@ -2435,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2453,7 +2468,7 @@
         <v>46310.31707032494</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2467,7 +2482,7 @@
         <v>108</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30">
         <v>0.2</v>
@@ -2494,10 +2509,10 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P30">
-        <v>46310.31706151488</v>
+        <v>46310.7170673743</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2511,7 +2526,7 @@
         <v>110</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G31">
         <v>0.2</v>
@@ -2541,10 +2556,10 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P31">
-        <v>46310.31706145219</v>
+        <v>46310.71706734345</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2591,7 +2606,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P32">
-        <v>46310.3170614677</v>
+        <v>46310.71706732902</v>
       </c>
       <c r="Q32" t="s">
         <v>23</v>
@@ -2608,7 +2623,7 @@
         <v>118</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G33">
         <v>0.2</v>
@@ -2638,10 +2653,10 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P33">
-        <v>46310.31706150002</v>
+        <v>46310.71706731404</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2655,10 +2670,10 @@
         <v>121</v>
       </c>
       <c r="E34" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" t="s">
         <v>84</v>
-      </c>
-      <c r="F34" t="s">
-        <v>85</v>
       </c>
       <c r="G34">
         <v>0.93</v>
@@ -2688,7 +2703,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P34">
-        <v>46310.31706148342</v>
+        <v>46310.71706735919</v>
       </c>
       <c r="Q34" t="s">
         <v>23</v>
@@ -2705,7 +2720,7 @@
         <v>124</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G35">
         <v>0.2</v>
@@ -2732,10 +2747,10 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P35">
-        <v>46310.31706140641</v>
+        <v>46310.71706727032</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2749,7 +2764,7 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G36">
         <v>0.2</v>
@@ -2776,10 +2791,10 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P36">
-        <v>46310.31706142161</v>
+        <v>46310.71706728528</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2793,7 +2808,7 @@
         <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G37">
         <v>0.2</v>
@@ -2823,10 +2838,10 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P37">
-        <v>46310.31706143728</v>
+        <v>46310.71706729976</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2873,7 +2888,7 @@
         <v>46310.31706138982</v>
       </c>
       <c r="P38">
-        <v>46310.31706138986</v>
+        <v>46310.71706725491</v>
       </c>
       <c r="Q38" t="s">
         <v>23</v>
@@ -2890,16 +2905,16 @@
         <v>136</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G39">
         <v>0.2</v>
       </c>
       <c r="H39" s="3">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I39">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J39" t="s">
         <v>137</v>
@@ -2917,13 +2932,13 @@
         <v>18</v>
       </c>
       <c r="O39">
-        <v>46309.72494253634</v>
+        <v>46310.71706723773</v>
       </c>
       <c r="P39">
-        <v>46310.3170613514</v>
+        <v>46310.71706723775</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2937,10 +2952,10 @@
         <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G40">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H40" s="3">
         <v>46324</v>
@@ -2964,13 +2979,13 @@
         <v>18</v>
       </c>
       <c r="O40">
-        <v>46310.31706133292</v>
+        <v>46309.72494253634</v>
       </c>
       <c r="P40">
-        <v>46310.31706133294</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>23</v>
+        <v>46310.71706709165</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2984,29 +2999,26 @@
         <v>142</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F41" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41">
+        <v>0.91</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46324</v>
+      </c>
+      <c r="I41">
+        <v>14</v>
+      </c>
+      <c r="J41" t="s">
         <v>143</v>
       </c>
-      <c r="G41">
-        <v>0.89</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46325</v>
-      </c>
-      <c r="I41">
-        <v>15</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
         <v>144</v>
       </c>
-      <c r="K41">
-        <v>2</v>
-      </c>
-      <c r="L41" t="s">
-        <v>145</v>
-      </c>
       <c r="M41" s="4" t="s">
         <v>18</v>
       </c>
@@ -3014,10 +3026,10 @@
         <v>18</v>
       </c>
       <c r="O41">
-        <v>46309.72494249383</v>
+        <v>46310.31706133292</v>
       </c>
       <c r="P41">
-        <v>46310.31706117826</v>
+        <v>46310.71706707685</v>
       </c>
       <c r="Q41" t="s">
         <v>23</v>
@@ -3031,25 +3043,31 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" t="s">
         <v>146</v>
       </c>
-      <c r="E42" t="s">
-        <v>48</v>
-      </c>
       <c r="G42">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="H42" s="3">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="I42">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J42" t="s">
         <v>147</v>
       </c>
       <c r="K42">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L42" t="s">
+        <v>148</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>18</v>
@@ -3058,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="O42">
-        <v>46300.75884768533</v>
+        <v>46309.72494249383</v>
       </c>
       <c r="P42">
-        <v>46310.31706114814</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>50</v>
+        <v>46310.71706706181</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -3075,31 +3093,25 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E43" t="s">
-        <v>114</v>
-      </c>
-      <c r="F43" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="G43">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H43" s="3">
-        <v>46328</v>
+        <v>46326</v>
       </c>
       <c r="I43">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K43">
-        <v>2</v>
-      </c>
-      <c r="L43" t="s">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>18</v>
@@ -3108,13 +3120,13 @@
         <v>18</v>
       </c>
       <c r="O43">
-        <v>46308.39986111095</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P43">
-        <v>46310.31706113207</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>23</v>
+        <v>46310.71706704683</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -3128,22 +3140,28 @@
         <v>151</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>114</v>
+      </c>
+      <c r="F44" t="s">
+        <v>115</v>
       </c>
       <c r="G44">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H44" s="3">
-        <v>46332</v>
+        <v>46328</v>
       </c>
       <c r="I44">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s">
         <v>152</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="L44" t="s">
+        <v>153</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>18</v>
@@ -3152,10 +3170,10 @@
         <v>18</v>
       </c>
       <c r="O44">
-        <v>46305.20575257758</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P44">
-        <v>46310.31706111562</v>
+        <v>46310.71706701682</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3169,29 +3187,26 @@
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G45">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="H45" s="3">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="I45">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J45" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="K45">
         <v>4</v>
       </c>
-      <c r="L45" t="s">
-        <v>154</v>
-      </c>
       <c r="M45" s="4" t="s">
         <v>18</v>
       </c>
@@ -3199,10 +3214,10 @@
         <v>18</v>
       </c>
       <c r="O45">
-        <v>46307.39549666931</v>
+        <v>46305.20575257758</v>
       </c>
       <c r="P45">
-        <v>46310.31706109887</v>
+        <v>46310.71706700103</v>
       </c>
       <c r="Q45" t="s">
         <v>23</v>
@@ -3216,13 +3231,13 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="G46">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H46" s="3">
         <v>46333</v>
@@ -3231,10 +3246,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L46" t="s">
+        <v>157</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>18</v>
@@ -3243,97 +3261,90 @@
         <v>18</v>
       </c>
       <c r="O46">
-        <v>46307.39549671811</v>
+        <v>46307.39549666931</v>
       </c>
       <c r="P46">
-        <v>46310.31706106838</v>
+        <v>46310.71706698506</v>
       </c>
       <c r="Q46" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" s="6" t="s">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
         <v>158</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="E47" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H47" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I47">
+        <v>23</v>
+      </c>
+      <c r="J47" t="s">
         <v>159</v>
       </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H47" s="6">
-        <v>46309</v>
-      </c>
-      <c r="I47" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="K47" s="6">
-        <v>1</v>
-      </c>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O47" s="6">
-        <v>46308.39987059968</v>
-      </c>
-      <c r="P47" s="6">
-        <v>46310.31707894053</v>
-      </c>
-      <c r="Q47" s="5" t="s">
-        <v>50</v>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47">
+        <v>46307.39549671811</v>
+      </c>
+      <c r="P47">
+        <v>46310.71706695442</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>115</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F48" s="6"/>
       <c r="G48" s="6">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H48" s="6">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I48" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K48" s="6">
         <v>1</v>
       </c>
-      <c r="L48" s="6" t="s">
-        <v>163</v>
-      </c>
+      <c r="L48" s="6"/>
       <c r="M48" s="6" t="s">
         <v>18</v>
       </c>
@@ -3341,32 +3352,34 @@
         <v>18</v>
       </c>
       <c r="O48" s="6">
-        <v>46300.75884788632</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P48" s="6">
-        <v>46310.31707895547</v>
-      </c>
-      <c r="Q48" s="6" t="s">
-        <v>23</v>
+        <v>46310.71708386733</v>
+      </c>
+      <c r="Q48" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:17">
       <c r="A49" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>164</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="6"/>
+        <v>114</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="G49" s="6">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H49" s="6">
         <v>46308</v>
@@ -3380,7 +3393,9 @@
       <c r="K49" s="6">
         <v>1</v>
       </c>
-      <c r="L49" s="6"/>
+      <c r="L49" s="6" t="s">
+        <v>166</v>
+      </c>
       <c r="M49" s="6" t="s">
         <v>18</v>
       </c>
@@ -3388,28 +3403,28 @@
         <v>18</v>
       </c>
       <c r="O49" s="6">
-        <v>46300.75884790152</v>
+        <v>46300.75884788632</v>
       </c>
       <c r="P49" s="6">
-        <v>46310.31707898439</v>
-      </c>
-      <c r="Q49" s="5" t="s">
-        <v>50</v>
+        <v>46310.71708392838</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
@@ -3422,7 +3437,7 @@
         <v>-2</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K50" s="6">
         <v>1</v>
@@ -3435,50 +3450,46 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46301.38232480602</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P50" s="6">
-        <v>46310.31707896989</v>
+        <v>46310.7170839139</v>
       </c>
       <c r="Q50" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="F51" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H51" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I51" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J51" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="G51" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="H51" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I51" s="6">
-        <v>-3</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>171</v>
-      </c>
       <c r="K51" s="6">
         <v>1</v>
       </c>
-      <c r="L51" s="6" t="s">
-        <v>172</v>
-      </c>
+      <c r="L51" s="6"/>
       <c r="M51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3486,41 +3497,41 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46300.75884793277</v>
+        <v>46301.38232480602</v>
       </c>
       <c r="P51" s="6">
-        <v>46310.31708858236</v>
-      </c>
-      <c r="Q51" s="6" t="s">
-        <v>23</v>
+        <v>46310.71708394251</v>
+      </c>
+      <c r="Q51" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
         <v>0.2</v>
       </c>
       <c r="H52" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I52" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K52" s="6">
         <v>1</v>
@@ -3533,34 +3544,34 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.7588479478</v>
+        <v>46310.71708389919</v>
       </c>
       <c r="P52" s="6">
-        <v>46310.31708860076</v>
+        <v>46310.7170838992</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="G53" s="6">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="H53" s="6">
         <v>46307</v>
@@ -3574,7 +3585,9 @@
       <c r="K53" s="6">
         <v>1</v>
       </c>
-      <c r="L53" s="6"/>
+      <c r="L53" s="6" t="s">
+        <v>177</v>
+      </c>
       <c r="M53" s="6" t="s">
         <v>18</v>
       </c>
@@ -3582,10 +3595,10 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.75884796329</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P53" s="6">
-        <v>46310.31707907124</v>
+        <v>46310.71709191583</v>
       </c>
       <c r="Q53" s="6" t="s">
         <v>23</v>
@@ -3593,17 +3606,17 @@
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6">
@@ -3616,14 +3629,12 @@
         <v>-3</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K54" s="6">
         <v>1</v>
       </c>
-      <c r="L54" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="L54" s="6"/>
       <c r="M54" s="6" t="s">
         <v>18</v>
       </c>
@@ -3631,32 +3642,34 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.75884799581</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P54" s="6">
-        <v>46309.72496072845</v>
+        <v>46310.71708398541</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>180</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="G55" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H55" s="6">
         <v>46307</v>
@@ -3678,32 +3691,32 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75885617639</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46310.31707899934</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>23</v>
+        <v>46310.31707907124</v>
+      </c>
+      <c r="Q55" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>182</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H56" s="6">
         <v>46307</v>
@@ -3712,13 +3725,13 @@
         <v>-3</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>18</v>
@@ -3727,34 +3740,32 @@
         <v>18</v>
       </c>
       <c r="O56" s="6">
-        <v>46300.75885619673</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46309.72496075697</v>
+        <v>46310.71709196248</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>85</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H57" s="6">
         <v>46307</v>
@@ -3763,14 +3774,12 @@
         <v>-3</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="K57" s="6">
-        <v>2</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>185</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L57" s="6"/>
       <c r="M57" s="6" t="s">
         <v>18</v>
       </c>
@@ -3778,43 +3787,41 @@
         <v>18</v>
       </c>
       <c r="O57" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46309.72496078632</v>
-      </c>
-      <c r="Q57" s="5" t="s">
-        <v>46</v>
+        <v>46310.71709193088</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F58" s="6"/>
       <c r="G58" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H58" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I58" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
@@ -3829,10 +3836,10 @@
         <v>18</v>
       </c>
       <c r="O58" s="6">
-        <v>46300.75885624527</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46310.31708867416</v>
+        <v>46310.71709194721</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3840,37 +3847,39 @@
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>189</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F59" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="G59" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H59" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I59" s="6">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J59" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K59" s="6">
+        <v>2</v>
+      </c>
+      <c r="L59" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="K59" s="6">
-        <v>1</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="M59" s="6" t="s">
         <v>18</v>
       </c>
@@ -3878,48 +3887,50 @@
         <v>18</v>
       </c>
       <c r="O59" s="6">
-        <v>46300.75885627908</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P59" s="6">
-        <v>46310.31708865982</v>
-      </c>
-      <c r="Q59" s="6" t="s">
-        <v>23</v>
+        <v>46309.72496078632</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F60" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="G60" s="6">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H60" s="6">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="I60" s="6">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="J60" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K60" s="6">
+        <v>1</v>
+      </c>
+      <c r="L60" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="K60" s="6">
-        <v>1</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>194</v>
-      </c>
       <c r="M60" s="6" t="s">
         <v>18</v>
       </c>
@@ -3927,10 +3938,10 @@
         <v>18</v>
       </c>
       <c r="O60" s="6">
-        <v>46300.75885633306</v>
+        <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46310.31708870408</v>
+        <v>46310.71709199282</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3938,36 +3949,36 @@
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>196</v>
+        <v>55</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H61" s="6">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="I61" s="6">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K61" s="6">
         <v>1</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>18</v>
@@ -3976,10 +3987,10 @@
         <v>18</v>
       </c>
       <c r="O61" s="6">
-        <v>46300.7588563655</v>
+        <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46310.31708873354</v>
+        <v>46310.71709202128</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -3987,38 +3998,36 @@
     </row>
     <row r="62" spans="1:17">
       <c r="A62" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>200</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F62" s="6"/>
       <c r="G62" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H62" s="6">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="I62" s="6">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K62" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>18</v>
@@ -4027,10 +4036,10 @@
         <v>18</v>
       </c>
       <c r="O62" s="6">
-        <v>46300.7588564207</v>
+        <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46310.31708879175</v>
+        <v>46310.71709205015</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4038,35 +4047,37 @@
     </row>
     <row r="63" spans="1:17">
       <c r="A63" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>48</v>
+        <v>201</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H63" s="6">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="I63" s="6">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K63" s="6">
         <v>1</v>
       </c>
-      <c r="L63" s="6"/>
+      <c r="L63" s="6" t="s">
+        <v>203</v>
+      </c>
       <c r="M63" s="6" t="s">
         <v>18</v>
       </c>
@@ -4074,40 +4085,40 @@
         <v>18</v>
       </c>
       <c r="O63" s="6">
-        <v>46300.75885647022</v>
+        <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46310.31708883602</v>
-      </c>
-      <c r="Q63" s="5" t="s">
-        <v>50</v>
+        <v>46310.71709209287</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="G64" s="6">
         <v>0.9399999999999999</v>
       </c>
       <c r="H64" s="6">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="I64" s="6">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>206</v>
@@ -4115,7 +4126,9 @@
       <c r="K64" s="6">
         <v>2</v>
       </c>
-      <c r="L64" s="6"/>
+      <c r="L64" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="M64" s="6" t="s">
         <v>18</v>
       </c>
@@ -4123,10 +4136,10 @@
         <v>18</v>
       </c>
       <c r="O64" s="6">
-        <v>46300.75885649968</v>
+        <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46310.31708886509</v>
+        <v>46310.71709213552</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
@@ -4134,27 +4147,27 @@
     </row>
     <row r="65" spans="1:17">
       <c r="A65" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H65" s="6">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="I65" s="6">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="J65" s="6" t="s">
         <v>209</v>
@@ -4170,46 +4183,46 @@
         <v>18</v>
       </c>
       <c r="O65" s="6">
-        <v>46300.75886463693</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P65" s="6">
-        <v>46310.31709693522</v>
-      </c>
-      <c r="Q65" s="6" t="s">
-        <v>23</v>
+        <v>46310.71709214953</v>
+      </c>
+      <c r="Q65" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:17">
       <c r="A66" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>210</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G66" s="6">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H66" s="6">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="I66" s="6">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J66" s="6" t="s">
         <v>211</v>
       </c>
       <c r="K66" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="6"/>
       <c r="M66" s="6" t="s">
@@ -4219,17 +4232,113 @@
         <v>18</v>
       </c>
       <c r="O66" s="6">
-        <v>46300.75886465221</v>
+        <v>46300.75885649968</v>
       </c>
       <c r="P66" s="6">
-        <v>46310.31709691979</v>
+        <v>46310.71710011137</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="H67" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I67" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O67" s="6">
+        <v>46300.75886463693</v>
+      </c>
+      <c r="P67" s="6">
+        <v>46310.7171001574</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H68" s="6">
+        <v>46300</v>
+      </c>
+      <c r="I68" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K68" s="6">
+        <v>1</v>
+      </c>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O68" s="6">
+        <v>46300.75886465221</v>
+      </c>
+      <c r="P68" s="6">
+        <v>46310.71710014256</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q66"/>
+  <autoFilter ref="A1:Q68"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4361,6 +4470,10 @@
     <hyperlink ref="N65" r:id="rId128"/>
     <hyperlink ref="M66" r:id="rId129"/>
     <hyperlink ref="N66" r:id="rId130"/>
+    <hyperlink ref="M67" r:id="rId131"/>
+    <hyperlink ref="N67" r:id="rId132"/>
+    <hyperlink ref="M68" r:id="rId133"/>
+    <hyperlink ref="N68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4368,7 +4481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4447,16 +4560,13 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G2" s="2">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H2" s="3">
         <v>46314</v>
@@ -4465,7 +4575,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -4477,13 +4587,13 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75884774033</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46309.72495190653</v>
+        <v>46310.71708373787</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4494,40 +4604,40 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
       </c>
       <c r="H3" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I3" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.75884772457</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46310.71707578342</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.75884775587</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46310.3170788213</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4538,25 +4648,28 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I4" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K4" s="2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -4565,13 +4678,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884772457</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46310.31707061251</v>
+        <v>46310.71707575507</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4582,28 +4695,25 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
       </c>
       <c r="H5" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I5" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
@@ -4612,13 +4722,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46302.26841507768</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46310.3170705706</v>
+        <v>46310.71707571246</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -4629,10 +4739,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2">
         <v>0.2</v>
@@ -4644,7 +4754,7 @@
         <v>7</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -4656,42 +4766,45 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46301.38232468421</v>
+        <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46310.31707052737</v>
+        <v>46310.71707572688</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="2" customFormat="1">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46317</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
+        <v>46319</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>88</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" t="s">
+        <v>89</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4699,14 +4812,14 @@
       <c r="N7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="2">
-        <v>46309.72495178872</v>
-      </c>
-      <c r="P7" s="2">
-        <v>46310.31707051331</v>
+      <c r="O7">
+        <v>46307.39549700746</v>
+      </c>
+      <c r="P7">
+        <v>46310.71707561009</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4717,10 +4830,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8">
         <v>0.2</v>
@@ -4732,13 +4845,10 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K8">
-        <v>2</v>
-      </c>
-      <c r="L8" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -4747,13 +4857,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46307.39549700746</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P8">
-        <v>46310.31707042759</v>
+        <v>46310.71707562462</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4764,10 +4874,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9">
         <v>0.2</v>
@@ -4779,7 +4889,7 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4791,13 +4901,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46307.3954970362</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P9">
-        <v>46310.31707041276</v>
+        <v>46310.71707556527</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4808,22 +4918,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4835,13 +4945,13 @@
         <v>18</v>
       </c>
       <c r="O10">
-        <v>46309.72495171529</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P10">
-        <v>46310.31707034108</v>
+        <v>46310.31707032494</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -4852,22 +4962,22 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11">
         <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4879,13 +4989,13 @@
         <v>18</v>
       </c>
       <c r="O11">
-        <v>46308.39986123197</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P11">
-        <v>46310.31707032494</v>
+        <v>46310.7170673743</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -4896,25 +5006,28 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G12">
         <v>0.2</v>
       </c>
       <c r="H12" s="3">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L12" t="s">
+        <v>112</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -4923,13 +5036,13 @@
         <v>18</v>
       </c>
       <c r="O12">
-        <v>46307.39549690609</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P12">
-        <v>46310.31706151488</v>
+        <v>46310.71706734345</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -4940,10 +5053,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13">
         <v>0.2</v>
@@ -4955,13 +5068,13 @@
         <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4970,13 +5083,13 @@
         <v>18</v>
       </c>
       <c r="O13">
-        <v>46307.39549680641</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P13">
-        <v>46310.31706145219</v>
+        <v>46310.71706731404</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -4987,29 +5100,26 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14">
         <v>0.2</v>
       </c>
       <c r="H14" s="3">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="L14" t="s">
-        <v>120</v>
-      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -5017,13 +5127,13 @@
         <v>18</v>
       </c>
       <c r="O14">
-        <v>46307.39549687663</v>
+        <v>46309.72494256633</v>
       </c>
       <c r="P14">
-        <v>46310.31706150002</v>
+        <v>46310.71706727032</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -5034,10 +5144,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15">
         <v>0.2</v>
@@ -5049,7 +5159,7 @@
         <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -5061,13 +5171,13 @@
         <v>18</v>
       </c>
       <c r="O15">
-        <v>46309.72494256633</v>
+        <v>46309.72494259723</v>
       </c>
       <c r="P15">
-        <v>46310.31706140641</v>
+        <v>46310.71706728528</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -5078,10 +5188,10 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16">
         <v>0.2</v>
@@ -5093,11 +5203,14 @@
         <v>13</v>
       </c>
       <c r="J16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
+      <c r="L16" t="s">
+        <v>130</v>
+      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -5105,13 +5218,13 @@
         <v>18</v>
       </c>
       <c r="O16">
-        <v>46309.72494259723</v>
+        <v>46309.72494262765</v>
       </c>
       <c r="P16">
-        <v>46310.31706142161</v>
+        <v>46310.71706729976</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -5122,10 +5235,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17">
         <v>0.2</v>
@@ -5137,13 +5250,13 @@
         <v>13</v>
       </c>
       <c r="J17" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
@@ -5152,13 +5265,13 @@
         <v>18</v>
       </c>
       <c r="O17">
-        <v>46309.72494262765</v>
+        <v>46310.71706723773</v>
       </c>
       <c r="P17">
-        <v>46310.31706143728</v>
+        <v>46310.71706723775</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -5169,10 +5282,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18">
         <v>0.2</v>
@@ -5184,13 +5297,13 @@
         <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -5202,10 +5315,10 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P18">
-        <v>46310.3170613514</v>
+        <v>46310.71706709165</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -5216,10 +5329,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19">
         <v>0.2</v>
@@ -5231,7 +5344,7 @@
         <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -5246,25 +5359,25 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P19">
-        <v>46310.31706114814</v>
+        <v>46310.71706704683</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6">
@@ -5277,7 +5390,7 @@
         <v>-1</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K20" s="6">
         <v>1</v>
@@ -5293,25 +5406,25 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P20" s="6">
-        <v>46310.31707894053</v>
+        <v>46310.71708386733</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6">
@@ -5324,7 +5437,7 @@
         <v>-2</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K21" s="6">
         <v>1</v>
@@ -5340,25 +5453,25 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P21" s="6">
-        <v>46310.31707898439</v>
+        <v>46310.7170839139</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6">
@@ -5371,7 +5484,7 @@
         <v>-2</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K22" s="6">
         <v>1</v>
@@ -5387,38 +5500,38 @@
         <v>46301.38232480602</v>
       </c>
       <c r="P22" s="6">
-        <v>46310.31707896989</v>
+        <v>46310.71708394251</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6">
         <v>0.2</v>
       </c>
       <c r="H23" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I23" s="6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
@@ -5431,28 +5544,28 @@
         <v>18</v>
       </c>
       <c r="O23" s="6">
-        <v>46300.7588479478</v>
+        <v>46310.71708389919</v>
       </c>
       <c r="P23" s="6">
-        <v>46310.31708860076</v>
+        <v>46310.7170838992</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6">
@@ -5465,14 +5578,12 @@
         <v>-3</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K24" s="6">
         <v>1</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="L24" s="6"/>
       <c r="M24" s="6" t="s">
         <v>18</v>
       </c>
@@ -5480,32 +5591,34 @@
         <v>18</v>
       </c>
       <c r="O24" s="6">
-        <v>46300.75884799581</v>
+        <v>46300.7588479478</v>
       </c>
       <c r="P24" s="6">
-        <v>46309.72496072845</v>
+        <v>46310.71708398541</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="G25" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H25" s="6">
         <v>46307</v>
@@ -5514,14 +5627,12 @@
         <v>-3</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K25" s="6">
         <v>1</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>183</v>
-      </c>
+      <c r="L25" s="6"/>
       <c r="M25" s="6" t="s">
         <v>18</v>
       </c>
@@ -5529,34 +5640,32 @@
         <v>18</v>
       </c>
       <c r="O25" s="6">
-        <v>46300.75885619673</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P25" s="6">
-        <v>46309.72496075697</v>
+        <v>46310.31707907124</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>85</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H26" s="6">
         <v>46307</v>
@@ -5565,13 +5674,13 @@
         <v>-3</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="K26" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>18</v>
@@ -5580,64 +5689,115 @@
         <v>18</v>
       </c>
       <c r="O26" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P26" s="6">
-        <v>46309.72496078632</v>
+        <v>46310.71709196248</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="6"/>
+        <v>83</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="G27" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H27" s="6">
+        <v>46307</v>
+      </c>
+      <c r="I27" s="6">
+        <v>-3</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K27" s="6">
+        <v>2</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="6">
+        <v>46305.20576106136</v>
+      </c>
+      <c r="P27" s="6">
+        <v>46309.72496078632</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6">
         <v>0.2</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H28" s="6">
         <v>46302</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I28" s="6">
         <v>-8</v>
       </c>
-      <c r="J27" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="K27" s="6">
-        <v>1</v>
-      </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O27" s="6">
+      <c r="J28" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K28" s="6">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="6">
         <v>46300.75885647022</v>
       </c>
-      <c r="P27" s="6">
-        <v>46310.31708883602</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>50</v>
+      <c r="P28" s="6">
+        <v>46310.71709214953</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q27"/>
+  <autoFilter ref="A1:Q28"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -5691,6 +5851,8 @@
     <hyperlink ref="N26" r:id="rId50"/>
     <hyperlink ref="M27" r:id="rId51"/>
     <hyperlink ref="N27" r:id="rId52"/>
+    <hyperlink ref="M28" r:id="rId53"/>
+    <hyperlink ref="N28" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5698,7 +5860,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5708,101 +5870,101 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B2">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D2">
         <v>193</v>
       </c>
       <c r="E2">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B3">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D3">
         <v>193</v>
       </c>
       <c r="E3">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -5811,53 +5973,53 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B4">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D4">
         <v>193</v>
       </c>
       <c r="E4">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B5">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D5">
         <v>193</v>
@@ -5869,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5886,13 +6048,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B6">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D6">
         <v>193</v>
@@ -5901,16 +6063,16 @@
         <v>3844</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -5921,48 +6083,48 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B7">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E7">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>381</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B8">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D8">
         <v>192</v>
@@ -5971,13 +6133,13 @@
         <v>3838</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5991,28 +6153,28 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B9">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D9">
         <v>192</v>
       </c>
       <c r="E9">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>369</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6021,18 +6183,18 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B10">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D10">
         <v>192</v>
@@ -6061,13 +6223,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B11">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D11">
         <v>192</v>
@@ -6079,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -6096,13 +6258,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B12">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D12">
         <v>192</v>
@@ -6131,13 +6293,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B13">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D13">
         <v>192</v>
@@ -6146,16 +6308,16 @@
         <v>3826</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -6166,48 +6328,48 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B14">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D14">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E14">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B15">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D15">
         <v>191</v>
@@ -6236,13 +6398,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B16">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D16">
         <v>191</v>
@@ -6254,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6271,13 +6433,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B17">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D17">
         <v>191</v>
@@ -6286,16 +6448,16 @@
         <v>3820</v>
       </c>
       <c r="F17">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H17">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -6306,48 +6468,48 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B18">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E18">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G18">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B19">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -6356,13 +6518,13 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -6371,18 +6533,18 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B20">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -6391,21 +6553,56 @@
         <v>160</v>
       </c>
       <c r="F20">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H20">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B21">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>160</v>
+      </c>
+      <c r="F21">
+        <v>157</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>132</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="226">
   <si>
     <t>Priority</t>
   </si>
@@ -79,522 +79,528 @@
     <t>Open</t>
   </si>
   <si>
+    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>MANISH AGARWALLA</t>
+  </si>
+  <si>
+    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>COMET GRANITO PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Anil Kashi Drolia</t>
+  </si>
+  <si>
+    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>ATKURU SAI PRASAD</t>
+  </si>
+  <si>
+    <t>Form-G Issued</t>
+  </si>
+  <si>
+    <t>M/s Margdarshak Financial Services Limited</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Jindal</t>
+  </si>
+  <si>
+    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
+  </si>
+  <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>Corrigendum dated 14 October 2026 to FORM G dated 28 September 2026</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chandra Kumar Jain</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>CORRIGENDUM TO FORM G INVITATION FOR EXPRESSION OF INTEREST FOR INDO PACIFIC PROJECTS LIMITED (Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SMO FERRO ALLOYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Rajesh Lohia</t>
+  </si>
+  <si>
+    <t>ALCOB INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRASHANT KHATAVKAR</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Kamal Agarwal</t>
+  </si>
+  <si>
+    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>The original Form G was published on 27th September 2026, with 12th October 2026 being the last date for submission of Expressions of Interest (EOIs). However, pursuant to the request received from the CoC members to extend the timeline for submission of</t>
+  </si>
+  <si>
+    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Abhit Kumar Singh</t>
+  </si>
+  <si>
+    <t>KUTE SONS DAIRYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ritesh R Mahajan</t>
+  </si>
+  <si>
+    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chirag Rajendra Kumar Shah</t>
+  </si>
+  <si>
+    <t>Form G published on 13th October 2026.</t>
+  </si>
+  <si>
+    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Hotel / Hospitality</t>
+  </si>
+  <si>
+    <t>Hotels / Resorts</t>
+  </si>
+  <si>
+    <t>Harsh Kumar Arora</t>
+  </si>
+  <si>
+    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
+  </si>
+  <si>
+    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Prashant Jain</t>
+  </si>
+  <si>
+    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
+  </si>
+  <si>
+    <t>STUTI COMTRADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
+  </si>
+  <si>
+    <t>2nd Form G.</t>
+  </si>
+  <si>
+    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shaikh Nafis Anjum</t>
+  </si>
+  <si>
+    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>JRA INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Parshva Manoj Shah</t>
+  </si>
+  <si>
+    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
     <t>Tripti Agarwal</t>
   </si>
   <si>
     <t>As per the latest available audited financial statement the Turnover in financial year 2022-2023 was Rs. 91.98 crore</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
-    <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>MANISH AGARWALLA</t>
-  </si>
-  <si>
-    <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
-  </si>
-  <si>
-    <t>COMET GRANITO PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Anil Kashi Drolia</t>
-  </si>
-  <si>
-    <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>ATKURU SAI PRASAD</t>
-  </si>
-  <si>
-    <t>Form-G Issued</t>
-  </si>
-  <si>
-    <t>M/s Margdarshak Financial Services Limited</t>
-  </si>
-  <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Jindal</t>
-  </si>
-  <si>
-    <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
-  </si>
-  <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chandra Kumar Jain</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>The addendum to form G was issued on 10th October, 2026.</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SMO FERRO ALLOYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Rajesh Lohia</t>
-  </si>
-  <si>
-    <t>ALCOB INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRASHANT KHATAVKAR</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>SUNSHINE FASTECH LIMITED</t>
-  </si>
-  <si>
-    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+    <t>KEW PRECISION PARTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shashi Bhushan Prasad</t>
+  </si>
+  <si>
+    <t>TV VISION LIMITED</t>
+  </si>
+  <si>
+    <t>ALOK KUMAR MURARKA</t>
+  </si>
+  <si>
+    <t>CITRON INFRAPROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Sunil Kumar Kabra</t>
+  </si>
+  <si>
+    <t>TECHNOFAB ENGINEERING LIMITED</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rahul Jindal</t>
+  </si>
+  <si>
+    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
+  </si>
+  <si>
+    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Ritu Rastogi</t>
+  </si>
+  <si>
+    <t>EXTOL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Ms. Teena Saraswat Pandey</t>
+  </si>
+  <si>
+    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
+  </si>
+  <si>
+    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Reetesh Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>XYRON TECHNOLOGIES LIMITED</t>
+  </si>
+  <si>
+    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
+  </si>
+  <si>
+    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
   </si>
   <si>
     <t>Not in latest IBBI listing - verify with RP</t>
   </si>
   <si>
-    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dev Vrat Rana</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
-  </si>
-  <si>
-    <t>SWADESH GREEN INFRA LIMITED</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Niraj Kumar</t>
-  </si>
-  <si>
-    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
-  </si>
-  <si>
-    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bishwa Ranjan Chatterjee</t>
-  </si>
-  <si>
-    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
-  </si>
-  <si>
-    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Kamal Agarwal</t>
-  </si>
-  <si>
-    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
-  </si>
-  <si>
-    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Abhit Kumar Singh</t>
-  </si>
-  <si>
-    <t>KUTE SONS DAIRYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ritesh R Mahajan</t>
-  </si>
-  <si>
-    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chirag Rajendra Kumar Shah</t>
-  </si>
-  <si>
-    <t>Form G published on 13th October 2026.</t>
-  </si>
-  <si>
-    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Hotel / Hospitality</t>
-  </si>
-  <si>
-    <t>Hotels / Resorts</t>
-  </si>
-  <si>
-    <t>Harsh Kumar Arora</t>
-  </si>
-  <si>
-    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
-  </si>
-  <si>
-    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Prashant Jain</t>
-  </si>
-  <si>
-    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
-  </si>
-  <si>
-    <t>STUTI COMTRADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
-  </si>
-  <si>
-    <t>2nd Form G.</t>
-  </si>
-  <si>
-    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Shaikh Nafis Anjum</t>
-  </si>
-  <si>
-    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>JRA INFRASTRUCTURE LIMITED</t>
-  </si>
-  <si>
-    <t>Parshva Manoj Shah</t>
-  </si>
-  <si>
-    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
-  </si>
-  <si>
-    <t>Resonance Paper Mill Private Limited</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
-    <t>KEW PRECISION PARTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Shashi Bhushan Prasad</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 28.09.2026.</t>
-  </si>
-  <si>
-    <t>TV VISION LIMITED</t>
-  </si>
-  <si>
-    <t>ALOK KUMAR MURARKA</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>CITRON INFRAPROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Sunil Kumar Kabra</t>
-  </si>
-  <si>
-    <t>TECHNOFAB ENGINEERING LIMITED</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Rahul Jindal</t>
-  </si>
-  <si>
-    <t>The Form G has been published on 27.09.2026 in newspapers all over India.</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>VIGNESHWARA DEVELOPERS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Ritu Rastogi</t>
-  </si>
-  <si>
-    <t>EXTOL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Ms. Teena Saraswat Pandey</t>
-  </si>
-  <si>
-    <t>unit closed, no employees / no workmen at CIRP commencement date</t>
-  </si>
-  <si>
-    <t>SURYA FOUNDRY PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Reetesh Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>XYRON TECHNOLOGIES LIMITED</t>
-  </si>
-  <si>
-    <t>unit closed As Per Information available no employees / No workmen at the commencement of CIRP Process</t>
-  </si>
-  <si>
-    <t>N KUMAR RETAILS &amp; PROPERTIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
-  </si>
-  <si>
     <t>A.P.J. LABORATORIES LIMITED</t>
   </si>
   <si>
@@ -656,21 +662,6 @@
   </si>
   <si>
     <t>Mr. Prem Chand Goyal</t>
-  </si>
-  <si>
-    <t>MORANI MOTORS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Automotive</t>
-  </si>
-  <si>
-    <t>Mr. Satyendra Prasad Khorania</t>
-  </si>
-  <si>
-    <t>SAKET PROMOTERS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Pratim Bayal</t>
   </si>
   <si>
     <t>Started</t>
@@ -1111,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1196,13 +1187,13 @@
         <v>20</v>
       </c>
       <c r="G2" s="2">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H2" s="3">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>21</v>
@@ -1220,10 +1211,10 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75884787029</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P2" s="2">
-        <v>46310.71708385317</v>
+        <v>46311.30744705819</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1243,13 +1234,13 @@
         <v>25</v>
       </c>
       <c r="G3" s="2">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="H3" s="3">
         <v>46312</v>
       </c>
       <c r="I3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>26</v>
@@ -1257,9 +1248,6 @@
       <c r="K3" s="2">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="M3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1267,10 +1255,10 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75884779022</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P3" s="2">
-        <v>46310.71708378154</v>
+        <v>46311.30744707253</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1284,10 +1272,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="G4" s="2">
         <v>0.93</v>
@@ -1296,14 +1284,17 @@
         <v>46312</v>
       </c>
       <c r="I4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="2">
-        <v>1</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1311,10 +1302,10 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884780569</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P4" s="2">
-        <v>46310.71708379548</v>
+        <v>46311.30744704161</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1331,25 +1322,25 @@
         <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H5" s="3">
         <v>46312</v>
       </c>
       <c r="I5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
@@ -1358,10 +1349,10 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P5" s="2">
-        <v>46310.71708380998</v>
+        <v>46311.30744702817</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1375,28 +1366,28 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2">
         <v>0.91</v>
       </c>
       <c r="H6" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I6" s="2">
         <v>2</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
@@ -1405,10 +1396,10 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75884783743</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P6" s="2">
-        <v>46310.7170838247</v>
+        <v>46311.3074470153</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1422,28 +1413,28 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G7" s="2">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H7" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I7" s="2">
         <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K7" s="2">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -1452,10 +1443,10 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46302.26841519317</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P7" s="2">
-        <v>46310.71708376709</v>
+        <v>46311.30744697552</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1469,22 +1460,19 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G8" s="2">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="3">
         <v>46314</v>
       </c>
       <c r="I8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>45</v>
@@ -1499,13 +1487,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.75884774033</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P8" s="2">
-        <v>46310.71708372193</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>46311.30744698845</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1516,19 +1504,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G9" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H9" s="3">
         <v>46314</v>
       </c>
       <c r="I9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>48</v>
@@ -1543,13 +1531,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.75884775587</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P9" s="2">
-        <v>46310.71708373787</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>49</v>
+        <v>46311.30744700151</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1560,22 +1548,22 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -1587,13 +1575,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.7588477715</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P10" s="2">
-        <v>46310.71708375273</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>23</v>
+        <v>46311.30744696164</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1604,19 +1592,19 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="G11" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H11" s="3">
         <v>46315</v>
       </c>
       <c r="I11" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>53</v>
@@ -1624,6 +1612,9 @@
       <c r="K11" s="2">
         <v>1</v>
       </c>
+      <c r="L11" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1631,13 +1622,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46300.75884772457</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P11" s="2">
-        <v>46310.71707578342</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>49</v>
+        <v>46311.30744694464</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1648,28 +1639,31 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="G12" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H12" s="3">
         <v>46315</v>
       </c>
       <c r="I12" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -1678,10 +1672,10 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46307.39550534703</v>
+        <v>46311.30744692709</v>
       </c>
       <c r="P12" s="2">
-        <v>46310.71707579794</v>
+        <v>46311.30744692712</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1695,10 +1689,10 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2">
         <v>0.2</v>
@@ -1707,16 +1701,16 @@
         <v>46316</v>
       </c>
       <c r="I13" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K13" s="2">
         <v>3</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -1728,10 +1722,10 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P13" s="2">
-        <v>46310.71707575507</v>
+        <v>46311.3074373737</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1742,10 +1736,10 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2">
         <v>0.92</v>
@@ -1754,16 +1748,16 @@
         <v>46316</v>
       </c>
       <c r="I14" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K14" s="2">
         <v>2</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -1775,7 +1769,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P14" s="2">
-        <v>46310.71707576897</v>
+        <v>46311.30743740102</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1789,10 +1783,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G15" s="2">
         <v>0.2</v>
@@ -1801,10 +1795,10 @@
         <v>46317</v>
       </c>
       <c r="I15" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
@@ -1819,10 +1813,10 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P15" s="2">
-        <v>46310.71707571246</v>
+        <v>46311.30743734578</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1833,13 +1827,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2">
         <v>0.9399999999999999</v>
@@ -1848,10 +1842,10 @@
         <v>46317</v>
       </c>
       <c r="I16" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
@@ -1866,7 +1860,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P16" s="2">
-        <v>46310.71707569752</v>
+        <v>46311.30743735946</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1880,10 +1874,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" s="2">
         <v>0.2</v>
@@ -1892,10 +1886,10 @@
         <v>46317</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
@@ -1910,45 +1904,45 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P17" s="2">
-        <v>46310.71707572688</v>
+        <v>46311.30743733215</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="2" customFormat="1">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="2">
         <v>0.96</v>
       </c>
       <c r="H18" s="3">
         <v>46318</v>
       </c>
-      <c r="I18">
-        <v>8</v>
-      </c>
-      <c r="J18" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>75</v>
+      <c r="I18" s="2">
+        <v>7</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -1956,46 +1950,46 @@
       <c r="N18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="2">
         <v>46305.20575267453</v>
       </c>
-      <c r="P18">
-        <v>46310.71707568316</v>
-      </c>
-      <c r="Q18" t="s">
+      <c r="P18" s="2">
+        <v>46311.30743726892</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19">
+    <row r="19" spans="1:17" s="2" customFormat="1">
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="2">
         <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="3">
         <v>46318</v>
       </c>
-      <c r="I19">
-        <v>8</v>
-      </c>
-      <c r="J19" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>79</v>
+      <c r="I19" s="2">
+        <v>7</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -2003,46 +1997,46 @@
       <c r="N19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="2">
         <v>46305.20575269723</v>
       </c>
-      <c r="P19">
-        <v>46310.7170756687</v>
-      </c>
-      <c r="Q19" t="s">
+      <c r="P19" s="2">
+        <v>46311.30743728172</v>
+      </c>
+      <c r="Q19" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20">
+    <row r="20" spans="1:17" s="2" customFormat="1">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="2">
         <v>0.91</v>
       </c>
       <c r="H20" s="3">
         <v>46318</v>
       </c>
-      <c r="I20">
-        <v>8</v>
-      </c>
-      <c r="J20" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20">
+      <c r="I20" s="2">
+        <v>7</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="2">
         <v>2</v>
       </c>
-      <c r="L20" t="s">
-        <v>81</v>
+      <c r="L20" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -2050,48 +2044,45 @@
       <c r="N20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="2">
         <v>46308.39986132324</v>
       </c>
-      <c r="P20">
-        <v>46310.71707565407</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="P20" s="2">
+        <v>46311.30743725552</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" t="s">
+    <row r="21" spans="1:17" s="2" customFormat="1">
+      <c r="A21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G21">
-        <v>0.93</v>
+      <c r="E21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.2</v>
       </c>
       <c r="H21" s="3">
-        <v>46319</v>
-      </c>
-      <c r="I21">
-        <v>9</v>
-      </c>
-      <c r="J21" t="s">
+        <v>46318</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>2</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" s="2" t="s">
         <v>86</v>
       </c>
       <c r="M21" s="4" t="s">
@@ -2100,14 +2091,14 @@
       <c r="N21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O21">
-        <v>46305.20575263901</v>
-      </c>
-      <c r="P21">
-        <v>46310.71707563939</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>23</v>
+      <c r="O21" s="2">
+        <v>46311.30743731892</v>
+      </c>
+      <c r="P21" s="2">
+        <v>46311.30743731892</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2121,25 +2112,28 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>88</v>
+      </c>
+      <c r="F22" t="s">
+        <v>89</v>
       </c>
       <c r="G22">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H22" s="3">
         <v>46319</v>
       </c>
       <c r="I22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K22">
         <v>2</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2148,13 +2142,13 @@
         <v>18</v>
       </c>
       <c r="O22">
-        <v>46307.39549700746</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P22">
-        <v>46310.71707561009</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>49</v>
+        <v>46311.30743724266</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2165,10 +2159,10 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G23">
         <v>0.2</v>
@@ -2177,13 +2171,16 @@
         <v>46319</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L23" t="s">
+        <v>94</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
@@ -2192,13 +2189,13 @@
         <v>18</v>
       </c>
       <c r="O23">
-        <v>46307.3954970362</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P23">
-        <v>46310.71707562462</v>
+        <v>46311.30743721643</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2209,25 +2206,25 @@
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="G24">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="H24" s="3">
         <v>46319</v>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2236,13 +2233,13 @@
         <v>18</v>
       </c>
       <c r="O24">
-        <v>46309.72495168629</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P24">
-        <v>46310.71707558073</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>23</v>
+        <v>46311.30743722944</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2253,25 +2250,25 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="G25">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H25" s="3">
         <v>46319</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2280,13 +2277,13 @@
         <v>18</v>
       </c>
       <c r="O25">
-        <v>46309.72495171529</v>
+        <v>46309.72495168629</v>
       </c>
       <c r="P25">
-        <v>46310.71707556527</v>
-      </c>
-      <c r="Q25" s="5" t="s">
-        <v>49</v>
+        <v>46311.30743717797</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2297,28 +2294,25 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="G26">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H26" s="3">
         <v>46319</v>
       </c>
       <c r="I26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2327,13 +2321,13 @@
         <v>18</v>
       </c>
       <c r="O26">
-        <v>46310.31707038325</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P26">
-        <v>46310.71707554919</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>23</v>
+        <v>46311.307437191</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2344,29 +2338,29 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>102</v>
+      </c>
+      <c r="F27" t="s">
+        <v>103</v>
       </c>
       <c r="G27">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H27" s="3">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
-      <c r="L27" t="s">
-        <v>102</v>
-      </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
       </c>
@@ -2374,10 +2368,10 @@
         <v>18</v>
       </c>
       <c r="O27">
-        <v>46307.3954969447</v>
+        <v>46310.31707038325</v>
       </c>
       <c r="P27">
-        <v>46310.71707551496</v>
+        <v>46311.30743720373</v>
       </c>
       <c r="Q27" t="s">
         <v>23</v>
@@ -2391,25 +2385,28 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G28">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H28" s="3">
         <v>46320</v>
       </c>
       <c r="I28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L28" t="s">
+        <v>107</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
@@ -2418,10 +2415,10 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46307.39549697415</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P28">
-        <v>46310.7170755324</v>
+        <v>46311.30743712274</v>
       </c>
       <c r="Q28" t="s">
         <v>23</v>
@@ -2435,22 +2432,22 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G29">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H29" s="3">
         <v>46320</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2462,13 +2459,13 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46308.39986123197</v>
+        <v>46307.39549697415</v>
       </c>
       <c r="P29">
-        <v>46310.31707032494</v>
-      </c>
-      <c r="Q29" s="5" t="s">
-        <v>107</v>
+        <v>46311.30743713841</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2479,22 +2476,22 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G30">
         <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46321</v>
+        <v>46320</v>
       </c>
       <c r="I30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2506,13 +2503,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46307.39549690609</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P30">
-        <v>46310.7170673743</v>
+        <v>46311.30743715168</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2523,28 +2520,25 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G31">
         <v>0.2</v>
       </c>
       <c r="H31" s="3">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K31">
-        <v>2</v>
-      </c>
-      <c r="L31" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2553,13 +2547,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46307.39549680641</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P31">
-        <v>46310.71706734345</v>
+        <v>46311.30742787745</v>
       </c>
       <c r="Q31" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2570,32 +2564,29 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="G32">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H32" s="3">
         <v>46322</v>
       </c>
       <c r="I32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J32" t="s">
+        <v>115</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32" t="s">
         <v>116</v>
       </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32" t="s">
-        <v>117</v>
-      </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
       </c>
@@ -2603,13 +2594,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46307.39549684311</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P32">
-        <v>46310.71706732902</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>23</v>
+        <v>46311.30742785161</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2620,29 +2611,32 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="F33" t="s">
+        <v>57</v>
       </c>
       <c r="G33">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H33" s="3">
         <v>46322</v>
       </c>
       <c r="I33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J33" t="s">
+        <v>118</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" t="s">
         <v>119</v>
       </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33" t="s">
-        <v>120</v>
-      </c>
       <c r="M33" s="4" t="s">
         <v>18</v>
       </c>
@@ -2650,13 +2644,13 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>46307.39549687663</v>
+        <v>46307.39549684311</v>
       </c>
       <c r="P33">
-        <v>46310.71706731404</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>49</v>
+        <v>46311.30742783823</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2667,32 +2661,29 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="G34">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H34" s="3">
         <v>46322</v>
       </c>
       <c r="I34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J34" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
         <v>122</v>
       </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="L34" t="s">
-        <v>123</v>
-      </c>
       <c r="M34" s="4" t="s">
         <v>18</v>
       </c>
@@ -2700,13 +2691,13 @@
         <v>18</v>
       </c>
       <c r="O34">
-        <v>46308.39986117012</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P34">
-        <v>46310.71706735919</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>23</v>
+        <v>46311.30742782442</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2717,26 +2708,32 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35">
+        <v>0.93</v>
+      </c>
+      <c r="H35" s="3">
+        <v>46322</v>
+      </c>
+      <c r="I35">
+        <v>11</v>
+      </c>
+      <c r="J35" t="s">
         <v>124</v>
       </c>
-      <c r="E35" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35">
-        <v>0.2</v>
-      </c>
-      <c r="H35" s="3">
-        <v>46323</v>
-      </c>
-      <c r="I35">
-        <v>13</v>
-      </c>
-      <c r="J35" t="s">
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" t="s">
         <v>125</v>
       </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
       <c r="M35" s="4" t="s">
         <v>18</v>
       </c>
@@ -2744,13 +2741,13 @@
         <v>18</v>
       </c>
       <c r="O35">
-        <v>46309.72494256633</v>
+        <v>46308.39986117012</v>
       </c>
       <c r="P35">
-        <v>46310.71706727032</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>49</v>
+        <v>46311.30742786467</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2764,22 +2761,25 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G36">
         <v>0.2</v>
       </c>
       <c r="H36" s="3">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="I36">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J36" t="s">
         <v>127</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L36" t="s">
+        <v>128</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>18</v>
@@ -2788,13 +2788,13 @@
         <v>18</v>
       </c>
       <c r="O36">
-        <v>46309.72494259723</v>
+        <v>46311.30742780836</v>
       </c>
       <c r="P36">
-        <v>46310.71706728528</v>
+        <v>46311.30742780838</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2805,10 +2805,10 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G37">
         <v>0.2</v>
@@ -2817,17 +2817,14 @@
         <v>46323</v>
       </c>
       <c r="I37">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="L37" t="s">
-        <v>130</v>
-      </c>
       <c r="M37" s="4" t="s">
         <v>18</v>
       </c>
@@ -2835,13 +2832,13 @@
         <v>18</v>
       </c>
       <c r="O37">
-        <v>46309.72494262765</v>
+        <v>46309.72494256633</v>
       </c>
       <c r="P37">
-        <v>46310.71706729976</v>
+        <v>46311.30742765773</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2855,29 +2852,23 @@
         <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>132</v>
-      </c>
-      <c r="F38" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="G38">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H38" s="3">
         <v>46323</v>
       </c>
       <c r="I38">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="L38" t="s">
-        <v>135</v>
-      </c>
       <c r="M38" s="4" t="s">
         <v>18</v>
       </c>
@@ -2885,13 +2876,13 @@
         <v>18</v>
       </c>
       <c r="O38">
-        <v>46310.31706138982</v>
+        <v>46309.72494259723</v>
       </c>
       <c r="P38">
-        <v>46310.71706725491</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>23</v>
+        <v>46311.30742767097</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2902,10 +2893,10 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G39">
         <v>0.2</v>
@@ -2914,16 +2905,16 @@
         <v>46323</v>
       </c>
       <c r="I39">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J39" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>18</v>
@@ -2932,13 +2923,13 @@
         <v>18</v>
       </c>
       <c r="O39">
-        <v>46310.71706723773</v>
+        <v>46309.72494262765</v>
       </c>
       <c r="P39">
-        <v>46310.71706723775</v>
+        <v>46311.30742768373</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2949,29 +2940,32 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40">
+        <v>0.96</v>
+      </c>
+      <c r="H40" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I40">
+        <v>12</v>
+      </c>
+      <c r="J40" t="s">
         <v>139</v>
       </c>
-      <c r="E40" t="s">
-        <v>47</v>
-      </c>
-      <c r="G40">
-        <v>0.2</v>
-      </c>
-      <c r="H40" s="3">
-        <v>46324</v>
-      </c>
-      <c r="I40">
-        <v>14</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
         <v>140</v>
       </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
-        <v>141</v>
-      </c>
       <c r="M40" s="4" t="s">
         <v>18</v>
       </c>
@@ -2979,13 +2973,13 @@
         <v>18</v>
       </c>
       <c r="O40">
-        <v>46309.72494253634</v>
+        <v>46310.31706138982</v>
       </c>
       <c r="P40">
-        <v>46310.71706709165</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>49</v>
+        <v>46311.30742764476</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -2996,29 +2990,29 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I41">
+        <v>12</v>
+      </c>
+      <c r="J41" t="s">
         <v>142</v>
       </c>
-      <c r="E41" t="s">
-        <v>39</v>
-      </c>
-      <c r="G41">
-        <v>0.91</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46324</v>
-      </c>
-      <c r="I41">
-        <v>14</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
         <v>143</v>
       </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-      <c r="L41" t="s">
-        <v>144</v>
-      </c>
       <c r="M41" s="4" t="s">
         <v>18</v>
       </c>
@@ -3026,13 +3020,13 @@
         <v>18</v>
       </c>
       <c r="O41">
-        <v>46310.31706133292</v>
+        <v>46310.71706723773</v>
       </c>
       <c r="P41">
-        <v>46310.71706707685</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>23</v>
+        <v>46311.30742763128</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -3043,32 +3037,29 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="3">
+        <v>46324</v>
+      </c>
+      <c r="I42">
+        <v>13</v>
+      </c>
+      <c r="J42" t="s">
         <v>145</v>
       </c>
-      <c r="E42" t="s">
-        <v>83</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
         <v>146</v>
       </c>
-      <c r="G42">
-        <v>0.89</v>
-      </c>
-      <c r="H42" s="3">
-        <v>46325</v>
-      </c>
-      <c r="I42">
-        <v>15</v>
-      </c>
-      <c r="J42" t="s">
-        <v>147</v>
-      </c>
-      <c r="K42">
-        <v>2</v>
-      </c>
-      <c r="L42" t="s">
-        <v>148</v>
-      </c>
       <c r="M42" s="4" t="s">
         <v>18</v>
       </c>
@@ -3076,13 +3067,13 @@
         <v>18</v>
       </c>
       <c r="O42">
-        <v>46309.72494249383</v>
+        <v>46309.72494253634</v>
       </c>
       <c r="P42">
-        <v>46310.71706706181</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>23</v>
+        <v>46311.30742761814</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -3093,26 +3084,29 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43">
+        <v>0.91</v>
+      </c>
+      <c r="H43" s="3">
+        <v>46324</v>
+      </c>
+      <c r="I43">
+        <v>13</v>
+      </c>
+      <c r="J43" t="s">
+        <v>148</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
         <v>149</v>
       </c>
-      <c r="E43" t="s">
-        <v>47</v>
-      </c>
-      <c r="G43">
-        <v>0.2</v>
-      </c>
-      <c r="H43" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I43">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>150</v>
-      </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
       <c r="M43" s="4" t="s">
         <v>18</v>
       </c>
@@ -3120,13 +3114,13 @@
         <v>18</v>
       </c>
       <c r="O43">
-        <v>46300.75884768533</v>
+        <v>46310.31706133292</v>
       </c>
       <c r="P43">
-        <v>46310.71706704683</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>49</v>
+        <v>46311.30742760486</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -3137,22 +3131,22 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" t="s">
         <v>151</v>
       </c>
-      <c r="E44" t="s">
-        <v>114</v>
-      </c>
-      <c r="F44" t="s">
-        <v>115</v>
-      </c>
       <c r="G44">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H44" s="3">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="I44">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J44" t="s">
         <v>152</v>
@@ -3170,10 +3164,10 @@
         <v>18</v>
       </c>
       <c r="O44">
-        <v>46308.39986111095</v>
+        <v>46309.72494249383</v>
       </c>
       <c r="P44">
-        <v>46310.71706701682</v>
+        <v>46311.30742759143</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3190,22 +3184,22 @@
         <v>154</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G45">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H45" s="3">
-        <v>46332</v>
+        <v>46326</v>
       </c>
       <c r="I45">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J45" t="s">
         <v>155</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>18</v>
@@ -3214,13 +3208,13 @@
         <v>18</v>
       </c>
       <c r="O45">
-        <v>46305.20575257758</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P45">
-        <v>46310.71706700103</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>23</v>
+        <v>46311.30742757768</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -3234,25 +3228,28 @@
         <v>156</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="F46" t="s">
+        <v>57</v>
       </c>
       <c r="G46">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H46" s="3">
-        <v>46333</v>
+        <v>46328</v>
       </c>
       <c r="I46">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J46" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>18</v>
@@ -3261,10 +3258,10 @@
         <v>18</v>
       </c>
       <c r="O46">
-        <v>46307.39549666931</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P46">
-        <v>46310.71706698506</v>
+        <v>46311.30742754995</v>
       </c>
       <c r="Q46" t="s">
         <v>23</v>
@@ -3278,25 +3275,25 @@
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E47" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="G47">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="H47" s="3">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="I47">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>18</v>
@@ -3305,136 +3302,129 @@
         <v>18</v>
       </c>
       <c r="O47">
-        <v>46307.39549671811</v>
+        <v>46305.20575257758</v>
       </c>
       <c r="P47">
-        <v>46310.71706695442</v>
+        <v>46311.30742753583</v>
       </c>
       <c r="Q47" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
         <v>161</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="E48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48">
+        <v>0.95</v>
+      </c>
+      <c r="H48" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I48">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>96</v>
+      </c>
+      <c r="K48">
+        <v>4</v>
+      </c>
+      <c r="L48" t="s">
         <v>162</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H48" s="6">
-        <v>46309</v>
-      </c>
-      <c r="I48" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J48" s="6" t="s">
+      <c r="M48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48">
+        <v>46307.39549666931</v>
+      </c>
+      <c r="P48">
+        <v>46311.30742752137</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
         <v>163</v>
       </c>
-      <c r="K48" s="6">
-        <v>1</v>
-      </c>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O48" s="6">
-        <v>46308.39987059968</v>
-      </c>
-      <c r="P48" s="6">
-        <v>46310.71708386733</v>
-      </c>
-      <c r="Q48" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17">
-      <c r="A49" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49" s="6" t="s">
+      <c r="E49" t="s">
+        <v>79</v>
+      </c>
+      <c r="G49">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H49" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I49">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
         <v>164</v>
       </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G49" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H49" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I49" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K49" s="6">
-        <v>1</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O49" s="6">
-        <v>46300.75884788632</v>
-      </c>
-      <c r="P49" s="6">
-        <v>46310.71708392838</v>
-      </c>
-      <c r="Q49" s="6" t="s">
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49">
+        <v>46307.39549671811</v>
+      </c>
+      <c r="P49">
+        <v>46311.30742749263</v>
+      </c>
+      <c r="Q49" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>167</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H50" s="6">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="I50" s="6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>168</v>
@@ -3442,7 +3432,9 @@
       <c r="K50" s="6">
         <v>1</v>
       </c>
-      <c r="L50" s="6"/>
+      <c r="L50" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
       </c>
@@ -3450,41 +3442,41 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75884790152</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P50" s="6">
-        <v>46310.7170839139</v>
-      </c>
-      <c r="Q50" s="5" t="s">
-        <v>49</v>
+        <v>46311.30744709933</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
         <v>0.2</v>
       </c>
       <c r="H51" s="6">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I51" s="6">
         <v>-2</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K51" s="6">
         <v>1</v>
@@ -3497,28 +3489,28 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46301.38232480602</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P51" s="6">
-        <v>46310.71708394251</v>
+        <v>46311.30744711268</v>
       </c>
       <c r="Q51" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
@@ -3528,10 +3520,10 @@
         <v>46308</v>
       </c>
       <c r="I52" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K52" s="6">
         <v>1</v>
@@ -3544,50 +3536,46 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46310.71708389919</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P52" s="6">
-        <v>46310.7170838992</v>
+        <v>46311.30744716735</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>175</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="6">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="H53" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I53" s="6">
         <v>-3</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K53" s="6">
         <v>1</v>
       </c>
-      <c r="L53" s="6" t="s">
-        <v>177</v>
-      </c>
+      <c r="L53" s="6"/>
       <c r="M53" s="6" t="s">
         <v>18</v>
       </c>
@@ -3595,38 +3583,40 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46300.75884793277</v>
+        <v>46310.71708389919</v>
       </c>
       <c r="P53" s="6">
-        <v>46310.71709191583</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>23</v>
+        <v>46311.30744715399</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F54" s="6"/>
+        <v>177</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="G54" s="6">
-        <v>0.2</v>
+        <v>0.88</v>
       </c>
       <c r="H54" s="6">
         <v>46307</v>
       </c>
       <c r="I54" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>179</v>
@@ -3634,7 +3624,9 @@
       <c r="K54" s="6">
         <v>1</v>
       </c>
-      <c r="L54" s="6"/>
+      <c r="L54" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="M54" s="6" t="s">
         <v>18</v>
       </c>
@@ -3642,31 +3634,31 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.7588479478</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P54" s="6">
-        <v>46310.71708398541</v>
-      </c>
-      <c r="Q54" s="5" t="s">
-        <v>49</v>
+        <v>46311.30745569724</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G55" s="6">
         <v>0.93</v>
@@ -3675,10 +3667,10 @@
         <v>46307</v>
       </c>
       <c r="I55" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K55" s="6">
         <v>1</v>
@@ -3694,25 +3686,25 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46310.31707907124</v>
-      </c>
-      <c r="Q55" s="5" t="s">
-        <v>107</v>
+        <v>46311.30745564263</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6">
@@ -3722,16 +3714,16 @@
         <v>46307</v>
       </c>
       <c r="I56" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K56" s="6">
         <v>1</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>18</v>
@@ -3743,25 +3735,25 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46310.71709196248</v>
+        <v>46311.30745573662</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6">
@@ -3771,10 +3763,10 @@
         <v>46307</v>
       </c>
       <c r="I57" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K57" s="6">
         <v>1</v>
@@ -3790,7 +3782,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46310.71709193088</v>
+        <v>46311.3074557103</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3798,17 +3790,17 @@
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6">
@@ -3818,16 +3810,16 @@
         <v>46307</v>
       </c>
       <c r="I58" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>18</v>
@@ -3839,7 +3831,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46310.71709194721</v>
+        <v>46311.30745572347</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3847,20 +3839,20 @@
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G59" s="6">
         <v>0.93</v>
@@ -3869,16 +3861,16 @@
         <v>46307</v>
       </c>
       <c r="I59" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K59" s="6">
         <v>2</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>18</v>
@@ -3893,25 +3885,25 @@
         <v>46309.72496078632</v>
       </c>
       <c r="Q59" s="5" t="s">
-        <v>107</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G60" s="6">
         <v>0.9399999999999999</v>
@@ -3920,16 +3912,16 @@
         <v>46306</v>
       </c>
       <c r="I60" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K60" s="6">
         <v>1</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>18</v>
@@ -3941,7 +3933,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46310.71709199282</v>
+        <v>46311.30745576383</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3949,17 +3941,17 @@
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6">
@@ -3969,16 +3961,16 @@
         <v>46306</v>
       </c>
       <c r="I61" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K61" s="6">
         <v>1</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>18</v>
@@ -3990,7 +3982,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46310.71709202128</v>
+        <v>46311.30745577747</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -3998,17 +3990,17 @@
     </row>
     <row r="62" spans="1:17">
       <c r="A62" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6">
@@ -4018,16 +4010,16 @@
         <v>46305</v>
       </c>
       <c r="I62" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K62" s="6">
         <v>1</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>18</v>
@@ -4039,7 +4031,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46310.71709205015</v>
+        <v>46311.30745581691</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4047,17 +4039,17 @@
     </row>
     <row r="63" spans="1:17">
       <c r="A63" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6">
@@ -4067,16 +4059,16 @@
         <v>46304</v>
       </c>
       <c r="I63" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K63" s="6">
         <v>1</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>18</v>
@@ -4088,7 +4080,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46310.71709209287</v>
+        <v>46311.30745584252</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4096,20 +4088,20 @@
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G64" s="6">
         <v>0.9399999999999999</v>
@@ -4118,16 +4110,16 @@
         <v>46303</v>
       </c>
       <c r="I64" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K64" s="6">
         <v>2</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>18</v>
@@ -4139,7 +4131,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46310.71709213552</v>
+        <v>46311.30745586863</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
@@ -4147,17 +4139,17 @@
     </row>
     <row r="65" spans="1:17">
       <c r="A65" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6">
@@ -4167,10 +4159,10 @@
         <v>46302</v>
       </c>
       <c r="I65" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K65" s="6">
         <v>1</v>
@@ -4186,28 +4178,28 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P65" s="6">
-        <v>46310.71709214953</v>
+        <v>46311.30746437659</v>
       </c>
       <c r="Q65" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:17">
       <c r="A66" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G66" s="6">
         <v>0.9399999999999999</v>
@@ -4216,10 +4208,10 @@
         <v>46301</v>
       </c>
       <c r="I66" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K66" s="6">
         <v>2</v>
@@ -4235,110 +4227,14 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P66" s="6">
-        <v>46310.71710011137</v>
+        <v>46311.3074644164</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:17">
-      <c r="A67" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="H67" s="6">
-        <v>46300</v>
-      </c>
-      <c r="I67" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J67" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="K67" s="6">
-        <v>1</v>
-      </c>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N67" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O67" s="6">
-        <v>46300.75886463693</v>
-      </c>
-      <c r="P67" s="6">
-        <v>46310.7171001574</v>
-      </c>
-      <c r="Q67" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17">
-      <c r="A68" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G68" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="H68" s="6">
-        <v>46300</v>
-      </c>
-      <c r="I68" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J68" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K68" s="6">
-        <v>1</v>
-      </c>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O68" s="6">
-        <v>46300.75886465221</v>
-      </c>
-      <c r="P68" s="6">
-        <v>46310.71710014256</v>
-      </c>
-      <c r="Q68" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q68"/>
+  <autoFilter ref="A1:Q66"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4470,10 +4366,6 @@
     <hyperlink ref="N65" r:id="rId128"/>
     <hyperlink ref="M66" r:id="rId129"/>
     <hyperlink ref="N66" r:id="rId130"/>
-    <hyperlink ref="M67" r:id="rId131"/>
-    <hyperlink ref="N67" r:id="rId132"/>
-    <hyperlink ref="M68" r:id="rId133"/>
-    <hyperlink ref="N68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4481,7 +4373,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4560,10 +4452,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
@@ -4572,10 +4464,10 @@
         <v>46314</v>
       </c>
       <c r="I2" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -4590,10 +4482,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46310.71708373787</v>
+        <v>46311.30744698845</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4604,10 +4496,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -4616,10 +4508,10 @@
         <v>46315</v>
       </c>
       <c r="I3" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4634,10 +4526,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46310.71707578342</v>
+        <v>46311.30744696164</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4648,10 +4540,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
@@ -4660,16 +4552,16 @@
         <v>46316</v>
       </c>
       <c r="I4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="2">
         <v>3</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -4681,10 +4573,10 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46310.71707575507</v>
+        <v>46311.3074373737</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4695,10 +4587,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -4707,10 +4599,10 @@
         <v>46317</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -4725,10 +4617,10 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46310.71707571246</v>
+        <v>46311.30743734578</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -4739,10 +4631,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2">
         <v>0.2</v>
@@ -4751,10 +4643,10 @@
         <v>46317</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -4769,42 +4661,42 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46310.71707572688</v>
+        <v>46311.30743733215</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="2" customFormat="1">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="2">
         <v>0.2</v>
       </c>
       <c r="H7" s="3">
-        <v>46319</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K7">
+        <v>46318</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="2">
         <v>2</v>
       </c>
-      <c r="L7" t="s">
-        <v>89</v>
+      <c r="L7" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4812,14 +4704,14 @@
       <c r="N7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O7">
-        <v>46307.39549700746</v>
-      </c>
-      <c r="P7">
-        <v>46310.71707561009</v>
+      <c r="O7" s="2">
+        <v>46311.30743731892</v>
+      </c>
+      <c r="P7" s="2">
+        <v>46311.30743731892</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4830,10 +4722,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G8">
         <v>0.2</v>
@@ -4842,13 +4734,16 @@
         <v>46319</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L8" t="s">
+        <v>94</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -4857,13 +4752,13 @@
         <v>18</v>
       </c>
       <c r="O8">
-        <v>46307.3954970362</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P8">
-        <v>46310.71707562462</v>
+        <v>46311.30743721643</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4874,10 +4769,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>0.2</v>
@@ -4886,10 +4781,10 @@
         <v>46319</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4901,13 +4796,13 @@
         <v>18</v>
       </c>
       <c r="O9">
-        <v>46309.72495171529</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P9">
-        <v>46310.71707556527</v>
+        <v>46311.30743722944</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4918,22 +4813,22 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -4945,13 +4840,13 @@
         <v>18</v>
       </c>
       <c r="O10">
-        <v>46308.39986123197</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P10">
-        <v>46310.31707032494</v>
+        <v>46311.307437191</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -4962,22 +4857,22 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G11">
         <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46321</v>
+        <v>46320</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4989,13 +4884,13 @@
         <v>18</v>
       </c>
       <c r="O11">
-        <v>46307.39549690609</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46310.7170673743</v>
+        <v>46311.30743715168</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -5006,28 +4901,25 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G12">
         <v>0.2</v>
       </c>
       <c r="H12" s="3">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K12">
-        <v>2</v>
-      </c>
-      <c r="L12" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -5036,13 +4928,13 @@
         <v>18</v>
       </c>
       <c r="O12">
-        <v>46307.39549680641</v>
+        <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46310.71706734345</v>
+        <v>46311.30742787745</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -5053,10 +4945,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G13">
         <v>0.2</v>
@@ -5065,16 +4957,16 @@
         <v>46322</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -5083,13 +4975,13 @@
         <v>18</v>
       </c>
       <c r="O13">
-        <v>46307.39549687663</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46310.71706731404</v>
+        <v>46311.30742785161</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -5100,26 +4992,29 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G14">
         <v>0.2</v>
       </c>
       <c r="H14" s="3">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="I14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
+      <c r="L14" t="s">
+        <v>122</v>
+      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -5127,13 +5022,13 @@
         <v>18</v>
       </c>
       <c r="O14">
-        <v>46309.72494256633</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46310.71706727032</v>
+        <v>46311.30742782442</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -5147,22 +5042,25 @@
         <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G15">
         <v>0.2</v>
       </c>
       <c r="H15" s="3">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J15" t="s">
         <v>127</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>128</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
@@ -5171,13 +5069,13 @@
         <v>18</v>
       </c>
       <c r="O15">
-        <v>46309.72494259723</v>
+        <v>46311.30742780836</v>
       </c>
       <c r="P15">
-        <v>46310.71706728528</v>
+        <v>46311.30742780838</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -5188,10 +5086,10 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16">
         <v>0.2</v>
@@ -5200,17 +5098,14 @@
         <v>46323</v>
       </c>
       <c r="I16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="L16" t="s">
-        <v>130</v>
-      </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
       </c>
@@ -5218,13 +5113,13 @@
         <v>18</v>
       </c>
       <c r="O16">
-        <v>46309.72494262765</v>
+        <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46310.71706729976</v>
+        <v>46311.30742765773</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -5235,10 +5130,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>0.2</v>
@@ -5247,17 +5142,14 @@
         <v>46323</v>
       </c>
       <c r="I17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="L17" t="s">
-        <v>138</v>
-      </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
       </c>
@@ -5265,13 +5157,13 @@
         <v>18</v>
       </c>
       <c r="O17">
-        <v>46310.71706723773</v>
+        <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46310.71706723775</v>
+        <v>46311.30742767097</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -5282,28 +5174,28 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G18">
         <v>0.2</v>
       </c>
       <c r="H18" s="3">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J18" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -5312,13 +5204,13 @@
         <v>18</v>
       </c>
       <c r="O18">
-        <v>46309.72494253634</v>
+        <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46310.71706709165</v>
+        <v>46311.30742768373</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -5329,162 +5221,162 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G19">
         <v>0.2</v>
       </c>
       <c r="H19" s="3">
+        <v>46323</v>
+      </c>
+      <c r="I19">
+        <v>12</v>
+      </c>
+      <c r="J19" t="s">
+        <v>142</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>143</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19">
+        <v>46310.71706723773</v>
+      </c>
+      <c r="P19">
+        <v>46311.30742763128</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>46324</v>
+      </c>
+      <c r="I20">
+        <v>13</v>
+      </c>
+      <c r="J20" t="s">
+        <v>145</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20">
+        <v>46309.72494253634</v>
+      </c>
+      <c r="P20">
+        <v>46311.30742761814</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21">
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="3">
         <v>46326</v>
       </c>
-      <c r="I19">
-        <v>16</v>
-      </c>
-      <c r="J19" t="s">
-        <v>150</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19">
+      <c r="I21">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21">
         <v>46300.75884768533</v>
       </c>
-      <c r="P19">
-        <v>46310.71706704683</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="6">
-        <v>46309</v>
-      </c>
-      <c r="I20" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K20" s="6">
-        <v>1</v>
-      </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46308.39987059968</v>
-      </c>
-      <c r="P20" s="6">
-        <v>46310.71708386733</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
-      <c r="A21" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H21" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I21" s="6">
-        <v>-2</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K21" s="6">
-        <v>1</v>
-      </c>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="6">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P21" s="6">
-        <v>46310.7170839139</v>
+      <c r="P21">
+        <v>46311.30742757768</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6">
         <v>0.2</v>
       </c>
       <c r="H22" s="6">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="I22" s="6">
         <v>-2</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K22" s="6">
         <v>1</v>
@@ -5497,28 +5389,28 @@
         <v>18</v>
       </c>
       <c r="O22" s="6">
-        <v>46301.38232480602</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P22" s="6">
-        <v>46310.71708394251</v>
+        <v>46311.30744711268</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6">
@@ -5528,10 +5420,10 @@
         <v>46308</v>
       </c>
       <c r="I23" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
@@ -5544,41 +5436,41 @@
         <v>18</v>
       </c>
       <c r="O23" s="6">
-        <v>46310.71708389919</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P23" s="6">
-        <v>46310.7170838992</v>
+        <v>46311.30744716735</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6">
         <v>0.2</v>
       </c>
       <c r="H24" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I24" s="6">
         <v>-3</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K24" s="6">
         <v>1</v>
@@ -5591,48 +5483,48 @@
         <v>18</v>
       </c>
       <c r="O24" s="6">
-        <v>46300.7588479478</v>
+        <v>46310.71708389919</v>
       </c>
       <c r="P24" s="6">
-        <v>46310.71708398541</v>
+        <v>46311.30744715399</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F25" s="6"/>
       <c r="G25" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="6">
         <v>46307</v>
       </c>
       <c r="I25" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K25" s="6">
         <v>1</v>
       </c>
-      <c r="L25" s="6"/>
+      <c r="L25" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="M25" s="6" t="s">
         <v>18</v>
       </c>
@@ -5640,47 +5532,49 @@
         <v>18</v>
       </c>
       <c r="O25" s="6">
-        <v>46300.75884796329</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P25" s="6">
-        <v>46310.31707907124</v>
+        <v>46311.30745573662</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="G26" s="6">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H26" s="6">
         <v>46307</v>
       </c>
       <c r="I26" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="K26" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>18</v>
@@ -5689,50 +5583,46 @@
         <v>18</v>
       </c>
       <c r="O26" s="6">
-        <v>46300.75884799581</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P26" s="6">
-        <v>46310.71709196248</v>
+        <v>46309.72496078632</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>49</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>84</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F27" s="6"/>
       <c r="G27" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H27" s="6">
-        <v>46307</v>
+        <v>46302</v>
       </c>
       <c r="I27" s="6">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="K27" s="6">
-        <v>2</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>190</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L27" s="6"/>
       <c r="M27" s="6" t="s">
         <v>18</v>
       </c>
@@ -5740,64 +5630,17 @@
         <v>18</v>
       </c>
       <c r="O27" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75885647022</v>
       </c>
       <c r="P27" s="6">
-        <v>46309.72496078632</v>
+        <v>46311.30746437659</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
-      <c r="A28" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H28" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I28" s="6">
-        <v>-8</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="K28" s="6">
-        <v>1</v>
-      </c>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O28" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P28" s="6">
-        <v>46310.71709214953</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q28"/>
+  <autoFilter ref="A1:Q27"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -5851,8 +5694,6 @@
     <hyperlink ref="N26" r:id="rId50"/>
     <hyperlink ref="M27" r:id="rId51"/>
     <hyperlink ref="N27" r:id="rId52"/>
-    <hyperlink ref="M28" r:id="rId53"/>
-    <hyperlink ref="N28" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5860,7 +5701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5870,136 +5711,136 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46310.71705220221</v>
+        <v>46311.3074085582</v>
       </c>
       <c r="B2">
-        <v>46310.71871343154</v>
+        <v>46311.31082826155</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E2">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>394</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3858</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B3">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D3">
         <v>193</v>
       </c>
       <c r="E3">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B4">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D4">
         <v>193</v>
       </c>
       <c r="E4">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -6008,53 +5849,53 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B5">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D5">
         <v>193</v>
       </c>
       <c r="E5">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B6">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D6">
         <v>193</v>
@@ -6066,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -6083,13 +5924,13 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B7">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D7">
         <v>193</v>
@@ -6098,16 +5939,16 @@
         <v>3844</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -6118,48 +5959,48 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B8">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E8">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>381</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B9">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D9">
         <v>192</v>
@@ -6168,13 +6009,13 @@
         <v>3838</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6188,28 +6029,28 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B10">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D10">
         <v>192</v>
       </c>
       <c r="E10">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>369</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6218,18 +6059,18 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B11">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D11">
         <v>192</v>
@@ -6258,13 +6099,13 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B12">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D12">
         <v>192</v>
@@ -6276,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -6293,13 +6134,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B13">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D13">
         <v>192</v>
@@ -6328,13 +6169,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B14">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D14">
         <v>192</v>
@@ -6343,16 +6184,16 @@
         <v>3826</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -6363,48 +6204,48 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B15">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D15">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E15">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B16">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D16">
         <v>191</v>
@@ -6433,13 +6274,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B17">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D17">
         <v>191</v>
@@ -6451,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -6468,13 +6309,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B18">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D18">
         <v>191</v>
@@ -6483,16 +6324,16 @@
         <v>3820</v>
       </c>
       <c r="F18">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H18">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -6503,48 +6344,48 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B19">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E19">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G19">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B20">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -6553,13 +6394,13 @@
         <v>160</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -6568,18 +6409,18 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B21">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -6588,21 +6429,56 @@
         <v>160</v>
       </c>
       <c r="F21">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H21">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B22">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>160</v>
+      </c>
+      <c r="F22">
+        <v>157</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>132</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="226">
   <si>
     <t>Priority</t>
   </si>
@@ -1214,7 +1214,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P2" s="2">
-        <v>46311.30744705819</v>
+        <v>46311.70088691096</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1258,7 +1258,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P3" s="2">
-        <v>46311.30744707253</v>
+        <v>46311.70088692041</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1305,7 +1305,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P4" s="2">
-        <v>46311.30744704161</v>
+        <v>46311.70088690126</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1352,7 +1352,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P5" s="2">
-        <v>46311.30744702817</v>
+        <v>46311.70088689196</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1399,7 +1399,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P6" s="2">
-        <v>46311.3074470153</v>
+        <v>46311.70088688222</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1446,7 +1446,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P7" s="2">
-        <v>46311.30744697552</v>
+        <v>46311.70088685404</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1490,7 +1490,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P8" s="2">
-        <v>46311.30744698845</v>
+        <v>46311.70088686351</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
@@ -1534,7 +1534,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P9" s="2">
-        <v>46311.30744700151</v>
+        <v>46311.70088687293</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>23</v>
@@ -1578,7 +1578,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P10" s="2">
-        <v>46311.30744696164</v>
+        <v>46311.70088684419</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -1625,7 +1625,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P11" s="2">
-        <v>46311.30744694464</v>
+        <v>46311.70088683406</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>23</v>
@@ -1675,7 +1675,7 @@
         <v>46311.30744692709</v>
       </c>
       <c r="P12" s="2">
-        <v>46311.30744692712</v>
+        <v>46311.70088682229</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1722,7 +1722,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P13" s="2">
-        <v>46311.3074373737</v>
+        <v>46311.70087868374</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -1769,7 +1769,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P14" s="2">
-        <v>46311.30743740102</v>
+        <v>46311.7008787021</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1813,7 +1813,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P15" s="2">
-        <v>46311.30743734578</v>
+        <v>46311.70087866466</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -1860,7 +1860,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P16" s="2">
-        <v>46311.30743735946</v>
+        <v>46311.70087867416</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1904,7 +1904,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P17" s="2">
-        <v>46311.30743733215</v>
+        <v>46311.70087865533</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -1954,7 +1954,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P18" s="2">
-        <v>46311.30743726892</v>
+        <v>46311.70087862734</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -2001,7 +2001,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P19" s="2">
-        <v>46311.30743728172</v>
+        <v>46311.70087863646</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>23</v>
@@ -2048,7 +2048,7 @@
         <v>46308.39986132324</v>
       </c>
       <c r="P20" s="2">
-        <v>46311.30743725552</v>
+        <v>46311.70087861818</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>23</v>
@@ -2095,7 +2095,7 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P21" s="2">
-        <v>46311.30743731892</v>
+        <v>46311.70087864589</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>46</v>
@@ -2145,7 +2145,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P22">
-        <v>46311.30743724266</v>
+        <v>46311.7008786087</v>
       </c>
       <c r="Q22" t="s">
         <v>23</v>
@@ -2192,7 +2192,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P23">
-        <v>46311.30743721643</v>
+        <v>46311.70087858952</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
@@ -2236,7 +2236,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P24">
-        <v>46311.30743722944</v>
+        <v>46311.70087859921</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>46</v>
@@ -2280,7 +2280,7 @@
         <v>46309.72495168629</v>
       </c>
       <c r="P25">
-        <v>46311.30743717797</v>
+        <v>46311.70087856058</v>
       </c>
       <c r="Q25" t="s">
         <v>23</v>
@@ -2324,7 +2324,7 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P26">
-        <v>46311.307437191</v>
+        <v>46311.70087857031</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>46</v>
@@ -2371,7 +2371,7 @@
         <v>46310.31707038325</v>
       </c>
       <c r="P27">
-        <v>46311.30743720373</v>
+        <v>46311.70087857965</v>
       </c>
       <c r="Q27" t="s">
         <v>23</v>
@@ -2418,7 +2418,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P28">
-        <v>46311.30743712274</v>
+        <v>46311.7008785186</v>
       </c>
       <c r="Q28" t="s">
         <v>23</v>
@@ -2462,7 +2462,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P29">
-        <v>46311.30743713841</v>
+        <v>46311.7008785302</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2506,7 +2506,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P30">
-        <v>46311.30743715168</v>
+        <v>46311.70087854062</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>46</v>
@@ -2550,7 +2550,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P31">
-        <v>46311.30742787745</v>
+        <v>46311.70087044157</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>46</v>
@@ -2597,7 +2597,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P32">
-        <v>46311.30742785161</v>
+        <v>46311.70087042241</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>46</v>
@@ -2647,7 +2647,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P33">
-        <v>46311.30742783823</v>
+        <v>46311.70087041293</v>
       </c>
       <c r="Q33" t="s">
         <v>23</v>
@@ -2694,7 +2694,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P34">
-        <v>46311.30742782442</v>
+        <v>46311.70087040275</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>46</v>
@@ -2744,7 +2744,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P35">
-        <v>46311.30742786467</v>
+        <v>46311.70087043183</v>
       </c>
       <c r="Q35" t="s">
         <v>23</v>
@@ -2791,7 +2791,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P36">
-        <v>46311.30742780838</v>
+        <v>46311.70087039313</v>
       </c>
       <c r="Q36" s="5" t="s">
         <v>46</v>
@@ -2835,7 +2835,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P37">
-        <v>46311.30742765773</v>
+        <v>46311.700870364</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>46</v>
@@ -2879,7 +2879,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P38">
-        <v>46311.30742767097</v>
+        <v>46311.70087037373</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>46</v>
@@ -2926,7 +2926,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P39">
-        <v>46311.30742768373</v>
+        <v>46311.70087038344</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>46</v>
@@ -2976,7 +2976,7 @@
         <v>46310.31706138982</v>
       </c>
       <c r="P40">
-        <v>46311.30742764476</v>
+        <v>46311.70087035413</v>
       </c>
       <c r="Q40" t="s">
         <v>23</v>
@@ -3023,7 +3023,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P41">
-        <v>46311.30742763128</v>
+        <v>46311.70087034364</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>46</v>
@@ -3070,7 +3070,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P42">
-        <v>46311.30742761814</v>
+        <v>46311.70087033371</v>
       </c>
       <c r="Q42" s="5" t="s">
         <v>46</v>
@@ -3117,7 +3117,7 @@
         <v>46310.31706133292</v>
       </c>
       <c r="P43">
-        <v>46311.30742760486</v>
+        <v>46311.70087032368</v>
       </c>
       <c r="Q43" t="s">
         <v>23</v>
@@ -3167,7 +3167,7 @@
         <v>46309.72494249383</v>
       </c>
       <c r="P44">
-        <v>46311.30742759143</v>
+        <v>46311.70087031323</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3211,7 +3211,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P45">
-        <v>46311.30742757768</v>
+        <v>46311.70087030291</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>46</v>
@@ -3261,7 +3261,7 @@
         <v>46308.39986111095</v>
       </c>
       <c r="P46">
-        <v>46311.30742754995</v>
+        <v>46311.7008702819</v>
       </c>
       <c r="Q46" t="s">
         <v>23</v>
@@ -3305,7 +3305,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P47">
-        <v>46311.30742753583</v>
+        <v>46311.70087027091</v>
       </c>
       <c r="Q47" t="s">
         <v>23</v>
@@ -3352,7 +3352,7 @@
         <v>46307.39549666931</v>
       </c>
       <c r="P48">
-        <v>46311.30742752137</v>
+        <v>46311.70087025949</v>
       </c>
       <c r="Q48" t="s">
         <v>23</v>
@@ -3396,7 +3396,7 @@
         <v>46307.39549671811</v>
       </c>
       <c r="P49">
-        <v>46311.30742749263</v>
+        <v>46311.70087023666</v>
       </c>
       <c r="Q49" t="s">
         <v>23</v>
@@ -3445,7 +3445,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P50" s="6">
-        <v>46311.30744709933</v>
+        <v>46311.70088693928</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3492,7 +3492,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P51" s="6">
-        <v>46311.30744711268</v>
+        <v>46311.70088694827</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>46</v>
@@ -3539,7 +3539,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P52" s="6">
-        <v>46311.30744716735</v>
+        <v>46311.70088698581</v>
       </c>
       <c r="Q52" s="5" t="s">
         <v>46</v>
@@ -3586,7 +3586,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P53" s="6">
-        <v>46311.30744715399</v>
+        <v>46311.70088697635</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>46</v>
@@ -3637,7 +3637,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P54" s="6">
-        <v>46311.30745569724</v>
+        <v>46311.70089512802</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>23</v>
@@ -3686,7 +3686,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46311.30745564263</v>
+        <v>46311.70089508668</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3735,7 +3735,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46311.30745573662</v>
+        <v>46311.70089515702</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>46</v>
@@ -3782,7 +3782,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46311.3074557103</v>
+        <v>46311.70089513763</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3831,7 +3831,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46311.30745572347</v>
+        <v>46311.70089514742</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3933,7 +3933,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46311.30745576383</v>
+        <v>46311.70089517583</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3982,7 +3982,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46311.30745577747</v>
+        <v>46311.70089518549</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -4031,7 +4031,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46311.30745581691</v>
+        <v>46311.70089521474</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4080,7 +4080,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46311.30745584252</v>
+        <v>46311.70089523357</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4131,7 +4131,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46311.30745586863</v>
+        <v>46311.7008952556</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
@@ -4178,7 +4178,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P65" s="6">
-        <v>46311.30746437659</v>
+        <v>46311.70090339411</v>
       </c>
       <c r="Q65" s="5" t="s">
         <v>46</v>
@@ -4227,7 +4227,7 @@
         <v>46300.75885649968</v>
       </c>
       <c r="P66" s="6">
-        <v>46311.3074644164</v>
+        <v>46311.70090342543</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>23</v>
@@ -4482,7 +4482,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46311.30744698845</v>
+        <v>46311.70088686351</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>46</v>
@@ -4526,7 +4526,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46311.30744696164</v>
+        <v>46311.70088684419</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>46</v>
@@ -4573,7 +4573,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46311.3074373737</v>
+        <v>46311.70087868374</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>46</v>
@@ -4617,7 +4617,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46311.30743734578</v>
+        <v>46311.70087866466</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>46</v>
@@ -4661,7 +4661,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46311.30743733215</v>
+        <v>46311.70087865533</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>46</v>
@@ -4708,7 +4708,7 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P7" s="2">
-        <v>46311.30743731892</v>
+        <v>46311.70087864589</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>46</v>
@@ -4755,7 +4755,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P8">
-        <v>46311.30743721643</v>
+        <v>46311.70087858952</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
@@ -4799,7 +4799,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P9">
-        <v>46311.30743722944</v>
+        <v>46311.70087859921</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>46</v>
@@ -4843,7 +4843,7 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P10">
-        <v>46311.307437191</v>
+        <v>46311.70087857031</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -4887,7 +4887,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46311.30743715168</v>
+        <v>46311.70087854062</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>46</v>
@@ -4931,7 +4931,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46311.30742787745</v>
+        <v>46311.70087044157</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>46</v>
@@ -4978,7 +4978,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46311.30742785161</v>
+        <v>46311.70087042241</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -5025,7 +5025,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46311.30742782442</v>
+        <v>46311.70087040275</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>46</v>
@@ -5072,7 +5072,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P15">
-        <v>46311.30742780838</v>
+        <v>46311.70087039313</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -5116,7 +5116,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46311.30742765773</v>
+        <v>46311.700870364</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>46</v>
@@ -5160,7 +5160,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46311.30742767097</v>
+        <v>46311.70087037373</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -5207,7 +5207,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46311.30742768373</v>
+        <v>46311.70087038344</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>46</v>
@@ -5254,7 +5254,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P19">
-        <v>46311.30742763128</v>
+        <v>46311.70087034364</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>46</v>
@@ -5301,7 +5301,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P20">
-        <v>46311.30742761814</v>
+        <v>46311.70087033371</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>46</v>
@@ -5345,7 +5345,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P21">
-        <v>46311.30742757768</v>
+        <v>46311.70087030291</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>46</v>
@@ -5392,7 +5392,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P22" s="6">
-        <v>46311.30744711268</v>
+        <v>46311.70088694827</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>46</v>
@@ -5439,7 +5439,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P23" s="6">
-        <v>46311.30744716735</v>
+        <v>46311.70088698581</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
@@ -5486,7 +5486,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P24" s="6">
-        <v>46311.30744715399</v>
+        <v>46311.70088697635</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>46</v>
@@ -5535,7 +5535,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P25" s="6">
-        <v>46311.30745573662</v>
+        <v>46311.70089515702</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>46</v>
@@ -5633,7 +5633,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P27" s="6">
-        <v>46311.30746437659</v>
+        <v>46311.70090339411</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>46</v>
@@ -5701,7 +5701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46311.3074085582</v>
+        <v>46311.70085467582</v>
       </c>
       <c r="B2">
-        <v>46311.31082826155</v>
+        <v>46311.70249357724</v>
       </c>
       <c r="C2" t="s">
         <v>225</v>
@@ -5764,16 +5764,16 @@
         <v>3861</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -5784,45 +5784,45 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46310.71705220221</v>
+        <v>46311.3074085582</v>
       </c>
       <c r="B3">
-        <v>46310.71871343154</v>
+        <v>46311.31082826155</v>
       </c>
       <c r="C3" t="s">
         <v>225</v>
       </c>
       <c r="D3">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E3">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>394</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3858</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B4">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C4" t="s">
         <v>225</v>
@@ -5831,33 +5831,33 @@
         <v>193</v>
       </c>
       <c r="E4">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B5">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C5" t="s">
         <v>225</v>
@@ -5866,16 +5866,16 @@
         <v>193</v>
       </c>
       <c r="E5">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -5884,15 +5884,15 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B6">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C6" t="s">
         <v>225</v>
@@ -5901,33 +5901,33 @@
         <v>193</v>
       </c>
       <c r="E6">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B7">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C7" t="s">
         <v>225</v>
@@ -5942,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B8">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C8" t="s">
         <v>225</v>
@@ -5974,16 +5974,16 @@
         <v>3844</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -5994,45 +5994,45 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B9">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
       </c>
       <c r="D9">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E9">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>381</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B10">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C10" t="s">
         <v>225</v>
@@ -6044,13 +6044,13 @@
         <v>3838</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B11">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C11" t="s">
         <v>225</v>
@@ -6076,16 +6076,16 @@
         <v>192</v>
       </c>
       <c r="E11">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>369</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -6094,15 +6094,15 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B12">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C12" t="s">
         <v>225</v>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B13">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C13" t="s">
         <v>225</v>
@@ -6152,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B14">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C14" t="s">
         <v>225</v>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B15">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C15" t="s">
         <v>225</v>
@@ -6219,16 +6219,16 @@
         <v>3826</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -6239,45 +6239,45 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B16">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C16" t="s">
         <v>225</v>
       </c>
       <c r="D16">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E16">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B17">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C17" t="s">
         <v>225</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B18">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C18" t="s">
         <v>225</v>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B19">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C19" t="s">
         <v>225</v>
@@ -6359,16 +6359,16 @@
         <v>3820</v>
       </c>
       <c r="F19">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H19">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -6379,45 +6379,45 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B20">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C20" t="s">
         <v>225</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E20">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G20">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B21">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C21" t="s">
         <v>225</v>
@@ -6429,13 +6429,13 @@
         <v>160</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -6444,15 +6444,15 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B22">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C22" t="s">
         <v>225</v>
@@ -6464,21 +6464,56 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="H22">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B23">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>160</v>
+      </c>
+      <c r="F23">
+        <v>157</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>132</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="224">
   <si>
     <t>Priority</t>
   </si>
@@ -656,12 +656,6 @@
   </si>
   <si>
     <t>Garima diggiwal</t>
-  </si>
-  <si>
-    <t>NOEL PHARMA (INDIA) PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Prem Chand Goyal</t>
   </si>
   <si>
     <t>Started</t>
@@ -1102,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1193,7 +1187,7 @@
         <v>46312</v>
       </c>
       <c r="I2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>21</v>
@@ -1214,7 +1208,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P2" s="2">
-        <v>46311.70088691096</v>
+        <v>46312.29485674985</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1240,7 +1234,7 @@
         <v>46312</v>
       </c>
       <c r="I3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>26</v>
@@ -1258,7 +1252,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P3" s="2">
-        <v>46311.70088692041</v>
+        <v>46312.29485676255</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1284,7 +1278,7 @@
         <v>46312</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>29</v>
@@ -1305,7 +1299,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P4" s="2">
-        <v>46311.70088690126</v>
+        <v>46312.29485673701</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1331,7 +1325,7 @@
         <v>46312</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>33</v>
@@ -1352,7 +1346,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P5" s="2">
-        <v>46311.70088689196</v>
+        <v>46312.29485672439</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1378,7 +1372,7 @@
         <v>46313</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>37</v>
@@ -1399,7 +1393,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P6" s="2">
-        <v>46311.70088688222</v>
+        <v>46312.29485671136</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1428,7 +1422,7 @@
         <v>46314</v>
       </c>
       <c r="I7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>42</v>
@@ -1446,7 +1440,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P7" s="2">
-        <v>46311.70088685404</v>
+        <v>46312.29485667367</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1472,7 +1466,7 @@
         <v>46314</v>
       </c>
       <c r="I8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>45</v>
@@ -1490,7 +1484,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P8" s="2">
-        <v>46311.70088686351</v>
+        <v>46312.29485668633</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
@@ -1516,7 +1510,7 @@
         <v>46314</v>
       </c>
       <c r="I9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>48</v>
@@ -1534,7 +1528,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P9" s="2">
-        <v>46311.70088687293</v>
+        <v>46312.29485669876</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>23</v>
@@ -1560,7 +1554,7 @@
         <v>46315</v>
       </c>
       <c r="I10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>50</v>
@@ -1578,7 +1572,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P10" s="2">
-        <v>46311.70088684419</v>
+        <v>46312.29485666077</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -1604,7 +1598,7 @@
         <v>46315</v>
       </c>
       <c r="I11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>53</v>
@@ -1625,7 +1619,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P11" s="2">
-        <v>46311.70088683406</v>
+        <v>46312.29485664792</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>23</v>
@@ -1654,7 +1648,7 @@
         <v>46315</v>
       </c>
       <c r="I12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>58</v>
@@ -1675,7 +1669,7 @@
         <v>46311.30744692709</v>
       </c>
       <c r="P12" s="2">
-        <v>46311.70088682229</v>
+        <v>46312.29485663317</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1701,7 +1695,7 @@
         <v>46316</v>
       </c>
       <c r="I13" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>61</v>
@@ -1722,7 +1716,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P13" s="2">
-        <v>46311.70087868374</v>
+        <v>46312.29484303323</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -1748,7 +1742,7 @@
         <v>46316</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>65</v>
@@ -1769,7 +1763,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P14" s="2">
-        <v>46311.7008787021</v>
+        <v>46312.29484306075</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1795,7 +1789,7 @@
         <v>46317</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>68</v>
@@ -1813,7 +1807,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P15" s="2">
-        <v>46311.70087866466</v>
+        <v>46312.29484300764</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -1842,7 +1836,7 @@
         <v>46317</v>
       </c>
       <c r="I16" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>72</v>
@@ -1860,7 +1854,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P16" s="2">
-        <v>46311.70087867416</v>
+        <v>46312.29484302051</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1886,7 +1880,7 @@
         <v>46317</v>
       </c>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>74</v>
@@ -1904,7 +1898,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P17" s="2">
-        <v>46311.70087865533</v>
+        <v>46312.29484299479</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -1933,7 +1927,7 @@
         <v>46318</v>
       </c>
       <c r="I18" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>76</v>
@@ -1954,7 +1948,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P18" s="2">
-        <v>46311.70087862734</v>
+        <v>46312.29484295692</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -1980,7 +1974,7 @@
         <v>46318</v>
       </c>
       <c r="I19" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>80</v>
@@ -2001,7 +1995,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P19" s="2">
-        <v>46311.70087863646</v>
+        <v>46312.29484296968</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>23</v>
@@ -2027,7 +2021,7 @@
         <v>46318</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>61</v>
@@ -2048,7 +2042,7 @@
         <v>46308.39986132324</v>
       </c>
       <c r="P20" s="2">
-        <v>46311.70087861818</v>
+        <v>46312.29484294421</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>23</v>
@@ -2074,7 +2068,7 @@
         <v>46318</v>
       </c>
       <c r="I21" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>85</v>
@@ -2095,44 +2089,44 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P21" s="2">
-        <v>46311.70087864589</v>
+        <v>46312.29484298224</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" t="s">
+    <row r="22" spans="1:17" s="2" customFormat="1">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>0.93</v>
       </c>
       <c r="H22" s="3">
         <v>46319</v>
       </c>
-      <c r="I22">
-        <v>8</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="I22" s="2">
+        <v>7</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>2</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" s="2" t="s">
         <v>91</v>
       </c>
       <c r="M22" s="4" t="s">
@@ -2141,45 +2135,45 @@
       <c r="N22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="2">
         <v>46305.20575263901</v>
       </c>
-      <c r="P22">
-        <v>46311.7008786087</v>
-      </c>
-      <c r="Q22" t="s">
+      <c r="P22" s="2">
+        <v>46312.29484293171</v>
+      </c>
+      <c r="Q22" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" t="s">
+    <row r="23" spans="1:17" s="2" customFormat="1">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>0.2</v>
       </c>
       <c r="H23" s="3">
         <v>46319</v>
       </c>
-      <c r="I23">
-        <v>8</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="I23" s="2">
+        <v>7</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>2</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M23" s="4" t="s">
@@ -2188,42 +2182,42 @@
       <c r="N23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="2">
         <v>46307.39549700746</v>
       </c>
-      <c r="P23">
-        <v>46311.70087858952</v>
+      <c r="P23" s="2">
+        <v>46312.29484290504</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="24" spans="1:17" s="2" customFormat="1">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>0.2</v>
       </c>
       <c r="H24" s="3">
         <v>46319</v>
       </c>
-      <c r="I24">
-        <v>8</v>
-      </c>
-      <c r="J24" t="s">
+      <c r="I24" s="2">
+        <v>7</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
@@ -2232,42 +2226,42 @@
       <c r="N24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="2">
         <v>46307.3954970362</v>
       </c>
-      <c r="P24">
-        <v>46311.70087859921</v>
+      <c r="P24" s="2">
+        <v>46312.29484291846</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="25" spans="1:17" s="2" customFormat="1">
+      <c r="A25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>0.95</v>
       </c>
       <c r="H25" s="3">
         <v>46319</v>
       </c>
-      <c r="I25">
-        <v>8</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="I25" s="2">
+        <v>7</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>2</v>
       </c>
       <c r="M25" s="4" t="s">
@@ -2276,42 +2270,42 @@
       <c r="N25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="2">
         <v>46309.72495168629</v>
       </c>
-      <c r="P25">
-        <v>46311.70087856058</v>
-      </c>
-      <c r="Q25" t="s">
+      <c r="P25" s="2">
+        <v>46312.29484286576</v>
+      </c>
+      <c r="Q25" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
+    <row r="26" spans="1:17" s="2" customFormat="1">
+      <c r="A26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>0.2</v>
       </c>
       <c r="H26" s="3">
         <v>46319</v>
       </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="I26" s="2">
+        <v>7</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>1</v>
       </c>
       <c r="M26" s="4" t="s">
@@ -2320,45 +2314,45 @@
       <c r="N26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="2">
         <v>46309.72495171529</v>
       </c>
-      <c r="P26">
-        <v>46311.70087857031</v>
+      <c r="P26" s="2">
+        <v>46312.29484287875</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" t="s">
+    <row r="27" spans="1:17" s="2" customFormat="1">
+      <c r="A27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>0.91</v>
       </c>
       <c r="H27" s="3">
         <v>46319</v>
       </c>
-      <c r="I27">
-        <v>8</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="I27" s="2">
+        <v>7</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>2</v>
       </c>
       <c r="M27" s="4" t="s">
@@ -2367,13 +2361,13 @@
       <c r="N27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="2">
         <v>46310.31707038325</v>
       </c>
-      <c r="P27">
-        <v>46311.70087857965</v>
-      </c>
-      <c r="Q27" t="s">
+      <c r="P27" s="2">
+        <v>46312.29484289186</v>
+      </c>
+      <c r="Q27" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2397,7 +2391,7 @@
         <v>46320</v>
       </c>
       <c r="I28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" t="s">
         <v>106</v>
@@ -2418,7 +2412,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P28">
-        <v>46311.7008785186</v>
+        <v>46312.29484281153</v>
       </c>
       <c r="Q28" t="s">
         <v>23</v>
@@ -2444,7 +2438,7 @@
         <v>46320</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J29" t="s">
         <v>109</v>
@@ -2462,7 +2456,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P29">
-        <v>46311.7008785302</v>
+        <v>46312.29484282663</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2488,7 +2482,7 @@
         <v>46320</v>
       </c>
       <c r="I30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" t="s">
         <v>111</v>
@@ -2506,7 +2500,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P30">
-        <v>46311.70087854062</v>
+        <v>46312.29484284001</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>46</v>
@@ -2532,7 +2526,7 @@
         <v>46321</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J31" t="s">
         <v>113</v>
@@ -2550,7 +2544,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P31">
-        <v>46311.70087044157</v>
+        <v>46312.29483166153</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>46</v>
@@ -2576,7 +2570,7 @@
         <v>46322</v>
       </c>
       <c r="I32">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J32" t="s">
         <v>115</v>
@@ -2597,7 +2591,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P32">
-        <v>46311.70087042241</v>
+        <v>46312.29483163588</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>46</v>
@@ -2626,7 +2620,7 @@
         <v>46322</v>
       </c>
       <c r="I33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J33" t="s">
         <v>118</v>
@@ -2647,7 +2641,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P33">
-        <v>46311.70087041293</v>
+        <v>46312.294831623</v>
       </c>
       <c r="Q33" t="s">
         <v>23</v>
@@ -2673,7 +2667,7 @@
         <v>46322</v>
       </c>
       <c r="I34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J34" t="s">
         <v>121</v>
@@ -2694,7 +2688,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P34">
-        <v>46311.70087040275</v>
+        <v>46312.29483160963</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>46</v>
@@ -2723,7 +2717,7 @@
         <v>46322</v>
       </c>
       <c r="I35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J35" t="s">
         <v>124</v>
@@ -2744,7 +2738,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P35">
-        <v>46311.70087043183</v>
+        <v>46312.29483164889</v>
       </c>
       <c r="Q35" t="s">
         <v>23</v>
@@ -2770,7 +2764,7 @@
         <v>46322</v>
       </c>
       <c r="I36">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J36" t="s">
         <v>127</v>
@@ -2791,7 +2785,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P36">
-        <v>46311.70087039313</v>
+        <v>46312.29483159653</v>
       </c>
       <c r="Q36" s="5" t="s">
         <v>46</v>
@@ -2817,7 +2811,7 @@
         <v>46323</v>
       </c>
       <c r="I37">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J37" t="s">
         <v>130</v>
@@ -2835,7 +2829,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P37">
-        <v>46311.700870364</v>
+        <v>46312.29483155741</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>46</v>
@@ -2861,7 +2855,7 @@
         <v>46323</v>
       </c>
       <c r="I38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J38" t="s">
         <v>132</v>
@@ -2879,7 +2873,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P38">
-        <v>46311.70087037373</v>
+        <v>46312.2948315709</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>46</v>
@@ -2905,7 +2899,7 @@
         <v>46323</v>
       </c>
       <c r="I39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J39" t="s">
         <v>134</v>
@@ -2926,7 +2920,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P39">
-        <v>46311.70087038344</v>
+        <v>46312.29483158379</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>46</v>
@@ -2955,7 +2949,7 @@
         <v>46323</v>
       </c>
       <c r="I40">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J40" t="s">
         <v>139</v>
@@ -2976,7 +2970,7 @@
         <v>46310.31706138982</v>
       </c>
       <c r="P40">
-        <v>46311.70087035413</v>
+        <v>46312.29483154425</v>
       </c>
       <c r="Q40" t="s">
         <v>23</v>
@@ -3002,7 +2996,7 @@
         <v>46323</v>
       </c>
       <c r="I41">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J41" t="s">
         <v>142</v>
@@ -3023,7 +3017,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P41">
-        <v>46311.70087034364</v>
+        <v>46312.29483153038</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>46</v>
@@ -3049,7 +3043,7 @@
         <v>46324</v>
       </c>
       <c r="I42">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J42" t="s">
         <v>145</v>
@@ -3070,7 +3064,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P42">
-        <v>46311.70087033371</v>
+        <v>46312.29483151647</v>
       </c>
       <c r="Q42" s="5" t="s">
         <v>46</v>
@@ -3096,7 +3090,7 @@
         <v>46324</v>
       </c>
       <c r="I43">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J43" t="s">
         <v>148</v>
@@ -3117,7 +3111,7 @@
         <v>46310.31706133292</v>
       </c>
       <c r="P43">
-        <v>46311.70087032368</v>
+        <v>46312.29483150326</v>
       </c>
       <c r="Q43" t="s">
         <v>23</v>
@@ -3146,7 +3140,7 @@
         <v>46325</v>
       </c>
       <c r="I44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J44" t="s">
         <v>152</v>
@@ -3167,7 +3161,7 @@
         <v>46309.72494249383</v>
       </c>
       <c r="P44">
-        <v>46311.70087031323</v>
+        <v>46312.29483148939</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3193,7 +3187,7 @@
         <v>46326</v>
       </c>
       <c r="I45">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J45" t="s">
         <v>155</v>
@@ -3211,7 +3205,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P45">
-        <v>46311.70087030291</v>
+        <v>46312.29483147463</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>46</v>
@@ -3240,7 +3234,7 @@
         <v>46328</v>
       </c>
       <c r="I46">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" t="s">
         <v>157</v>
@@ -3261,7 +3255,7 @@
         <v>46308.39986111095</v>
       </c>
       <c r="P46">
-        <v>46311.7008702819</v>
+        <v>46312.29483144655</v>
       </c>
       <c r="Q46" t="s">
         <v>23</v>
@@ -3287,7 +3281,7 @@
         <v>46332</v>
       </c>
       <c r="I47">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s">
         <v>160</v>
@@ -3305,7 +3299,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P47">
-        <v>46311.70087027091</v>
+        <v>46312.29483143263</v>
       </c>
       <c r="Q47" t="s">
         <v>23</v>
@@ -3331,7 +3325,7 @@
         <v>46333</v>
       </c>
       <c r="I48">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
         <v>96</v>
@@ -3352,7 +3346,7 @@
         <v>46307.39549666931</v>
       </c>
       <c r="P48">
-        <v>46311.70087025949</v>
+        <v>46312.29483141792</v>
       </c>
       <c r="Q48" t="s">
         <v>23</v>
@@ -3378,7 +3372,7 @@
         <v>46333</v>
       </c>
       <c r="I49">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
         <v>164</v>
@@ -3396,7 +3390,7 @@
         <v>46307.39549671811</v>
       </c>
       <c r="P49">
-        <v>46311.70087023666</v>
+        <v>46312.29483138782</v>
       </c>
       <c r="Q49" t="s">
         <v>23</v>
@@ -3424,7 +3418,7 @@
         <v>46310</v>
       </c>
       <c r="I50" s="6">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>168</v>
@@ -3445,7 +3439,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P50" s="6">
-        <v>46311.70088693928</v>
+        <v>46312.29485678871</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3473,7 +3467,7 @@
         <v>46309</v>
       </c>
       <c r="I51" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>171</v>
@@ -3492,7 +3486,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P51" s="6">
-        <v>46311.70088694827</v>
+        <v>46312.29485680167</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>46</v>
@@ -3520,7 +3514,7 @@
         <v>46308</v>
       </c>
       <c r="I52" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>173</v>
@@ -3539,7 +3533,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P52" s="6">
-        <v>46311.70088698581</v>
+        <v>46312.29485685294</v>
       </c>
       <c r="Q52" s="5" t="s">
         <v>46</v>
@@ -3567,7 +3561,7 @@
         <v>46308</v>
       </c>
       <c r="I53" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>175</v>
@@ -3586,7 +3580,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P53" s="6">
-        <v>46311.70088697635</v>
+        <v>46312.29485684038</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>46</v>
@@ -3616,7 +3610,7 @@
         <v>46307</v>
       </c>
       <c r="I54" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>179</v>
@@ -3637,7 +3631,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P54" s="6">
-        <v>46311.70089512802</v>
+        <v>46312.29486540094</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>23</v>
@@ -3667,7 +3661,7 @@
         <v>46307</v>
       </c>
       <c r="I55" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>182</v>
@@ -3686,7 +3680,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46311.70089508668</v>
+        <v>46312.2948653477</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3714,7 +3708,7 @@
         <v>46307</v>
       </c>
       <c r="I56" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>184</v>
@@ -3735,7 +3729,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46311.70089515702</v>
+        <v>46312.29486543904</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>46</v>
@@ -3763,7 +3757,7 @@
         <v>46307</v>
       </c>
       <c r="I57" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J57" s="6" t="s">
         <v>187</v>
@@ -3782,7 +3776,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46311.70089513763</v>
+        <v>46312.29486541387</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3810,7 +3804,7 @@
         <v>46307</v>
       </c>
       <c r="I58" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>184</v>
@@ -3831,7 +3825,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46311.70089514742</v>
+        <v>46312.29486542654</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3861,7 +3855,7 @@
         <v>46307</v>
       </c>
       <c r="I59" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J59" s="6" t="s">
         <v>85</v>
@@ -3912,7 +3906,7 @@
         <v>46306</v>
       </c>
       <c r="I60" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J60" s="6" t="s">
         <v>194</v>
@@ -3933,7 +3927,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46311.70089517583</v>
+        <v>46312.29486546413</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3961,7 +3955,7 @@
         <v>46306</v>
       </c>
       <c r="I61" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>197</v>
@@ -3982,7 +3976,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46311.70089518549</v>
+        <v>46312.29486547723</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -4010,7 +4004,7 @@
         <v>46305</v>
       </c>
       <c r="I62" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>200</v>
@@ -4031,7 +4025,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46311.70089521474</v>
+        <v>46312.29486551596</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4059,7 +4053,7 @@
         <v>46304</v>
       </c>
       <c r="I63" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J63" s="6" t="s">
         <v>204</v>
@@ -4080,7 +4074,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46311.70089523357</v>
+        <v>46312.29486554277</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4110,7 +4104,7 @@
         <v>46303</v>
       </c>
       <c r="I64" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>208</v>
@@ -4131,7 +4125,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46311.7008952556</v>
+        <v>46312.29486556918</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
@@ -4159,7 +4153,7 @@
         <v>46302</v>
       </c>
       <c r="I65" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J65" s="6" t="s">
         <v>211</v>
@@ -4178,63 +4172,14 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P65" s="6">
-        <v>46311.70090339411</v>
+        <v>46312.29487409964</v>
       </c>
       <c r="Q65" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:17">
-      <c r="A66" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G66" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H66" s="6">
-        <v>46301</v>
-      </c>
-      <c r="I66" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K66" s="6">
-        <v>2</v>
-      </c>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O66" s="6">
-        <v>46300.75885649968</v>
-      </c>
-      <c r="P66" s="6">
-        <v>46311.70090342543</v>
-      </c>
-      <c r="Q66" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q66"/>
+  <autoFilter ref="A1:Q65"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4364,8 +4309,6 @@
     <hyperlink ref="N64" r:id="rId126"/>
     <hyperlink ref="M65" r:id="rId127"/>
     <hyperlink ref="N65" r:id="rId128"/>
-    <hyperlink ref="M66" r:id="rId129"/>
-    <hyperlink ref="N66" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4464,7 +4407,7 @@
         <v>46314</v>
       </c>
       <c r="I2" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>45</v>
@@ -4482,7 +4425,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46311.70088686351</v>
+        <v>46312.29485668633</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>46</v>
@@ -4508,7 +4451,7 @@
         <v>46315</v>
       </c>
       <c r="I3" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>50</v>
@@ -4526,7 +4469,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46311.70088684419</v>
+        <v>46312.29485666077</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>46</v>
@@ -4552,7 +4495,7 @@
         <v>46316</v>
       </c>
       <c r="I4" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>61</v>
@@ -4573,7 +4516,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46311.70087868374</v>
+        <v>46312.29484303323</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>46</v>
@@ -4599,7 +4542,7 @@
         <v>46317</v>
       </c>
       <c r="I5" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>68</v>
@@ -4617,7 +4560,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46311.70087866466</v>
+        <v>46312.29484300764</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>46</v>
@@ -4643,7 +4586,7 @@
         <v>46317</v>
       </c>
       <c r="I6" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>74</v>
@@ -4661,7 +4604,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46311.70087865533</v>
+        <v>46312.29484299479</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>46</v>
@@ -4687,7 +4630,7 @@
         <v>46318</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>85</v>
@@ -4708,41 +4651,41 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P7" s="2">
-        <v>46311.70087864589</v>
+        <v>46312.29484298224</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="8" spans="1:17" s="2" customFormat="1">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>0.2</v>
       </c>
       <c r="H8" s="3">
         <v>46319</v>
       </c>
-      <c r="I8">
-        <v>8</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="I8" s="2">
+        <v>7</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="2" t="s">
         <v>94</v>
       </c>
       <c r="M8" s="4" t="s">
@@ -4751,42 +4694,42 @@
       <c r="N8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="2">
         <v>46307.39549700746</v>
       </c>
-      <c r="P8">
-        <v>46311.70087858952</v>
+      <c r="P8" s="2">
+        <v>46312.29484290504</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="9" spans="1:17" s="2" customFormat="1">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>0.2</v>
       </c>
       <c r="H9" s="3">
         <v>46319</v>
       </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="I9" s="2">
+        <v>7</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>1</v>
       </c>
       <c r="M9" s="4" t="s">
@@ -4795,42 +4738,42 @@
       <c r="N9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="2">
         <v>46307.3954970362</v>
       </c>
-      <c r="P9">
-        <v>46311.70087859921</v>
+      <c r="P9" s="2">
+        <v>46312.29484291846</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:17" s="2" customFormat="1">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>0.2</v>
       </c>
       <c r="H10" s="3">
         <v>46319</v>
       </c>
-      <c r="I10">
-        <v>8</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="I10" s="2">
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
@@ -4839,11 +4782,11 @@
       <c r="N10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>46309.72495171529</v>
       </c>
-      <c r="P10">
-        <v>46311.70087857031</v>
+      <c r="P10" s="2">
+        <v>46312.29484287875</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -4869,7 +4812,7 @@
         <v>46320</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" t="s">
         <v>111</v>
@@ -4887,7 +4830,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46311.70087854062</v>
+        <v>46312.29484284001</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>46</v>
@@ -4913,7 +4856,7 @@
         <v>46321</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" t="s">
         <v>113</v>
@@ -4931,7 +4874,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46311.70087044157</v>
+        <v>46312.29483166153</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>46</v>
@@ -4957,7 +4900,7 @@
         <v>46322</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
         <v>115</v>
@@ -4978,7 +4921,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46311.70087042241</v>
+        <v>46312.29483163588</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -5004,7 +4947,7 @@
         <v>46322</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" t="s">
         <v>121</v>
@@ -5025,7 +4968,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46311.70087040275</v>
+        <v>46312.29483160963</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>46</v>
@@ -5051,7 +4994,7 @@
         <v>46322</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J15" t="s">
         <v>127</v>
@@ -5072,7 +5015,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P15">
-        <v>46311.70087039313</v>
+        <v>46312.29483159653</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -5098,7 +5041,7 @@
         <v>46323</v>
       </c>
       <c r="I16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J16" t="s">
         <v>130</v>
@@ -5116,7 +5059,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46311.700870364</v>
+        <v>46312.29483155741</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>46</v>
@@ -5142,7 +5085,7 @@
         <v>46323</v>
       </c>
       <c r="I17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J17" t="s">
         <v>132</v>
@@ -5160,7 +5103,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46311.70087037373</v>
+        <v>46312.2948315709</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -5186,7 +5129,7 @@
         <v>46323</v>
       </c>
       <c r="I18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J18" t="s">
         <v>134</v>
@@ -5207,7 +5150,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46311.70087038344</v>
+        <v>46312.29483158379</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>46</v>
@@ -5233,7 +5176,7 @@
         <v>46323</v>
       </c>
       <c r="I19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J19" t="s">
         <v>142</v>
@@ -5254,7 +5197,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P19">
-        <v>46311.70087034364</v>
+        <v>46312.29483153038</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>46</v>
@@ -5280,7 +5223,7 @@
         <v>46324</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J20" t="s">
         <v>145</v>
@@ -5301,7 +5244,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P20">
-        <v>46311.70087033371</v>
+        <v>46312.29483151647</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>46</v>
@@ -5327,7 +5270,7 @@
         <v>46326</v>
       </c>
       <c r="I21">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J21" t="s">
         <v>155</v>
@@ -5345,7 +5288,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P21">
-        <v>46311.70087030291</v>
+        <v>46312.29483147463</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>46</v>
@@ -5373,7 +5316,7 @@
         <v>46309</v>
       </c>
       <c r="I22" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>171</v>
@@ -5392,7 +5335,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P22" s="6">
-        <v>46311.70088694827</v>
+        <v>46312.29485680167</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>46</v>
@@ -5420,7 +5363,7 @@
         <v>46308</v>
       </c>
       <c r="I23" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>173</v>
@@ -5439,7 +5382,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P23" s="6">
-        <v>46311.70088698581</v>
+        <v>46312.29485685294</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
@@ -5467,7 +5410,7 @@
         <v>46308</v>
       </c>
       <c r="I24" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>175</v>
@@ -5486,7 +5429,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P24" s="6">
-        <v>46311.70088697635</v>
+        <v>46312.29485684038</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>46</v>
@@ -5514,7 +5457,7 @@
         <v>46307</v>
       </c>
       <c r="I25" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>184</v>
@@ -5535,7 +5478,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P25" s="6">
-        <v>46311.70089515702</v>
+        <v>46312.29486543904</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>46</v>
@@ -5565,7 +5508,7 @@
         <v>46307</v>
       </c>
       <c r="I26" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>85</v>
@@ -5614,7 +5557,7 @@
         <v>46302</v>
       </c>
       <c r="I27" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>211</v>
@@ -5633,7 +5576,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P27" s="6">
-        <v>46311.70090339411</v>
+        <v>46312.29487409964</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>46</v>
@@ -5701,7 +5644,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5711,51 +5654,51 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46311.70085467582</v>
+        <v>46312.29481460934</v>
       </c>
       <c r="B2">
-        <v>46311.70249357724</v>
+        <v>46312.29886374016</v>
       </c>
       <c r="C2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D2">
         <v>194</v>
@@ -5767,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5784,13 +5727,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46311.3074085582</v>
+        <v>46311.70085467582</v>
       </c>
       <c r="B3">
-        <v>46311.31082826155</v>
+        <v>46311.70249357724</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D3">
         <v>194</v>
@@ -5799,16 +5742,16 @@
         <v>3861</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -5819,98 +5762,98 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46310.71705220221</v>
+        <v>46311.3074085582</v>
       </c>
       <c r="B4">
-        <v>46310.71871343154</v>
+        <v>46311.31082826155</v>
       </c>
       <c r="C4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D4">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E4">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>394</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3858</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B5">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5">
         <v>193</v>
       </c>
       <c r="E5">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B6">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D6">
         <v>193</v>
       </c>
       <c r="E6">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -5919,53 +5862,53 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B7">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D7">
         <v>193</v>
       </c>
       <c r="E7">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B8">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D8">
         <v>193</v>
@@ -5977,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -5994,13 +5937,13 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B9">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D9">
         <v>193</v>
@@ -6009,16 +5952,16 @@
         <v>3844</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -6029,48 +5972,48 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B10">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D10">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E10">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>381</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B11">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D11">
         <v>192</v>
@@ -6079,13 +6022,13 @@
         <v>3838</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -6099,28 +6042,28 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B12">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D12">
         <v>192</v>
       </c>
       <c r="E12">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>369</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -6129,18 +6072,18 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B13">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D13">
         <v>192</v>
@@ -6169,13 +6112,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B14">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D14">
         <v>192</v>
@@ -6187,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6204,13 +6147,13 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B15">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D15">
         <v>192</v>
@@ -6239,13 +6182,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B16">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D16">
         <v>192</v>
@@ -6254,16 +6197,16 @@
         <v>3826</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -6274,48 +6217,48 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B17">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D17">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B18">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D18">
         <v>191</v>
@@ -6344,13 +6287,13 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B19">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D19">
         <v>191</v>
@@ -6362,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -6379,13 +6322,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B20">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D20">
         <v>191</v>
@@ -6394,16 +6337,16 @@
         <v>3820</v>
       </c>
       <c r="F20">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H20">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -6414,48 +6357,48 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B21">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E21">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G21">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B22">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -6464,13 +6407,13 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -6479,18 +6422,18 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B23">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -6499,21 +6442,56 @@
         <v>160</v>
       </c>
       <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>160</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B24">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>160</v>
+      </c>
+      <c r="F24">
         <v>157</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>3</v>
       </c>
-      <c r="H23">
+      <c r="H24">
         <v>132</v>
       </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="224">
   <si>
     <t>Priority</t>
   </si>
@@ -1208,7 +1208,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P2" s="2">
-        <v>46312.29485674985</v>
+        <v>46312.65711586995</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1252,7 +1252,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P3" s="2">
-        <v>46312.29485676255</v>
+        <v>46312.65711588449</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1299,7 +1299,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P4" s="2">
-        <v>46312.29485673701</v>
+        <v>46312.65711585592</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>23</v>
@@ -1346,7 +1346,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P5" s="2">
-        <v>46312.29485672439</v>
+        <v>46312.65711584162</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1393,7 +1393,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P6" s="2">
-        <v>46312.29485671136</v>
+        <v>46312.65711582667</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>23</v>
@@ -1440,7 +1440,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P7" s="2">
-        <v>46312.29485667367</v>
+        <v>46312.65711578376</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1484,7 +1484,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P8" s="2">
-        <v>46312.29485668633</v>
+        <v>46312.65711579815</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
@@ -1528,7 +1528,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P9" s="2">
-        <v>46312.29485669876</v>
+        <v>46312.6571158125</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>23</v>
@@ -1572,7 +1572,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P10" s="2">
-        <v>46312.29485666077</v>
+        <v>46312.65711576909</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -1619,7 +1619,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P11" s="2">
-        <v>46312.29485664792</v>
+        <v>46312.65711575456</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>23</v>
@@ -1669,7 +1669,7 @@
         <v>46311.30744692709</v>
       </c>
       <c r="P12" s="2">
-        <v>46312.29485663317</v>
+        <v>46312.65711573853</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1716,7 +1716,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P13" s="2">
-        <v>46312.29484303323</v>
+        <v>46312.65710777805</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -1763,7 +1763,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P14" s="2">
-        <v>46312.29484306075</v>
+        <v>46312.65710780673</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1807,7 +1807,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P15" s="2">
-        <v>46312.29484300764</v>
+        <v>46312.65710774902</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -1854,7 +1854,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P16" s="2">
-        <v>46312.29484302051</v>
+        <v>46312.65710776359</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1898,7 +1898,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P17" s="2">
-        <v>46312.29484299479</v>
+        <v>46312.65710773495</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -1948,7 +1948,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P18" s="2">
-        <v>46312.29484295692</v>
+        <v>46312.65710769239</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -1995,7 +1995,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P19" s="2">
-        <v>46312.29484296968</v>
+        <v>46312.65710770644</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>23</v>
@@ -2042,7 +2042,7 @@
         <v>46308.39986132324</v>
       </c>
       <c r="P20" s="2">
-        <v>46312.29484294421</v>
+        <v>46312.65710767791</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>23</v>
@@ -2089,7 +2089,7 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P21" s="2">
-        <v>46312.29484298224</v>
+        <v>46312.65710772065</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>46</v>
@@ -2139,7 +2139,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P22" s="2">
-        <v>46312.29484293171</v>
+        <v>46312.65710766351</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>23</v>
@@ -2186,7 +2186,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P23" s="2">
-        <v>46312.29484290504</v>
+        <v>46312.65710763459</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
@@ -2230,7 +2230,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P24" s="2">
-        <v>46312.29484291846</v>
+        <v>46312.65710764895</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>46</v>
@@ -2274,7 +2274,7 @@
         <v>46309.72495168629</v>
       </c>
       <c r="P25" s="2">
-        <v>46312.29484286576</v>
+        <v>46312.65710759105</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>23</v>
@@ -2318,7 +2318,7 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P26" s="2">
-        <v>46312.29484287875</v>
+        <v>46312.65710760548</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>46</v>
@@ -2365,7 +2365,7 @@
         <v>46310.31707038325</v>
       </c>
       <c r="P27" s="2">
-        <v>46312.29484289186</v>
+        <v>46312.65710761982</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>23</v>
@@ -2412,7 +2412,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P28">
-        <v>46312.29484281153</v>
+        <v>46312.65710753087</v>
       </c>
       <c r="Q28" t="s">
         <v>23</v>
@@ -2456,7 +2456,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P29">
-        <v>46312.29484282663</v>
+        <v>46312.65710754672</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2500,7 +2500,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P30">
-        <v>46312.29484284001</v>
+        <v>46312.65710756149</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>46</v>
@@ -2544,7 +2544,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P31">
-        <v>46312.29483166153</v>
+        <v>46312.65709963298</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>46</v>
@@ -2591,7 +2591,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P32">
-        <v>46312.29483163588</v>
+        <v>46312.65709960293</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>46</v>
@@ -2641,7 +2641,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P33">
-        <v>46312.294831623</v>
+        <v>46312.65709958807</v>
       </c>
       <c r="Q33" t="s">
         <v>23</v>
@@ -2688,7 +2688,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P34">
-        <v>46312.29483160963</v>
+        <v>46312.65709957341</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>46</v>
@@ -2738,7 +2738,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P35">
-        <v>46312.29483164889</v>
+        <v>46312.65709961824</v>
       </c>
       <c r="Q35" t="s">
         <v>23</v>
@@ -2785,7 +2785,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P36">
-        <v>46312.29483159653</v>
+        <v>46312.65709955859</v>
       </c>
       <c r="Q36" s="5" t="s">
         <v>46</v>
@@ -2829,7 +2829,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P37">
-        <v>46312.29483155741</v>
+        <v>46312.65709951358</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>46</v>
@@ -2873,7 +2873,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P38">
-        <v>46312.2948315709</v>
+        <v>46312.65709952823</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>46</v>
@@ -2920,7 +2920,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P39">
-        <v>46312.29483158379</v>
+        <v>46312.6570995425</v>
       </c>
       <c r="Q39" s="5" t="s">
         <v>46</v>
@@ -2970,7 +2970,7 @@
         <v>46310.31706138982</v>
       </c>
       <c r="P40">
-        <v>46312.29483154425</v>
+        <v>46312.65709949912</v>
       </c>
       <c r="Q40" t="s">
         <v>23</v>
@@ -3017,7 +3017,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P41">
-        <v>46312.29483153038</v>
+        <v>46312.65709948403</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>46</v>
@@ -3064,7 +3064,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P42">
-        <v>46312.29483151647</v>
+        <v>46312.65709946943</v>
       </c>
       <c r="Q42" s="5" t="s">
         <v>46</v>
@@ -3111,7 +3111,7 @@
         <v>46310.31706133292</v>
       </c>
       <c r="P43">
-        <v>46312.29483150326</v>
+        <v>46312.65709945454</v>
       </c>
       <c r="Q43" t="s">
         <v>23</v>
@@ -3161,7 +3161,7 @@
         <v>46309.72494249383</v>
       </c>
       <c r="P44">
-        <v>46312.29483148939</v>
+        <v>46312.65709943903</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3205,7 +3205,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P45">
-        <v>46312.29483147463</v>
+        <v>46312.65709942421</v>
       </c>
       <c r="Q45" s="5" t="s">
         <v>46</v>
@@ -3255,7 +3255,7 @@
         <v>46308.39986111095</v>
       </c>
       <c r="P46">
-        <v>46312.29483144655</v>
+        <v>46312.65709939371</v>
       </c>
       <c r="Q46" t="s">
         <v>23</v>
@@ -3299,7 +3299,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P47">
-        <v>46312.29483143263</v>
+        <v>46312.65709937788</v>
       </c>
       <c r="Q47" t="s">
         <v>23</v>
@@ -3346,7 +3346,7 @@
         <v>46307.39549666931</v>
       </c>
       <c r="P48">
-        <v>46312.29483141792</v>
+        <v>46312.65709936203</v>
       </c>
       <c r="Q48" t="s">
         <v>23</v>
@@ -3390,7 +3390,7 @@
         <v>46307.39549671811</v>
       </c>
       <c r="P49">
-        <v>46312.29483138782</v>
+        <v>46312.65709933193</v>
       </c>
       <c r="Q49" t="s">
         <v>23</v>
@@ -3439,7 +3439,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P50" s="6">
-        <v>46312.29485678871</v>
+        <v>46312.65711591329</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3486,7 +3486,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P51" s="6">
-        <v>46312.29485680167</v>
+        <v>46312.65711592732</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>46</v>
@@ -3533,7 +3533,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P52" s="6">
-        <v>46312.29485685294</v>
+        <v>46312.65711598445</v>
       </c>
       <c r="Q52" s="5" t="s">
         <v>46</v>
@@ -3580,7 +3580,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P53" s="6">
-        <v>46312.29485684038</v>
+        <v>46312.65711597015</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>46</v>
@@ -3631,7 +3631,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P54" s="6">
-        <v>46312.29486540094</v>
+        <v>46312.65712399615</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>23</v>
@@ -3680,7 +3680,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46312.2948653477</v>
+        <v>46312.65712393675</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3729,7 +3729,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46312.29486543904</v>
+        <v>46312.65712403938</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>46</v>
@@ -3776,7 +3776,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46312.29486541387</v>
+        <v>46312.6571240104</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3825,7 +3825,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46312.29486542654</v>
+        <v>46312.65712402533</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3927,7 +3927,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46312.29486546413</v>
+        <v>46312.65712406745</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3976,7 +3976,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46312.29486547723</v>
+        <v>46312.65712408235</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -4025,7 +4025,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46312.29486551596</v>
+        <v>46312.65712412516</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4074,7 +4074,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46312.29486554277</v>
+        <v>46312.6571241546</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4125,7 +4125,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46312.29486556918</v>
+        <v>46312.65712418339</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
@@ -4172,7 +4172,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P65" s="6">
-        <v>46312.29487409964</v>
+        <v>46312.65713212876</v>
       </c>
       <c r="Q65" s="5" t="s">
         <v>46</v>
@@ -4425,7 +4425,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46312.29485668633</v>
+        <v>46312.65711579815</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>46</v>
@@ -4469,7 +4469,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46312.29485666077</v>
+        <v>46312.65711576909</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>46</v>
@@ -4516,7 +4516,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46312.29484303323</v>
+        <v>46312.65710777805</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>46</v>
@@ -4560,7 +4560,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46312.29484300764</v>
+        <v>46312.65710774902</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>46</v>
@@ -4604,7 +4604,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46312.29484299479</v>
+        <v>46312.65710773495</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>46</v>
@@ -4651,7 +4651,7 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P7" s="2">
-        <v>46312.29484298224</v>
+        <v>46312.65710772065</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>46</v>
@@ -4698,7 +4698,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P8" s="2">
-        <v>46312.29484290504</v>
+        <v>46312.65710763459</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>46</v>
@@ -4742,7 +4742,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P9" s="2">
-        <v>46312.29484291846</v>
+        <v>46312.65710764895</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>46</v>
@@ -4786,7 +4786,7 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P10" s="2">
-        <v>46312.29484287875</v>
+        <v>46312.65710760548</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>46</v>
@@ -4830,7 +4830,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11">
-        <v>46312.29484284001</v>
+        <v>46312.65710756149</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>46</v>
@@ -4874,7 +4874,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46312.29483166153</v>
+        <v>46312.65709963298</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>46</v>
@@ -4921,7 +4921,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46312.29483163588</v>
+        <v>46312.65709960293</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>46</v>
@@ -4968,7 +4968,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46312.29483160963</v>
+        <v>46312.65709957341</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>46</v>
@@ -5015,7 +5015,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P15">
-        <v>46312.29483159653</v>
+        <v>46312.65709955859</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>46</v>
@@ -5059,7 +5059,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46312.29483155741</v>
+        <v>46312.65709951358</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>46</v>
@@ -5103,7 +5103,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46312.2948315709</v>
+        <v>46312.65709952823</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>46</v>
@@ -5150,7 +5150,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46312.29483158379</v>
+        <v>46312.6570995425</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>46</v>
@@ -5197,7 +5197,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P19">
-        <v>46312.29483153038</v>
+        <v>46312.65709948403</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>46</v>
@@ -5244,7 +5244,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P20">
-        <v>46312.29483151647</v>
+        <v>46312.65709946943</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>46</v>
@@ -5288,7 +5288,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P21">
-        <v>46312.29483147463</v>
+        <v>46312.65709942421</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>46</v>
@@ -5335,7 +5335,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P22" s="6">
-        <v>46312.29485680167</v>
+        <v>46312.65711592732</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>46</v>
@@ -5382,7 +5382,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P23" s="6">
-        <v>46312.29485685294</v>
+        <v>46312.65711598445</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>46</v>
@@ -5429,7 +5429,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P24" s="6">
-        <v>46312.29485684038</v>
+        <v>46312.65711597015</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>46</v>
@@ -5478,7 +5478,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P25" s="6">
-        <v>46312.29486543904</v>
+        <v>46312.65712403938</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>46</v>
@@ -5576,7 +5576,7 @@
         <v>46300.75885647022</v>
       </c>
       <c r="P27" s="6">
-        <v>46312.29487409964</v>
+        <v>46312.65713212876</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>46</v>
@@ -5644,7 +5644,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46312.29481460934</v>
+        <v>46312.65708521284</v>
       </c>
       <c r="B2">
-        <v>46312.29886374016</v>
+        <v>46312.65865222656</v>
       </c>
       <c r="C2" t="s">
         <v>223</v>
@@ -5727,10 +5727,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46311.70085467582</v>
+        <v>46312.29481460934</v>
       </c>
       <c r="B3">
-        <v>46311.70249357724</v>
+        <v>46312.29886374016</v>
       </c>
       <c r="C3" t="s">
         <v>223</v>
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46311.3074085582</v>
+        <v>46311.70085467582</v>
       </c>
       <c r="B4">
-        <v>46311.31082826155</v>
+        <v>46311.70249357724</v>
       </c>
       <c r="C4" t="s">
         <v>223</v>
@@ -5777,16 +5777,16 @@
         <v>3861</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -5797,45 +5797,45 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46310.71705220221</v>
+        <v>46311.3074085582</v>
       </c>
       <c r="B5">
-        <v>46310.71871343154</v>
+        <v>46311.31082826155</v>
       </c>
       <c r="C5" t="s">
         <v>223</v>
       </c>
       <c r="D5">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>394</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3858</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B6">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C6" t="s">
         <v>223</v>
@@ -5844,33 +5844,33 @@
         <v>193</v>
       </c>
       <c r="E6">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B7">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C7" t="s">
         <v>223</v>
@@ -5879,16 +5879,16 @@
         <v>193</v>
       </c>
       <c r="E7">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5897,15 +5897,15 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B8">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C8" t="s">
         <v>223</v>
@@ -5914,33 +5914,33 @@
         <v>193</v>
       </c>
       <c r="E8">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B9">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C9" t="s">
         <v>223</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5972,10 +5972,10 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B10">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C10" t="s">
         <v>223</v>
@@ -5987,16 +5987,16 @@
         <v>3844</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -6007,45 +6007,45 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B11">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C11" t="s">
         <v>223</v>
       </c>
       <c r="D11">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E11">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>381</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B12">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C12" t="s">
         <v>223</v>
@@ -6057,13 +6057,13 @@
         <v>3838</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -6077,10 +6077,10 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B13">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C13" t="s">
         <v>223</v>
@@ -6089,16 +6089,16 @@
         <v>192</v>
       </c>
       <c r="E13">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>369</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -6107,15 +6107,15 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B14">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C14" t="s">
         <v>223</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B15">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C15" t="s">
         <v>223</v>
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -6182,10 +6182,10 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B16">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C16" t="s">
         <v>223</v>
@@ -6217,10 +6217,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B17">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C17" t="s">
         <v>223</v>
@@ -6232,16 +6232,16 @@
         <v>3826</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -6252,45 +6252,45 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B18">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C18" t="s">
         <v>223</v>
       </c>
       <c r="D18">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E18">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B19">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C19" t="s">
         <v>223</v>
@@ -6322,10 +6322,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B20">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C20" t="s">
         <v>223</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B21">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C21" t="s">
         <v>223</v>
@@ -6372,16 +6372,16 @@
         <v>3820</v>
       </c>
       <c r="F21">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H21">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -6392,45 +6392,45 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B22">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C22" t="s">
         <v>223</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E22">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G22">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B23">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C23" t="s">
         <v>223</v>
@@ -6442,13 +6442,13 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -6457,15 +6457,15 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B24">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C24" t="s">
         <v>223</v>
@@ -6477,21 +6477,56 @@
         <v>160</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>160</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B25">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>160</v>
+      </c>
+      <c r="F25">
         <v>157</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>3</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <v>132</v>
       </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="222">
   <si>
     <t>Priority</t>
   </si>
@@ -79,36 +79,432 @@
     <t>Open</t>
   </si>
   <si>
+    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>ishant jain</t>
+  </si>
+  <si>
+    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>Corrigendum dated 14 October 2026 to FORM G dated 28 September 2026</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chandra Kumar Jain</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>CORRIGENDUM TO FORM G INVITATION FOR EXPRESSION OF INTEREST FOR INDO PACIFIC PROJECTS LIMITED (Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SMO FERRO ALLOYS LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Rajesh Lohia</t>
+  </si>
+  <si>
+    <t>ALCOB INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRASHANT KHATAVKAR</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Kamal Agarwal</t>
+  </si>
+  <si>
+    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>The original Form G was published on 27th September 2026, with 12th October 2026 being the last date for submission of Expressions of Interest (EOIs). However, pursuant to the request received from the CoC members to extend the timeline for submission of</t>
+  </si>
+  <si>
+    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Abhit Kumar Singh</t>
+  </si>
+  <si>
+    <t>KUTE SONS DAIRYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ritesh R Mahajan</t>
+  </si>
+  <si>
+    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chirag Rajendra Kumar Shah</t>
+  </si>
+  <si>
+    <t>Form G published on 13th October 2026.</t>
+  </si>
+  <si>
+    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Hotel / Hospitality</t>
+  </si>
+  <si>
+    <t>Hotels / Resorts</t>
+  </si>
+  <si>
+    <t>Harsh Kumar Arora</t>
+  </si>
+  <si>
+    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
+  </si>
+  <si>
+    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Prashant Jain</t>
+  </si>
+  <si>
+    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
+  </si>
+  <si>
+    <t>STUTI COMTRADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
+  </si>
+  <si>
+    <t>2nd Form G.</t>
+  </si>
+  <si>
+    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shaikh Nafis Anjum</t>
+  </si>
+  <si>
+    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>JRA INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Parshva Manoj Shah</t>
+  </si>
+  <si>
+    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
     <t>MANISH AGARWALLA</t>
   </si>
   <si>
     <t>Fixed assets location are taken as per the latest audited balance sheet &amp; address mention as D3/1401 NOIDA Extension .No documents and details are received from the Suspended Board of Directors. Section 19(2) application filed with the Hon'ble NC</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
     <t>COMET GRANITO PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
     <t>Anil Kashi Drolia</t>
   </si>
   <si>
     <t>VAASUDEVA MILK FOODS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
     <t>ATKURU SAI PRASAD</t>
   </si>
   <si>
@@ -127,402 +523,6 @@
     <t>Form G was published for the third time with the approval of the CoC and the NCLT.</t>
   </si>
   <si>
-    <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
-    <t>ishant jain</t>
-  </si>
-  <si>
-    <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>Corrigendum dated 14 October 2026 to FORM G dated 28 September 2026</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chandra Kumar Jain</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>The addendum to form G was issued on 10th October, 2026.</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>CORRIGENDUM TO FORM G INVITATION FOR EXPRESSION OF INTEREST FOR INDO PACIFIC PROJECTS LIMITED (Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SMO FERRO ALLOYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Rajesh Lohia</t>
-  </si>
-  <si>
-    <t>ALCOB INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRASHANT KHATAVKAR</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>SUNSHINE FASTECH LIMITED</t>
-  </si>
-  <si>
-    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
-  </si>
-  <si>
-    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dev Vrat Rana</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
-  </si>
-  <si>
-    <t>SWADESH GREEN INFRA LIMITED</t>
-  </si>
-  <si>
-    <t>Niraj Kumar</t>
-  </si>
-  <si>
-    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
-  </si>
-  <si>
-    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bishwa Ranjan Chatterjee</t>
-  </si>
-  <si>
-    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
-  </si>
-  <si>
-    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Kamal Agarwal</t>
-  </si>
-  <si>
-    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>The original Form G was published on 27th September 2026, with 12th October 2026 being the last date for submission of Expressions of Interest (EOIs). However, pursuant to the request received from the CoC members to extend the timeline for submission of</t>
-  </si>
-  <si>
-    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Abhit Kumar Singh</t>
-  </si>
-  <si>
-    <t>KUTE SONS DAIRYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ritesh R Mahajan</t>
-  </si>
-  <si>
-    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chirag Rajendra Kumar Shah</t>
-  </si>
-  <si>
-    <t>Form G published on 13th October 2026.</t>
-  </si>
-  <si>
-    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Hotel / Hospitality</t>
-  </si>
-  <si>
-    <t>Hotels / Resorts</t>
-  </si>
-  <si>
-    <t>Harsh Kumar Arora</t>
-  </si>
-  <si>
-    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
-  </si>
-  <si>
-    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Prashant Jain</t>
-  </si>
-  <si>
-    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
-  </si>
-  <si>
-    <t>STUTI COMTRADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
-  </si>
-  <si>
-    <t>2nd Form G.</t>
-  </si>
-  <si>
-    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Shaikh Nafis Anjum</t>
-  </si>
-  <si>
-    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>JRA INFRASTRUCTURE LIMITED</t>
-  </si>
-  <si>
-    <t>Parshva Manoj Shah</t>
-  </si>
-  <si>
-    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
-  </si>
-  <si>
-    <t>Resonance Paper Mill Private Limited</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>BHUBANESHWARI SEAFOOD PRIVATE LIMITED</t>
   </si>
   <si>
@@ -650,12 +650,6 @@
   </si>
   <si>
     <t>_</t>
-  </si>
-  <si>
-    <t>SNEH EXPORTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Garima diggiwal</t>
   </si>
   <si>
     <t>Started</t>
@@ -1096,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1181,10 +1175,10 @@
         <v>20</v>
       </c>
       <c r="G2" s="2">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H2" s="3">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
@@ -1193,7 +1187,7 @@
         <v>21</v>
       </c>
       <c r="K2" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>22</v>
@@ -1205,10 +1199,10 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46300.75884779022</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P2" s="2">
-        <v>46312.65711586995</v>
+        <v>46313.30532584916</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1227,17 +1221,20 @@
       <c r="E3" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="G3" s="2">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="H3" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -1249,10 +1246,10 @@
         <v>18</v>
       </c>
       <c r="O3" s="2">
-        <v>46300.75884780569</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P3" s="2">
-        <v>46312.65711588449</v>
+        <v>46313.30532580941</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1266,29 +1263,26 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H4" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1296,13 +1290,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884782107</v>
+        <v>46300.75884775587</v>
       </c>
       <c r="P4" s="2">
-        <v>46312.65711585592</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>23</v>
+        <v>46313.30532582265</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1313,29 +1307,26 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="H5" s="3">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1343,10 +1334,10 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.75884783743</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P5" s="2">
-        <v>46312.65711584162</v>
+        <v>46313.30532583613</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1363,25 +1354,22 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46315</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46313</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="K6" s="2">
-        <v>3</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
@@ -1390,13 +1378,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46302.26841519317</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P6" s="2">
-        <v>46312.65711582667</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>46313.30532579589</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1407,29 +1395,29 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I7" s="2">
         <v>2</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
+      <c r="L7" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
       </c>
@@ -1437,10 +1425,10 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46300.75884774033</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P7" s="2">
-        <v>46312.65711578376</v>
+        <v>46313.30532578268</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1454,26 +1442,32 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G8" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H8" s="3">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1481,13 +1475,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46300.75884775587</v>
+        <v>46311.30744692709</v>
       </c>
       <c r="P8" s="2">
-        <v>46312.65711579815</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>46</v>
+        <v>46313.30532576742</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1498,26 +1492,29 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46316</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.93</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
       <c r="M9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1525,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46300.7588477715</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P9" s="2">
-        <v>46312.6571158125</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>23</v>
+        <v>46313.30531728507</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1545,22 +1542,25 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H10" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I10" s="2">
         <v>3</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
@@ -1569,13 +1569,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46300.75884772457</v>
+        <v>46307.39549714451</v>
       </c>
       <c r="P10" s="2">
-        <v>46312.65711576909</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>46</v>
+        <v>46313.30531731113</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1586,29 +1586,26 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G11" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="M11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1616,13 +1613,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46307.39550534703</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P11" s="2">
-        <v>46312.65711575456</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>23</v>
+        <v>46313.30531725841</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1642,22 +1639,19 @@
         <v>57</v>
       </c>
       <c r="G12" s="2">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" s="3">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="I12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>58</v>
       </c>
       <c r="K12" s="2">
-        <v>2</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>18</v>
@@ -1666,10 +1660,10 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46311.30744692709</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P12" s="2">
-        <v>46312.65711573853</v>
+        <v>46313.30531727153</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1683,28 +1677,25 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G13" s="2">
         <v>0.2</v>
       </c>
       <c r="H13" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I13" s="2">
         <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K13" s="2">
-        <v>3</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -1713,13 +1704,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46302.26841507768</v>
+        <v>46309.72495178872</v>
       </c>
       <c r="P13" s="2">
-        <v>46312.65710777805</v>
+        <v>46313.30531724413</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1730,29 +1721,32 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.96</v>
+      </c>
+      <c r="H14" s="3">
+        <v>46318</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.92</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46316</v>
-      </c>
-      <c r="I14" s="2">
-        <v>4</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" s="2">
-        <v>2</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
       </c>
@@ -1760,10 +1754,10 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46307.39549714451</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P14" s="2">
-        <v>46312.65710780673</v>
+        <v>46313.30531720298</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1777,26 +1771,29 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H15" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I15" s="2">
         <v>5</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
+      <c r="L15" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1804,13 +1801,13 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46301.38232468421</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P15" s="2">
-        <v>46312.65710774902</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>46</v>
+        <v>46313.3053172166</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="2" customFormat="1">
@@ -1821,28 +1818,28 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="G16" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H16" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I16" s="2">
         <v>5</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="K16" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="M16" s="4" t="s">
         <v>18</v>
@@ -1851,10 +1848,10 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46302.26841501552</v>
+        <v>46308.39986132324</v>
       </c>
       <c r="P16" s="2">
-        <v>46312.65710776359</v>
+        <v>46313.30531718949</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1868,25 +1865,28 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G17" s="2">
         <v>0.2</v>
       </c>
       <c r="H17" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I17" s="2">
         <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K17" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
@@ -1895,13 +1895,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46309.72495178872</v>
+        <v>46311.30743731892</v>
       </c>
       <c r="P17" s="2">
-        <v>46312.65710773495</v>
+        <v>46313.30531722958</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1912,19 +1912,19 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="G18" s="2">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H18" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I18" s="2">
         <v>6</v>
@@ -1933,7 +1933,7 @@
         <v>76</v>
       </c>
       <c r="K18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>77</v>
@@ -1945,10 +1945,10 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46305.20575267453</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P18" s="2">
-        <v>46312.65710769239</v>
+        <v>46313.30531717594</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -1965,26 +1965,26 @@
         <v>78</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="G19" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I19" s="2">
         <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="2">
+        <v>2</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
       </c>
@@ -1992,13 +1992,13 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46305.20575269723</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P19" s="2">
-        <v>46312.65710770644</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>23</v>
+        <v>46313.30531714948</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1">
@@ -2009,28 +2009,25 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G20" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I20" s="2">
         <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="K20" s="2">
-        <v>2</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -2039,13 +2036,13 @@
         <v>18</v>
       </c>
       <c r="O20" s="2">
-        <v>46308.39986132324</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P20" s="2">
-        <v>46312.65710767791</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>23</v>
+        <v>46313.30531716249</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="2" customFormat="1">
@@ -2056,16 +2053,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G21" s="2">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H21" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I21" s="2">
         <v>6</v>
@@ -2076,9 +2073,6 @@
       <c r="K21" s="2">
         <v>2</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
       </c>
@@ -2086,13 +2080,13 @@
         <v>18</v>
       </c>
       <c r="O21" s="2">
-        <v>46311.30743731892</v>
+        <v>46309.72495168629</v>
       </c>
       <c r="P21" s="2">
-        <v>46312.65710772065</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>46</v>
+        <v>46313.30531711045</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1">
@@ -2103,31 +2097,25 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="G22" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H22" s="3">
         <v>46319</v>
       </c>
       <c r="I22" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K22" s="2">
-        <v>2</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2136,13 +2124,13 @@
         <v>18</v>
       </c>
       <c r="O22" s="2">
-        <v>46305.20575263901</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P22" s="2">
-        <v>46312.65710766351</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>23</v>
+        <v>46313.30531712321</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="2" customFormat="1">
@@ -2153,29 +2141,29 @@
         <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>44</v>
+        <v>89</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="G23" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H23" s="3">
         <v>46319</v>
       </c>
       <c r="I23" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K23" s="2">
         <v>2</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
       </c>
@@ -2183,13 +2171,13 @@
         <v>18</v>
       </c>
       <c r="O23" s="2">
-        <v>46307.39549700746</v>
+        <v>46310.31707038325</v>
       </c>
       <c r="P23" s="2">
-        <v>46312.65710763459</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>46</v>
+        <v>46313.30531713596</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="2" customFormat="1">
@@ -2200,25 +2188,28 @@
         <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H24" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I24" s="2">
         <v>7</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K24" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2227,13 +2218,13 @@
         <v>18</v>
       </c>
       <c r="O24" s="2">
-        <v>46307.3954970362</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P24" s="2">
-        <v>46312.65710764895</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>46</v>
+        <v>46313.30531705452</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="2" customFormat="1">
@@ -2244,25 +2235,25 @@
         <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="2">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H25" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I25" s="2">
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>18</v>
@@ -2271,10 +2262,10 @@
         <v>18</v>
       </c>
       <c r="O25" s="2">
-        <v>46309.72495168629</v>
+        <v>46307.39549697415</v>
       </c>
       <c r="P25" s="2">
-        <v>46312.65710759105</v>
+        <v>46313.30531706983</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>23</v>
@@ -2288,72 +2279,69 @@
         <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G26" s="2">
         <v>0.2</v>
       </c>
       <c r="H26" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I26" s="2">
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="2">
+        <v>46308.39986123197</v>
+      </c>
+      <c r="P26" s="2">
+        <v>46313.3053170835</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
         <v>100</v>
       </c>
-      <c r="K26" s="2">
-        <v>1</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O26" s="2">
-        <v>46309.72495171529</v>
-      </c>
-      <c r="P26" s="2">
-        <v>46312.65710760548</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="2" customFormat="1">
-      <c r="A27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27">
+        <v>0.2</v>
+      </c>
+      <c r="H27" s="3">
+        <v>46321</v>
+      </c>
+      <c r="I27">
+        <v>8</v>
+      </c>
+      <c r="J27" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0.91</v>
-      </c>
-      <c r="H27" s="3">
-        <v>46319</v>
-      </c>
-      <c r="I27" s="2">
-        <v>7</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="2">
-        <v>2</v>
+      <c r="K27">
+        <v>1</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>18</v>
@@ -2361,14 +2349,14 @@
       <c r="N27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O27" s="2">
-        <v>46310.31707038325</v>
-      </c>
-      <c r="P27" s="2">
-        <v>46312.65710761982</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>23</v>
+      <c r="O27">
+        <v>46307.39549690609</v>
+      </c>
+      <c r="P27">
+        <v>46313.30530860629</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2379,28 +2367,28 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G28">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H28" s="3">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K28">
         <v>2</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
@@ -2409,13 +2397,13 @@
         <v>18</v>
       </c>
       <c r="O28">
-        <v>46307.3954969447</v>
+        <v>46307.39549680641</v>
       </c>
       <c r="P28">
-        <v>46312.65710753087</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>23</v>
+        <v>46313.30530857794</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2426,26 +2414,32 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>43</v>
       </c>
       <c r="G29">
         <v>0.91</v>
       </c>
       <c r="H29" s="3">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
+      <c r="L29" t="s">
+        <v>107</v>
+      </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2453,10 +2447,10 @@
         <v>18</v>
       </c>
       <c r="O29">
-        <v>46307.39549697415</v>
+        <v>46307.39549684311</v>
       </c>
       <c r="P29">
-        <v>46312.65710754672</v>
+        <v>46313.3053085645</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2470,26 +2464,29 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G30">
         <v>0.2</v>
       </c>
       <c r="H30" s="3">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K30">
         <v>1</v>
       </c>
+      <c r="L30" t="s">
+        <v>110</v>
+      </c>
       <c r="M30" s="4" t="s">
         <v>18</v>
       </c>
@@ -2497,13 +2494,13 @@
         <v>18</v>
       </c>
       <c r="O30">
-        <v>46308.39986123197</v>
+        <v>46307.39549687663</v>
       </c>
       <c r="P30">
-        <v>46312.65710756149</v>
+        <v>46313.30530854941</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2514,26 +2511,32 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>74</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
       </c>
       <c r="G31">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H31" s="3">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I31">
         <v>9</v>
       </c>
       <c r="J31" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" t="s">
         <v>113</v>
       </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
       </c>
@@ -2541,13 +2544,13 @@
         <v>18</v>
       </c>
       <c r="O31">
-        <v>46307.39549690609</v>
+        <v>46308.39986117012</v>
       </c>
       <c r="P31">
-        <v>46312.65709963298</v>
-      </c>
-      <c r="Q31" s="5" t="s">
-        <v>46</v>
+        <v>46313.30530859238</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2561,7 +2564,7 @@
         <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G32">
         <v>0.2</v>
@@ -2570,7 +2573,7 @@
         <v>46322</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" t="s">
         <v>115</v>
@@ -2588,13 +2591,13 @@
         <v>18</v>
       </c>
       <c r="O32">
-        <v>46307.39549680641</v>
+        <v>46311.30742780836</v>
       </c>
       <c r="P32">
-        <v>46312.65709960293</v>
+        <v>46313.30530853521</v>
       </c>
       <c r="Q32" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2608,16 +2611,13 @@
         <v>117</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G33">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H33" s="3">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I33">
         <v>10</v>
@@ -2628,9 +2628,6 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="L33" t="s">
-        <v>119</v>
-      </c>
       <c r="M33" s="4" t="s">
         <v>18</v>
       </c>
@@ -2638,13 +2635,13 @@
         <v>18</v>
       </c>
       <c r="O33">
-        <v>46307.39549684311</v>
+        <v>46309.72494256633</v>
       </c>
       <c r="P33">
-        <v>46312.65709958807</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>23</v>
+        <v>46313.30530849531</v>
+      </c>
+      <c r="Q33" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2655,29 +2652,26 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G34">
         <v>0.2</v>
       </c>
       <c r="H34" s="3">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I34">
         <v>10</v>
       </c>
       <c r="J34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34" t="s">
-        <v>122</v>
-      </c>
       <c r="M34" s="4" t="s">
         <v>18</v>
       </c>
@@ -2685,13 +2679,13 @@
         <v>18</v>
       </c>
       <c r="O34">
-        <v>46307.39549687663</v>
+        <v>46309.72494259723</v>
       </c>
       <c r="P34">
-        <v>46312.65709957341</v>
+        <v>46313.30530850866</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2702,31 +2696,28 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="G35">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H35" s="3">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I35">
         <v>10</v>
       </c>
       <c r="J35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>18</v>
@@ -2735,13 +2726,13 @@
         <v>18</v>
       </c>
       <c r="O35">
-        <v>46308.39986117012</v>
+        <v>46309.72494262765</v>
       </c>
       <c r="P35">
-        <v>46312.65709961824</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>23</v>
+        <v>46313.30530852199</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2752,16 +2743,19 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" t="s">
         <v>126</v>
       </c>
-      <c r="E36" t="s">
-        <v>44</v>
-      </c>
       <c r="G36">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H36" s="3">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I36">
         <v>10</v>
@@ -2770,7 +2764,7 @@
         <v>127</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" t="s">
         <v>128</v>
@@ -2782,13 +2776,13 @@
         <v>18</v>
       </c>
       <c r="O36">
-        <v>46311.30742780836</v>
+        <v>46310.31706138982</v>
       </c>
       <c r="P36">
-        <v>46312.65709955859</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>46</v>
+        <v>46313.30530848172</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2802,7 +2796,7 @@
         <v>129</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G37">
         <v>0.2</v>
@@ -2811,7 +2805,7 @@
         <v>46323</v>
       </c>
       <c r="I37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J37" t="s">
         <v>130</v>
@@ -2819,6 +2813,9 @@
       <c r="K37">
         <v>1</v>
       </c>
+      <c r="L37" t="s">
+        <v>131</v>
+      </c>
       <c r="M37" s="4" t="s">
         <v>18</v>
       </c>
@@ -2826,13 +2823,13 @@
         <v>18</v>
       </c>
       <c r="O37">
-        <v>46309.72494256633</v>
+        <v>46310.71706723773</v>
       </c>
       <c r="P37">
-        <v>46312.65709951358</v>
+        <v>46313.3053084683</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2843,26 +2840,29 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G38">
         <v>0.2</v>
       </c>
       <c r="H38" s="3">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="I38">
         <v>11</v>
       </c>
       <c r="J38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K38">
         <v>1</v>
       </c>
+      <c r="L38" t="s">
+        <v>134</v>
+      </c>
       <c r="M38" s="4" t="s">
         <v>18</v>
       </c>
@@ -2870,13 +2870,13 @@
         <v>18</v>
       </c>
       <c r="O38">
-        <v>46309.72494259723</v>
+        <v>46309.72494253634</v>
       </c>
       <c r="P38">
-        <v>46312.65709952823</v>
+        <v>46313.3053084546</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2887,28 +2887,28 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G39">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H39" s="3">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="I39">
         <v>11</v>
       </c>
       <c r="J39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>18</v>
@@ -2917,13 +2917,13 @@
         <v>18</v>
       </c>
       <c r="O39">
-        <v>46309.72494262765</v>
+        <v>46310.31706133292</v>
       </c>
       <c r="P39">
-        <v>46312.6570995425</v>
-      </c>
-      <c r="Q39" s="5" t="s">
-        <v>46</v>
+        <v>46313.30530844122</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2934,31 +2934,31 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G40">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="H40" s="3">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="I40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>18</v>
@@ -2967,10 +2967,10 @@
         <v>18</v>
       </c>
       <c r="O40">
-        <v>46310.31706138982</v>
+        <v>46309.72494249383</v>
       </c>
       <c r="P40">
-        <v>46312.65709949912</v>
+        <v>46313.30530842762</v>
       </c>
       <c r="Q40" t="s">
         <v>23</v>
@@ -2984,29 +2984,26 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G41">
         <v>0.2</v>
       </c>
       <c r="H41" s="3">
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K41">
         <v>1</v>
       </c>
-      <c r="L41" t="s">
-        <v>143</v>
-      </c>
       <c r="M41" s="4" t="s">
         <v>18</v>
       </c>
@@ -3014,13 +3011,13 @@
         <v>18</v>
       </c>
       <c r="O41">
-        <v>46310.71706723773</v>
+        <v>46300.75884768533</v>
       </c>
       <c r="P41">
-        <v>46312.65709948403</v>
+        <v>46313.30530841411</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -3034,22 +3031,25 @@
         <v>144</v>
       </c>
       <c r="E42" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="F42" t="s">
+        <v>43</v>
       </c>
       <c r="G42">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H42" s="3">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="I42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J42" t="s">
         <v>145</v>
       </c>
       <c r="K42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" t="s">
         <v>146</v>
@@ -3061,13 +3061,13 @@
         <v>18</v>
       </c>
       <c r="O42">
-        <v>46309.72494253634</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P42">
-        <v>46312.65709946943</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>46</v>
+        <v>46313.30530838588</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -3081,25 +3081,22 @@
         <v>147</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="G43">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H43" s="3">
-        <v>46324</v>
+        <v>46332</v>
       </c>
       <c r="I43">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s">
         <v>148</v>
       </c>
       <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43" t="s">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>18</v>
@@ -3108,10 +3105,10 @@
         <v>18</v>
       </c>
       <c r="O43">
-        <v>46310.31706133292</v>
+        <v>46305.20575257758</v>
       </c>
       <c r="P43">
-        <v>46312.65709945454</v>
+        <v>46313.30530837171</v>
       </c>
       <c r="Q43" t="s">
         <v>23</v>
@@ -3125,32 +3122,29 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44" t="s">
+        <v>38</v>
+      </c>
+      <c r="G44">
+        <v>0.95</v>
+      </c>
+      <c r="H44" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I44">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s">
+        <v>82</v>
+      </c>
+      <c r="K44">
+        <v>4</v>
+      </c>
+      <c r="L44" t="s">
         <v>150</v>
       </c>
-      <c r="E44" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" t="s">
-        <v>151</v>
-      </c>
-      <c r="G44">
-        <v>0.89</v>
-      </c>
-      <c r="H44" s="3">
-        <v>46325</v>
-      </c>
-      <c r="I44">
-        <v>13</v>
-      </c>
-      <c r="J44" t="s">
-        <v>152</v>
-      </c>
-      <c r="K44">
-        <v>2</v>
-      </c>
-      <c r="L44" t="s">
-        <v>153</v>
-      </c>
       <c r="M44" s="4" t="s">
         <v>18</v>
       </c>
@@ -3158,10 +3152,10 @@
         <v>18</v>
       </c>
       <c r="O44">
-        <v>46309.72494249383</v>
+        <v>46307.39549666931</v>
       </c>
       <c r="P44">
-        <v>46312.65709943903</v>
+        <v>46313.3053083565</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3175,240 +3169,249 @@
         <v>18</v>
       </c>
       <c r="C45" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H45" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I45">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s">
+        <v>152</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45">
+        <v>46307.39549671811</v>
+      </c>
+      <c r="P45">
+        <v>46313.30530832517</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E45" t="s">
-        <v>44</v>
-      </c>
-      <c r="G45">
-        <v>0.2</v>
-      </c>
-      <c r="H45" s="3">
-        <v>46326</v>
-      </c>
-      <c r="I45">
-        <v>14</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="C46" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O45">
-        <v>46300.75884768533</v>
-      </c>
-      <c r="P45">
-        <v>46312.65709942421</v>
-      </c>
-      <c r="Q45" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
-      <c r="A46" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="D46" s="6"/>
+      <c r="E46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H46" s="6">
+        <v>46312</v>
+      </c>
+      <c r="I46" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E46" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" t="s">
-        <v>57</v>
-      </c>
-      <c r="G46">
+      <c r="K46" s="6">
+        <v>1</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46" s="6">
+        <v>46300.75884779022</v>
+      </c>
+      <c r="P46" s="6">
+        <v>46313.30532588915</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H47" s="6">
+        <v>46312</v>
+      </c>
+      <c r="I47" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K47" s="6">
+        <v>1</v>
+      </c>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47" s="6">
+        <v>46300.75884780569</v>
+      </c>
+      <c r="P47" s="6">
+        <v>46313.30532590194</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="H48" s="6">
+        <v>46312</v>
+      </c>
+      <c r="I48" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K48" s="6">
+        <v>1</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" s="6">
+        <v>46300.75884782107</v>
+      </c>
+      <c r="P48" s="6">
+        <v>46313.30532587588</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6">
         <v>0.91</v>
       </c>
-      <c r="H46" s="3">
-        <v>46328</v>
-      </c>
-      <c r="I46">
-        <v>16</v>
-      </c>
-      <c r="J46" t="s">
-        <v>157</v>
-      </c>
-      <c r="K46">
-        <v>2</v>
-      </c>
-      <c r="L46" t="s">
-        <v>158</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O46">
-        <v>46308.39986111095</v>
-      </c>
-      <c r="P46">
-        <v>46312.65709939371</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17">
-      <c r="A47" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" t="s">
-        <v>159</v>
-      </c>
-      <c r="E47" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47">
-        <v>0.92</v>
-      </c>
-      <c r="H47" s="3">
-        <v>46332</v>
-      </c>
-      <c r="I47">
-        <v>20</v>
-      </c>
-      <c r="J47" t="s">
-        <v>160</v>
-      </c>
-      <c r="K47">
-        <v>4</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O47">
-        <v>46305.20575257758</v>
-      </c>
-      <c r="P47">
-        <v>46312.65709937788</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="A48" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" t="s">
-        <v>161</v>
-      </c>
-      <c r="E48" t="s">
-        <v>52</v>
-      </c>
-      <c r="G48">
-        <v>0.95</v>
-      </c>
-      <c r="H48" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I48">
-        <v>21</v>
-      </c>
-      <c r="J48" t="s">
-        <v>96</v>
-      </c>
-      <c r="K48">
-        <v>4</v>
-      </c>
-      <c r="L48" t="s">
-        <v>162</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O48">
-        <v>46307.39549666931</v>
-      </c>
-      <c r="P48">
-        <v>46312.65709936203</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17">
-      <c r="A49" t="s">
-        <v>18</v>
-      </c>
-      <c r="B49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" t="s">
-        <v>163</v>
-      </c>
-      <c r="E49" t="s">
-        <v>79</v>
-      </c>
-      <c r="G49">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H49" s="3">
-        <v>46333</v>
-      </c>
-      <c r="I49">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s">
-        <v>164</v>
-      </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O49">
-        <v>46307.39549671811</v>
-      </c>
-      <c r="P49">
-        <v>46312.65709933193</v>
-      </c>
-      <c r="Q49" t="s">
+      <c r="H49" s="6">
+        <v>46312</v>
+      </c>
+      <c r="I49" s="6">
+        <v>-1</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K49" s="6">
+        <v>1</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49" s="6">
+        <v>46300.75884783743</v>
+      </c>
+      <c r="P49" s="6">
+        <v>46313.30532586262</v>
+      </c>
+      <c r="Q49" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>167</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
@@ -3418,7 +3421,7 @@
         <v>46310</v>
       </c>
       <c r="I50" s="6">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>168</v>
@@ -3439,7 +3442,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P50" s="6">
-        <v>46312.65711591329</v>
+        <v>46313.30532592876</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3447,17 +3450,17 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>170</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
@@ -3467,7 +3470,7 @@
         <v>46309</v>
       </c>
       <c r="I51" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>171</v>
@@ -3486,25 +3489,25 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P51" s="6">
-        <v>46312.65711592732</v>
+        <v>46313.30532594294</v>
       </c>
       <c r="Q51" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>172</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
@@ -3514,7 +3517,7 @@
         <v>46308</v>
       </c>
       <c r="I52" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>173</v>
@@ -3533,25 +3536,25 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P52" s="6">
-        <v>46312.65711598445</v>
+        <v>46313.30532599742</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>174</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6">
@@ -3561,7 +3564,7 @@
         <v>46308</v>
       </c>
       <c r="I53" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>175</v>
@@ -3580,18 +3583,18 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P53" s="6">
-        <v>46312.65711597015</v>
+        <v>46313.30532598343</v>
       </c>
       <c r="Q53" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>176</v>
@@ -3610,7 +3613,7 @@
         <v>46307</v>
       </c>
       <c r="I54" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>179</v>
@@ -3631,7 +3634,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P54" s="6">
-        <v>46312.65712399615</v>
+        <v>46313.30533904954</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>23</v>
@@ -3639,20 +3642,20 @@
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>181</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G55" s="6">
         <v>0.93</v>
@@ -3661,7 +3664,7 @@
         <v>46307</v>
       </c>
       <c r="I55" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>182</v>
@@ -3680,7 +3683,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46312.65712393675</v>
+        <v>46313.30533899343</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3688,17 +3691,17 @@
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>183</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6">
@@ -3708,7 +3711,7 @@
         <v>46307</v>
       </c>
       <c r="I56" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>184</v>
@@ -3729,25 +3732,25 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46312.65712403938</v>
+        <v>46313.3053390893</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>186</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6">
@@ -3757,7 +3760,7 @@
         <v>46307</v>
       </c>
       <c r="I57" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J57" s="6" t="s">
         <v>187</v>
@@ -3776,7 +3779,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46312.6571240104</v>
+        <v>46313.30533906279</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3784,17 +3787,17 @@
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>188</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6">
@@ -3804,7 +3807,7 @@
         <v>46307</v>
       </c>
       <c r="I58" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>184</v>
@@ -3825,7 +3828,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46312.65712402533</v>
+        <v>46313.30533907594</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3833,20 +3836,20 @@
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>190</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G59" s="6">
         <v>0.93</v>
@@ -3855,10 +3858,10 @@
         <v>46307</v>
       </c>
       <c r="I59" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K59" s="6">
         <v>2</v>
@@ -3884,20 +3887,20 @@
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>193</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G60" s="6">
         <v>0.9399999999999999</v>
@@ -3906,7 +3909,7 @@
         <v>46306</v>
       </c>
       <c r="I60" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J60" s="6" t="s">
         <v>194</v>
@@ -3927,7 +3930,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46312.65712406745</v>
+        <v>46313.30533911665</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3935,17 +3938,17 @@
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>196</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6">
@@ -3955,7 +3958,7 @@
         <v>46306</v>
       </c>
       <c r="I61" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>197</v>
@@ -3976,7 +3979,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46312.65712408235</v>
+        <v>46313.30533913011</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -3984,17 +3987,17 @@
     </row>
     <row r="62" spans="1:17">
       <c r="A62" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>199</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6">
@@ -4004,7 +4007,7 @@
         <v>46305</v>
       </c>
       <c r="I62" s="6">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>200</v>
@@ -4025,7 +4028,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46312.65712412516</v>
+        <v>46313.30533917051</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4033,10 +4036,10 @@
     </row>
     <row r="63" spans="1:17">
       <c r="A63" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>202</v>
@@ -4053,7 +4056,7 @@
         <v>46304</v>
       </c>
       <c r="I63" s="6">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J63" s="6" t="s">
         <v>204</v>
@@ -4074,7 +4077,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46312.6571241546</v>
+        <v>46313.30533919778</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4082,17 +4085,17 @@
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>206</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>207</v>
@@ -4104,7 +4107,7 @@
         <v>46303</v>
       </c>
       <c r="I64" s="6">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>208</v>
@@ -4125,61 +4128,14 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46312.65712418339</v>
+        <v>46313.30533922432</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:17">
-      <c r="A65" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H65" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I65" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="K65" s="6">
-        <v>1</v>
-      </c>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N65" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O65" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P65" s="6">
-        <v>46312.65713212876</v>
-      </c>
-      <c r="Q65" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q65"/>
+  <autoFilter ref="A1:Q64"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4307,8 +4263,6 @@
     <hyperlink ref="N63" r:id="rId124"/>
     <hyperlink ref="M64" r:id="rId125"/>
     <hyperlink ref="N64" r:id="rId126"/>
-    <hyperlink ref="M65" r:id="rId127"/>
-    <hyperlink ref="N65" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4316,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4395,10 +4349,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
@@ -4407,10 +4361,10 @@
         <v>46314</v>
       </c>
       <c r="I2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -4425,10 +4379,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46312.65711579815</v>
+        <v>46313.30532582265</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4439,10 +4393,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -4451,10 +4405,10 @@
         <v>46315</v>
       </c>
       <c r="I3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4469,10 +4423,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46312.65711576909</v>
+        <v>46313.30532579589</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4483,10 +4437,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
@@ -4495,16 +4449,16 @@
         <v>46316</v>
       </c>
       <c r="I4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2">
         <v>3</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -4516,10 +4470,10 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46312.65710777805</v>
+        <v>46313.30531728507</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4530,10 +4484,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -4542,10 +4496,10 @@
         <v>46317</v>
       </c>
       <c r="I5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -4560,10 +4514,10 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46312.65710774902</v>
+        <v>46313.30531725841</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -4574,10 +4528,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2">
         <v>0.2</v>
@@ -4586,10 +4540,10 @@
         <v>46317</v>
       </c>
       <c r="I6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -4604,10 +4558,10 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46312.65710773495</v>
+        <v>46313.30531724413</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -4618,10 +4572,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G7" s="2">
         <v>0.2</v>
@@ -4630,16 +4584,16 @@
         <v>46318</v>
       </c>
       <c r="I7" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4651,10 +4605,10 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P7" s="2">
-        <v>46312.65710772065</v>
+        <v>46313.30531722958</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -4665,10 +4619,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G8" s="2">
         <v>0.2</v>
@@ -4677,16 +4631,16 @@
         <v>46319</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K8" s="2">
         <v>2</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -4698,10 +4652,10 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P8" s="2">
-        <v>46312.65710763459</v>
+        <v>46313.30531714948</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -4712,10 +4666,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G9" s="2">
         <v>0.2</v>
@@ -4724,10 +4678,10 @@
         <v>46319</v>
       </c>
       <c r="I9" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -4742,10 +4696,10 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P9" s="2">
-        <v>46312.65710764895</v>
+        <v>46313.30531716249</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -4756,10 +4710,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2">
         <v>0.2</v>
@@ -4768,10 +4722,10 @@
         <v>46319</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -4786,38 +4740,38 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P10" s="2">
-        <v>46312.65710760548</v>
+        <v>46313.30531712321</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="2" customFormat="1">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2">
         <v>0.2</v>
       </c>
       <c r="H11" s="3">
         <v>46320</v>
       </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11" t="s">
-        <v>111</v>
-      </c>
-      <c r="K11">
+      <c r="I11" s="2">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
@@ -4826,14 +4780,14 @@
       <c r="N11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>46308.39986123197</v>
       </c>
-      <c r="P11">
-        <v>46312.65710756149</v>
+      <c r="P11" s="2">
+        <v>46313.3053170835</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -4844,10 +4798,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>0.2</v>
@@ -4856,10 +4810,10 @@
         <v>46321</v>
       </c>
       <c r="I12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -4874,10 +4828,10 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46312.65709963298</v>
+        <v>46313.30530860629</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -4888,10 +4842,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>0.2</v>
@@ -4900,16 +4854,16 @@
         <v>46322</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4921,10 +4875,10 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46312.65709960293</v>
+        <v>46313.30530857794</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -4935,10 +4889,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G14">
         <v>0.2</v>
@@ -4947,16 +4901,16 @@
         <v>46322</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -4968,10 +4922,10 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46312.65709957341</v>
+        <v>46313.30530854941</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -4982,10 +4936,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G15">
         <v>0.2</v>
@@ -4994,16 +4948,16 @@
         <v>46322</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
@@ -5015,10 +4969,10 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P15">
-        <v>46312.65709955859</v>
+        <v>46313.30530853521</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -5029,10 +4983,10 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G16">
         <v>0.2</v>
@@ -5041,10 +4995,10 @@
         <v>46323</v>
       </c>
       <c r="I16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -5059,10 +5013,10 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46312.65709951358</v>
+        <v>46313.30530849531</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -5073,10 +5027,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G17">
         <v>0.2</v>
@@ -5085,10 +5039,10 @@
         <v>46323</v>
       </c>
       <c r="I17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -5103,10 +5057,10 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46312.65709952823</v>
+        <v>46313.30530850866</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -5117,10 +5071,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G18">
         <v>0.2</v>
@@ -5129,16 +5083,16 @@
         <v>46323</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -5150,10 +5104,10 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46312.6570995425</v>
+        <v>46313.30530852199</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -5164,10 +5118,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G19">
         <v>0.2</v>
@@ -5176,16 +5130,16 @@
         <v>46323</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -5197,10 +5151,10 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P19">
-        <v>46312.65709948403</v>
+        <v>46313.3053084683</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -5211,10 +5165,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G20">
         <v>0.2</v>
@@ -5223,16 +5177,16 @@
         <v>46324</v>
       </c>
       <c r="I20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K20">
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -5244,10 +5198,10 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P20">
-        <v>46312.65709946943</v>
+        <v>46313.3053084546</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -5258,10 +5212,10 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G21">
         <v>0.2</v>
@@ -5270,10 +5224,10 @@
         <v>46326</v>
       </c>
       <c r="I21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J21" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -5288,25 +5242,25 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P21">
-        <v>46312.65709942421</v>
+        <v>46313.30530841411</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>170</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6">
@@ -5316,7 +5270,7 @@
         <v>46309</v>
       </c>
       <c r="I22" s="6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>171</v>
@@ -5335,25 +5289,25 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P22" s="6">
-        <v>46312.65711592732</v>
+        <v>46313.30532594294</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>172</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6">
@@ -5363,7 +5317,7 @@
         <v>46308</v>
       </c>
       <c r="I23" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>173</v>
@@ -5382,25 +5336,25 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P23" s="6">
-        <v>46312.65711598445</v>
+        <v>46313.30532599742</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>174</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6">
@@ -5410,7 +5364,7 @@
         <v>46308</v>
       </c>
       <c r="I24" s="6">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>175</v>
@@ -5429,25 +5383,25 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P24" s="6">
-        <v>46312.65711597015</v>
+        <v>46313.30532598343</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>183</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6">
@@ -5457,7 +5411,7 @@
         <v>46307</v>
       </c>
       <c r="I25" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>184</v>
@@ -5478,28 +5432,28 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P25" s="6">
-        <v>46312.65712403938</v>
+        <v>46313.3053390893</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>190</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G26" s="6">
         <v>0.93</v>
@@ -5508,10 +5462,10 @@
         <v>46307</v>
       </c>
       <c r="I26" s="6">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K26" s="6">
         <v>2</v>
@@ -5535,55 +5489,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H27" s="6">
-        <v>46302</v>
-      </c>
-      <c r="I27" s="6">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="K27" s="6">
-        <v>1</v>
-      </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O27" s="6">
-        <v>46300.75885647022</v>
-      </c>
-      <c r="P27" s="6">
-        <v>46312.65713212876</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q27"/>
+  <autoFilter ref="A1:Q26"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -5635,8 +5542,6 @@
     <hyperlink ref="N25" r:id="rId48"/>
     <hyperlink ref="M26" r:id="rId49"/>
     <hyperlink ref="N26" r:id="rId50"/>
-    <hyperlink ref="M27" r:id="rId51"/>
-    <hyperlink ref="N27" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5644,7 +5549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5654,51 +5559,51 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46312.65708521284</v>
+        <v>46313.30528009156</v>
       </c>
       <c r="B2">
-        <v>46312.65865222656</v>
+        <v>46313.3091804056</v>
       </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D2">
         <v>194</v>
@@ -5727,13 +5632,13 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46312.29481460934</v>
+        <v>46312.65708521284</v>
       </c>
       <c r="B3">
-        <v>46312.29886374016</v>
+        <v>46312.65865222656</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D3">
         <v>194</v>
@@ -5762,13 +5667,13 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46311.70085467582</v>
+        <v>46312.29481460934</v>
       </c>
       <c r="B4">
-        <v>46311.70249357724</v>
+        <v>46312.29886374016</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D4">
         <v>194</v>
@@ -5780,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5797,13 +5702,13 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46311.3074085582</v>
+        <v>46311.70085467582</v>
       </c>
       <c r="B5">
-        <v>46311.31082826155</v>
+        <v>46311.70249357724</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D5">
         <v>194</v>
@@ -5812,16 +5717,16 @@
         <v>3861</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -5832,98 +5737,98 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46310.71705220221</v>
+        <v>46311.3074085582</v>
       </c>
       <c r="B6">
-        <v>46310.71871343154</v>
+        <v>46311.31082826155</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D6">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>394</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3858</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B7">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D7">
         <v>193</v>
       </c>
       <c r="E7">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B8">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8">
         <v>193</v>
       </c>
       <c r="E8">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -5932,53 +5837,53 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B9">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D9">
         <v>193</v>
       </c>
       <c r="E9">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B10">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10">
         <v>193</v>
@@ -5990,7 +5895,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -6007,13 +5912,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B11">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D11">
         <v>193</v>
@@ -6022,16 +5927,16 @@
         <v>3844</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -6042,48 +5947,48 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B12">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D12">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E12">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>381</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B13">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D13">
         <v>192</v>
@@ -6092,13 +5997,13 @@
         <v>3838</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -6112,28 +6017,28 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B14">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D14">
         <v>192</v>
       </c>
       <c r="E14">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>369</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -6142,18 +6047,18 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B15">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D15">
         <v>192</v>
@@ -6182,13 +6087,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B16">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D16">
         <v>192</v>
@@ -6200,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6217,13 +6122,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B17">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D17">
         <v>192</v>
@@ -6252,13 +6157,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B18">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D18">
         <v>192</v>
@@ -6267,16 +6172,16 @@
         <v>3826</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -6287,48 +6192,48 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B19">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D19">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E19">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B20">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D20">
         <v>191</v>
@@ -6357,13 +6262,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B21">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D21">
         <v>191</v>
@@ -6375,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -6392,13 +6297,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B22">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D22">
         <v>191</v>
@@ -6407,16 +6312,16 @@
         <v>3820</v>
       </c>
       <c r="F22">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H22">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -6427,48 +6332,48 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B23">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C23" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E23">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G23">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B24">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -6477,13 +6382,13 @@
         <v>160</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -6492,18 +6397,18 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B25">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -6512,21 +6417,56 @@
         <v>160</v>
       </c>
       <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>160</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B26">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C26" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>160</v>
+      </c>
+      <c r="F26">
         <v>157</v>
       </c>
-      <c r="G25">
+      <c r="G26">
         <v>3</v>
       </c>
-      <c r="H25">
+      <c r="H26">
         <v>132</v>
       </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="222">
   <si>
     <t>Priority</t>
   </si>
@@ -1202,7 +1202,7 @@
         <v>46302.26841519317</v>
       </c>
       <c r="P2" s="2">
-        <v>46313.30532584916</v>
+        <v>46313.66772332653</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1249,7 +1249,7 @@
         <v>46300.75884774033</v>
       </c>
       <c r="P3" s="2">
-        <v>46313.30532580941</v>
+        <v>46313.66772328764</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>23</v>
@@ -1293,7 +1293,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P4" s="2">
-        <v>46313.30532582265</v>
+        <v>46313.66772330055</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>31</v>
@@ -1337,7 +1337,7 @@
         <v>46300.7588477715</v>
       </c>
       <c r="P5" s="2">
-        <v>46313.30532583613</v>
+        <v>46313.66772331384</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>23</v>
@@ -1381,7 +1381,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P6" s="2">
-        <v>46313.30532579589</v>
+        <v>46313.66772327427</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>31</v>
@@ -1428,7 +1428,7 @@
         <v>46307.39550534703</v>
       </c>
       <c r="P7" s="2">
-        <v>46313.30532578268</v>
+        <v>46313.66772326059</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1478,7 +1478,7 @@
         <v>46311.30744692709</v>
       </c>
       <c r="P8" s="2">
-        <v>46313.30532576742</v>
+        <v>46313.6677232455</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>23</v>
@@ -1525,7 +1525,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P9" s="2">
-        <v>46313.30531728507</v>
+        <v>46313.6677142169</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>31</v>
@@ -1572,7 +1572,7 @@
         <v>46307.39549714451</v>
       </c>
       <c r="P10" s="2">
-        <v>46313.30531731113</v>
+        <v>46313.66771424172</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>23</v>
@@ -1616,7 +1616,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P11" s="2">
-        <v>46313.30531725841</v>
+        <v>46313.66771419167</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>31</v>
@@ -1663,7 +1663,7 @@
         <v>46302.26841501552</v>
       </c>
       <c r="P12" s="2">
-        <v>46313.30531727153</v>
+        <v>46313.66771420432</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>23</v>
@@ -1707,7 +1707,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P13" s="2">
-        <v>46313.30531724413</v>
+        <v>46313.66771417948</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>31</v>
@@ -1757,7 +1757,7 @@
         <v>46305.20575267453</v>
       </c>
       <c r="P14" s="2">
-        <v>46313.30531720298</v>
+        <v>46313.66771414227</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1804,7 +1804,7 @@
         <v>46305.20575269723</v>
       </c>
       <c r="P15" s="2">
-        <v>46313.3053172166</v>
+        <v>46313.66771415442</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>23</v>
@@ -1851,7 +1851,7 @@
         <v>46308.39986132324</v>
       </c>
       <c r="P16" s="2">
-        <v>46313.30531718949</v>
+        <v>46313.66771412977</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>23</v>
@@ -1898,7 +1898,7 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P17" s="2">
-        <v>46313.30531722958</v>
+        <v>46313.66771416669</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>31</v>
@@ -1948,7 +1948,7 @@
         <v>46305.20575263901</v>
       </c>
       <c r="P18" s="2">
-        <v>46313.30531717594</v>
+        <v>46313.66771411694</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>23</v>
@@ -1995,7 +1995,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P19" s="2">
-        <v>46313.30531714948</v>
+        <v>46313.66771409143</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>31</v>
@@ -2039,7 +2039,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P20" s="2">
-        <v>46313.30531716249</v>
+        <v>46313.66771410416</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>31</v>
@@ -2083,7 +2083,7 @@
         <v>46309.72495168629</v>
       </c>
       <c r="P21" s="2">
-        <v>46313.30531711045</v>
+        <v>46313.66771405283</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>23</v>
@@ -2127,7 +2127,7 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P22" s="2">
-        <v>46313.30531712321</v>
+        <v>46313.66771406602</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>31</v>
@@ -2174,7 +2174,7 @@
         <v>46310.31707038325</v>
       </c>
       <c r="P23" s="2">
-        <v>46313.30531713596</v>
+        <v>46313.66771407861</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>23</v>
@@ -2221,7 +2221,7 @@
         <v>46307.3954969447</v>
       </c>
       <c r="P24" s="2">
-        <v>46313.30531705452</v>
+        <v>46313.66771399752</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>23</v>
@@ -2265,7 +2265,7 @@
         <v>46307.39549697415</v>
       </c>
       <c r="P25" s="2">
-        <v>46313.30531706983</v>
+        <v>46313.66771401245</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>23</v>
@@ -2309,7 +2309,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P26" s="2">
-        <v>46313.3053170835</v>
+        <v>46313.66771402624</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>31</v>
@@ -2353,7 +2353,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P27">
-        <v>46313.30530860629</v>
+        <v>46313.66770577192</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>31</v>
@@ -2400,7 +2400,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P28">
-        <v>46313.30530857794</v>
+        <v>46313.66770574598</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>31</v>
@@ -2450,7 +2450,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P29">
-        <v>46313.3053085645</v>
+        <v>46313.66770573297</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2497,7 +2497,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P30">
-        <v>46313.30530854941</v>
+        <v>46313.66770571972</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>31</v>
@@ -2547,7 +2547,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P31">
-        <v>46313.30530859238</v>
+        <v>46313.66770575889</v>
       </c>
       <c r="Q31" t="s">
         <v>23</v>
@@ -2594,7 +2594,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P32">
-        <v>46313.30530853521</v>
+        <v>46313.66770570714</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>31</v>
@@ -2638,7 +2638,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P33">
-        <v>46313.30530849531</v>
+        <v>46313.6677056671</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>31</v>
@@ -2682,7 +2682,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P34">
-        <v>46313.30530850866</v>
+        <v>46313.66770568074</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>31</v>
@@ -2729,7 +2729,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P35">
-        <v>46313.30530852199</v>
+        <v>46313.66770569394</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>31</v>
@@ -2779,7 +2779,7 @@
         <v>46310.31706138982</v>
       </c>
       <c r="P36">
-        <v>46313.30530848172</v>
+        <v>46313.66770565418</v>
       </c>
       <c r="Q36" t="s">
         <v>23</v>
@@ -2826,7 +2826,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P37">
-        <v>46313.3053084683</v>
+        <v>46313.66770564076</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>31</v>
@@ -2873,7 +2873,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P38">
-        <v>46313.3053084546</v>
+        <v>46313.66770562722</v>
       </c>
       <c r="Q38" s="5" t="s">
         <v>31</v>
@@ -2920,7 +2920,7 @@
         <v>46310.31706133292</v>
       </c>
       <c r="P39">
-        <v>46313.30530844122</v>
+        <v>46313.66770561394</v>
       </c>
       <c r="Q39" t="s">
         <v>23</v>
@@ -2970,7 +2970,7 @@
         <v>46309.72494249383</v>
       </c>
       <c r="P40">
-        <v>46313.30530842762</v>
+        <v>46313.66770560007</v>
       </c>
       <c r="Q40" t="s">
         <v>23</v>
@@ -3014,7 +3014,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P41">
-        <v>46313.30530841411</v>
+        <v>46313.66770558676</v>
       </c>
       <c r="Q41" s="5" t="s">
         <v>31</v>
@@ -3064,7 +3064,7 @@
         <v>46308.39986111095</v>
       </c>
       <c r="P42">
-        <v>46313.30530838588</v>
+        <v>46313.66770555852</v>
       </c>
       <c r="Q42" t="s">
         <v>23</v>
@@ -3108,7 +3108,7 @@
         <v>46305.20575257758</v>
       </c>
       <c r="P43">
-        <v>46313.30530837171</v>
+        <v>46313.66770554411</v>
       </c>
       <c r="Q43" t="s">
         <v>23</v>
@@ -3155,7 +3155,7 @@
         <v>46307.39549666931</v>
       </c>
       <c r="P44">
-        <v>46313.3053083565</v>
+        <v>46313.66770552914</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3199,7 +3199,7 @@
         <v>46307.39549671811</v>
       </c>
       <c r="P45">
-        <v>46313.30530832517</v>
+        <v>46313.66770549942</v>
       </c>
       <c r="Q45" t="s">
         <v>23</v>
@@ -3248,7 +3248,7 @@
         <v>46300.75884779022</v>
       </c>
       <c r="P46" s="6">
-        <v>46313.30532588915</v>
+        <v>46313.66772336456</v>
       </c>
       <c r="Q46" s="6" t="s">
         <v>23</v>
@@ -3295,7 +3295,7 @@
         <v>46300.75884780569</v>
       </c>
       <c r="P47" s="6">
-        <v>46313.30532590194</v>
+        <v>46313.6677233767</v>
       </c>
       <c r="Q47" s="6" t="s">
         <v>23</v>
@@ -3344,7 +3344,7 @@
         <v>46300.75884782107</v>
       </c>
       <c r="P48" s="6">
-        <v>46313.30532587588</v>
+        <v>46313.66772335224</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>23</v>
@@ -3393,7 +3393,7 @@
         <v>46300.75884783743</v>
       </c>
       <c r="P49" s="6">
-        <v>46313.30532586262</v>
+        <v>46313.66772333956</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>23</v>
@@ -3442,7 +3442,7 @@
         <v>46300.75884787029</v>
       </c>
       <c r="P50" s="6">
-        <v>46313.30532592876</v>
+        <v>46313.66772340168</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3489,7 +3489,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P51" s="6">
-        <v>46313.30532594294</v>
+        <v>46313.6677234138</v>
       </c>
       <c r="Q51" s="5" t="s">
         <v>31</v>
@@ -3536,7 +3536,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P52" s="6">
-        <v>46313.30532599742</v>
+        <v>46313.66772346423</v>
       </c>
       <c r="Q52" s="5" t="s">
         <v>31</v>
@@ -3583,7 +3583,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P53" s="6">
-        <v>46313.30532598343</v>
+        <v>46313.66772345122</v>
       </c>
       <c r="Q53" s="5" t="s">
         <v>31</v>
@@ -3634,7 +3634,7 @@
         <v>46300.75884793277</v>
       </c>
       <c r="P54" s="6">
-        <v>46313.30533904954</v>
+        <v>46313.66773176777</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>23</v>
@@ -3683,7 +3683,7 @@
         <v>46300.75884796329</v>
       </c>
       <c r="P55" s="6">
-        <v>46313.30533899343</v>
+        <v>46313.66773171356</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3732,7 +3732,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P56" s="6">
-        <v>46313.3053390893</v>
+        <v>46313.66773180514</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>31</v>
@@ -3779,7 +3779,7 @@
         <v>46300.75885617639</v>
       </c>
       <c r="P57" s="6">
-        <v>46313.30533906279</v>
+        <v>46313.66773178015</v>
       </c>
       <c r="Q57" s="6" t="s">
         <v>23</v>
@@ -3828,7 +3828,7 @@
         <v>46300.75885619673</v>
       </c>
       <c r="P58" s="6">
-        <v>46313.30533907594</v>
+        <v>46313.66773179277</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>23</v>
@@ -3930,7 +3930,7 @@
         <v>46300.75885624527</v>
       </c>
       <c r="P60" s="6">
-        <v>46313.30533911665</v>
+        <v>46313.66773183009</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3979,7 +3979,7 @@
         <v>46300.75885627908</v>
       </c>
       <c r="P61" s="6">
-        <v>46313.30533913011</v>
+        <v>46313.66773184277</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>23</v>
@@ -4028,7 +4028,7 @@
         <v>46300.75885633306</v>
       </c>
       <c r="P62" s="6">
-        <v>46313.30533917051</v>
+        <v>46313.66773188084</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4077,7 +4077,7 @@
         <v>46300.7588563655</v>
       </c>
       <c r="P63" s="6">
-        <v>46313.30533919778</v>
+        <v>46313.66773190629</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4128,7 +4128,7 @@
         <v>46300.7588564207</v>
       </c>
       <c r="P64" s="6">
-        <v>46313.30533922432</v>
+        <v>46313.66773193169</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
@@ -4379,7 +4379,7 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46313.30532582265</v>
+        <v>46313.66772330055</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>31</v>
@@ -4423,7 +4423,7 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46313.30532579589</v>
+        <v>46313.66772327427</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>31</v>
@@ -4470,7 +4470,7 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46313.30531728507</v>
+        <v>46313.6677142169</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>31</v>
@@ -4514,7 +4514,7 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46313.30531725841</v>
+        <v>46313.66771419167</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>31</v>
@@ -4558,7 +4558,7 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46313.30531724413</v>
+        <v>46313.66771417948</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>31</v>
@@ -4605,7 +4605,7 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P7" s="2">
-        <v>46313.30531722958</v>
+        <v>46313.66771416669</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
@@ -4652,7 +4652,7 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P8" s="2">
-        <v>46313.30531714948</v>
+        <v>46313.66771409143</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>31</v>
@@ -4696,7 +4696,7 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P9" s="2">
-        <v>46313.30531716249</v>
+        <v>46313.66771410416</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>31</v>
@@ -4740,7 +4740,7 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P10" s="2">
-        <v>46313.30531712321</v>
+        <v>46313.66771406602</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>31</v>
@@ -4784,7 +4784,7 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11" s="2">
-        <v>46313.3053170835</v>
+        <v>46313.66771402624</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>31</v>
@@ -4828,7 +4828,7 @@
         <v>46307.39549690609</v>
       </c>
       <c r="P12">
-        <v>46313.30530860629</v>
+        <v>46313.66770577192</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>31</v>
@@ -4875,7 +4875,7 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46313.30530857794</v>
+        <v>46313.66770574598</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>31</v>
@@ -4922,7 +4922,7 @@
         <v>46307.39549687663</v>
       </c>
       <c r="P14">
-        <v>46313.30530854941</v>
+        <v>46313.66770571972</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>31</v>
@@ -4969,7 +4969,7 @@
         <v>46311.30742780836</v>
       </c>
       <c r="P15">
-        <v>46313.30530853521</v>
+        <v>46313.66770570714</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>31</v>
@@ -5013,7 +5013,7 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46313.30530849531</v>
+        <v>46313.6677056671</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>31</v>
@@ -5057,7 +5057,7 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46313.30530850866</v>
+        <v>46313.66770568074</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>31</v>
@@ -5104,7 +5104,7 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46313.30530852199</v>
+        <v>46313.66770569394</v>
       </c>
       <c r="Q18" s="5" t="s">
         <v>31</v>
@@ -5151,7 +5151,7 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P19">
-        <v>46313.3053084683</v>
+        <v>46313.66770564076</v>
       </c>
       <c r="Q19" s="5" t="s">
         <v>31</v>
@@ -5198,7 +5198,7 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P20">
-        <v>46313.3053084546</v>
+        <v>46313.66770562722</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>31</v>
@@ -5242,7 +5242,7 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P21">
-        <v>46313.30530841411</v>
+        <v>46313.66770558676</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>31</v>
@@ -5289,7 +5289,7 @@
         <v>46308.39987059968</v>
       </c>
       <c r="P22" s="6">
-        <v>46313.30532594294</v>
+        <v>46313.6677234138</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>31</v>
@@ -5336,7 +5336,7 @@
         <v>46300.75884790152</v>
       </c>
       <c r="P23" s="6">
-        <v>46313.30532599742</v>
+        <v>46313.66772346423</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>31</v>
@@ -5383,7 +5383,7 @@
         <v>46310.71708389919</v>
       </c>
       <c r="P24" s="6">
-        <v>46313.30532598343</v>
+        <v>46313.66772345122</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>31</v>
@@ -5432,7 +5432,7 @@
         <v>46300.75884799581</v>
       </c>
       <c r="P25" s="6">
-        <v>46313.3053390893</v>
+        <v>46313.66773180514</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>31</v>
@@ -5549,7 +5549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>46313.30528009156</v>
+        <v>46313.66768650556</v>
       </c>
       <c r="B2">
-        <v>46313.3091804056</v>
+        <v>46313.66945401487</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>46312.65708521284</v>
+        <v>46313.30528009156</v>
       </c>
       <c r="B3">
-        <v>46312.65865222656</v>
+        <v>46313.3091804056</v>
       </c>
       <c r="C3" t="s">
         <v>221</v>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>46312.29481460934</v>
+        <v>46312.65708521284</v>
       </c>
       <c r="B4">
-        <v>46312.29886374016</v>
+        <v>46312.65865222656</v>
       </c>
       <c r="C4" t="s">
         <v>221</v>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>46311.70085467582</v>
+        <v>46312.29481460934</v>
       </c>
       <c r="B5">
-        <v>46311.70249357724</v>
+        <v>46312.29886374016</v>
       </c>
       <c r="C5" t="s">
         <v>221</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>46311.3074085582</v>
+        <v>46311.70085467582</v>
       </c>
       <c r="B6">
-        <v>46311.31082826155</v>
+        <v>46311.70249357724</v>
       </c>
       <c r="C6" t="s">
         <v>221</v>
@@ -5752,16 +5752,16 @@
         <v>3861</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -5772,45 +5772,45 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>46310.71705220221</v>
+        <v>46311.3074085582</v>
       </c>
       <c r="B7">
-        <v>46310.71871343154</v>
+        <v>46311.31082826155</v>
       </c>
       <c r="C7" t="s">
         <v>221</v>
       </c>
       <c r="D7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E7">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <v>394</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3858</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>46310.31704895089</v>
+        <v>46310.71705220221</v>
       </c>
       <c r="B8">
-        <v>46310.31885341345</v>
+        <v>46310.71871343154</v>
       </c>
       <c r="C8" t="s">
         <v>221</v>
@@ -5819,33 +5819,33 @@
         <v>193</v>
       </c>
       <c r="E8">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3856</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>46309.72492152842</v>
+        <v>46310.31704895089</v>
       </c>
       <c r="B9">
-        <v>46309.72666770707</v>
+        <v>46310.31885341345</v>
       </c>
       <c r="C9" t="s">
         <v>221</v>
@@ -5854,16 +5854,16 @@
         <v>193</v>
       </c>
       <c r="E9">
-        <v>3854</v>
+        <v>3856</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -5872,15 +5872,15 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3854</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>46309.32656703098</v>
+        <v>46309.72492152842</v>
       </c>
       <c r="B10">
-        <v>46309.3297855199</v>
+        <v>46309.72666770707</v>
       </c>
       <c r="C10" t="s">
         <v>221</v>
@@ -5889,33 +5889,33 @@
         <v>193</v>
       </c>
       <c r="E10">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3844</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>46308.80857426515</v>
+        <v>46309.32656703098</v>
       </c>
       <c r="B11">
-        <v>46308.81014075634</v>
+        <v>46309.3297855199</v>
       </c>
       <c r="C11" t="s">
         <v>221</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>46308.39983395509</v>
+        <v>46308.80857426515</v>
       </c>
       <c r="B12">
-        <v>46308.40210717713</v>
+        <v>46308.81014075634</v>
       </c>
       <c r="C12" t="s">
         <v>221</v>
@@ -5962,16 +5962,16 @@
         <v>3844</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -5982,45 +5982,45 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>46307.88901948844</v>
+        <v>46308.39983395509</v>
       </c>
       <c r="B13">
-        <v>46307.89058348727</v>
+        <v>46308.40210717713</v>
       </c>
       <c r="C13" t="s">
         <v>221</v>
       </c>
       <c r="D13">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E13">
-        <v>3838</v>
+        <v>3844</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>381</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>3838</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>46307.39547700758</v>
+        <v>46307.88901948844</v>
       </c>
       <c r="B14">
-        <v>46307.40588718568</v>
+        <v>46307.89058348727</v>
       </c>
       <c r="C14" t="s">
         <v>221</v>
@@ -6032,13 +6032,13 @@
         <v>3838</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -6052,10 +6052,10 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46306.73887016933</v>
+        <v>46307.39547700758</v>
       </c>
       <c r="B15">
-        <v>46306.74049537522</v>
+        <v>46307.40588718568</v>
       </c>
       <c r="C15" t="s">
         <v>221</v>
@@ -6064,16 +6064,16 @@
         <v>192</v>
       </c>
       <c r="E15">
-        <v>3826</v>
+        <v>3838</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>369</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -6082,15 +6082,15 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>3826</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>46306.45016971852</v>
+        <v>46306.73887016933</v>
       </c>
       <c r="B16">
-        <v>46306.45174895023</v>
+        <v>46306.74049537522</v>
       </c>
       <c r="C16" t="s">
         <v>221</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>46305.7254269891</v>
+        <v>46306.45016971852</v>
       </c>
       <c r="B17">
-        <v>46305.72703482325</v>
+        <v>46306.45174895023</v>
       </c>
       <c r="C17" t="s">
         <v>221</v>
@@ -6140,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -6157,10 +6157,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>46305.36271514557</v>
+        <v>46305.7254269891</v>
       </c>
       <c r="B18">
-        <v>46305.36432437652</v>
+        <v>46305.72703482325</v>
       </c>
       <c r="C18" t="s">
         <v>221</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>46305.20573401557</v>
+        <v>46305.36271514557</v>
       </c>
       <c r="B19">
-        <v>46305.20740965955</v>
+        <v>46305.36432437652</v>
       </c>
       <c r="C19" t="s">
         <v>221</v>
@@ -6207,16 +6207,16 @@
         <v>3826</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -6227,45 +6227,45 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>46303.78900727724</v>
+        <v>46305.20573401557</v>
       </c>
       <c r="B20">
-        <v>46303.79055355475</v>
+        <v>46305.20740965955</v>
       </c>
       <c r="C20" t="s">
         <v>221</v>
       </c>
       <c r="D20">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E20">
-        <v>3820</v>
+        <v>3826</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>3820</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>46303.38326038567</v>
+        <v>46303.78900727724</v>
       </c>
       <c r="B21">
-        <v>46303.38502199544</v>
+        <v>46303.79055355475</v>
       </c>
       <c r="C21" t="s">
         <v>221</v>
@@ -6297,10 +6297,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>46302.79187874035</v>
+        <v>46303.38326038567</v>
       </c>
       <c r="B22">
-        <v>46302.79368556542</v>
+        <v>46303.38502199544</v>
       </c>
       <c r="C22" t="s">
         <v>221</v>
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>46302.26839808295</v>
+        <v>46302.79187874035</v>
       </c>
       <c r="B23">
-        <v>46302.2700367639</v>
+        <v>46302.79368556542</v>
       </c>
       <c r="C23" t="s">
         <v>221</v>
@@ -6347,16 +6347,16 @@
         <v>3820</v>
       </c>
       <c r="F23">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="H23">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -6367,45 +6367,45 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>46301.38230919655</v>
+        <v>46302.26839808295</v>
       </c>
       <c r="B24">
-        <v>46301.3823941568</v>
+        <v>46302.2700367639</v>
       </c>
       <c r="C24" t="s">
         <v>221</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>191</v>
       </c>
       <c r="E24">
-        <v>160</v>
+        <v>3820</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="G24">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>3817</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>46300.7718278824</v>
+        <v>46301.38230919655</v>
       </c>
       <c r="B25">
-        <v>46300.77190961051</v>
+        <v>46301.3823941568</v>
       </c>
       <c r="C25" t="s">
         <v>221</v>
@@ -6417,13 +6417,13 @@
         <v>160</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -6432,15 +6432,15 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>3814</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>46300.75883115231</v>
+        <v>46300.7718278824</v>
       </c>
       <c r="B26">
-        <v>46300.75891177973</v>
+        <v>46300.77190961051</v>
       </c>
       <c r="C26" t="s">
         <v>221</v>
@@ -6452,21 +6452,56 @@
         <v>160</v>
       </c>
       <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>160</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27">
+        <v>46300.75883115231</v>
+      </c>
+      <c r="B27">
+        <v>46300.75891177973</v>
+      </c>
+      <c r="C27" t="s">
+        <v>221</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>160</v>
+      </c>
+      <c r="F27">
         <v>157</v>
       </c>
-      <c r="G26">
+      <c r="G27">
         <v>3</v>
       </c>
-      <c r="H26">
+      <c r="H27">
         <v>132</v>
       </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>3814</v>
       </c>
     </row>

--- a/docs/cirp-eoi-monitor.xlsx
+++ b/docs/cirp-eoi-monitor.xlsx
@@ -12,15 +12,15 @@
     <sheet name="Runs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30-Day Working List'!$A$1:$Q$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Review'!$A$1:$Q$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="228">
   <si>
     <t>Priority</t>
   </si>
@@ -79,414 +79,453 @@
     <t>Open</t>
   </si>
   <si>
+    <t>KM TOLL ROAD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Roads / Toll Roads</t>
+  </si>
+  <si>
+    <t>Roads / Highways</t>
+  </si>
+  <si>
+    <t>Mr. Ashish Saoji</t>
+  </si>
+  <si>
+    <t>Auto-classified</t>
+  </si>
+  <si>
+    <t>ORGANIC WORLD PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Other / Unclear</t>
+  </si>
+  <si>
+    <t>Prakul Thadi</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>SUN GRANITE EXPORT LIMITED</t>
+  </si>
+  <si>
+    <t>Cement / Building Materials</t>
+  </si>
+  <si>
+    <t>Raghunath Bhandari</t>
+  </si>
+  <si>
+    <t>SHRENIK LIMITED</t>
+  </si>
+  <si>
+    <t>RAHUL SHAH</t>
+  </si>
+  <si>
+    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Power / Energy</t>
+  </si>
+  <si>
+    <t>CJ Davis</t>
+  </si>
+  <si>
+    <t>The company is not functioning</t>
+  </si>
+  <si>
+    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Infrastructure / EPC</t>
+  </si>
+  <si>
+    <t>Mr. Bimal Kumar Agarwal</t>
+  </si>
+  <si>
+    <t>Corrigendum dated 14 October 2026 to FORM G dated 28 September 2026</t>
+  </si>
+  <si>
+    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Neha Jain Nemani</t>
+  </si>
+  <si>
+    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
+  </si>
+  <si>
+    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Logistics / Transportation</t>
+  </si>
+  <si>
+    <t>Dipti Narayan Mundra</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Manish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
+  </si>
+  <si>
+    <t>Pharma / Healthcare</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>kuldeep tank</t>
+  </si>
+  <si>
+    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chandra Kumar Jain</t>
+  </si>
+  <si>
+    <t>Sion Panvel Tollways Private Limited</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Mishra</t>
+  </si>
+  <si>
+    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
+  </si>
+  <si>
+    <t>AXLE PAPER PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Mr. Kailash Shah</t>
+  </si>
+  <si>
+    <t>The installed capacity of main Products is 150MTPD.</t>
+  </si>
+  <si>
+    <t>ALVI TECH SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>IT / Technology</t>
+  </si>
+  <si>
+    <t>The addendum to form G was issued on 10th October, 2026.</t>
+  </si>
+  <si>
+    <t>INDO PACIFIC PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Mrs. Megha Agrawal</t>
+  </si>
+  <si>
+    <t>CORRIGENDUM TO FORM G INVITATION FOR EXPRESSION OF INTEREST FOR INDO PACIFIC PROJECTS LIMITED (Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2</t>
+  </si>
+  <si>
+    <t>Raheja Developers Limited - Revanta Project</t>
+  </si>
+  <si>
+    <t>Realty / Construction</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Mr. Surendra Raj Gang</t>
+  </si>
+  <si>
+    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
+  </si>
+  <si>
+    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Amrish Navinchandra Gandhi</t>
+  </si>
+  <si>
+    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
+  </si>
+  <si>
+    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
+  </si>
+  <si>
+    <t>Mr. Bijay Murmuria</t>
+  </si>
+  <si>
+    <t>SMO FERRO ALLOYS LIMITED</t>
+  </si>
+  <si>
+    <t>Steel / Metals</t>
+  </si>
+  <si>
+    <t>Mr. Rajesh Lohia</t>
+  </si>
+  <si>
+    <t>ALCOB INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRASHANT KHATAVKAR</t>
+  </si>
+  <si>
+    <t>ALLFLEX PLASTIC LLP</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Plastics / Polymers</t>
+  </si>
+  <si>
+    <t>Mr. Hansraj Jaria</t>
+  </si>
+  <si>
+    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Agriculture / Food</t>
+  </si>
+  <si>
+    <t>Mr. Manoj Sehgal</t>
+  </si>
+  <si>
+    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
+  </si>
+  <si>
+    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Dharmendra Dhelariya</t>
+  </si>
+  <si>
+    <t>SUNSHINE FASTECH LIMITED</t>
+  </si>
+  <si>
+    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
+  </si>
+  <si>
+    <t>SEL TEXTILES LIMITED</t>
+  </si>
+  <si>
+    <t>Textiles</t>
+  </si>
+  <si>
+    <t>Rajeev Sharma</t>
+  </si>
+  <si>
+    <t>Form-G issued in pursuant to NCLT order</t>
+  </si>
+  <si>
+    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Dev Vrat Rana</t>
+  </si>
+  <si>
+    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Gupta</t>
+  </si>
+  <si>
+    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
+  </si>
+  <si>
+    <t>SWADESH GREEN INFRA LIMITED</t>
+  </si>
+  <si>
+    <t>Niraj Kumar</t>
+  </si>
+  <si>
+    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
+  </si>
+  <si>
+    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Bishwa Ranjan Chatterjee</t>
+  </si>
+  <si>
+    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
+  </si>
+  <si>
+    <t>Not in latest IBBI listing - verify with RP</t>
+  </si>
+  <si>
+    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Kamal Agarwal</t>
+  </si>
+  <si>
+    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
+  </si>
+  <si>
+    <t>STC VENTURES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PURUSOTTAM BEHERA</t>
+  </si>
+  <si>
+    <t>The original Form G was published on 27th September 2026, with 12th October 2026 being the last date for submission of Expressions of Interest (EOIs). However, pursuant to the request received from the CoC members to extend the timeline for submission of</t>
+  </si>
+  <si>
+    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
+  </si>
+  <si>
+    <t>Abhit Kumar Singh</t>
+  </si>
+  <si>
+    <t>KUTE SONS DAIRYS LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Ritesh R Mahajan</t>
+  </si>
+  <si>
+    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chirag Rajendra Kumar Shah</t>
+  </si>
+  <si>
+    <t>Form G published on 13th October 2026.</t>
+  </si>
+  <si>
+    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Hotel / Hospitality</t>
+  </si>
+  <si>
+    <t>Hotels / Resorts</t>
+  </si>
+  <si>
+    <t>Harsh Kumar Arora</t>
+  </si>
+  <si>
+    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
+  </si>
+  <si>
+    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Prashant Jain</t>
+  </si>
+  <si>
+    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
+  </si>
+  <si>
+    <t>STUTI COMTRADE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
+  </si>
+  <si>
+    <t>2nd Form G.</t>
+  </si>
+  <si>
+    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shaikh Nafis Anjum</t>
+  </si>
+  <si>
+    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
+  </si>
+  <si>
+    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Construction / EPC</t>
+  </si>
+  <si>
+    <t>Manindra Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
+  </si>
+  <si>
+    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Mahesh Goverdhan Bagla</t>
+  </si>
+  <si>
+    <t>CAPBRIDGE VENTURE LLP</t>
+  </si>
+  <si>
+    <t>Saurabh Mittal</t>
+  </si>
+  <si>
+    <t>KRISHNAGANGA SPINNING MILLS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Chillale Rajesh</t>
+  </si>
+  <si>
+    <t>JRA INFRASTRUCTURE LIMITED</t>
+  </si>
+  <si>
+    <t>Parshva Manoj Shah</t>
+  </si>
+  <si>
+    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
+  </si>
+  <si>
+    <t>SHRIVALLABH PITTIE RESEARCH AND TRAINING PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Sunil Kumar Kabra</t>
+  </si>
+  <si>
+    <t>JUMBO SAMRIDDHI (INDIA) LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Shailesh Desai</t>
+  </si>
+  <si>
+    <t>SIMARA FOODS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>Mr. Navin Khandelwal</t>
+  </si>
+  <si>
+    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
+  </si>
+  <si>
+    <t>Resonance Paper Mill Private Limited</t>
+  </si>
+  <si>
+    <t>Siddhant Agrawal</t>
+  </si>
+  <si>
+    <t>Recently closed</t>
+  </si>
+  <si>
+    <t>Closed recently</t>
+  </si>
+  <si>
     <t>IN2IT TECHNOLOGIES PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>IT / Technology</t>
-  </si>
-  <si>
     <t>ishant jain</t>
   </si>
   <si>
     <t>Re-issuance of Form G: Form G was re-issued on 17.09.2026, with 03.10.2026 as the last date for submission of EOI. Pursuant to the directions of the CoC, an Addendum to Form G was issued, revising and extending the stipulated timelines accordingly.</t>
   </si>
   <si>
-    <t>Auto-classified</t>
-  </si>
-  <si>
-    <t>KM TOLL ROAD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Roads / Toll Roads</t>
-  </si>
-  <si>
-    <t>Roads / Highways</t>
-  </si>
-  <si>
-    <t>Mr. Ashish Saoji</t>
-  </si>
-  <si>
-    <t>ORGANIC WORLD PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Other / Unclear</t>
-  </si>
-  <si>
-    <t>Prakul Thadi</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>SUN GRANITE EXPORT LIMITED</t>
-  </si>
-  <si>
-    <t>Cement / Building Materials</t>
-  </si>
-  <si>
-    <t>Raghunath Bhandari</t>
-  </si>
-  <si>
-    <t>SHRENIK LIMITED</t>
-  </si>
-  <si>
-    <t>RAHUL SHAH</t>
-  </si>
-  <si>
-    <t>SOURA NATURAL ENERGY SOLUTIONS INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Power / Energy</t>
-  </si>
-  <si>
-    <t>CJ Davis</t>
-  </si>
-  <si>
-    <t>The company is not functioning</t>
-  </si>
-  <si>
-    <t>VAS INFRASTRUCTURE LIMITED (CN)</t>
-  </si>
-  <si>
-    <t>Infrastructure</t>
-  </si>
-  <si>
-    <t>Infrastructure / EPC</t>
-  </si>
-  <si>
-    <t>Mr. Bimal Kumar Agarwal</t>
-  </si>
-  <si>
-    <t>Corrigendum dated 14 October 2026 to FORM G dated 28 September 2026</t>
-  </si>
-  <si>
-    <t>OMKARA VIJAYALAKSHMI STRIPS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Neha Jain Nemani</t>
-  </si>
-  <si>
-    <t>A fresh Form-G is issued upon taking approval from the CoC on 6th October 2026. The last day for submission of EOI is 21st October 2026.</t>
-  </si>
-  <si>
-    <t>VELEX LOGISTICS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Logistics / Transportation</t>
-  </si>
-  <si>
-    <t>Dipti Narayan Mundra</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>G &amp; L PROFILE AND EQUIPMENTS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Manish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>SOCRUS PHARMACEUTICALS LIMITED</t>
-  </si>
-  <si>
-    <t>Pharma / Healthcare</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>kuldeep tank</t>
-  </si>
-  <si>
-    <t>SHIVALAY INFRACON PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chandra Kumar Jain</t>
-  </si>
-  <si>
-    <t>Sion Panvel Tollways Private Limited</t>
-  </si>
-  <si>
-    <t>Mr. Sanjay Kumar Mishra</t>
-  </si>
-  <si>
-    <t>1. Since CD is in business of road construction, there are no major tangible assets available; 2. No employee on the rolls of CD since ICD; 3. Current Form G is pursuant to NCLT order - 29 Sept'26 and 59th CoC meeting on 06 Oct'26.</t>
-  </si>
-  <si>
-    <t>AXLE PAPER PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Mr. Kailash Shah</t>
-  </si>
-  <si>
-    <t>The installed capacity of main Products is 150MTPD.</t>
-  </si>
-  <si>
-    <t>ALVI TECH SERVICES PVT LTD</t>
-  </si>
-  <si>
-    <t>The addendum to form G was issued on 10th October, 2026.</t>
-  </si>
-  <si>
-    <t>INDO PACIFIC PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Mrs. Megha Agrawal</t>
-  </si>
-  <si>
-    <t>CORRIGENDUM TO FORM G INVITATION FOR EXPRESSION OF INTEREST FOR INDO PACIFIC PROJECTS LIMITED (Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2</t>
-  </si>
-  <si>
-    <t>Raheja Developers Limited - Revanta Project</t>
-  </si>
-  <si>
-    <t>Realty / Construction</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Mr. Surendra Raj Gang</t>
-  </si>
-  <si>
-    <t>The CoC in its 4th meeting has resolved to scrap the earlier EOI process pursuant to Form-G dated 03 September 2026 and publish the current invitation for EOI for submission of Resolution Plans. The details of product are available in attached document.</t>
-  </si>
-  <si>
-    <t>RNA LIFESTYLE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Amrish Navinchandra Gandhi</t>
-  </si>
-  <si>
-    <t>Form G has been re-issued as only one prospective resolution applicant submitted an EOI in response to the Form G published earlier on 22 August 2026</t>
-  </si>
-  <si>
-    <t>CMP EURO TECHNOPLAST PVT. LTD.</t>
-  </si>
-  <si>
-    <t>Mr. Bijay Murmuria</t>
-  </si>
-  <si>
-    <t>SMO FERRO ALLOYS LIMITED</t>
-  </si>
-  <si>
-    <t>Steel / Metals</t>
-  </si>
-  <si>
-    <t>Mr. Rajesh Lohia</t>
-  </si>
-  <si>
-    <t>ALCOB INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PRASHANT KHATAVKAR</t>
-  </si>
-  <si>
-    <t>ALLFLEX PLASTIC LLP</t>
-  </si>
-  <si>
-    <t>Chemicals</t>
-  </si>
-  <si>
-    <t>Plastics / Polymers</t>
-  </si>
-  <si>
-    <t>Mr. Hansraj Jaria</t>
-  </si>
-  <si>
-    <t>SHIVANGI AGRO INDIA PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Agriculture / Food</t>
-  </si>
-  <si>
-    <t>Mr. Manoj Sehgal</t>
-  </si>
-  <si>
-    <t>The CoC has extended the date of submission of EOI to 25.10.2026, hence addendum to Form G dated 22.09.2026 issued on 11.10.2026. Addendum Form G Published on 11.10.2026 in Financial Express (English, Licknow Edition) &amp; Jansatta (Hindi, Lucknow Editio</t>
-  </si>
-  <si>
-    <t>MAARS SOFTWARE INTERNATIONAL LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Dharmendra Dhelariya</t>
-  </si>
-  <si>
-    <t>SUNSHINE FASTECH LIMITED</t>
-  </si>
-  <si>
-    <t>KINJALKUMAR MADHUBHAI CHAUDHARY</t>
-  </si>
-  <si>
-    <t>HOURS OVERSEAS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Dev Vrat Rana</t>
-  </si>
-  <si>
-    <t>GENESIS INFRATECH PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Gupta</t>
-  </si>
-  <si>
-    <t>Published in All India editions of Business Standard (English &amp; Hindi), Jaipur edition of Indian Express (English) and Alwar edition of Mahanagar Times (Hindi) on 12.10.2026</t>
-  </si>
-  <si>
-    <t>SWADESH GREEN INFRA LIMITED</t>
-  </si>
-  <si>
-    <t>Niraj Kumar</t>
-  </si>
-  <si>
-    <t>The details for eligibility for resolution applicants under section 25(2)(h) of the Code and last available financial statements(with schedules) of two years, list of creditors, relevant dates of subsequent events of the process will be provided via email</t>
-  </si>
-  <si>
-    <t>KRISHNA ELECTRICAL INDUSTRIES LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Bishwa Ranjan Chatterjee</t>
-  </si>
-  <si>
-    <t>Form G has been published. Please upload the same at IBBI Portal.</t>
-  </si>
-  <si>
-    <t>J - SEVENTY ONE PROPERTIES &amp; PICTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Kamal Agarwal</t>
-  </si>
-  <si>
-    <t>There is total non cooperation from suspended board of directors and application under section 19(2) is listed on 12.10.2026 vide IA 4407/MB/ 2026 where notice is issued and is next listed on 03.11.2026</t>
-  </si>
-  <si>
-    <t>STC VENTURES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>PURUSOTTAM BEHERA</t>
-  </si>
-  <si>
-    <t>The original Form G was published on 27th September 2026, with 12th October 2026 being the last date for submission of Expressions of Interest (EOIs). However, pursuant to the request received from the CoC members to extend the timeline for submission of</t>
-  </si>
-  <si>
-    <t>ARTHUR TURNKEY PROJECTS LIMITED</t>
-  </si>
-  <si>
-    <t>Abhit Kumar Singh</t>
-  </si>
-  <si>
-    <t>KUTE SONS DAIRYS LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Ritesh R Mahajan</t>
-  </si>
-  <si>
-    <t>KALAHRIDHAAN TRENDZ LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Chirag Rajendra Kumar Shah</t>
-  </si>
-  <si>
-    <t>Form G published on 13th October 2026.</t>
-  </si>
-  <si>
-    <t>DAUPHIN AKG HOTELS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Hotel / Hospitality</t>
-  </si>
-  <si>
-    <t>Hotels / Resorts</t>
-  </si>
-  <si>
-    <t>Harsh Kumar Arora</t>
-  </si>
-  <si>
-    <t>Number of employees and workmen are not in the knowledge of the Resolution Professional. Details of main products and services are not ascertainable from the available records with Resolution Professional</t>
-  </si>
-  <si>
-    <t>CHINTAMANIS JEWELLERY ARCADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Prashant Jain</t>
-  </si>
-  <si>
-    <t>Kindly note that This is a Form G for extension in submission of expression of Interest which is published on 15th October, 2026 with approval of COC.</t>
-  </si>
-  <si>
-    <t>STUTI COMTRADE PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>CA GOMTI RAMCHANDRA CHOUDHARY</t>
-  </si>
-  <si>
-    <t>2nd Form G.</t>
-  </si>
-  <si>
-    <t>BUOYANT TECHNOLOGY CONSTELLATIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Shaikh Nafis Anjum</t>
-  </si>
-  <si>
-    <t>Form-G was published on 14 October 2026 in the following newspapers and editions: Financial Express (English) – Bengaluru Edition; Financial Express (English) – Chennai Edition; The Hindu (Tamil) – Chennai Edition; and Vijay Karnataka (K</t>
-  </si>
-  <si>
-    <t>REAL TECH CONSTRUCTIONS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Construction / EPC</t>
-  </si>
-  <si>
-    <t>Manindra Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>"Re-issue of Form G published on 14.10.2026 pursuant to the applicable CoC decision, with revised EOI deadline of 30.10.2026. This publication supersedes the earlier invitation to the extent of the revised EOI process and timelines."</t>
-  </si>
-  <si>
-    <t>PRATHAM-HEERA SALES PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Mahesh Goverdhan Bagla</t>
-  </si>
-  <si>
-    <t>JRA INFRASTRUCTURE LIMITED</t>
-  </si>
-  <si>
-    <t>Parshva Manoj Shah</t>
-  </si>
-  <si>
-    <t>Note: The last date of CIRP is 17 November 2026. The above timelines and resolution process are subject to the Hon’ble NCLT granting further extension of the CIRP period. Accordingly, further steps, including submission of resolution plans, shall be</t>
-  </si>
-  <si>
-    <t>SIMARA FOODS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Mr. Navin Khandelwal</t>
-  </si>
-  <si>
-    <t>RANKINI POWER GENERATION PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>The corporate debtor holds stake in Abhijeet MADC Nagpur Energy Private Limited (AMNEPL) which has a 246 MW power plant with 25.6 MW DG Sets at Nagpur. However, post the initiation date/ CIRP Initiation Application filing date, certain dilutions in the sh</t>
-  </si>
-  <si>
-    <t>Resonance Paper Mill Private Limited</t>
-  </si>
-  <si>
-    <t>Siddhant Agrawal</t>
-  </si>
-  <si>
-    <t>Recently closed</t>
-  </si>
-  <si>
-    <t>Closed recently</t>
-  </si>
-  <si>
     <t>GOODWILL IRON &amp; STEEL TRADERS PRIVATE LIMITED</t>
   </si>
   <si>
@@ -547,9 +586,6 @@
     <t>CITRON INFRAPROJECTS LIMITED</t>
   </si>
   <si>
-    <t>Mr. Sunil Kumar Kabra</t>
-  </si>
-  <si>
     <t>TECHNOFAB ENGINEERING LIMITED</t>
   </si>
   <si>
@@ -598,9 +634,6 @@
     <t>(Under sub-regulation (1) of regulation 36A of the Insolvency and Bankruptcy Board of India (Insolvency Resolution Process for Corporate Persons) Regulations, 2016), this corrigendum is being issued in respect of the Form G published on 18.09.2026 invitin</t>
   </si>
   <si>
-    <t>Not in latest IBBI listing - verify with RP</t>
-  </si>
-  <si>
     <t>A.P.J. LABORATORIES LIMITED</t>
   </si>
   <si>
@@ -631,25 +664,10 @@
     <t>Shree Shiddhanath Cotex Private Limited</t>
   </si>
   <si>
-    <t>Textiles</t>
-  </si>
-  <si>
     <t>Akhil Ahuja</t>
   </si>
   <si>
     <t>The FORM G is published for the second time as per the approval by the CoC Members.</t>
-  </si>
-  <si>
-    <t>TRUWEIGHT WELLNESS PRIVATE LIMITED</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Chakrala Sannidhi</t>
-  </si>
-  <si>
-    <t>_</t>
   </si>
   <si>
     <t>Started</t>
@@ -1090,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1174,23 +1192,23 @@
       <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="2">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H2" s="3">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I2" s="2">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2">
-        <v>3</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>18</v>
@@ -1199,10 +1217,10 @@
         <v>18</v>
       </c>
       <c r="O2" s="2">
-        <v>46302.26841519317</v>
+        <v>46300.75884774033</v>
       </c>
       <c r="P2" s="2">
-        <v>46313.66772332653</v>
+        <v>46314.33170497791</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>23</v>
@@ -1221,38 +1239,35 @@
       <c r="E3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="G3" s="2">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="3">
         <v>46314</v>
       </c>
       <c r="I3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46300.75884775587</v>
+      </c>
+      <c r="P3" s="2">
+        <v>46314.33170494929</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O3" s="2">
-        <v>46300.75884774033</v>
-      </c>
-      <c r="P3" s="2">
-        <v>46313.66772328764</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -1269,13 +1284,13 @@
         <v>29</v>
       </c>
       <c r="G4" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H4" s="3">
         <v>46314</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>30</v>
@@ -1290,13 +1305,13 @@
         <v>18</v>
       </c>
       <c r="O4" s="2">
-        <v>46300.75884775587</v>
+        <v>46300.7588477715</v>
       </c>
       <c r="P4" s="2">
-        <v>46313.66772330055</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>31</v>
+        <v>46314.33170496405</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -1307,23 +1322,23 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>46315</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.93</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46314</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
@@ -1334,13 +1349,13 @@
         <v>18</v>
       </c>
       <c r="O5" s="2">
-        <v>46300.7588477715</v>
+        <v>46300.75884772457</v>
       </c>
       <c r="P5" s="2">
-        <v>46313.66772331384</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>23</v>
+        <v>46314.33170493501</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -1351,26 +1366,29 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" s="3">
         <v>46315</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
       <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
@@ -1378,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="O6" s="2">
-        <v>46300.75884772457</v>
+        <v>46307.39550534703</v>
       </c>
       <c r="P6" s="2">
-        <v>46313.66772327427</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>31</v>
+        <v>46314.33170490677</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -1400,23 +1418,26 @@
       <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="G7" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H7" s="3">
         <v>46315</v>
       </c>
       <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
       <c r="L7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -1425,10 +1446,10 @@
         <v>18</v>
       </c>
       <c r="O7" s="2">
-        <v>46307.39550534703</v>
+        <v>46311.30744692709</v>
       </c>
       <c r="P7" s="2">
-        <v>46313.66772326059</v>
+        <v>46314.33170492076</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>23</v>
@@ -1442,32 +1463,29 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G8" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="3">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2">
+        <v>3</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1475,13 +1493,13 @@
         <v>18</v>
       </c>
       <c r="O8" s="2">
-        <v>46311.30744692709</v>
+        <v>46302.26841507768</v>
       </c>
       <c r="P8" s="2">
-        <v>46313.6677232455</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>46314.33170487836</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -1492,25 +1510,25 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G9" s="2">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="H9" s="3">
         <v>46316</v>
       </c>
       <c r="I9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>47</v>
       </c>
       <c r="K9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>48</v>
@@ -1522,13 +1540,13 @@
         <v>18</v>
       </c>
       <c r="O9" s="2">
-        <v>46302.26841507768</v>
+        <v>46307.39549714451</v>
       </c>
       <c r="P9" s="2">
-        <v>46313.6677142169</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>31</v>
+        <v>46314.331704864</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -1542,25 +1560,22 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="3">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="I10" s="2">
         <v>3</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K10" s="2">
-        <v>2</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>18</v>
@@ -1569,13 +1584,13 @@
         <v>18</v>
       </c>
       <c r="O10" s="2">
-        <v>46307.39549714451</v>
+        <v>46301.38232468421</v>
       </c>
       <c r="P10" s="2">
-        <v>46313.66771424172</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>23</v>
+        <v>46314.3317048496</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -1586,19 +1601,22 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G11" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H11" s="3">
         <v>46317</v>
       </c>
       <c r="I11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>54</v>
@@ -1613,13 +1631,13 @@
         <v>18</v>
       </c>
       <c r="O11" s="2">
-        <v>46301.38232468421</v>
+        <v>46302.26841501552</v>
       </c>
       <c r="P11" s="2">
-        <v>46313.66771419167</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>31</v>
+        <v>46314.33170483473</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="2" customFormat="1">
@@ -1633,22 +1651,19 @@
         <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G12" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="3">
         <v>46317</v>
       </c>
       <c r="I12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
@@ -1660,13 +1675,13 @@
         <v>18</v>
       </c>
       <c r="O12" s="2">
-        <v>46302.26841501552</v>
+        <v>46309.72495178872</v>
       </c>
       <c r="P12" s="2">
-        <v>46313.66771420432</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>23</v>
+        <v>46314.33170481848</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1">
@@ -1677,26 +1692,32 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="G13" s="2">
-        <v>0.2</v>
+        <v>0.96</v>
       </c>
       <c r="H13" s="3">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I13" s="2">
         <v>4</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
+      <c r="L13" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1704,13 +1725,13 @@
         <v>18</v>
       </c>
       <c r="O13" s="2">
-        <v>46309.72495178872</v>
+        <v>46305.20575267453</v>
       </c>
       <c r="P13" s="2">
-        <v>46313.66771417948</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>31</v>
+        <v>46314.3316969048</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="2" customFormat="1">
@@ -1721,22 +1742,19 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="G14" s="2">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H14" s="3">
         <v>46318</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>62</v>
@@ -1754,10 +1772,10 @@
         <v>18</v>
       </c>
       <c r="O14" s="2">
-        <v>46305.20575267453</v>
+        <v>46305.20575269723</v>
       </c>
       <c r="P14" s="2">
-        <v>46313.66771414227</v>
+        <v>46314.33169691901</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>23</v>
@@ -1777,23 +1795,23 @@
         <v>65</v>
       </c>
       <c r="G15" s="2">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H15" s="3">
         <v>46318</v>
       </c>
       <c r="I15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1801,10 +1819,10 @@
         <v>18</v>
       </c>
       <c r="O15" s="2">
-        <v>46305.20575269723</v>
+        <v>46308.39986132324</v>
       </c>
       <c r="P15" s="2">
-        <v>46313.66771415442</v>
+        <v>46314.33169693295</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>23</v>
@@ -1818,22 +1836,22 @@
         <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G16" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="3">
         <v>46318</v>
       </c>
       <c r="I16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="K16" s="2">
         <v>2</v>
@@ -1848,13 +1866,13 @@
         <v>18</v>
       </c>
       <c r="O16" s="2">
-        <v>46308.39986132324</v>
+        <v>46311.30743731892</v>
       </c>
       <c r="P16" s="2">
-        <v>46313.66771412977</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>23</v>
+        <v>46314.33169694684</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="2" customFormat="1">
@@ -1868,25 +1886,28 @@
         <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>29</v>
+        <v>71</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="G17" s="2">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H17" s="3">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I17" s="2">
         <v>5</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K17" s="2">
         <v>2</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>18</v>
@@ -1895,13 +1916,13 @@
         <v>18</v>
       </c>
       <c r="O17" s="2">
-        <v>46311.30743731892</v>
+        <v>46305.20575263901</v>
       </c>
       <c r="P17" s="2">
-        <v>46313.66771416669</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>31</v>
+        <v>46314.33169680443</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="2" customFormat="1">
@@ -1912,22 +1933,19 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H18" s="3">
         <v>46319</v>
       </c>
       <c r="I18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>76</v>
@@ -1945,13 +1963,13 @@
         <v>18</v>
       </c>
       <c r="O18" s="2">
-        <v>46305.20575263901</v>
+        <v>46307.39549700746</v>
       </c>
       <c r="P18" s="2">
-        <v>46313.66771411694</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>23</v>
+        <v>46314.33169683327</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="2" customFormat="1">
@@ -1965,7 +1983,7 @@
         <v>78</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2">
         <v>0.2</v>
@@ -1974,16 +1992,13 @@
         <v>46319</v>
       </c>
       <c r="I19" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>79</v>
       </c>
       <c r="K19" s="2">
-        <v>2</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -1992,13 +2007,13 @@
         <v>18</v>
       </c>
       <c r="O19" s="2">
-        <v>46307.39549700746</v>
+        <v>46307.3954970362</v>
       </c>
       <c r="P19" s="2">
-        <v>46313.66771409143</v>
+        <v>46314.33169681875</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="2" customFormat="1">
@@ -2009,25 +2024,25 @@
         <v>18</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G20" s="2">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H20" s="3">
         <v>46319</v>
       </c>
       <c r="I20" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="K20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -2036,13 +2051,13 @@
         <v>18</v>
       </c>
       <c r="O20" s="2">
-        <v>46307.3954970362</v>
+        <v>46309.72495168629</v>
       </c>
       <c r="P20" s="2">
-        <v>46313.66771410416</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>31</v>
+        <v>46314.33169689067</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="2" customFormat="1">
@@ -2056,22 +2071,22 @@
         <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="G21" s="2">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="H21" s="3">
         <v>46319</v>
       </c>
       <c r="I21" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>18</v>
@@ -2080,13 +2095,13 @@
         <v>18</v>
       </c>
       <c r="O21" s="2">
-        <v>46309.72495168629</v>
+        <v>46309.72495171529</v>
       </c>
       <c r="P21" s="2">
-        <v>46313.66771405283</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>23</v>
+        <v>46314.33169686199</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="2" customFormat="1">
@@ -2097,25 +2112,28 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>29</v>
+      <c r="F22" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="G22" s="2">
-        <v>0.2</v>
+        <v>0.91</v>
       </c>
       <c r="H22" s="3">
         <v>46319</v>
       </c>
       <c r="I22" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>18</v>
@@ -2124,13 +2142,13 @@
         <v>18</v>
       </c>
       <c r="O22" s="2">
-        <v>46309.72495171529</v>
+        <v>46310.31707038325</v>
       </c>
       <c r="P22" s="2">
-        <v>46313.66771406602</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>31</v>
+        <v>46314.33169684733</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="2" customFormat="1">
@@ -2141,19 +2159,16 @@
         <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H23" s="3">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I23" s="2">
         <v>6</v>
@@ -2164,6 +2179,9 @@
       <c r="K23" s="2">
         <v>2</v>
       </c>
+      <c r="L23" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="M23" s="4" t="s">
         <v>18</v>
       </c>
@@ -2171,10 +2189,10 @@
         <v>18</v>
       </c>
       <c r="O23" s="2">
-        <v>46310.31707038325</v>
+        <v>46307.3954969447</v>
       </c>
       <c r="P23" s="2">
-        <v>46313.66771407861</v>
+        <v>46314.33169678966</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>23</v>
@@ -2188,28 +2206,25 @@
         <v>18</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H24" s="3">
         <v>46320</v>
       </c>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>18</v>
@@ -2218,10 +2233,10 @@
         <v>18</v>
       </c>
       <c r="O24" s="2">
-        <v>46307.3954969447</v>
+        <v>46307.39549697415</v>
       </c>
       <c r="P24" s="2">
-        <v>46313.66771399752</v>
+        <v>46314.33169677422</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>23</v>
@@ -2235,22 +2250,22 @@
         <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G25" s="2">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="3">
         <v>46320</v>
       </c>
       <c r="I25" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K25" s="2">
         <v>1</v>
@@ -2262,13 +2277,13 @@
         <v>18</v>
       </c>
       <c r="O25" s="2">
-        <v>46307.39549697415</v>
+        <v>46308.39986123197</v>
       </c>
       <c r="P25" s="2">
-        <v>46313.66771401245</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>23</v>
+        <v>46314.33169675977</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="2" customFormat="1">
@@ -2279,25 +2294,28 @@
         <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G26" s="2">
-        <v>0.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H26" s="3">
         <v>46320</v>
       </c>
       <c r="I26" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>99</v>
       </c>
       <c r="K26" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>18</v>
@@ -2306,41 +2324,41 @@
         <v>18</v>
       </c>
       <c r="O26" s="2">
-        <v>46308.39986123197</v>
+        <v>46314.33169674601</v>
       </c>
       <c r="P26" s="2">
-        <v>46313.66771402624</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27">
+        <v>46314.33169674603</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="2" customFormat="1">
+      <c r="A27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="2">
         <v>0.2</v>
       </c>
       <c r="H27" s="3">
         <v>46321</v>
       </c>
-      <c r="I27">
-        <v>8</v>
-      </c>
-      <c r="J27" t="s">
-        <v>101</v>
-      </c>
-      <c r="K27">
+      <c r="I27" s="2">
+        <v>7</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="M27" s="4" t="s">
@@ -2349,14 +2367,14 @@
       <c r="N27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="2">
         <v>46307.39549690609</v>
       </c>
-      <c r="P27">
-        <v>46313.66770577192</v>
+      <c r="P27" s="2">
+        <v>46314.33169667637</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2367,10 +2385,10 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G28">
         <v>0.2</v>
@@ -2379,16 +2397,16 @@
         <v>46322</v>
       </c>
       <c r="I28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K28">
         <v>2</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>18</v>
@@ -2400,10 +2418,10 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P28">
-        <v>46313.66770574598</v>
+        <v>46314.33169664627</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2414,13 +2432,13 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G29">
         <v>0.91</v>
@@ -2429,16 +2447,16 @@
         <v>46322</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M29" s="4" t="s">
         <v>18</v>
@@ -2450,7 +2468,7 @@
         <v>46307.39549684311</v>
       </c>
       <c r="P29">
-        <v>46313.66770573297</v>
+        <v>46314.33169666144</v>
       </c>
       <c r="Q29" t="s">
         <v>23</v>
@@ -2464,10 +2482,10 @@
         <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>0.2</v>
@@ -2476,16 +2494,16 @@
         <v>46322</v>
       </c>
       <c r="I30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K30">
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>18</v>
@@ -2500,7 +2518,7 @@
         <v>46313.66770571972</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2511,13 +2529,13 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G31">
         <v>0.93</v>
@@ -2526,16 +2544,16 @@
         <v>46322</v>
       </c>
       <c r="I31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>18</v>
@@ -2547,7 +2565,7 @@
         <v>46308.39986117012</v>
       </c>
       <c r="P31">
-        <v>46313.66770575889</v>
+        <v>46314.33169663035</v>
       </c>
       <c r="Q31" t="s">
         <v>23</v>
@@ -2561,10 +2579,10 @@
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G32">
         <v>0.2</v>
@@ -2573,16 +2591,16 @@
         <v>46322</v>
       </c>
       <c r="I32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K32">
         <v>2</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>18</v>
@@ -2597,7 +2615,7 @@
         <v>46313.66770570714</v>
       </c>
       <c r="Q32" s="5" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2608,10 +2626,10 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <v>0.2</v>
@@ -2620,10 +2638,10 @@
         <v>46323</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2638,10 +2656,10 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P33">
-        <v>46313.6677056671</v>
+        <v>46314.33168880571</v>
       </c>
       <c r="Q33" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2652,10 +2670,10 @@
         <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G34">
         <v>0.2</v>
@@ -2664,10 +2682,10 @@
         <v>46323</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -2682,10 +2700,10 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P34">
-        <v>46313.66770568074</v>
+        <v>46314.33168879073</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2696,10 +2714,10 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G35">
         <v>0.2</v>
@@ -2708,16 +2726,16 @@
         <v>46323</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>18</v>
@@ -2729,10 +2747,10 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P35">
-        <v>46313.66770569394</v>
+        <v>46314.3316888202</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2743,13 +2761,13 @@
         <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G36">
         <v>0.96</v>
@@ -2758,16 +2776,16 @@
         <v>46323</v>
       </c>
       <c r="I36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>18</v>
@@ -2779,7 +2797,7 @@
         <v>46310.31706138982</v>
       </c>
       <c r="P36">
-        <v>46313.66770565418</v>
+        <v>46314.33168877615</v>
       </c>
       <c r="Q36" t="s">
         <v>23</v>
@@ -2793,10 +2811,10 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G37">
         <v>0.2</v>
@@ -2805,16 +2823,16 @@
         <v>46323</v>
       </c>
       <c r="I37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>18</v>
@@ -2826,10 +2844,10 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P37">
-        <v>46313.66770564076</v>
+        <v>46314.33168883479</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2840,10 +2858,10 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G38">
         <v>0.2</v>
@@ -2852,16 +2870,16 @@
         <v>46324</v>
       </c>
       <c r="I38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K38">
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>18</v>
@@ -2873,10 +2891,10 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P38">
-        <v>46313.66770562722</v>
+        <v>46314.33168874637</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2887,10 +2905,10 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="G39">
         <v>0.91</v>
@@ -2899,16 +2917,16 @@
         <v>46324</v>
       </c>
       <c r="I39">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>18</v>
@@ -2920,7 +2938,7 @@
         <v>46310.31706133292</v>
       </c>
       <c r="P39">
-        <v>46313.66770561394</v>
+        <v>46314.3316887614</v>
       </c>
       <c r="Q39" t="s">
         <v>23</v>
@@ -2934,13 +2952,13 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G40">
         <v>0.89</v>
@@ -2949,16 +2967,16 @@
         <v>46325</v>
       </c>
       <c r="I40">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K40">
         <v>2</v>
       </c>
       <c r="L40" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>18</v>
@@ -2970,7 +2988,7 @@
         <v>46309.72494249383</v>
       </c>
       <c r="P40">
-        <v>46313.66770560007</v>
+        <v>46314.33168873169</v>
       </c>
       <c r="Q40" t="s">
         <v>23</v>
@@ -2984,10 +3002,10 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E41" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G41">
         <v>0.2</v>
@@ -2996,10 +3014,10 @@
         <v>46326</v>
       </c>
       <c r="I41">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3014,10 +3032,10 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P41">
-        <v>46313.66770558676</v>
+        <v>46314.33168871688</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -3028,31 +3046,25 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G42">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H42" s="3">
-        <v>46328</v>
+        <v>46326</v>
       </c>
       <c r="I42">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J42" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K42">
-        <v>2</v>
-      </c>
-      <c r="L42" t="s">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="M42" s="4" t="s">
         <v>18</v>
@@ -3061,13 +3073,13 @@
         <v>18</v>
       </c>
       <c r="O42">
-        <v>46308.39986111095</v>
+        <v>46314.3316886879</v>
       </c>
       <c r="P42">
-        <v>46313.66770555852</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>23</v>
+        <v>46314.3316886879</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -3078,25 +3090,25 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G43">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H43" s="3">
-        <v>46332</v>
+        <v>46327</v>
       </c>
       <c r="I43">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>18</v>
@@ -3105,10 +3117,10 @@
         <v>18</v>
       </c>
       <c r="O43">
-        <v>46305.20575257758</v>
+        <v>46314.33168865994</v>
       </c>
       <c r="P43">
-        <v>46313.66770554411</v>
+        <v>46314.33168865996</v>
       </c>
       <c r="Q43" t="s">
         <v>23</v>
@@ -3122,28 +3134,31 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E44" t="s">
         <v>38</v>
       </c>
+      <c r="F44" t="s">
+        <v>39</v>
+      </c>
       <c r="G44">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H44" s="3">
-        <v>46333</v>
+        <v>46328</v>
       </c>
       <c r="I44">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J44" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="K44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L44" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>18</v>
@@ -3152,10 +3167,10 @@
         <v>18</v>
       </c>
       <c r="O44">
-        <v>46307.39549666931</v>
+        <v>46308.39986111095</v>
       </c>
       <c r="P44">
-        <v>46313.66770552914</v>
+        <v>46314.33168862844</v>
       </c>
       <c r="Q44" t="s">
         <v>23</v>
@@ -3169,268 +3184,253 @@
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E45" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="G45">
+        <v>0.2</v>
+      </c>
+      <c r="H45" s="3">
+        <v>46329</v>
+      </c>
+      <c r="I45">
+        <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>154</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45">
+        <v>46314.33168861312</v>
+      </c>
+      <c r="P45">
+        <v>46314.33168861314</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>0.2</v>
+      </c>
+      <c r="H46" s="3">
+        <v>46331</v>
+      </c>
+      <c r="I46">
+        <v>17</v>
+      </c>
+      <c r="J46" t="s">
+        <v>156</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46">
+        <v>46314.33168857944</v>
+      </c>
+      <c r="P46">
+        <v>46314.33168857947</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>157</v>
+      </c>
+      <c r="E47" t="s">
+        <v>90</v>
+      </c>
+      <c r="G47">
+        <v>0.92</v>
+      </c>
+      <c r="H47" s="3">
+        <v>46332</v>
+      </c>
+      <c r="I47">
+        <v>18</v>
+      </c>
+      <c r="J47" t="s">
+        <v>158</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47">
+        <v>46305.20575257758</v>
+      </c>
+      <c r="P47">
+        <v>46314.33168844028</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48">
+        <v>0.95</v>
+      </c>
+      <c r="H48" s="3">
+        <v>46333</v>
+      </c>
+      <c r="I48">
+        <v>19</v>
+      </c>
+      <c r="J48" t="s">
+        <v>79</v>
+      </c>
+      <c r="K48">
+        <v>4</v>
+      </c>
+      <c r="L48" t="s">
+        <v>160</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48">
+        <v>46307.39549666931</v>
+      </c>
+      <c r="P48">
+        <v>46314.33168839412</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>161</v>
+      </c>
+      <c r="E49" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H49" s="3">
         <v>46333</v>
       </c>
-      <c r="I45">
-        <v>20</v>
-      </c>
-      <c r="J45" t="s">
-        <v>152</v>
-      </c>
-      <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O45">
+      <c r="I49">
+        <v>19</v>
+      </c>
+      <c r="J49" t="s">
+        <v>162</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49">
         <v>46307.39549671811</v>
       </c>
-      <c r="P45">
-        <v>46313.66770549942</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
-      <c r="A46" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="H46" s="6">
-        <v>46312</v>
-      </c>
-      <c r="I46" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K46" s="6">
-        <v>1</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O46" s="6">
-        <v>46300.75884779022</v>
-      </c>
-      <c r="P46" s="6">
-        <v>46313.66772336456</v>
-      </c>
-      <c r="Q46" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17">
-      <c r="A47" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="H47" s="6">
-        <v>46312</v>
-      </c>
-      <c r="I47" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K47" s="6">
-        <v>1</v>
-      </c>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O47" s="6">
-        <v>46300.75884780569</v>
-      </c>
-      <c r="P47" s="6">
-        <v>46313.6677233767</v>
-      </c>
-      <c r="Q47" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
-      <c r="A48" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="H48" s="6">
-        <v>46312</v>
-      </c>
-      <c r="I48" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K48" s="6">
-        <v>1</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O48" s="6">
-        <v>46300.75884782107</v>
-      </c>
-      <c r="P48" s="6">
-        <v>46313.66772335224</v>
-      </c>
-      <c r="Q48" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17">
-      <c r="A49" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="H49" s="6">
-        <v>46312</v>
-      </c>
-      <c r="I49" s="6">
-        <v>-1</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K49" s="6">
-        <v>1</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O49" s="6">
-        <v>46300.75884783743</v>
-      </c>
-      <c r="P49" s="6">
-        <v>46313.66772333956</v>
-      </c>
-      <c r="Q49" s="6" t="s">
+      <c r="P49">
+        <v>46314.33168842444</v>
+      </c>
+      <c r="Q49" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17">
       <c r="A50" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="H50" s="6">
-        <v>46310</v>
+        <v>46313</v>
       </c>
       <c r="I50" s="6">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K50" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
@@ -3439,10 +3439,10 @@
         <v>18</v>
       </c>
       <c r="O50" s="6">
-        <v>46300.75884787029</v>
+        <v>46302.26841519317</v>
       </c>
       <c r="P50" s="6">
-        <v>46313.66772340168</v>
+        <v>46314.33170499192</v>
       </c>
       <c r="Q50" s="6" t="s">
         <v>23</v>
@@ -3450,35 +3450,37 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H51" s="6">
-        <v>46309</v>
+        <v>46312</v>
       </c>
       <c r="I51" s="6">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K51" s="6">
         <v>1</v>
       </c>
-      <c r="L51" s="6"/>
+      <c r="L51" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="M51" s="6" t="s">
         <v>18</v>
       </c>
@@ -3486,24 +3488,24 @@
         <v>18</v>
       </c>
       <c r="O51" s="6">
-        <v>46308.39987059968</v>
+        <v>46300.75884779022</v>
       </c>
       <c r="P51" s="6">
-        <v>46313.6677234138</v>
-      </c>
-      <c r="Q51" s="5" t="s">
-        <v>31</v>
+        <v>46314.33170500596</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:17">
       <c r="A52" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
@@ -3511,16 +3513,16 @@
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H52" s="6">
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="I52" s="6">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K52" s="6">
         <v>1</v>
@@ -3533,46 +3535,48 @@
         <v>18</v>
       </c>
       <c r="O52" s="6">
-        <v>46300.75884790152</v>
+        <v>46300.75884780569</v>
       </c>
       <c r="P52" s="6">
-        <v>46313.66772346423</v>
-      </c>
-      <c r="Q52" s="5" t="s">
-        <v>31</v>
+        <v>46314.33170503424</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:17">
       <c r="A53" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="H53" s="6">
-        <v>46308</v>
+        <v>46312</v>
       </c>
       <c r="I53" s="6">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="J53" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K53" s="6">
+        <v>1</v>
+      </c>
+      <c r="L53" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="K53" s="6">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6"/>
       <c r="M53" s="6" t="s">
         <v>18</v>
       </c>
@@ -3580,21 +3584,21 @@
         <v>18</v>
       </c>
       <c r="O53" s="6">
-        <v>46310.71708389919</v>
+        <v>46300.75884782107</v>
       </c>
       <c r="P53" s="6">
-        <v>46313.66772345122</v>
-      </c>
-      <c r="Q53" s="5" t="s">
-        <v>31</v>
+        <v>46314.33170502017</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:17">
       <c r="A54" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>176</v>
@@ -3603,27 +3607,25 @@
       <c r="E54" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="6"/>
+      <c r="G54" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H54" s="6">
+        <v>46312</v>
+      </c>
+      <c r="I54" s="6">
+        <v>-2</v>
+      </c>
+      <c r="J54" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G54" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="H54" s="6">
-        <v>46307</v>
-      </c>
-      <c r="I54" s="6">
-        <v>-6</v>
-      </c>
-      <c r="J54" s="6" t="s">
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K54" s="6">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>180</v>
-      </c>
       <c r="M54" s="6" t="s">
         <v>18</v>
       </c>
@@ -3631,10 +3633,10 @@
         <v>18</v>
       </c>
       <c r="O54" s="6">
-        <v>46300.75884793277</v>
+        <v>46300.75884783743</v>
       </c>
       <c r="P54" s="6">
-        <v>46313.66773176777</v>
+        <v>46314.33170504807</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>23</v>
@@ -3642,37 +3644,37 @@
     </row>
     <row r="55" spans="1:17">
       <c r="A55" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F55" s="6"/>
       <c r="G55" s="6">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H55" s="6">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="I55" s="6">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="J55" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K55" s="6">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="K55" s="6">
-        <v>1</v>
-      </c>
-      <c r="L55" s="6"/>
       <c r="M55" s="6" t="s">
         <v>18</v>
       </c>
@@ -3680,10 +3682,10 @@
         <v>18</v>
       </c>
       <c r="O55" s="6">
-        <v>46300.75884796329</v>
+        <v>46300.75884787029</v>
       </c>
       <c r="P55" s="6">
-        <v>46313.66773171356</v>
+        <v>46314.33170507625</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3691,27 +3693,27 @@
     </row>
     <row r="56" spans="1:17">
       <c r="A56" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>183</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6">
         <v>0.2</v>
       </c>
       <c r="H56" s="6">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I56" s="6">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>184</v>
@@ -3719,9 +3721,7 @@
       <c r="K56" s="6">
         <v>1</v>
       </c>
-      <c r="L56" s="6" t="s">
-        <v>185</v>
-      </c>
+      <c r="L56" s="6"/>
       <c r="M56" s="6" t="s">
         <v>18</v>
       </c>
@@ -3729,41 +3729,41 @@
         <v>18</v>
       </c>
       <c r="O56" s="6">
-        <v>46300.75884799581</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P56" s="6">
-        <v>46313.66773180514</v>
+        <v>46314.33170509027</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:17">
       <c r="A57" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H57" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I57" s="6">
         <v>-6</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K57" s="6">
         <v>1</v>
@@ -3776,48 +3776,46 @@
         <v>18</v>
       </c>
       <c r="O57" s="6">
-        <v>46300.75885617639</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P57" s="6">
-        <v>46313.66773178015</v>
-      </c>
-      <c r="Q57" s="6" t="s">
-        <v>23</v>
+        <v>46314.33171287029</v>
+      </c>
+      <c r="Q57" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:17">
       <c r="A58" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H58" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I58" s="6">
         <v>-6</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="K58" s="6">
         <v>1</v>
       </c>
-      <c r="L58" s="6" t="s">
-        <v>189</v>
-      </c>
+      <c r="L58" s="6"/>
       <c r="M58" s="6" t="s">
         <v>18</v>
       </c>
@@ -3825,49 +3823,49 @@
         <v>18</v>
       </c>
       <c r="O58" s="6">
-        <v>46300.75885619673</v>
+        <v>46310.71708389919</v>
       </c>
       <c r="P58" s="6">
-        <v>46313.66773179277</v>
-      </c>
-      <c r="Q58" s="6" t="s">
-        <v>23</v>
+        <v>46314.33171283938</v>
+      </c>
+      <c r="Q58" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="G59" s="6">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="H59" s="6">
         <v>46307</v>
       </c>
       <c r="I59" s="6">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="K59" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>18</v>
@@ -3876,37 +3874,37 @@
         <v>18</v>
       </c>
       <c r="O59" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75884793277</v>
       </c>
       <c r="P59" s="6">
-        <v>46309.72496078632</v>
-      </c>
-      <c r="Q59" s="5" t="s">
-        <v>192</v>
+        <v>46314.33171298478</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:17">
       <c r="A60" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>193</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="G60" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H60" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I60" s="6">
         <v>-7</v>
@@ -3917,9 +3915,7 @@
       <c r="K60" s="6">
         <v>1</v>
       </c>
-      <c r="L60" s="6" t="s">
-        <v>195</v>
-      </c>
+      <c r="L60" s="6"/>
       <c r="M60" s="6" t="s">
         <v>18</v>
       </c>
@@ -3927,10 +3923,10 @@
         <v>18</v>
       </c>
       <c r="O60" s="6">
-        <v>46300.75885624527</v>
+        <v>46300.75884796329</v>
       </c>
       <c r="P60" s="6">
-        <v>46313.66773183009</v>
+        <v>46314.33171297063</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>23</v>
@@ -3938,37 +3934,37 @@
     </row>
     <row r="61" spans="1:17">
       <c r="A61" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="H61" s="6">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I61" s="6">
         <v>-7</v>
       </c>
       <c r="J61" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="K61" s="6">
-        <v>1</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="M61" s="6" t="s">
         <v>18</v>
       </c>
@@ -3976,48 +3972,46 @@
         <v>18</v>
       </c>
       <c r="O61" s="6">
-        <v>46300.75885627908</v>
+        <v>46300.75884799581</v>
       </c>
       <c r="P61" s="6">
-        <v>46313.66773184277</v>
-      </c>
-      <c r="Q61" s="6" t="s">
-        <v>23</v>
+        <v>46314.33171289923</v>
+      </c>
+      <c r="Q61" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:17">
       <c r="A62" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H62" s="6">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="I62" s="6">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K62" s="6">
         <v>1</v>
       </c>
-      <c r="L62" s="6" t="s">
-        <v>201</v>
-      </c>
+      <c r="L62" s="6"/>
       <c r="M62" s="6" t="s">
         <v>18</v>
       </c>
@@ -4025,10 +4019,10 @@
         <v>18</v>
       </c>
       <c r="O62" s="6">
-        <v>46300.75885633306</v>
+        <v>46300.75885617639</v>
       </c>
       <c r="P62" s="6">
-        <v>46313.66773188084</v>
+        <v>46314.33171295658</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>23</v>
@@ -4036,36 +4030,36 @@
     </row>
     <row r="63" spans="1:17">
       <c r="A63" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H63" s="6">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="I63" s="6">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K63" s="6">
         <v>1</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>18</v>
@@ -4074,10 +4068,10 @@
         <v>18</v>
       </c>
       <c r="O63" s="6">
-        <v>46300.7588563655</v>
+        <v>46300.75885619673</v>
       </c>
       <c r="P63" s="6">
-        <v>46313.66773190629</v>
+        <v>46314.33171294258</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>23</v>
@@ -4085,38 +4079,38 @@
     </row>
     <row r="64" spans="1:17">
       <c r="A64" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="G64" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H64" s="6">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="I64" s="6">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>208</v>
+        <v>68</v>
       </c>
       <c r="K64" s="6">
         <v>2</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>18</v>
@@ -4125,17 +4119,215 @@
         <v>18</v>
       </c>
       <c r="O64" s="6">
-        <v>46300.7588564207</v>
+        <v>46305.20576106136</v>
       </c>
       <c r="P64" s="6">
-        <v>46313.66773193169</v>
+        <v>46314.33171292829</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="65" spans="1:17">
+      <c r="A65" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G65" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H65" s="6">
+        <v>46306</v>
+      </c>
+      <c r="I65" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O65" s="6">
+        <v>46300.75885624527</v>
+      </c>
+      <c r="P65" s="6">
+        <v>46314.33171305523</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H66" s="6">
+        <v>46306</v>
+      </c>
+      <c r="I66" s="6">
+        <v>-8</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="K66" s="6">
+        <v>1</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O66" s="6">
+        <v>46300.75885627908</v>
+      </c>
+      <c r="P66" s="6">
+        <v>46314.33171306941</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="H67" s="6">
+        <v>46305</v>
+      </c>
+      <c r="I67" s="6">
+        <v>-9</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O67" s="6">
+        <v>46300.75885633306</v>
+      </c>
+      <c r="P67" s="6">
+        <v>46314.33171311164</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H68" s="6">
+        <v>46304</v>
+      </c>
+      <c r="I68" s="6">
+        <v>-10</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="K68" s="6">
+        <v>1</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O68" s="6">
+        <v>46300.7588563655</v>
+      </c>
+      <c r="P68" s="6">
+        <v>46314.33172102019</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q64"/>
+  <autoFilter ref="A1:Q68"/>
   <hyperlinks>
     <hyperlink ref="M2" r:id="rId1"/>
     <hyperlink ref="N2" r:id="rId2"/>
@@ -4263,6 +4455,14 @@
     <hyperlink ref="N63" r:id="rId124"/>
     <hyperlink ref="M64" r:id="rId125"/>
     <hyperlink ref="N64" r:id="rId126"/>
+    <hyperlink ref="M65" r:id="rId127"/>
+    <hyperlink ref="N65" r:id="rId128"/>
+    <hyperlink ref="M66" r:id="rId129"/>
+    <hyperlink ref="N66" r:id="rId130"/>
+    <hyperlink ref="M67" r:id="rId131"/>
+    <hyperlink ref="N67" r:id="rId132"/>
+    <hyperlink ref="M68" r:id="rId133"/>
+    <hyperlink ref="N68" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4270,7 +4470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -4349,10 +4549,10 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2">
         <v>0.2</v>
@@ -4361,10 +4561,10 @@
         <v>46314</v>
       </c>
       <c r="I2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
@@ -4379,10 +4579,10 @@
         <v>46300.75884775587</v>
       </c>
       <c r="P2" s="2">
-        <v>46313.66772330055</v>
+        <v>46314.33170494929</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="2" customFormat="1">
@@ -4393,10 +4593,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2">
         <v>0.2</v>
@@ -4405,10 +4605,10 @@
         <v>46315</v>
       </c>
       <c r="I3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
@@ -4423,10 +4623,10 @@
         <v>46300.75884772457</v>
       </c>
       <c r="P3" s="2">
-        <v>46313.66772327427</v>
+        <v>46314.33170493501</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="2" customFormat="1">
@@ -4437,10 +4637,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2">
         <v>0.2</v>
@@ -4449,16 +4649,16 @@
         <v>46316</v>
       </c>
       <c r="I4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K4" s="2">
         <v>3</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>18</v>
@@ -4470,10 +4670,10 @@
         <v>46302.26841507768</v>
       </c>
       <c r="P4" s="2">
-        <v>46313.6677142169</v>
+        <v>46314.33170487836</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="2" customFormat="1">
@@ -4484,10 +4684,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2">
         <v>0.2</v>
@@ -4496,10 +4696,10 @@
         <v>46317</v>
       </c>
       <c r="I5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -4514,10 +4714,10 @@
         <v>46301.38232468421</v>
       </c>
       <c r="P5" s="2">
-        <v>46313.66771419167</v>
+        <v>46314.3317048496</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="2" customFormat="1">
@@ -4528,10 +4728,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2">
         <v>0.2</v>
@@ -4540,10 +4740,10 @@
         <v>46317</v>
       </c>
       <c r="I6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -4558,10 +4758,10 @@
         <v>46309.72495178872</v>
       </c>
       <c r="P6" s="2">
-        <v>46313.66771417948</v>
+        <v>46314.33170481848</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1">
@@ -4572,10 +4772,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G7" s="2">
         <v>0.2</v>
@@ -4584,16 +4784,16 @@
         <v>46318</v>
       </c>
       <c r="I7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>18</v>
@@ -4605,10 +4805,10 @@
         <v>46311.30743731892</v>
       </c>
       <c r="P7" s="2">
-        <v>46313.66771416669</v>
+        <v>46314.33169694684</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="2" customFormat="1">
@@ -4619,10 +4819,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G8" s="2">
         <v>0.2</v>
@@ -4631,16 +4831,16 @@
         <v>46319</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K8" s="2">
         <v>2</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>18</v>
@@ -4652,10 +4852,10 @@
         <v>46307.39549700746</v>
       </c>
       <c r="P8" s="2">
-        <v>46313.66771409143</v>
+        <v>46314.33169683327</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="2" customFormat="1">
@@ -4666,10 +4866,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G9" s="2">
         <v>0.2</v>
@@ -4678,10 +4878,10 @@
         <v>46319</v>
       </c>
       <c r="I9" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -4696,10 +4896,10 @@
         <v>46307.3954970362</v>
       </c>
       <c r="P9" s="2">
-        <v>46313.66771410416</v>
+        <v>46314.33169681875</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1">
@@ -4710,10 +4910,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2">
         <v>0.2</v>
@@ -4722,10 +4922,10 @@
         <v>46319</v>
       </c>
       <c r="I10" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -4740,10 +4940,10 @@
         <v>46309.72495171529</v>
       </c>
       <c r="P10" s="2">
-        <v>46313.66771406602</v>
+        <v>46314.33169686199</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="2" customFormat="1">
@@ -4754,10 +4954,10 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G11" s="2">
         <v>0.2</v>
@@ -4766,10 +4966,10 @@
         <v>46320</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -4784,38 +4984,38 @@
         <v>46308.39986123197</v>
       </c>
       <c r="P11" s="2">
-        <v>46313.66771402624</v>
+        <v>46314.33169675977</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="2" customFormat="1">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2">
         <v>0.2</v>
       </c>
       <c r="H12" s="3">
         <v>46321</v>
       </c>
-      <c r="I12">
-        <v>8</v>
-      </c>
-      <c r="J12" t="s">
-        <v>101</v>
-      </c>
-      <c r="K12">
+      <c r="I12" s="2">
+        <v>7</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="2">
         <v>1</v>
       </c>
       <c r="M12" s="4" t="s">
@@ -4824,14 +5024,14 @@
       <c r="N12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="2">
         <v>46307.39549690609</v>
       </c>
-      <c r="P12">
-        <v>46313.66770577192</v>
+      <c r="P12" s="2">
+        <v>46314.33169667637</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -4842,10 +5042,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G13">
         <v>0.2</v>
@@ -4854,16 +5054,16 @@
         <v>46322</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>18</v>
@@ -4875,10 +5075,10 @@
         <v>46307.39549680641</v>
       </c>
       <c r="P13">
-        <v>46313.66770574598</v>
+        <v>46314.33169664627</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -4889,10 +5089,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G14">
         <v>0.2</v>
@@ -4901,16 +5101,16 @@
         <v>46322</v>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M14" s="4" t="s">
         <v>18</v>
@@ -4925,7 +5125,7 @@
         <v>46313.66770571972</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -4936,10 +5136,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <v>0.2</v>
@@ -4948,16 +5148,16 @@
         <v>46322</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K15">
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
@@ -4972,7 +5172,7 @@
         <v>46313.66770570714</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -4983,10 +5183,10 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G16">
         <v>0.2</v>
@@ -4995,10 +5195,10 @@
         <v>46323</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -5013,10 +5213,10 @@
         <v>46309.72494256633</v>
       </c>
       <c r="P16">
-        <v>46313.6677056671</v>
+        <v>46314.33168880571</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -5027,10 +5227,10 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G17">
         <v>0.2</v>
@@ -5039,10 +5239,10 @@
         <v>46323</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -5057,10 +5257,10 @@
         <v>46309.72494259723</v>
       </c>
       <c r="P17">
-        <v>46313.66770568074</v>
+        <v>46314.33168879073</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -5071,10 +5271,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <v>0.2</v>
@@ -5083,16 +5283,16 @@
         <v>46323</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>18</v>
@@ -5104,10 +5304,10 @@
         <v>46309.72494262765</v>
       </c>
       <c r="P18">
-        <v>46313.66770569394</v>
+        <v>46314.3316888202</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -5118,10 +5318,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G19">
         <v>0.2</v>
@@ -5130,16 +5330,16 @@
         <v>46323</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>18</v>
@@ -5151,10 +5351,10 @@
         <v>46310.71706723773</v>
       </c>
       <c r="P19">
-        <v>46313.66770564076</v>
+        <v>46314.33168883479</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -5165,10 +5365,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G20">
         <v>0.2</v>
@@ -5177,16 +5377,16 @@
         <v>46324</v>
       </c>
       <c r="I20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K20">
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>18</v>
@@ -5198,10 +5398,10 @@
         <v>46309.72494253634</v>
       </c>
       <c r="P20">
-        <v>46313.66770562722</v>
+        <v>46314.33168874637</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -5212,10 +5412,10 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <v>0.2</v>
@@ -5224,10 +5424,10 @@
         <v>46326</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -5242,176 +5442,167 @@
         <v>46300.75884768533</v>
       </c>
       <c r="P21">
-        <v>46313.66770558676</v>
+        <v>46314.33168871688</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="6" t="s">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="3">
+        <v>46326</v>
+      </c>
+      <c r="I22">
+        <v>12</v>
+      </c>
+      <c r="J22" t="s">
+        <v>147</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22">
+        <v>46314.3316886879</v>
+      </c>
+      <c r="P22">
+        <v>46314.3316886879</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>46329</v>
+      </c>
+      <c r="I23">
+        <v>15</v>
+      </c>
+      <c r="J23" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23">
+        <v>46314.33168861312</v>
+      </c>
+      <c r="P23">
+        <v>46314.33168861314</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24">
         <v>0.2</v>
       </c>
-      <c r="H22" s="6">
-        <v>46309</v>
-      </c>
-      <c r="I22" s="6">
-        <v>-4</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K22" s="6">
-        <v>1</v>
-      </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="6">
-        <v>46308.39987059968</v>
-      </c>
-      <c r="P22" s="6">
-        <v>46313.6677234138</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H23" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I23" s="6">
-        <v>-5</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="6">
-        <v>1</v>
-      </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O23" s="6">
-        <v>46300.75884790152</v>
-      </c>
-      <c r="P23" s="6">
-        <v>46313.66772346423</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="H24" s="6">
-        <v>46308</v>
-      </c>
-      <c r="I24" s="6">
-        <v>-5</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" s="6">
-        <v>1</v>
-      </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O24" s="6">
-        <v>46310.71708389919</v>
-      </c>
-      <c r="P24" s="6">
-        <v>46313.66772345122</v>
+      <c r="H24" s="3">
+        <v>46331</v>
+      </c>
+      <c r="I24">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s">
+        <v>156</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24">
+        <v>46314.33168857944</v>
+      </c>
+      <c r="P24">
+        <v>46314.33168857947</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>183</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6">
         <v>0.2</v>
       </c>
       <c r="H25" s="6">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="I25" s="6">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>184</v>
@@ -5419,9 +5610,7 @@
       <c r="K25" s="6">
         <v>1</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>185</v>
-      </c>
+      <c r="L25" s="6"/>
       <c r="M25" s="6" t="s">
         <v>18</v>
       </c>
@@ -5429,50 +5618,46 @@
         <v>18</v>
       </c>
       <c r="O25" s="6">
-        <v>46300.75884799581</v>
+        <v>46308.39987059968</v>
       </c>
       <c r="P25" s="6">
-        <v>46313.66773180514</v>
+        <v>46314.33170509027</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="6">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="H26" s="6">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="I26" s="6">
         <v>-6</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="K26" s="6">
-        <v>2</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>191</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L26" s="6"/>
       <c r="M26" s="6" t="s">
         <v>18</v>
       </c>
@@ -5480,17 +5665,113 @@
         <v>18</v>
       </c>
       <c r="O26" s="6">
-        <v>46305.20576106136</v>
+        <v>46300.75884790152</v>
       </c>
       <c r="P26" s="6">
-        <v>46309.72496078632</v>
+        <v>46314.33171287029</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>192</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="H27" s="6">
+        <v>46308</v>
+      </c>
+      <c r="I27" s="6">
+        <v>-6</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K27" s="6">
+        <v>1</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="6">
+        <v>46310.71708389919</v>
+      </c>
+      <c r="P27" s="6">
+        <v>46314.33171283938</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" s=